--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -339,28 +339,56 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>999</v>
+      </c>
+      <c r="C3" s="2">
+        <v>586</v>
+      </c>
+      <c r="D3" s="2">
+        <v>413</v>
+      </c>
+      <c r="E3" s="2">
+        <v>958</v>
+      </c>
+      <c r="F3" s="2">
+        <v>41</v>
+      </c>
+      <c r="G3" s="2">
+        <v>321</v>
+      </c>
+      <c r="H3" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" s="5">
-        <v>1059</v>
-      </c>
-      <c r="C3" s="5">
-        <v>591</v>
-      </c>
-      <c r="D3" s="5">
-        <v>468</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1018</v>
-      </c>
-      <c r="F3" s="5">
-        <v>41</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="B4" s="5">
+        <v>2058</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1177</v>
+      </c>
+      <c r="D4" s="5">
+        <v>881</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1976</v>
+      </c>
+      <c r="F4" s="5">
+        <v>82</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -375,18 +403,18 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="21" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,14 +450,14 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Everyday greetings</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Friendship</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Love &amp; romance</t>
@@ -437,47 +465,47 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Congratulations</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Inspirational &amp; sympathy</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Keeping in touch</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Cute</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Family &amp; loved ones</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Pets</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Business &amp; work</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>World languages</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Flowers</t>
         </is>
       </c>
     </row>
@@ -512,89 +540,147 @@
         <v>19</v>
       </c>
       <c r="J2" s="2">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2">
         <v>12</v>
       </c>
-      <c r="K2" s="2">
-        <v>10</v>
-      </c>
       <c r="L2" s="2">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2">
         <v>6</v>
-      </c>
-      <c r="M2" s="2">
-        <v>4</v>
-      </c>
-      <c r="N2" s="2">
-        <v>3</v>
       </c>
       <c r="O2" s="2">
         <v>3</v>
       </c>
       <c r="P2" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>3</v>
+      </c>
+      <c r="R2" s="2">
         <v>2</v>
       </c>
-      <c r="Q2" s="2">
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>958</v>
+      </c>
+      <c r="C3" s="2">
+        <v>544</v>
+      </c>
+      <c r="D3" s="2">
+        <v>167</v>
+      </c>
+      <c r="E3" s="2">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2">
+        <v>52</v>
+      </c>
+      <c r="G3" s="2">
+        <v>41</v>
+      </c>
+      <c r="H3" s="2">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2">
+        <v>11</v>
+      </c>
+      <c r="L3" s="2">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2">
+        <v>8</v>
+      </c>
+      <c r="N3" s="2">
         <v>2</v>
       </c>
-      <c r="R2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="O3" s="2">
+        <v>3</v>
+      </c>
+      <c r="P3" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" s="5">
-        <v>1018</v>
-      </c>
-      <c r="C3" s="5">
-        <v>572</v>
-      </c>
-      <c r="D3" s="5">
-        <v>241</v>
-      </c>
-      <c r="E3" s="5">
-        <v>57</v>
-      </c>
-      <c r="F3" s="5">
-        <v>30</v>
-      </c>
-      <c r="G3" s="5">
-        <v>28</v>
-      </c>
-      <c r="H3" s="5">
-        <v>28</v>
-      </c>
-      <c r="I3" s="5">
-        <v>19</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="B4" s="5">
+        <v>1976</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1116</v>
+      </c>
+      <c r="D4" s="5">
+        <v>408</v>
+      </c>
+      <c r="E4" s="5">
+        <v>92</v>
+      </c>
+      <c r="F4" s="5">
+        <v>82</v>
+      </c>
+      <c r="G4" s="5">
+        <v>69</v>
+      </c>
+      <c r="H4" s="5">
+        <v>68</v>
+      </c>
+      <c r="I4" s="5">
+        <v>43</v>
+      </c>
+      <c r="J4" s="5">
+        <v>29</v>
+      </c>
+      <c r="K4" s="5">
+        <v>23</v>
+      </c>
+      <c r="L4" s="5">
         <v>12</v>
       </c>
-      <c r="K3" s="5">
-        <v>10</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="M4" s="5">
+        <v>9</v>
+      </c>
+      <c r="N4" s="5">
+        <v>8</v>
+      </c>
+      <c r="O4" s="5">
         <v>6</v>
       </c>
-      <c r="M3" s="5">
+      <c r="P4" s="5">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="5">
         <v>4</v>
       </c>
-      <c r="N3" s="5">
-        <v>3</v>
-      </c>
-      <c r="O3" s="5">
-        <v>3</v>
-      </c>
-      <c r="P3" s="5">
+      <c r="R4" s="5">
         <v>2</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>2</v>
-      </c>
-      <c r="R3" s="5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1190,6 +1276,508 @@
       </c>
       <c r="H18" s="4"/>
     </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D19" s="2">
+        <v>343</v>
+      </c>
+      <c r="E19" s="2">
+        <v>201</v>
+      </c>
+      <c r="F19" s="2">
+        <v>544</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.5678496868475992</v>
+      </c>
+      <c r="H19" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D20" s="2">
+        <v>106</v>
+      </c>
+      <c r="E20" s="2">
+        <v>61</v>
+      </c>
+      <c r="F20" s="2">
+        <v>167</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.174321503131524</v>
+      </c>
+      <c r="H20" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D21" s="2">
+        <v>21</v>
+      </c>
+      <c r="E21" s="2">
+        <v>31</v>
+      </c>
+      <c r="F21" s="2">
+        <v>52</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.054279749478079335</v>
+      </c>
+      <c r="H21" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D22" s="2">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2">
+        <v>32</v>
+      </c>
+      <c r="F22" s="2">
+        <v>41</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.04279749478079332</v>
+      </c>
+      <c r="H22" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D23" s="2">
+        <v>33</v>
+      </c>
+      <c r="E23" s="2">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2">
+        <v>40</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.04175365344467641</v>
+      </c>
+      <c r="H23" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D24" s="2">
+        <v>19</v>
+      </c>
+      <c r="E24" s="2">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2">
+        <v>35</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.03653444676409186</v>
+      </c>
+      <c r="H24" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D25" s="2">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2">
+        <v>24</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.025052192066805846</v>
+      </c>
+      <c r="H25" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D26" s="2">
+        <v>12</v>
+      </c>
+      <c r="E26" s="2">
+        <v>7</v>
+      </c>
+      <c r="F26" s="2">
+        <v>19</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0.019832985386221295</v>
+      </c>
+      <c r="H26" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D27" s="2">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>6</v>
+      </c>
+      <c r="F27" s="2">
+        <v>11</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0.011482254697286013</v>
+      </c>
+      <c r="H27" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D28" s="2">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0.010438413361169102</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D29" s="2">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0.008350730688935281</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0.003131524008350731</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0.0020876826722338203</v>
+      </c>
+      <c r="H31" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0.0010438413361169101</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0.0010438413361169101</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-02</t>
+        </is>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5">
+        <v>586</v>
+      </c>
+      <c r="E34" s="5">
+        <v>372</v>
+      </c>
+      <c r="F34" s="5">
+        <v>958</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H34" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3799,6 +4387,2904 @@
       </c>
       <c r="F93" s="4"/>
     </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E94" s="2">
+        <v>432</v>
+      </c>
+      <c r="F94" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E95" s="2">
+        <v>69</v>
+      </c>
+      <c r="F95" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E96" s="2">
+        <v>23</v>
+      </c>
+      <c r="F96" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E97" s="2">
+        <v>23</v>
+      </c>
+      <c r="F97" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E98" s="2">
+        <v>19</v>
+      </c>
+      <c r="F98" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E99" s="2">
+        <v>17</v>
+      </c>
+      <c r="F99" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E100" s="2">
+        <v>17</v>
+      </c>
+      <c r="F100" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E101" s="2">
+        <v>15</v>
+      </c>
+      <c r="F101" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E102" s="2">
+        <v>12</v>
+      </c>
+      <c r="F102" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E103" s="2">
+        <v>12</v>
+      </c>
+      <c r="F103" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E104" s="2">
+        <v>12</v>
+      </c>
+      <c r="F104" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="E105" s="2">
+        <v>12</v>
+      </c>
+      <c r="F105" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E106" s="2">
+        <v>12</v>
+      </c>
+      <c r="F106" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E107" s="2">
+        <v>12</v>
+      </c>
+      <c r="F107" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E108" s="2">
+        <v>10</v>
+      </c>
+      <c r="F108" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_thanku</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_thanku</t>
+        </is>
+      </c>
+      <c r="E109" s="2">
+        <v>10</v>
+      </c>
+      <c r="F109" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="E110" s="2">
+        <v>10</v>
+      </c>
+      <c r="F110" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E111" s="2">
+        <v>10</v>
+      </c>
+      <c r="F111" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E112" s="2">
+        <v>10</v>
+      </c>
+      <c r="F112" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E113" s="2">
+        <v>8</v>
+      </c>
+      <c r="F113" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E114" s="2">
+        <v>8</v>
+      </c>
+      <c r="F114" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E115" s="2">
+        <v>8</v>
+      </c>
+      <c r="F115" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E116" s="2">
+        <v>8</v>
+      </c>
+      <c r="F116" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E117" s="2">
+        <v>7</v>
+      </c>
+      <c r="F117" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>friendsforever</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendsforever</t>
+        </is>
+      </c>
+      <c r="E118" s="2">
+        <v>7</v>
+      </c>
+      <c r="F118" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E119" s="2">
+        <v>7</v>
+      </c>
+      <c r="F119" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>hindi_indian</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t>w_hindi_indian</t>
+        </is>
+      </c>
+      <c r="E120" s="2">
+        <v>7</v>
+      </c>
+      <c r="F120" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E121" s="2">
+        <v>6</v>
+      </c>
+      <c r="F121" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_heart</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_heart</t>
+        </is>
+      </c>
+      <c r="E122" s="2">
+        <v>6</v>
+      </c>
+      <c r="F122" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E123" s="2">
+        <v>6</v>
+      </c>
+      <c r="F123" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>friendship</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t>thank_friendship</t>
+        </is>
+      </c>
+      <c r="E124" s="2">
+        <v>6</v>
+      </c>
+      <c r="F124" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E125" s="2">
+        <v>5</v>
+      </c>
+      <c r="F125" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="E126" s="2">
+        <v>5</v>
+      </c>
+      <c r="F126" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E127" s="2">
+        <v>5</v>
+      </c>
+      <c r="F127" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E128" s="2">
+        <v>4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_more</t>
+        </is>
+      </c>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_more</t>
+        </is>
+      </c>
+      <c r="E129" s="2">
+        <v>4</v>
+      </c>
+      <c r="F129" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E130" s="2">
+        <v>4</v>
+      </c>
+      <c r="F130" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t>anniv_belated</t>
+        </is>
+      </c>
+      <c r="E131" s="2">
+        <v>3</v>
+      </c>
+      <c r="F131" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E132" s="2">
+        <v>3</v>
+      </c>
+      <c r="F132" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E133" s="2">
+        <v>3</v>
+      </c>
+      <c r="F133" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E134" s="2">
+        <v>3</v>
+      </c>
+      <c r="F134" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E135" s="2">
+        <v>3</v>
+      </c>
+      <c r="F135" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>onotheroccasions</t>
+        </is>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t>congrats_onotheroccasions</t>
+        </is>
+      </c>
+      <c r="E136" s="2">
+        <v>3</v>
+      </c>
+      <c r="F136" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t>congrats_retirement</t>
+        </is>
+      </c>
+      <c r="E137" s="2">
+        <v>3</v>
+      </c>
+      <c r="F137" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D138" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E138" s="2">
+        <v>3</v>
+      </c>
+      <c r="F138" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_flowers</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_flowers</t>
+        </is>
+      </c>
+      <c r="E139" s="2">
+        <v>3</v>
+      </c>
+      <c r="F139" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwatermelon_day</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwatermelon_day</t>
+        </is>
+      </c>
+      <c r="E140" s="2">
+        <v>3</v>
+      </c>
+      <c r="F140" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>specialfriend</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t>friend_specialfriend</t>
+        </is>
+      </c>
+      <c r="E141" s="2">
+        <v>3</v>
+      </c>
+      <c r="F141" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D142" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E142" s="2">
+        <v>3</v>
+      </c>
+      <c r="F142" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D143" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E143" s="2">
+        <v>3</v>
+      </c>
+      <c r="F143" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E144" s="2">
+        <v>2</v>
+      </c>
+      <c r="F144" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D145" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E145" s="2">
+        <v>2</v>
+      </c>
+      <c r="F145" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D146" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E146" s="2">
+        <v>2</v>
+      </c>
+      <c r="F146" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E147" s="2">
+        <v>2</v>
+      </c>
+      <c r="F147" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_soulmates</t>
+        </is>
+      </c>
+      <c r="D148" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_soulmates</t>
+        </is>
+      </c>
+      <c r="E148" s="2">
+        <v>2</v>
+      </c>
+      <c r="F148" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>eaug_icecream_sandwich_day</t>
+        </is>
+      </c>
+      <c r="D149" s="0" t="inlineStr">
+        <is>
+          <t>eaug_icecream_sandwich_day</t>
+        </is>
+      </c>
+      <c r="E149" s="2">
+        <v>2</v>
+      </c>
+      <c r="F149" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>edec_christworldday_english</t>
+        </is>
+      </c>
+      <c r="D150" s="0" t="inlineStr">
+        <is>
+          <t>edec_christworldday_english</t>
+        </is>
+      </c>
+      <c r="E150" s="2">
+        <v>2</v>
+      </c>
+      <c r="F150" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="E151" s="2">
+        <v>2</v>
+      </c>
+      <c r="F151" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>esep_nathoneymonth</t>
+        </is>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t>esep_nathoneymonth</t>
+        </is>
+      </c>
+      <c r="E152" s="2">
+        <v>2</v>
+      </c>
+      <c r="F152" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>friendshipetc</t>
+        </is>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendshipetc</t>
+        </is>
+      </c>
+      <c r="E153" s="2">
+        <v>2</v>
+      </c>
+      <c r="F153" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E154" s="2">
+        <v>2</v>
+      </c>
+      <c r="F154" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t>friend_missingyou</t>
+        </is>
+      </c>
+      <c r="E155" s="2">
+        <v>2</v>
+      </c>
+      <c r="F155" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E156" s="2">
+        <v>2</v>
+      </c>
+      <c r="F156" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E157" s="2">
+        <v>2</v>
+      </c>
+      <c r="F157" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E158" s="2">
+        <v>2</v>
+      </c>
+      <c r="F158" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="E159" s="2">
+        <v>2</v>
+      </c>
+      <c r="F159" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t>thank_flower</t>
+        </is>
+      </c>
+      <c r="E160" s="2">
+        <v>2</v>
+      </c>
+      <c r="F160" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>german_birthday</t>
+        </is>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t>w_german_birthday</t>
+        </is>
+      </c>
+      <c r="E161" s="2">
+        <v>2</v>
+      </c>
+      <c r="F161" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>balloons</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t>birth_balloons</t>
+        </is>
+      </c>
+      <c r="E162" s="2">
+        <v>1</v>
+      </c>
+      <c r="F162" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E163" s="2">
+        <v>1</v>
+      </c>
+      <c r="F163" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t>birth_missyou</t>
+        </is>
+      </c>
+      <c r="E164" s="2">
+        <v>1</v>
+      </c>
+      <c r="F164" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E165" s="2">
+        <v>1</v>
+      </c>
+      <c r="F165" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E166" s="2">
+        <v>1</v>
+      </c>
+      <c r="F166" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>kiss</t>
+        </is>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t>cute_kiss</t>
+        </is>
+      </c>
+      <c r="E167" s="2">
+        <v>1</v>
+      </c>
+      <c r="F167" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_makesmile</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_makesmile</t>
+        </is>
+      </c>
+      <c r="E168" s="2">
+        <v>1</v>
+      </c>
+      <c r="F168" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>eaug_justbecauseday</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t>eaug_justbecauseday</t>
+        </is>
+      </c>
+      <c r="E169" s="2">
+        <v>1</v>
+      </c>
+      <c r="F169" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_cream_pie_day</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_cream_pie_day</t>
+        </is>
+      </c>
+      <c r="E170" s="2">
+        <v>1</v>
+      </c>
+      <c r="F170" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E171" s="2">
+        <v>1</v>
+      </c>
+      <c r="F171" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E172" s="2">
+        <v>1</v>
+      </c>
+      <c r="F172" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>efeb_friendweek</t>
+        </is>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>efeb_friendweek</t>
+        </is>
+      </c>
+      <c r="E173" s="2">
+        <v>1</v>
+      </c>
+      <c r="F173" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>lovedones</t>
+        </is>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>fkt_lovedones</t>
+        </is>
+      </c>
+      <c r="E174" s="2">
+        <v>1</v>
+      </c>
+      <c r="F174" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>loveyoudad</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>fkt_loveyoudad</t>
+        </is>
+      </c>
+      <c r="E175" s="2">
+        <v>1</v>
+      </c>
+      <c r="F175" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E176" s="2">
+        <v>1</v>
+      </c>
+      <c r="F176" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>flwr_friend</t>
+        </is>
+      </c>
+      <c r="E177" s="2">
+        <v>1</v>
+      </c>
+      <c r="F177" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E178" s="2">
+        <v>1</v>
+      </c>
+      <c r="F178" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>hugsncaring</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>friend_hugsncaring</t>
+        </is>
+      </c>
+      <c r="E179" s="2">
+        <v>1</v>
+      </c>
+      <c r="F179" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>smiles</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>friend_smiles</t>
+        </is>
+      </c>
+      <c r="E180" s="2">
+        <v>1</v>
+      </c>
+      <c r="F180" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E181" s="2">
+        <v>1</v>
+      </c>
+      <c r="F181" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E182" s="2">
+        <v>1</v>
+      </c>
+      <c r="F182" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E183" s="2">
+        <v>1</v>
+      </c>
+      <c r="F183" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E184" s="2">
+        <v>1</v>
+      </c>
+      <c r="F184" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E185" s="2">
+        <v>1</v>
+      </c>
+      <c r="F185" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>poetry</t>
+        </is>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t>insp_poetry</t>
+        </is>
+      </c>
+      <c r="E186" s="2">
+        <v>1</v>
+      </c>
+      <c r="F186" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E187" s="2">
+        <v>1</v>
+      </c>
+      <c r="F187" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>acrossthemiles</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t>intouch_acrossthemiles</t>
+        </is>
+      </c>
+      <c r="E188" s="2">
+        <v>1</v>
+      </c>
+      <c r="F188" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>intouch_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E189" s="2">
+        <v>1</v>
+      </c>
+      <c r="F189" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E190" s="2">
+        <v>1</v>
+      </c>
+      <c r="F190" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E191" s="2">
+        <v>1</v>
+      </c>
+      <c r="F191" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>hihello</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>pet_hihello</t>
+        </is>
+      </c>
+      <c r="E192" s="2">
+        <v>1</v>
+      </c>
+      <c r="F192" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t>thank_congratulations</t>
+        </is>
+      </c>
+      <c r="E193" s="2">
+        <v>1</v>
+      </c>
+      <c r="F193" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E194" s="2">
+        <v>1</v>
+      </c>
+      <c r="F194" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E195" s="2">
+        <v>1</v>
+      </c>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t>spanish_secretariesday</t>
+        </is>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t>w_spanish_secretariesday</t>
+        </is>
+      </c>
+      <c r="E196" s="2">
+        <v>1</v>
+      </c>
+      <c r="F196" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-02</t>
+        </is>
+      </c>
+      <c r="B197" s="4"/>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="5">
+        <v>958</v>
+      </c>
+      <c r="F197" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3815,6 +7301,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3863,6 +7350,11 @@
           <t>Skype</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Google_Plus_Post</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -3894,36 +7386,76 @@
       <c r="I2" s="2">
         <v>12</v>
       </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>999</v>
+      </c>
+      <c r="C3" s="2">
+        <v>355</v>
+      </c>
+      <c r="D3" s="2">
+        <v>266</v>
+      </c>
+      <c r="E3" s="2">
+        <v>174</v>
+      </c>
+      <c r="F3" s="2">
+        <v>118</v>
+      </c>
+      <c r="G3" s="2">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2">
+        <v>34</v>
+      </c>
+      <c r="I3" s="2">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" s="5">
-        <v>1059</v>
-      </c>
-      <c r="C3" s="5">
-        <v>404</v>
-      </c>
-      <c r="D3" s="5">
-        <v>280</v>
-      </c>
-      <c r="E3" s="5">
-        <v>177</v>
-      </c>
-      <c r="F3" s="5">
-        <v>108</v>
-      </c>
-      <c r="G3" s="5">
-        <v>47</v>
-      </c>
-      <c r="H3" s="5">
-        <v>31</v>
-      </c>
-      <c r="I3" s="5">
-        <v>12</v>
+      <c r="B4" s="5">
+        <v>2058</v>
+      </c>
+      <c r="C4" s="5">
+        <v>759</v>
+      </c>
+      <c r="D4" s="5">
+        <v>546</v>
+      </c>
+      <c r="E4" s="5">
+        <v>351</v>
+      </c>
+      <c r="F4" s="5">
+        <v>226</v>
+      </c>
+      <c r="G4" s="5">
+        <v>85</v>
+      </c>
+      <c r="H4" s="5">
+        <v>65</v>
+      </c>
+      <c r="I4" s="5">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -367,28 +367,56 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>765</v>
+      </c>
+      <c r="C4" s="2">
+        <v>494</v>
+      </c>
+      <c r="D4" s="2">
+        <v>271</v>
+      </c>
+      <c r="E4" s="2">
+        <v>726</v>
+      </c>
+      <c r="F4" s="2">
+        <v>39</v>
+      </c>
+      <c r="G4" s="2">
+        <v>256</v>
+      </c>
+      <c r="H4" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <v>2058</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1177</v>
-      </c>
-      <c r="D4" s="5">
-        <v>881</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1976</v>
-      </c>
-      <c r="F4" s="5">
-        <v>82</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="B5" s="5">
+        <v>2823</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1671</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1152</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2702</v>
+      </c>
+      <c r="F5" s="5">
+        <v>121</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -403,16 +431,16 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="21" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="21" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
   </cols>
@@ -450,14 +478,14 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Friendship</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Everyday greetings</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Love &amp; romance</t>
@@ -480,22 +508,22 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Flowers</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Keeping in touch</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Family &amp; loved ones</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Cute</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -549,16 +577,16 @@
         <v>2</v>
       </c>
       <c r="M2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N2" s="2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2">
         <v>6</v>
       </c>
-      <c r="O2" s="2">
+      <c r="P2" s="2">
         <v>3</v>
-      </c>
-      <c r="P2" s="2">
-        <v>4</v>
       </c>
       <c r="Q2" s="2">
         <v>3</v>
@@ -589,10 +617,10 @@
         <v>52</v>
       </c>
       <c r="G3" s="2">
+        <v>40</v>
+      </c>
+      <c r="H3" s="2">
         <v>41</v>
-      </c>
-      <c r="H3" s="2">
-        <v>40</v>
       </c>
       <c r="I3" s="2">
         <v>24</v>
@@ -607,16 +635,16 @@
         <v>10</v>
       </c>
       <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2">
         <v>8</v>
       </c>
-      <c r="N3" s="2">
+      <c r="O3" s="2">
         <v>2</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>3</v>
-      </c>
-      <c r="P3" s="2">
-        <v>1</v>
       </c>
       <c r="Q3" s="2">
         <v>1</v>
@@ -626,60 +654,118 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>726</v>
+      </c>
+      <c r="C4" s="2">
+        <v>491</v>
+      </c>
+      <c r="D4" s="2">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2">
+        <v>16</v>
+      </c>
+      <c r="K4" s="2">
+        <v>17</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <v>1976</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1116</v>
-      </c>
-      <c r="D4" s="5">
-        <v>408</v>
-      </c>
-      <c r="E4" s="5">
-        <v>92</v>
-      </c>
-      <c r="F4" s="5">
-        <v>82</v>
-      </c>
-      <c r="G4" s="5">
-        <v>69</v>
-      </c>
-      <c r="H4" s="5">
-        <v>68</v>
-      </c>
-      <c r="I4" s="5">
-        <v>43</v>
-      </c>
-      <c r="J4" s="5">
-        <v>29</v>
-      </c>
-      <c r="K4" s="5">
-        <v>23</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="B5" s="5">
+        <v>2702</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1607</v>
+      </c>
+      <c r="D5" s="5">
+        <v>453</v>
+      </c>
+      <c r="E5" s="5">
+        <v>149</v>
+      </c>
+      <c r="F5" s="5">
+        <v>112</v>
+      </c>
+      <c r="G5" s="5">
+        <v>104</v>
+      </c>
+      <c r="H5" s="5">
+        <v>80</v>
+      </c>
+      <c r="I5" s="5">
+        <v>61</v>
+      </c>
+      <c r="J5" s="5">
+        <v>45</v>
+      </c>
+      <c r="K5" s="5">
+        <v>40</v>
+      </c>
+      <c r="L5" s="5">
         <v>12</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M5" s="5">
+        <v>10</v>
+      </c>
+      <c r="N5" s="5">
         <v>9</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O5" s="5">
         <v>8</v>
       </c>
-      <c r="O4" s="5">
+      <c r="P5" s="5">
         <v>6</v>
       </c>
-      <c r="P4" s="5">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="5">
+      <c r="Q5" s="5">
         <v>4</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R5" s="5">
         <v>2</v>
       </c>
     </row>
@@ -1778,6 +1864,348 @@
       </c>
       <c r="H34" s="4"/>
     </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
+        <v>335</v>
+      </c>
+      <c r="E35" s="2">
+        <v>156</v>
+      </c>
+      <c r="F35" s="2">
+        <v>491</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0.6763085399449036</v>
+      </c>
+      <c r="H35" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D36" s="2">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2">
+        <v>18</v>
+      </c>
+      <c r="F36" s="2">
+        <v>57</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0.07851239669421488</v>
+      </c>
+      <c r="H36" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D37" s="2">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2">
+        <v>6</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0.06198347107438017</v>
+      </c>
+      <c r="H37" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
+        <v>27</v>
+      </c>
+      <c r="E38" s="2">
+        <v>9</v>
+      </c>
+      <c r="F38" s="2">
+        <v>36</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0.049586776859504134</v>
+      </c>
+      <c r="H38" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D39" s="2">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2">
+        <v>25</v>
+      </c>
+      <c r="F39" s="2">
+        <v>30</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0.04132231404958678</v>
+      </c>
+      <c r="H39" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D40" s="2">
+        <v>15</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>18</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0.024793388429752067</v>
+      </c>
+      <c r="H40" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0.023415977961432508</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <v>16</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>16</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.02203856749311295</v>
+      </c>
+      <c r="H42" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D43" s="2">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2">
+        <v>11</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0.015151515151515152</v>
+      </c>
+      <c r="H43" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0.006887052341597796</v>
+      </c>
+      <c r="H44" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-03</t>
+        </is>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5">
+        <v>494</v>
+      </c>
+      <c r="E45" s="5">
+        <v>232</v>
+      </c>
+      <c r="F45" s="5">
+        <v>726</v>
+      </c>
+      <c r="G45" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -7284,6 +7712,2120 @@
         <v>958</v>
       </c>
       <c r="F197" s="4"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B198" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E198" s="2">
+        <v>368</v>
+      </c>
+      <c r="F198" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E199" s="2">
+        <v>42</v>
+      </c>
+      <c r="F199" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E200" s="2">
+        <v>24</v>
+      </c>
+      <c r="F200" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwatermelon_day</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwatermelon_day</t>
+        </is>
+      </c>
+      <c r="E201" s="2">
+        <v>24</v>
+      </c>
+      <c r="F201" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E202" s="2">
+        <v>17</v>
+      </c>
+      <c r="F202" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E203" s="2">
+        <v>16</v>
+      </c>
+      <c r="F203" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E204" s="2">
+        <v>13</v>
+      </c>
+      <c r="F204" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E205" s="2">
+        <v>13</v>
+      </c>
+      <c r="F205" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E206" s="2">
+        <v>12</v>
+      </c>
+      <c r="F206" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B207" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D207" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E207" s="2">
+        <v>10</v>
+      </c>
+      <c r="F207" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B208" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E208" s="2">
+        <v>9</v>
+      </c>
+      <c r="F208" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E209" s="2">
+        <v>9</v>
+      </c>
+      <c r="F209" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E210" s="2">
+        <v>9</v>
+      </c>
+      <c r="F210" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B211" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D211" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E211" s="2">
+        <v>9</v>
+      </c>
+      <c r="F211" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B212" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D212" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E212" s="2">
+        <v>8</v>
+      </c>
+      <c r="F212" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B213" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D213" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E213" s="2">
+        <v>8</v>
+      </c>
+      <c r="F213" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B214" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D214" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E214" s="2">
+        <v>6</v>
+      </c>
+      <c r="F214" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D215" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E215" s="2">
+        <v>6</v>
+      </c>
+      <c r="F215" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D216" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E216" s="2">
+        <v>5</v>
+      </c>
+      <c r="F216" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E217" s="2">
+        <v>5</v>
+      </c>
+      <c r="F217" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D218" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E218" s="2">
+        <v>5</v>
+      </c>
+      <c r="F218" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D219" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E219" s="2">
+        <v>5</v>
+      </c>
+      <c r="F219" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D220" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E220" s="2">
+        <v>5</v>
+      </c>
+      <c r="F220" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D221" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E221" s="2">
+        <v>5</v>
+      </c>
+      <c r="F221" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>balloons</t>
+        </is>
+      </c>
+      <c r="D222" s="0" t="inlineStr">
+        <is>
+          <t>birth_balloons</t>
+        </is>
+      </c>
+      <c r="E222" s="2">
+        <v>4</v>
+      </c>
+      <c r="F222" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D223" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E223" s="2">
+        <v>4</v>
+      </c>
+      <c r="F223" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D224" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E224" s="2">
+        <v>4</v>
+      </c>
+      <c r="F224" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D225" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E225" s="2">
+        <v>4</v>
+      </c>
+      <c r="F225" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>gifts</t>
+        </is>
+      </c>
+      <c r="D226" s="0" t="inlineStr">
+        <is>
+          <t>anniv_gifts</t>
+        </is>
+      </c>
+      <c r="E226" s="2">
+        <v>3</v>
+      </c>
+      <c r="F226" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D227" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E227" s="2">
+        <v>3</v>
+      </c>
+      <c r="F227" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B228" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>teddy</t>
+        </is>
+      </c>
+      <c r="D228" s="0" t="inlineStr">
+        <is>
+          <t>cute_teddy</t>
+        </is>
+      </c>
+      <c r="E228" s="2">
+        <v>3</v>
+      </c>
+      <c r="F228" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B229" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>eaug_dollarday</t>
+        </is>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>eaug_dollarday</t>
+        </is>
+      </c>
+      <c r="E229" s="2">
+        <v>3</v>
+      </c>
+      <c r="F229" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B230" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalzucchini_day</t>
+        </is>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalzucchini_day</t>
+        </is>
+      </c>
+      <c r="E230" s="2">
+        <v>3</v>
+      </c>
+      <c r="F230" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E231" s="2">
+        <v>3</v>
+      </c>
+      <c r="F231" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>monblues</t>
+        </is>
+      </c>
+      <c r="D232" s="0" t="inlineStr">
+        <is>
+          <t>gen_monblues</t>
+        </is>
+      </c>
+      <c r="E232" s="2">
+        <v>3</v>
+      </c>
+      <c r="F232" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D233" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E233" s="2">
+        <v>3</v>
+      </c>
+      <c r="F233" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B234" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D234" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E234" s="2">
+        <v>3</v>
+      </c>
+      <c r="F234" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D235" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E235" s="2">
+        <v>2</v>
+      </c>
+      <c r="F235" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E236" s="2">
+        <v>2</v>
+      </c>
+      <c r="F236" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D237" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E237" s="2">
+        <v>2</v>
+      </c>
+      <c r="F237" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B238" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>zodiac</t>
+        </is>
+      </c>
+      <c r="D238" s="0" t="inlineStr">
+        <is>
+          <t>birth_zodiac</t>
+        </is>
+      </c>
+      <c r="E238" s="2">
+        <v>2</v>
+      </c>
+      <c r="F238" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B239" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D239" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E239" s="2">
+        <v>2</v>
+      </c>
+      <c r="F239" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B240" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D240" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E240" s="2">
+        <v>2</v>
+      </c>
+      <c r="F240" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D241" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E241" s="2">
+        <v>2</v>
+      </c>
+      <c r="F241" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B242" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwhite_wine_day</t>
+        </is>
+      </c>
+      <c r="D242" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwhite_wine_day</t>
+        </is>
+      </c>
+      <c r="E242" s="2">
+        <v>2</v>
+      </c>
+      <c r="F242" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B243" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="D243" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="E243" s="2">
+        <v>2</v>
+      </c>
+      <c r="F243" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D244" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E244" s="2">
+        <v>2</v>
+      </c>
+      <c r="F244" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E245" s="2">
+        <v>2</v>
+      </c>
+      <c r="F245" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B246" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D246" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E246" s="2">
+        <v>2</v>
+      </c>
+      <c r="F246" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E247" s="2">
+        <v>1</v>
+      </c>
+      <c r="F247" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E248" s="2">
+        <v>1</v>
+      </c>
+      <c r="F248" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E249" s="2">
+        <v>1</v>
+      </c>
+      <c r="F249" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B250" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E250" s="2">
+        <v>1</v>
+      </c>
+      <c r="F250" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B251" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D251" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E251" s="2">
+        <v>1</v>
+      </c>
+      <c r="F251" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B252" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D252" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E252" s="2">
+        <v>1</v>
+      </c>
+      <c r="F252" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B253" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="D253" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="E253" s="2">
+        <v>1</v>
+      </c>
+      <c r="F253" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B254" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="E254" s="2">
+        <v>1</v>
+      </c>
+      <c r="F254" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B255" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="D255" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="E255" s="2">
+        <v>1</v>
+      </c>
+      <c r="F255" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B256" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t>edec_c_thankyou</t>
+        </is>
+      </c>
+      <c r="D256" s="0" t="inlineStr">
+        <is>
+          <t>edec_c_thankyou</t>
+        </is>
+      </c>
+      <c r="E256" s="2">
+        <v>1</v>
+      </c>
+      <c r="F256" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t>ejan_sendahugday_love</t>
+        </is>
+      </c>
+      <c r="D257" s="0" t="inlineStr">
+        <is>
+          <t>ejan_sendahugday_love</t>
+        </is>
+      </c>
+      <c r="E257" s="2">
+        <v>1</v>
+      </c>
+      <c r="F257" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="D258" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="E258" s="2">
+        <v>1</v>
+      </c>
+      <c r="F258" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B259" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D259" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E259" s="2">
+        <v>1</v>
+      </c>
+      <c r="F259" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B260" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D260" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E260" s="2">
+        <v>1</v>
+      </c>
+      <c r="F260" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B261" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D261" s="0" t="inlineStr">
+        <is>
+          <t>gen_blessings</t>
+        </is>
+      </c>
+      <c r="E261" s="2">
+        <v>1</v>
+      </c>
+      <c r="F261" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B262" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>cheerup</t>
+        </is>
+      </c>
+      <c r="D262" s="0" t="inlineStr">
+        <is>
+          <t>gen_cheerup</t>
+        </is>
+      </c>
+      <c r="E262" s="2">
+        <v>1</v>
+      </c>
+      <c r="F262" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B263" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D263" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E263" s="2">
+        <v>1</v>
+      </c>
+      <c r="F263" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B264" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D264" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E264" s="2">
+        <v>1</v>
+      </c>
+      <c r="F264" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B265" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D265" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E265" s="2">
+        <v>1</v>
+      </c>
+      <c r="F265" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B266" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D266" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E266" s="2">
+        <v>1</v>
+      </c>
+      <c r="F266" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B267" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D267" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E267" s="2">
+        <v>1</v>
+      </c>
+      <c r="F267" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B268" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D268" s="0" t="inlineStr">
+        <is>
+          <t>love_cute</t>
+        </is>
+      </c>
+      <c r="E268" s="2">
+        <v>1</v>
+      </c>
+      <c r="F268" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B269" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D269" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E269" s="2">
+        <v>1</v>
+      </c>
+      <c r="F269" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B270" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D270" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E270" s="2">
+        <v>1</v>
+      </c>
+      <c r="F270" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B271" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D271" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E271" s="2">
+        <v>1</v>
+      </c>
+      <c r="F271" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B272" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="D272" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="E272" s="2">
+        <v>1</v>
+      </c>
+      <c r="F272" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-03</t>
+        </is>
+      </c>
+      <c r="B273" s="4"/>
+      <c r="C273" s="4"/>
+      <c r="D273" s="4"/>
+      <c r="E273" s="5">
+        <v>726</v>
+      </c>
+      <c r="F273" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -7425,36 +9967,70 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>765</v>
+      </c>
+      <c r="C4" s="2">
+        <v>242</v>
+      </c>
+      <c r="D4" s="2">
+        <v>238</v>
+      </c>
+      <c r="E4" s="2">
+        <v>148</v>
+      </c>
+      <c r="F4" s="2">
+        <v>84</v>
+      </c>
+      <c r="G4" s="2">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <v>2058</v>
-      </c>
-      <c r="C4" s="5">
-        <v>759</v>
-      </c>
-      <c r="D4" s="5">
-        <v>546</v>
-      </c>
-      <c r="E4" s="5">
-        <v>351</v>
-      </c>
-      <c r="F4" s="5">
-        <v>226</v>
-      </c>
-      <c r="G4" s="5">
-        <v>85</v>
-      </c>
-      <c r="H4" s="5">
-        <v>65</v>
-      </c>
-      <c r="I4" s="5">
-        <v>25</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="B5" s="5">
+        <v>2823</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1001</v>
+      </c>
+      <c r="D5" s="5">
+        <v>784</v>
+      </c>
+      <c r="E5" s="5">
+        <v>499</v>
+      </c>
+      <c r="F5" s="5">
+        <v>310</v>
+      </c>
+      <c r="G5" s="5">
+        <v>104</v>
+      </c>
+      <c r="H5" s="5">
+        <v>96</v>
+      </c>
+      <c r="I5" s="5">
+        <v>28</v>
+      </c>
+      <c r="J5" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -395,28 +395,56 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>805</v>
+      </c>
+      <c r="C5" s="2">
+        <v>554</v>
+      </c>
+      <c r="D5" s="2">
+        <v>251</v>
+      </c>
+      <c r="E5" s="2">
+        <v>770</v>
+      </c>
+      <c r="F5" s="2">
+        <v>35</v>
+      </c>
+      <c r="G5" s="2">
+        <v>252</v>
+      </c>
+      <c r="H5" s="2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <v>2823</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1671</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1152</v>
-      </c>
-      <c r="E5" s="5">
-        <v>2702</v>
-      </c>
-      <c r="F5" s="5">
-        <v>121</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="B6" s="5">
+        <v>3628</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2225</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1403</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3472</v>
+      </c>
+      <c r="F6" s="5">
+        <v>156</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -438,9 +466,9 @@
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="21" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
   </cols>
@@ -513,17 +541,17 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Flowers</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Keeping in touch</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Family &amp; loved ones</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -580,13 +608,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2">
         <v>6</v>
-      </c>
-      <c r="P2" s="2">
-        <v>3</v>
       </c>
       <c r="Q2" s="2">
         <v>3</v>
@@ -638,13 +666,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="2">
+        <v>3</v>
+      </c>
+      <c r="O3" s="2">
         <v>8</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>2</v>
-      </c>
-      <c r="P3" s="2">
-        <v>3</v>
       </c>
       <c r="Q3" s="2">
         <v>1</v>
@@ -712,60 +740,118 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>770</v>
+      </c>
+      <c r="C5" s="2">
+        <v>555</v>
+      </c>
+      <c r="D5" s="2">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2">
+        <v>22</v>
+      </c>
+      <c r="I5" s="2">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2">
+        <v>15</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2">
+        <v>5</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <v>2702</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1607</v>
-      </c>
-      <c r="D5" s="5">
-        <v>453</v>
-      </c>
-      <c r="E5" s="5">
-        <v>149</v>
-      </c>
-      <c r="F5" s="5">
-        <v>112</v>
-      </c>
-      <c r="G5" s="5">
-        <v>104</v>
-      </c>
-      <c r="H5" s="5">
-        <v>80</v>
-      </c>
-      <c r="I5" s="5">
-        <v>61</v>
-      </c>
-      <c r="J5" s="5">
-        <v>45</v>
-      </c>
-      <c r="K5" s="5">
-        <v>40</v>
-      </c>
-      <c r="L5" s="5">
-        <v>12</v>
-      </c>
-      <c r="M5" s="5">
-        <v>10</v>
-      </c>
-      <c r="N5" s="5">
+      <c r="B6" s="5">
+        <v>3472</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2162</v>
+      </c>
+      <c r="D6" s="5">
+        <v>482</v>
+      </c>
+      <c r="E6" s="5">
+        <v>195</v>
+      </c>
+      <c r="F6" s="5">
+        <v>140</v>
+      </c>
+      <c r="G6" s="5">
+        <v>138</v>
+      </c>
+      <c r="H6" s="5">
+        <v>102</v>
+      </c>
+      <c r="I6" s="5">
+        <v>87</v>
+      </c>
+      <c r="J6" s="5">
+        <v>60</v>
+      </c>
+      <c r="K6" s="5">
+        <v>44</v>
+      </c>
+      <c r="L6" s="5">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5">
+        <v>11</v>
+      </c>
+      <c r="N6" s="5">
+        <v>11</v>
+      </c>
+      <c r="O6" s="5">
         <v>9</v>
       </c>
-      <c r="O5" s="5">
-        <v>8</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="P6" s="5">
+        <v>9</v>
+      </c>
+      <c r="Q6" s="5">
         <v>6</v>
       </c>
-      <c r="Q5" s="5">
-        <v>4</v>
-      </c>
-      <c r="R5" s="5">
+      <c r="R6" s="5">
         <v>2</v>
       </c>
     </row>
@@ -2206,6 +2292,476 @@
       </c>
       <c r="H45" s="4"/>
     </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D46" s="2">
+        <v>398</v>
+      </c>
+      <c r="E46" s="2">
+        <v>157</v>
+      </c>
+      <c r="F46" s="2">
+        <v>555</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0.7207792207792207</v>
+      </c>
+      <c r="H46" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D47" s="2">
+        <v>34</v>
+      </c>
+      <c r="E47" s="2">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2">
+        <v>46</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0.05974025974025974</v>
+      </c>
+      <c r="H47" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D48" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2">
+        <v>13</v>
+      </c>
+      <c r="F48" s="2">
+        <v>34</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0.04415584415584416</v>
+      </c>
+      <c r="H48" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D49" s="2">
+        <v>23</v>
+      </c>
+      <c r="E49" s="2">
+        <v>6</v>
+      </c>
+      <c r="F49" s="2">
+        <v>29</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0.03766233766233766</v>
+      </c>
+      <c r="H49" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D50" s="2">
+        <v>9</v>
+      </c>
+      <c r="E50" s="2">
+        <v>19</v>
+      </c>
+      <c r="F50" s="2">
+        <v>28</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="H50" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D51" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2">
+        <v>6</v>
+      </c>
+      <c r="F51" s="2">
+        <v>26</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0.033766233766233764</v>
+      </c>
+      <c r="H51" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D52" s="2">
+        <v>22</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <v>22</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="H52" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D53" s="2">
+        <v>13</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2</v>
+      </c>
+      <c r="F53" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0.01948051948051948</v>
+      </c>
+      <c r="H53" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="H54" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D55" s="2">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>4</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0.005194805194805195</v>
+      </c>
+      <c r="H55" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
+        <v>2</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0.0025974025974025974</v>
+      </c>
+      <c r="H56" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2">
+        <v>2</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0.0025974025974025974</v>
+      </c>
+      <c r="H57" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0.0012987012987012987</v>
+      </c>
+      <c r="H58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0.0012987012987012987</v>
+      </c>
+      <c r="H59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-04</t>
+        </is>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5">
+        <v>554</v>
+      </c>
+      <c r="E60" s="5">
+        <v>216</v>
+      </c>
+      <c r="F60" s="5">
+        <v>770</v>
+      </c>
+      <c r="G60" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -9826,6 +10382,2232 @@
         <v>726</v>
       </c>
       <c r="F273" s="4"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B274" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D274" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E274" s="2">
+        <v>417</v>
+      </c>
+      <c r="F274" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B275" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D275" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E275" s="2">
+        <v>36</v>
+      </c>
+      <c r="F275" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B276" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D276" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E276" s="2">
+        <v>18</v>
+      </c>
+      <c r="F276" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B277" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D277" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E277" s="2">
+        <v>18</v>
+      </c>
+      <c r="F277" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B278" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D278" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E278" s="2">
+        <v>18</v>
+      </c>
+      <c r="F278" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B279" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D279" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E279" s="2">
+        <v>18</v>
+      </c>
+      <c r="F279" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B280" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D280" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E280" s="2">
+        <v>17</v>
+      </c>
+      <c r="F280" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B281" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D281" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E281" s="2">
+        <v>13</v>
+      </c>
+      <c r="F281" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B282" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D282" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E282" s="2">
+        <v>13</v>
+      </c>
+      <c r="F282" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B283" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D283" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E283" s="2">
+        <v>13</v>
+      </c>
+      <c r="F283" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B284" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D284" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E284" s="2">
+        <v>11</v>
+      </c>
+      <c r="F284" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B285" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D285" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E285" s="2">
+        <v>10</v>
+      </c>
+      <c r="F285" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B286" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D286" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E286" s="2">
+        <v>10</v>
+      </c>
+      <c r="F286" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B287" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D287" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E287" s="2">
+        <v>9</v>
+      </c>
+      <c r="F287" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B288" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D288" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E288" s="2">
+        <v>8</v>
+      </c>
+      <c r="F288" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B289" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D289" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E289" s="2">
+        <v>7</v>
+      </c>
+      <c r="F289" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B290" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D290" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E290" s="2">
+        <v>7</v>
+      </c>
+      <c r="F290" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B291" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D291" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E291" s="2">
+        <v>7</v>
+      </c>
+      <c r="F291" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B292" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwhite_wine_day</t>
+        </is>
+      </c>
+      <c r="D292" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwhite_wine_day</t>
+        </is>
+      </c>
+      <c r="E292" s="2">
+        <v>7</v>
+      </c>
+      <c r="F292" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B293" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D293" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E293" s="2">
+        <v>6</v>
+      </c>
+      <c r="F293" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B294" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D294" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E294" s="2">
+        <v>5</v>
+      </c>
+      <c r="F294" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B295" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D295" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E295" s="2">
+        <v>5</v>
+      </c>
+      <c r="F295" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B296" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C296" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="D296" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="E296" s="2">
+        <v>5</v>
+      </c>
+      <c r="F296" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B297" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t>eaug_coastguard_day</t>
+        </is>
+      </c>
+      <c r="D297" s="0" t="inlineStr">
+        <is>
+          <t>eaug_coastguard_day</t>
+        </is>
+      </c>
+      <c r="E297" s="2">
+        <v>4</v>
+      </c>
+      <c r="F297" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B298" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D298" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E298" s="2">
+        <v>4</v>
+      </c>
+      <c r="F298" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B299" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D299" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E299" s="2">
+        <v>4</v>
+      </c>
+      <c r="F299" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B300" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D300" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E300" s="2">
+        <v>4</v>
+      </c>
+      <c r="F300" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B301" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C301" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D301" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E301" s="2">
+        <v>4</v>
+      </c>
+      <c r="F301" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B302" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C302" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D302" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E302" s="2">
+        <v>4</v>
+      </c>
+      <c r="F302" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C303" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D303" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E303" s="2">
+        <v>3</v>
+      </c>
+      <c r="F303" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B304" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C304" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D304" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E304" s="2">
+        <v>3</v>
+      </c>
+      <c r="F304" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B305" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D305" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E305" s="2">
+        <v>3</v>
+      </c>
+      <c r="F305" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B306" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D306" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E306" s="2">
+        <v>3</v>
+      </c>
+      <c r="F306" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B307" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D307" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E307" s="2">
+        <v>3</v>
+      </c>
+      <c r="F307" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B308" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D308" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E308" s="2">
+        <v>2</v>
+      </c>
+      <c r="F308" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B309" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D309" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E309" s="2">
+        <v>2</v>
+      </c>
+      <c r="F309" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B310" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D310" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E310" s="2">
+        <v>2</v>
+      </c>
+      <c r="F310" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B311" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D311" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E311" s="2">
+        <v>2</v>
+      </c>
+      <c r="F311" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B312" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D312" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E312" s="2">
+        <v>2</v>
+      </c>
+      <c r="F312" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B313" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D313" s="0" t="inlineStr">
+        <is>
+          <t>love_cute</t>
+        </is>
+      </c>
+      <c r="E313" s="2">
+        <v>2</v>
+      </c>
+      <c r="F313" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B314" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C314" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D314" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E314" s="2">
+        <v>2</v>
+      </c>
+      <c r="F314" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B315" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C315" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D315" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E315" s="2">
+        <v>2</v>
+      </c>
+      <c r="F315" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B316" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C316" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D316" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E316" s="2">
+        <v>1</v>
+      </c>
+      <c r="F316" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B317" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C317" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D317" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E317" s="2">
+        <v>1</v>
+      </c>
+      <c r="F317" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B318" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C318" s="0" t="inlineStr">
+        <is>
+          <t>collassociates</t>
+        </is>
+      </c>
+      <c r="D318" s="0" t="inlineStr">
+        <is>
+          <t>birth_collassociates</t>
+        </is>
+      </c>
+      <c r="E318" s="2">
+        <v>1</v>
+      </c>
+      <c r="F318" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B319" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C319" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D319" s="0" t="inlineStr">
+        <is>
+          <t>birth_missyou</t>
+        </is>
+      </c>
+      <c r="E319" s="2">
+        <v>1</v>
+      </c>
+      <c r="F319" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B320" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C320" s="0" t="inlineStr">
+        <is>
+          <t>businessandworkplace</t>
+        </is>
+      </c>
+      <c r="D320" s="0" t="inlineStr">
+        <is>
+          <t>congrats_businessandworkplace</t>
+        </is>
+      </c>
+      <c r="E320" s="2">
+        <v>1</v>
+      </c>
+      <c r="F320" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B321" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C321" s="0" t="inlineStr">
+        <is>
+          <t>teddy</t>
+        </is>
+      </c>
+      <c r="D321" s="0" t="inlineStr">
+        <is>
+          <t>cute_teddy</t>
+        </is>
+      </c>
+      <c r="E321" s="2">
+        <v>1</v>
+      </c>
+      <c r="F321" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B322" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C322" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="D322" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="E322" s="2">
+        <v>1</v>
+      </c>
+      <c r="F322" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B323" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C323" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D323" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E323" s="2">
+        <v>1</v>
+      </c>
+      <c r="F323" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B324" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C324" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D324" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E324" s="2">
+        <v>1</v>
+      </c>
+      <c r="F324" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C325" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalyouth_day</t>
+        </is>
+      </c>
+      <c r="D325" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalyouth_day</t>
+        </is>
+      </c>
+      <c r="E325" s="2">
+        <v>1</v>
+      </c>
+      <c r="F325" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B326" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C326" s="0" t="inlineStr">
+        <is>
+          <t>eaug_justbecauseday</t>
+        </is>
+      </c>
+      <c r="D326" s="0" t="inlineStr">
+        <is>
+          <t>eaug_justbecauseday</t>
+        </is>
+      </c>
+      <c r="E326" s="2">
+        <v>1</v>
+      </c>
+      <c r="F326" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B327" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C327" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalchocolate_chip_cookie_day</t>
+        </is>
+      </c>
+      <c r="D327" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalchocolate_chip_cookie_day</t>
+        </is>
+      </c>
+      <c r="E327" s="2">
+        <v>1</v>
+      </c>
+      <c r="F327" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B328" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C328" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="D328" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="E328" s="2">
+        <v>1</v>
+      </c>
+      <c r="F328" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B329" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C329" s="0" t="inlineStr">
+        <is>
+          <t>ejun_friendinneed</t>
+        </is>
+      </c>
+      <c r="D329" s="0" t="inlineStr">
+        <is>
+          <t>ejun_friendinneed</t>
+        </is>
+      </c>
+      <c r="E329" s="2">
+        <v>1</v>
+      </c>
+      <c r="F329" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B330" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C330" s="0" t="inlineStr">
+        <is>
+          <t>enov_allsaintsday</t>
+        </is>
+      </c>
+      <c r="D330" s="0" t="inlineStr">
+        <is>
+          <t>enov_allsaintsday</t>
+        </is>
+      </c>
+      <c r="E330" s="2">
+        <v>1</v>
+      </c>
+      <c r="F330" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B331" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C331" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_missyou</t>
+        </is>
+      </c>
+      <c r="D331" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_missyou</t>
+        </is>
+      </c>
+      <c r="E331" s="2">
+        <v>1</v>
+      </c>
+      <c r="F331" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B332" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C332" s="0" t="inlineStr">
+        <is>
+          <t>esep_allangelsday</t>
+        </is>
+      </c>
+      <c r="D332" s="0" t="inlineStr">
+        <is>
+          <t>esep_allangelsday</t>
+        </is>
+      </c>
+      <c r="E332" s="2">
+        <v>1</v>
+      </c>
+      <c r="F332" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B333" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C333" s="0" t="inlineStr">
+        <is>
+          <t>huswife</t>
+        </is>
+      </c>
+      <c r="D333" s="0" t="inlineStr">
+        <is>
+          <t>fkt_huswife</t>
+        </is>
+      </c>
+      <c r="E333" s="2">
+        <v>1</v>
+      </c>
+      <c r="F333" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B334" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C334" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D334" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E334" s="2">
+        <v>1</v>
+      </c>
+      <c r="F334" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B335" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C335" s="0" t="inlineStr">
+        <is>
+          <t>joke</t>
+        </is>
+      </c>
+      <c r="D335" s="0" t="inlineStr">
+        <is>
+          <t>gen_joke</t>
+        </is>
+      </c>
+      <c r="E335" s="2">
+        <v>1</v>
+      </c>
+      <c r="F335" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B336" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C336" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D336" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E336" s="2">
+        <v>1</v>
+      </c>
+      <c r="F336" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B337" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C337" s="0" t="inlineStr">
+        <is>
+          <t>angels</t>
+        </is>
+      </c>
+      <c r="D337" s="0" t="inlineStr">
+        <is>
+          <t>insp_angels</t>
+        </is>
+      </c>
+      <c r="E337" s="2">
+        <v>1</v>
+      </c>
+      <c r="F337" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B338" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C338" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D338" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E338" s="2">
+        <v>1</v>
+      </c>
+      <c r="F338" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B339" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C339" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D339" s="0" t="inlineStr">
+        <is>
+          <t>intouch_hi</t>
+        </is>
+      </c>
+      <c r="E339" s="2">
+        <v>1</v>
+      </c>
+      <c r="F339" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B340" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C340" s="0" t="inlineStr">
+        <is>
+          <t>foreverlove</t>
+        </is>
+      </c>
+      <c r="D340" s="0" t="inlineStr">
+        <is>
+          <t>love_foreverlove</t>
+        </is>
+      </c>
+      <c r="E340" s="2">
+        <v>1</v>
+      </c>
+      <c r="F340" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B341" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C341" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D341" s="0" t="inlineStr">
+        <is>
+          <t>love_hugs</t>
+        </is>
+      </c>
+      <c r="E341" s="2">
+        <v>1</v>
+      </c>
+      <c r="F341" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B342" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C342" s="0" t="inlineStr">
+        <is>
+          <t>iamsorry</t>
+        </is>
+      </c>
+      <c r="D342" s="0" t="inlineStr">
+        <is>
+          <t>love_iamsorry</t>
+        </is>
+      </c>
+      <c r="E342" s="2">
+        <v>1</v>
+      </c>
+      <c r="F342" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B343" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C343" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D343" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E343" s="2">
+        <v>1</v>
+      </c>
+      <c r="F343" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B344" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C344" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D344" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E344" s="2">
+        <v>1</v>
+      </c>
+      <c r="F344" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B345" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C345" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D345" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E345" s="2">
+        <v>1</v>
+      </c>
+      <c r="F345" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B346" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C346" s="0" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="D346" s="0" t="inlineStr">
+        <is>
+          <t>thank_family</t>
+        </is>
+      </c>
+      <c r="E346" s="2">
+        <v>1</v>
+      </c>
+      <c r="F346" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B347" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C347" s="0" t="inlineStr">
+        <is>
+          <t>friendship</t>
+        </is>
+      </c>
+      <c r="D347" s="0" t="inlineStr">
+        <is>
+          <t>thank_friendship</t>
+        </is>
+      </c>
+      <c r="E347" s="2">
+        <v>1</v>
+      </c>
+      <c r="F347" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B348" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C348" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D348" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E348" s="2">
+        <v>1</v>
+      </c>
+      <c r="F348" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B349" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C349" s="0" t="inlineStr">
+        <is>
+          <t>german_birthday</t>
+        </is>
+      </c>
+      <c r="D349" s="0" t="inlineStr">
+        <is>
+          <t>w_german_birthday</t>
+        </is>
+      </c>
+      <c r="E349" s="2">
+        <v>1</v>
+      </c>
+      <c r="F349" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B350" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C350" s="0" t="inlineStr">
+        <is>
+          <t>spanish_love</t>
+        </is>
+      </c>
+      <c r="D350" s="0" t="inlineStr">
+        <is>
+          <t>w_spanish_love</t>
+        </is>
+      </c>
+      <c r="E350" s="2">
+        <v>1</v>
+      </c>
+      <c r="F350" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B351" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C351" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="D351" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="E351" s="2">
+        <v>1</v>
+      </c>
+      <c r="F351" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B352" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C352" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D352" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E352" s="2">
+        <v>1</v>
+      </c>
+      <c r="F352" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-04</t>
+        </is>
+      </c>
+      <c r="B353" s="4"/>
+      <c r="C353" s="4"/>
+      <c r="D353" s="4"/>
+      <c r="E353" s="5">
+        <v>770</v>
+      </c>
+      <c r="F353" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -9879,12 +12661,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Telegram</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Facebook</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -9920,10 +12702,10 @@
         <v>108</v>
       </c>
       <c r="G2" s="2">
+        <v>31</v>
+      </c>
+      <c r="H2" s="2">
         <v>47</v>
-      </c>
-      <c r="H2" s="2">
-        <v>31</v>
       </c>
       <c r="I2" s="2">
         <v>12</v>
@@ -9954,10 +12736,10 @@
         <v>118</v>
       </c>
       <c r="G3" s="2">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2">
         <v>38</v>
-      </c>
-      <c r="H3" s="2">
-        <v>34</v>
       </c>
       <c r="I3" s="2">
         <v>13</v>
@@ -9988,10 +12770,10 @@
         <v>84</v>
       </c>
       <c r="G4" s="2">
+        <v>31</v>
+      </c>
+      <c r="H4" s="2">
         <v>19</v>
-      </c>
-      <c r="H4" s="2">
-        <v>31</v>
       </c>
       <c r="I4" s="2">
         <v>3</v>
@@ -10001,36 +12783,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>805</v>
+      </c>
+      <c r="C5" s="2">
+        <v>247</v>
+      </c>
+      <c r="D5" s="2">
+        <v>268</v>
+      </c>
+      <c r="E5" s="2">
+        <v>160</v>
+      </c>
+      <c r="F5" s="2">
+        <v>72</v>
+      </c>
+      <c r="G5" s="2">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2">
+        <v>20</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <v>2823</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1001</v>
-      </c>
-      <c r="D5" s="5">
-        <v>784</v>
-      </c>
-      <c r="E5" s="5">
-        <v>499</v>
-      </c>
-      <c r="F5" s="5">
-        <v>310</v>
-      </c>
-      <c r="G5" s="5">
-        <v>104</v>
-      </c>
-      <c r="H5" s="5">
-        <v>96</v>
-      </c>
-      <c r="I5" s="5">
+      <c r="B6" s="5">
+        <v>3628</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1248</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1052</v>
+      </c>
+      <c r="E6" s="5">
+        <v>659</v>
+      </c>
+      <c r="F6" s="5">
+        <v>382</v>
+      </c>
+      <c r="G6" s="5">
+        <v>134</v>
+      </c>
+      <c r="H6" s="5">
+        <v>124</v>
+      </c>
+      <c r="I6" s="5">
         <v>28</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J6" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -423,28 +423,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>742</v>
+      </c>
+      <c r="C6" s="2">
+        <v>483</v>
+      </c>
+      <c r="D6" s="2">
+        <v>259</v>
+      </c>
+      <c r="E6" s="2">
+        <v>702</v>
+      </c>
+      <c r="F6" s="2">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2">
+        <v>230</v>
+      </c>
+      <c r="H6" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>738</v>
+      </c>
+      <c r="C7" s="2">
+        <v>507</v>
+      </c>
+      <c r="D7" s="2">
+        <v>231</v>
+      </c>
+      <c r="E7" s="2">
+        <v>715</v>
+      </c>
+      <c r="F7" s="2">
+        <v>23</v>
+      </c>
+      <c r="G7" s="2">
+        <v>237</v>
+      </c>
+      <c r="H7" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>760</v>
+      </c>
+      <c r="C8" s="2">
+        <v>511</v>
+      </c>
+      <c r="D8" s="2">
+        <v>249</v>
+      </c>
+      <c r="E8" s="2">
+        <v>731</v>
+      </c>
+      <c r="F8" s="2">
+        <v>29</v>
+      </c>
+      <c r="G8" s="2">
+        <v>251</v>
+      </c>
+      <c r="H8" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <v>3628</v>
-      </c>
-      <c r="C6" s="5">
-        <v>2225</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1403</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3472</v>
-      </c>
-      <c r="F6" s="5">
-        <v>156</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="B9" s="5">
+        <v>5868</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3726</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2142</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5620</v>
+      </c>
+      <c r="F9" s="5">
+        <v>248</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -458,19 +542,20 @@
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,14 +586,14 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Thank you</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Everyday greetings</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Friendship</t>
@@ -531,37 +616,42 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>World languages</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Cute</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Family &amp; loved ones</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Flowers</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Keeping in touch</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Pets</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
         </is>
       </c>
     </row>
@@ -584,10 +674,10 @@
         <v>57</v>
       </c>
       <c r="F2" s="2">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2">
         <v>30</v>
-      </c>
-      <c r="G2" s="2">
-        <v>28</v>
       </c>
       <c r="H2" s="2">
         <v>28</v>
@@ -602,25 +692,28 @@
         <v>12</v>
       </c>
       <c r="L2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2">
+        <v>3</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>3</v>
+      </c>
+      <c r="P2" s="2">
         <v>4</v>
       </c>
-      <c r="N2" s="2">
-        <v>3</v>
-      </c>
-      <c r="O2" s="2">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2">
+      <c r="Q2" s="2">
         <v>6</v>
       </c>
-      <c r="Q2" s="2">
-        <v>3</v>
-      </c>
       <c r="R2" s="2">
         <v>2</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -642,10 +735,10 @@
         <v>35</v>
       </c>
       <c r="F3" s="2">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2">
         <v>52</v>
-      </c>
-      <c r="G3" s="2">
-        <v>40</v>
       </c>
       <c r="H3" s="2">
         <v>41</v>
@@ -660,26 +753,29 @@
         <v>11</v>
       </c>
       <c r="L3" s="2">
+        <v>8</v>
+      </c>
+      <c r="M3" s="2">
+        <v>3</v>
+      </c>
+      <c r="N3" s="2">
         <v>10</v>
       </c>
-      <c r="M3" s="2">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2">
-        <v>3</v>
-      </c>
       <c r="O3" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" s="2">
         <v>0</v>
       </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -700,10 +796,10 @@
         <v>57</v>
       </c>
       <c r="F4" s="2">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2">
         <v>30</v>
-      </c>
-      <c r="G4" s="2">
-        <v>36</v>
       </c>
       <c r="H4" s="2">
         <v>11</v>
@@ -721,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
         <v>0</v>
@@ -730,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="2">
         <v>0</v>
@@ -738,6 +834,9 @@
       <c r="R4" s="2">
         <v>0</v>
       </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -758,10 +857,10 @@
         <v>46</v>
       </c>
       <c r="F5" s="2">
+        <v>34</v>
+      </c>
+      <c r="G5" s="2">
         <v>28</v>
-      </c>
-      <c r="G5" s="2">
-        <v>34</v>
       </c>
       <c r="H5" s="2">
         <v>22</v>
@@ -776,82 +875,271 @@
         <v>4</v>
       </c>
       <c r="L5" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O5" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="2">
         <v>1</v>
       </c>
       <c r="Q5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2">
         <v>0</v>
       </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>702</v>
+      </c>
+      <c r="C6" s="2">
+        <v>509</v>
+      </c>
+      <c r="D6" s="2">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2">
+        <v>13</v>
+      </c>
+      <c r="J6" s="2">
+        <v>15</v>
+      </c>
+      <c r="K6" s="2">
+        <v>8</v>
+      </c>
+      <c r="L6" s="2">
+        <v>17</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
+        <v>4</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2</v>
+      </c>
+      <c r="S6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>715</v>
+      </c>
+      <c r="C7" s="2">
+        <v>520</v>
+      </c>
+      <c r="D7" s="2">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2">
+        <v>11</v>
+      </c>
+      <c r="J7" s="2">
+        <v>12</v>
+      </c>
+      <c r="K7" s="2">
+        <v>10</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>8</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>731</v>
+      </c>
+      <c r="C8" s="2">
+        <v>506</v>
+      </c>
+      <c r="D8" s="2">
+        <v>54</v>
+      </c>
+      <c r="E8" s="2">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2">
+        <v>27</v>
+      </c>
+      <c r="G8" s="2">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2">
+        <v>7</v>
+      </c>
+      <c r="I8" s="2">
+        <v>17</v>
+      </c>
+      <c r="J8" s="2">
+        <v>14</v>
+      </c>
+      <c r="K8" s="2">
+        <v>8</v>
+      </c>
+      <c r="L8" s="2">
+        <v>6</v>
+      </c>
+      <c r="M8" s="2">
+        <v>6</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>3</v>
+      </c>
+      <c r="P8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <v>3472</v>
-      </c>
-      <c r="C6" s="5">
-        <v>2162</v>
-      </c>
-      <c r="D6" s="5">
-        <v>482</v>
-      </c>
-      <c r="E6" s="5">
-        <v>195</v>
-      </c>
-      <c r="F6" s="5">
-        <v>140</v>
-      </c>
-      <c r="G6" s="5">
-        <v>138</v>
-      </c>
-      <c r="H6" s="5">
-        <v>102</v>
-      </c>
-      <c r="I6" s="5">
-        <v>87</v>
-      </c>
-      <c r="J6" s="5">
-        <v>60</v>
-      </c>
-      <c r="K6" s="5">
-        <v>44</v>
-      </c>
-      <c r="L6" s="5">
-        <v>14</v>
-      </c>
-      <c r="M6" s="5">
-        <v>11</v>
-      </c>
-      <c r="N6" s="5">
-        <v>11</v>
-      </c>
-      <c r="O6" s="5">
+      <c r="B9" s="5">
+        <v>5620</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3697</v>
+      </c>
+      <c r="D9" s="5">
+        <v>588</v>
+      </c>
+      <c r="E9" s="5">
+        <v>328</v>
+      </c>
+      <c r="F9" s="5">
+        <v>238</v>
+      </c>
+      <c r="G9" s="5">
+        <v>214</v>
+      </c>
+      <c r="H9" s="5">
+        <v>136</v>
+      </c>
+      <c r="I9" s="5">
+        <v>128</v>
+      </c>
+      <c r="J9" s="5">
+        <v>101</v>
+      </c>
+      <c r="K9" s="5">
+        <v>70</v>
+      </c>
+      <c r="L9" s="5">
+        <v>32</v>
+      </c>
+      <c r="M9" s="5">
+        <v>26</v>
+      </c>
+      <c r="N9" s="5">
+        <v>16</v>
+      </c>
+      <c r="O9" s="5">
+        <v>15</v>
+      </c>
+      <c r="P9" s="5">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="5">
         <v>9</v>
       </c>
-      <c r="P6" s="5">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>6</v>
-      </c>
-      <c r="R6" s="5">
+      <c r="R9" s="5">
+        <v>8</v>
+      </c>
+      <c r="S9" s="5">
         <v>2</v>
       </c>
     </row>
@@ -2762,6 +3050,1448 @@
       </c>
       <c r="H60" s="4"/>
     </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D61" s="2">
+        <v>348</v>
+      </c>
+      <c r="E61" s="2">
+        <v>161</v>
+      </c>
+      <c r="F61" s="2">
+        <v>509</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0.7250712250712251</v>
+      </c>
+      <c r="H61" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D62" s="2">
+        <v>29</v>
+      </c>
+      <c r="E62" s="2">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2">
+        <v>40</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0.05698005698005698</v>
+      </c>
+      <c r="H62" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D63" s="2">
+        <v>22</v>
+      </c>
+      <c r="E63" s="2">
+        <v>12</v>
+      </c>
+      <c r="F63" s="2">
+        <v>34</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0.04843304843304843</v>
+      </c>
+      <c r="H63" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D64" s="2">
+        <v>7</v>
+      </c>
+      <c r="E64" s="2">
+        <v>17</v>
+      </c>
+      <c r="F64" s="2">
+        <v>24</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0.03418803418803419</v>
+      </c>
+      <c r="H64" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D65" s="2">
+        <v>13</v>
+      </c>
+      <c r="E65" s="2">
+        <v>9</v>
+      </c>
+      <c r="F65" s="2">
+        <v>22</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0.03133903133903134</v>
+      </c>
+      <c r="H65" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D66" s="2">
+        <v>17</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2">
+        <v>17</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0.024216524216524215</v>
+      </c>
+      <c r="H66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D67" s="2">
+        <v>14</v>
+      </c>
+      <c r="E67" s="2">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0.021367521367521368</v>
+      </c>
+      <c r="H67" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D68" s="2">
+        <v>11</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
+      </c>
+      <c r="F68" s="2">
+        <v>13</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="H68" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D69" s="2">
+        <v>9</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
+      </c>
+      <c r="F69" s="2">
+        <v>11</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0.01566951566951567</v>
+      </c>
+      <c r="H69" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D70" s="2">
+        <v>6</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2</v>
+      </c>
+      <c r="F70" s="2">
+        <v>8</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0.011396011396011397</v>
+      </c>
+      <c r="H70" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D71" s="2">
+        <v>4</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
+        <v>4</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0.005698005698005698</v>
+      </c>
+      <c r="H71" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D72" s="2">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2">
+        <v>2</v>
+      </c>
+      <c r="F72" s="2">
+        <v>2</v>
+      </c>
+      <c r="G72" s="3">
+        <v>0.002849002849002849</v>
+      </c>
+      <c r="H72" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0.0014245014245014246</v>
+      </c>
+      <c r="H73" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D74" s="2">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0.0014245014245014246</v>
+      </c>
+      <c r="H74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2">
+        <v>1</v>
+      </c>
+      <c r="F75" s="2">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0.0014245014245014246</v>
+      </c>
+      <c r="H75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-05</t>
+        </is>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="5">
+        <v>481</v>
+      </c>
+      <c r="E76" s="5">
+        <v>221</v>
+      </c>
+      <c r="F76" s="5">
+        <v>702</v>
+      </c>
+      <c r="G76" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D77" s="2">
+        <v>369</v>
+      </c>
+      <c r="E77" s="2">
+        <v>151</v>
+      </c>
+      <c r="F77" s="2">
+        <v>520</v>
+      </c>
+      <c r="G77" s="3">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="H77" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D78" s="2">
+        <v>33</v>
+      </c>
+      <c r="E78" s="2">
+        <v>16</v>
+      </c>
+      <c r="F78" s="2">
+        <v>49</v>
+      </c>
+      <c r="G78" s="3">
+        <v>0.06853146853146853</v>
+      </c>
+      <c r="H78" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D79" s="2">
+        <v>25</v>
+      </c>
+      <c r="E79" s="2">
+        <v>8</v>
+      </c>
+      <c r="F79" s="2">
+        <v>33</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0.046153846153846156</v>
+      </c>
+      <c r="H79" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D80" s="2">
+        <v>25</v>
+      </c>
+      <c r="E80" s="2">
+        <v>5</v>
+      </c>
+      <c r="F80" s="2">
+        <v>30</v>
+      </c>
+      <c r="G80" s="3">
+        <v>0.04195804195804196</v>
+      </c>
+      <c r="H80" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D81" s="2">
+        <v>3</v>
+      </c>
+      <c r="E81" s="2">
+        <v>17</v>
+      </c>
+      <c r="F81" s="2">
+        <v>20</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0.027972027972027972</v>
+      </c>
+      <c r="H81" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D82" s="2">
+        <v>15</v>
+      </c>
+      <c r="E82" s="2">
+        <v>1</v>
+      </c>
+      <c r="F82" s="2">
+        <v>16</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0.022377622377622378</v>
+      </c>
+      <c r="H82" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D83" s="2">
+        <v>10</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>12</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0.016783216783216783</v>
+      </c>
+      <c r="H83" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D84" s="2">
+        <v>9</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>11</v>
+      </c>
+      <c r="G84" s="3">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="H84" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D85" s="2">
+        <v>7</v>
+      </c>
+      <c r="E85" s="2">
+        <v>3</v>
+      </c>
+      <c r="F85" s="2">
+        <v>10</v>
+      </c>
+      <c r="G85" s="3">
+        <v>0.013986013986013986</v>
+      </c>
+      <c r="H85" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D86" s="2">
+        <v>6</v>
+      </c>
+      <c r="E86" s="2">
+        <v>2</v>
+      </c>
+      <c r="F86" s="2">
+        <v>8</v>
+      </c>
+      <c r="G86" s="3">
+        <v>0.011188811188811189</v>
+      </c>
+      <c r="H86" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2">
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <v>3</v>
+      </c>
+      <c r="G87" s="3">
+        <v>0.004195804195804196</v>
+      </c>
+      <c r="H87" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D88" s="2">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <v>2</v>
+      </c>
+      <c r="G88" s="3">
+        <v>0.002797202797202797</v>
+      </c>
+      <c r="H88" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D89" s="2">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2">
+        <v>1</v>
+      </c>
+      <c r="F89" s="2">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0.0013986013986013986</v>
+      </c>
+      <c r="H89" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-06</t>
+        </is>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="5">
+        <v>505</v>
+      </c>
+      <c r="E90" s="5">
+        <v>210</v>
+      </c>
+      <c r="F90" s="5">
+        <v>715</v>
+      </c>
+      <c r="G90" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D91" s="2">
+        <v>336</v>
+      </c>
+      <c r="E91" s="2">
+        <v>170</v>
+      </c>
+      <c r="F91" s="2">
+        <v>506</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0.6922024623803009</v>
+      </c>
+      <c r="H91" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D92" s="2">
+        <v>53</v>
+      </c>
+      <c r="E92" s="2">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2">
+        <v>54</v>
+      </c>
+      <c r="G92" s="3">
+        <v>0.07387140902872777</v>
+      </c>
+      <c r="H92" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D93" s="2">
+        <v>35</v>
+      </c>
+      <c r="E93" s="2">
+        <v>15</v>
+      </c>
+      <c r="F93" s="2">
+        <v>50</v>
+      </c>
+      <c r="G93" s="3">
+        <v>0.06839945280437756</v>
+      </c>
+      <c r="H93" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D94" s="2">
+        <v>10</v>
+      </c>
+      <c r="E94" s="2">
+        <v>20</v>
+      </c>
+      <c r="F94" s="2">
+        <v>30</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0.04103967168262654</v>
+      </c>
+      <c r="H94" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D95" s="2">
+        <v>22</v>
+      </c>
+      <c r="E95" s="2">
+        <v>5</v>
+      </c>
+      <c r="F95" s="2">
+        <v>27</v>
+      </c>
+      <c r="G95" s="3">
+        <v>0.036935704514363885</v>
+      </c>
+      <c r="H95" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D96" s="2">
+        <v>10</v>
+      </c>
+      <c r="E96" s="2">
+        <v>7</v>
+      </c>
+      <c r="F96" s="2">
+        <v>17</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="H96" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D97" s="2">
+        <v>11</v>
+      </c>
+      <c r="E97" s="2">
+        <v>3</v>
+      </c>
+      <c r="F97" s="2">
+        <v>14</v>
+      </c>
+      <c r="G97" s="3">
+        <v>0.019151846785225718</v>
+      </c>
+      <c r="H97" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D98" s="2">
+        <v>7</v>
+      </c>
+      <c r="E98" s="2">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>8</v>
+      </c>
+      <c r="G98" s="3">
+        <v>0.01094391244870041</v>
+      </c>
+      <c r="H98" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D99" s="2">
+        <v>7</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2">
+        <v>7</v>
+      </c>
+      <c r="G99" s="3">
+        <v>0.009575923392612859</v>
+      </c>
+      <c r="H99" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D100" s="2">
+        <v>3</v>
+      </c>
+      <c r="E100" s="2">
+        <v>3</v>
+      </c>
+      <c r="F100" s="2">
+        <v>6</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0.008207934336525308</v>
+      </c>
+      <c r="H100" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D101" s="2">
+        <v>6</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2">
+        <v>6</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0.008207934336525308</v>
+      </c>
+      <c r="H101" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D102" s="2">
+        <v>3</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0.004103967168262654</v>
+      </c>
+      <c r="H102" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D103" s="2">
+        <v>1</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3">
+        <v>0.0013679890560875513</v>
+      </c>
+      <c r="H103" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D104" s="2">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2">
+        <v>1</v>
+      </c>
+      <c r="G104" s="3">
+        <v>0.0013679890560875513</v>
+      </c>
+      <c r="H104" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D105" s="2">
+        <v>1</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2">
+        <v>1</v>
+      </c>
+      <c r="G105" s="3">
+        <v>0.0013679890560875513</v>
+      </c>
+      <c r="H105" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-07</t>
+        </is>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="5">
+        <v>506</v>
+      </c>
+      <c r="E106" s="5">
+        <v>225</v>
+      </c>
+      <c r="F106" s="5">
+        <v>731</v>
+      </c>
+      <c r="G106" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -12608,6 +14338,6488 @@
         <v>770</v>
       </c>
       <c r="F353" s="4"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B354" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C354" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D354" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E354" s="2">
+        <v>396</v>
+      </c>
+      <c r="F354" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B355" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C355" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D355" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E355" s="2">
+        <v>29</v>
+      </c>
+      <c r="F355" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B356" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C356" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D356" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E356" s="2">
+        <v>17</v>
+      </c>
+      <c r="F356" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B357" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C357" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D357" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E357" s="2">
+        <v>14</v>
+      </c>
+      <c r="F357" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B358" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C358" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D358" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E358" s="2">
+        <v>14</v>
+      </c>
+      <c r="F358" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B359" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C359" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D359" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E359" s="2">
+        <v>14</v>
+      </c>
+      <c r="F359" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B360" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C360" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D360" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E360" s="2">
+        <v>13</v>
+      </c>
+      <c r="F360" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B361" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C361" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D361" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E361" s="2">
+        <v>13</v>
+      </c>
+      <c r="F361" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B362" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C362" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D362" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E362" s="2">
+        <v>12</v>
+      </c>
+      <c r="F362" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C363" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D363" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E363" s="2">
+        <v>11</v>
+      </c>
+      <c r="F363" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B364" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C364" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D364" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E364" s="2">
+        <v>10</v>
+      </c>
+      <c r="F364" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C365" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D365" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E365" s="2">
+        <v>10</v>
+      </c>
+      <c r="F365" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B366" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C366" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D366" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E366" s="2">
+        <v>10</v>
+      </c>
+      <c r="F366" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B367" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C367" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D367" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E367" s="2">
+        <v>9</v>
+      </c>
+      <c r="F367" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B368" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C368" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D368" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E368" s="2">
+        <v>8</v>
+      </c>
+      <c r="F368" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B369" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C369" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D369" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E369" s="2">
+        <v>7</v>
+      </c>
+      <c r="F369" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B370" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C370" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D370" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E370" s="2">
+        <v>7</v>
+      </c>
+      <c r="F370" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B371" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C371" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D371" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E371" s="2">
+        <v>6</v>
+      </c>
+      <c r="F371" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B372" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C372" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D372" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E372" s="2">
+        <v>6</v>
+      </c>
+      <c r="F372" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B373" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C373" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D373" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E373" s="2">
+        <v>6</v>
+      </c>
+      <c r="F373" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B374" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C374" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D374" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E374" s="2">
+        <v>5</v>
+      </c>
+      <c r="F374" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B375" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C375" s="0" t="inlineStr">
+        <is>
+          <t>eaug_worklike_a_dog_day</t>
+        </is>
+      </c>
+      <c r="D375" s="0" t="inlineStr">
+        <is>
+          <t>eaug_worklike_a_dog_day</t>
+        </is>
+      </c>
+      <c r="E375" s="2">
+        <v>5</v>
+      </c>
+      <c r="F375" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B376" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C376" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D376" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E376" s="2">
+        <v>5</v>
+      </c>
+      <c r="F376" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B377" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C377" s="0" t="inlineStr">
+        <is>
+          <t>balloons</t>
+        </is>
+      </c>
+      <c r="D377" s="0" t="inlineStr">
+        <is>
+          <t>birth_balloons</t>
+        </is>
+      </c>
+      <c r="E377" s="2">
+        <v>4</v>
+      </c>
+      <c r="F377" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B378" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C378" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D378" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E378" s="2">
+        <v>4</v>
+      </c>
+      <c r="F378" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B379" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C379" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D379" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E379" s="2">
+        <v>4</v>
+      </c>
+      <c r="F379" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B380" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C380" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D380" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E380" s="2">
+        <v>4</v>
+      </c>
+      <c r="F380" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B381" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C381" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D381" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E381" s="2">
+        <v>3</v>
+      </c>
+      <c r="F381" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B382" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C382" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D382" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E382" s="2">
+        <v>3</v>
+      </c>
+      <c r="F382" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B383" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C383" s="0" t="inlineStr">
+        <is>
+          <t>friendsforever</t>
+        </is>
+      </c>
+      <c r="D383" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendsforever</t>
+        </is>
+      </c>
+      <c r="E383" s="2">
+        <v>3</v>
+      </c>
+      <c r="F383" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B384" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C384" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D384" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E384" s="2">
+        <v>2</v>
+      </c>
+      <c r="F384" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B385" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C385" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D385" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E385" s="2">
+        <v>2</v>
+      </c>
+      <c r="F385" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B386" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C386" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D386" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E386" s="2">
+        <v>2</v>
+      </c>
+      <c r="F386" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B387" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C387" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D387" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E387" s="2">
+        <v>2</v>
+      </c>
+      <c r="F387" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B388" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C388" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="D388" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="E388" s="2">
+        <v>2</v>
+      </c>
+      <c r="F388" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B389" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C389" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D389" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E389" s="2">
+        <v>2</v>
+      </c>
+      <c r="F389" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B390" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C390" s="0" t="inlineStr">
+        <is>
+          <t>cheerup</t>
+        </is>
+      </c>
+      <c r="D390" s="0" t="inlineStr">
+        <is>
+          <t>gen_cheerup</t>
+        </is>
+      </c>
+      <c r="E390" s="2">
+        <v>2</v>
+      </c>
+      <c r="F390" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B391" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C391" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D391" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E391" s="2">
+        <v>2</v>
+      </c>
+      <c r="F391" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C392" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D392" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E392" s="2">
+        <v>2</v>
+      </c>
+      <c r="F392" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B393" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C393" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D393" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E393" s="2">
+        <v>2</v>
+      </c>
+      <c r="F393" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B394" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C394" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D394" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E394" s="2">
+        <v>2</v>
+      </c>
+      <c r="F394" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C395" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D395" s="0" t="inlineStr">
+        <is>
+          <t>anniv_belated</t>
+        </is>
+      </c>
+      <c r="E395" s="2">
+        <v>1</v>
+      </c>
+      <c r="F395" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C396" s="0" t="inlineStr">
+        <is>
+          <t>collassociates</t>
+        </is>
+      </c>
+      <c r="D396" s="0" t="inlineStr">
+        <is>
+          <t>birth_collassociates</t>
+        </is>
+      </c>
+      <c r="E396" s="2">
+        <v>1</v>
+      </c>
+      <c r="F396" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B397" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C397" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D397" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E397" s="2">
+        <v>1</v>
+      </c>
+      <c r="F397" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B398" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C398" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D398" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E398" s="2">
+        <v>1</v>
+      </c>
+      <c r="F398" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B399" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C399" s="0" t="inlineStr">
+        <is>
+          <t>farewell</t>
+        </is>
+      </c>
+      <c r="D399" s="0" t="inlineStr">
+        <is>
+          <t>bus_farewell</t>
+        </is>
+      </c>
+      <c r="E399" s="2">
+        <v>1</v>
+      </c>
+      <c r="F399" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B400" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C400" s="0" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="D400" s="0" t="inlineStr">
+        <is>
+          <t>bus_humor</t>
+        </is>
+      </c>
+      <c r="E400" s="2">
+        <v>1</v>
+      </c>
+      <c r="F400" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B401" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C401" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D401" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E401" s="2">
+        <v>1</v>
+      </c>
+      <c r="F401" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B402" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C402" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D402" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E402" s="2">
+        <v>1</v>
+      </c>
+      <c r="F402" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B403" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C403" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D403" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E403" s="2">
+        <v>1</v>
+      </c>
+      <c r="F403" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B404" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C404" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="D404" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="E404" s="2">
+        <v>1</v>
+      </c>
+      <c r="F404" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B405" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C405" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="D405" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="E405" s="2">
+        <v>1</v>
+      </c>
+      <c r="F405" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C406" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D406" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E406" s="2">
+        <v>1</v>
+      </c>
+      <c r="F406" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B407" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C407" s="0" t="inlineStr">
+        <is>
+          <t>efeb_lent</t>
+        </is>
+      </c>
+      <c r="D407" s="0" t="inlineStr">
+        <is>
+          <t>efeb_lent</t>
+        </is>
+      </c>
+      <c r="E407" s="2">
+        <v>1</v>
+      </c>
+      <c r="F407" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B408" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C408" s="0" t="inlineStr">
+        <is>
+          <t>efeb_proposeday</t>
+        </is>
+      </c>
+      <c r="D408" s="0" t="inlineStr">
+        <is>
+          <t>efeb_proposeday</t>
+        </is>
+      </c>
+      <c r="E408" s="2">
+        <v>1</v>
+      </c>
+      <c r="F408" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B409" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C409" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sayheyday</t>
+        </is>
+      </c>
+      <c r="D409" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sayheyday</t>
+        </is>
+      </c>
+      <c r="E409" s="2">
+        <v>1</v>
+      </c>
+      <c r="F409" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B410" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C410" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D410" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E410" s="2">
+        <v>1</v>
+      </c>
+      <c r="F410" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B411" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C411" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D411" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E411" s="2">
+        <v>1</v>
+      </c>
+      <c r="F411" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B412" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C412" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D412" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E412" s="2">
+        <v>1</v>
+      </c>
+      <c r="F412" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B413" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C413" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D413" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E413" s="2">
+        <v>1</v>
+      </c>
+      <c r="F413" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B414" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C414" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E414" s="2">
+        <v>1</v>
+      </c>
+      <c r="F414" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B415" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D415" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E415" s="2">
+        <v>1</v>
+      </c>
+      <c r="F415" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B416" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C416" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D416" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E416" s="2">
+        <v>1</v>
+      </c>
+      <c r="F416" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B417" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C417" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D417" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E417" s="2">
+        <v>1</v>
+      </c>
+      <c r="F417" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B418" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C418" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D418" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E418" s="2">
+        <v>1</v>
+      </c>
+      <c r="F418" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B419" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C419" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D419" s="0" t="inlineStr">
+        <is>
+          <t>pet_missyou</t>
+        </is>
+      </c>
+      <c r="E419" s="2">
+        <v>1</v>
+      </c>
+      <c r="F419" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B420" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C420" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D420" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E420" s="2">
+        <v>1</v>
+      </c>
+      <c r="F420" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B421" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C421" s="0" t="inlineStr">
+        <is>
+          <t>russian_birthday</t>
+        </is>
+      </c>
+      <c r="D421" s="0" t="inlineStr">
+        <is>
+          <t>w_russian_birthday</t>
+        </is>
+      </c>
+      <c r="E421" s="2">
+        <v>1</v>
+      </c>
+      <c r="F421" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B422" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C422" s="0" t="inlineStr">
+        <is>
+          <t>wed_belatedwishes</t>
+        </is>
+      </c>
+      <c r="D422" s="0" t="inlineStr">
+        <is>
+          <t>wed_belatedwishes</t>
+        </is>
+      </c>
+      <c r="E422" s="2">
+        <v>1</v>
+      </c>
+      <c r="F422" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-05</t>
+        </is>
+      </c>
+      <c r="B423" s="4"/>
+      <c r="C423" s="4"/>
+      <c r="D423" s="4"/>
+      <c r="E423" s="5">
+        <v>702</v>
+      </c>
+      <c r="F423" s="4"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B424" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C424" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D424" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E424" s="2">
+        <v>412</v>
+      </c>
+      <c r="F424" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C425" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D425" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E425" s="2">
+        <v>38</v>
+      </c>
+      <c r="F425" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C426" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D426" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E426" s="2">
+        <v>21</v>
+      </c>
+      <c r="F426" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C427" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalroot_beer_float_day</t>
+        </is>
+      </c>
+      <c r="D427" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalroot_beer_float_day</t>
+        </is>
+      </c>
+      <c r="E427" s="2">
+        <v>18</v>
+      </c>
+      <c r="F427" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C428" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D428" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E428" s="2">
+        <v>12</v>
+      </c>
+      <c r="F428" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C429" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D429" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E429" s="2">
+        <v>12</v>
+      </c>
+      <c r="F429" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B430" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C430" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D430" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E430" s="2">
+        <v>11</v>
+      </c>
+      <c r="F430" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B431" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C431" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D431" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E431" s="2">
+        <v>10</v>
+      </c>
+      <c r="F431" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B432" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C432" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D432" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E432" s="2">
+        <v>10</v>
+      </c>
+      <c r="F432" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B433" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C433" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D433" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E433" s="2">
+        <v>9</v>
+      </c>
+      <c r="F433" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B434" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C434" s="0" t="inlineStr">
+        <is>
+          <t>funny</t>
+        </is>
+      </c>
+      <c r="D434" s="0" t="inlineStr">
+        <is>
+          <t>friend_funny</t>
+        </is>
+      </c>
+      <c r="E434" s="2">
+        <v>9</v>
+      </c>
+      <c r="F434" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B435" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C435" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D435" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E435" s="2">
+        <v>8</v>
+      </c>
+      <c r="F435" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B436" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C436" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D436" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E436" s="2">
+        <v>8</v>
+      </c>
+      <c r="F436" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B437" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C437" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D437" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E437" s="2">
+        <v>7</v>
+      </c>
+      <c r="F437" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B438" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C438" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D438" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E438" s="2">
+        <v>6</v>
+      </c>
+      <c r="F438" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B439" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C439" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D439" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E439" s="2">
+        <v>6</v>
+      </c>
+      <c r="F439" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B440" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C440" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D440" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E440" s="2">
+        <v>6</v>
+      </c>
+      <c r="F440" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B441" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C441" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D441" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E441" s="2">
+        <v>6</v>
+      </c>
+      <c r="F441" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B442" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C442" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D442" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E442" s="2">
+        <v>5</v>
+      </c>
+      <c r="F442" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B443" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C443" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D443" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E443" s="2">
+        <v>5</v>
+      </c>
+      <c r="F443" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B444" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C444" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D444" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E444" s="2">
+        <v>5</v>
+      </c>
+      <c r="F444" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B445" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C445" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D445" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E445" s="2">
+        <v>5</v>
+      </c>
+      <c r="F445" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B446" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C446" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D446" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E446" s="2">
+        <v>4</v>
+      </c>
+      <c r="F446" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B447" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C447" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D447" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E447" s="2">
+        <v>4</v>
+      </c>
+      <c r="F447" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B448" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C448" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D448" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E448" s="2">
+        <v>4</v>
+      </c>
+      <c r="F448" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B449" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C449" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D449" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E449" s="2">
+        <v>4</v>
+      </c>
+      <c r="F449" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B450" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C450" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D450" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E450" s="2">
+        <v>3</v>
+      </c>
+      <c r="F450" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B451" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C451" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D451" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E451" s="2">
+        <v>3</v>
+      </c>
+      <c r="F451" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B452" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C452" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D452" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E452" s="2">
+        <v>3</v>
+      </c>
+      <c r="F452" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B453" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C453" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D453" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E453" s="2">
+        <v>3</v>
+      </c>
+      <c r="F453" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B454" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C454" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D454" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E454" s="2">
+        <v>2</v>
+      </c>
+      <c r="F454" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B455" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C455" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D455" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E455" s="2">
+        <v>2</v>
+      </c>
+      <c r="F455" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B456" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C456" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D456" s="0" t="inlineStr">
+        <is>
+          <t>birth_missyou</t>
+        </is>
+      </c>
+      <c r="E456" s="2">
+        <v>2</v>
+      </c>
+      <c r="F456" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B457" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C457" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D457" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E457" s="2">
+        <v>2</v>
+      </c>
+      <c r="F457" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B458" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C458" s="0" t="inlineStr">
+        <is>
+          <t>appreciate</t>
+        </is>
+      </c>
+      <c r="D458" s="0" t="inlineStr">
+        <is>
+          <t>bus_appreciate</t>
+        </is>
+      </c>
+      <c r="E458" s="2">
+        <v>2</v>
+      </c>
+      <c r="F458" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B459" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C459" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D459" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E459" s="2">
+        <v>2</v>
+      </c>
+      <c r="F459" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B460" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C460" s="0" t="inlineStr">
+        <is>
+          <t>esep_ganeshchaturthi</t>
+        </is>
+      </c>
+      <c r="D460" s="0" t="inlineStr">
+        <is>
+          <t>esep_ganeshchaturthi</t>
+        </is>
+      </c>
+      <c r="E460" s="2">
+        <v>2</v>
+      </c>
+      <c r="F460" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B461" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C461" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D461" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E461" s="2">
+        <v>2</v>
+      </c>
+      <c r="F461" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B462" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C462" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D462" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E462" s="2">
+        <v>2</v>
+      </c>
+      <c r="F462" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B463" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C463" s="0" t="inlineStr">
+        <is>
+          <t>midcrisis</t>
+        </is>
+      </c>
+      <c r="D463" s="0" t="inlineStr">
+        <is>
+          <t>gen_midcrisis</t>
+        </is>
+      </c>
+      <c r="E463" s="2">
+        <v>2</v>
+      </c>
+      <c r="F463" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B464" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C464" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D464" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E464" s="2">
+        <v>2</v>
+      </c>
+      <c r="F464" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B465" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C465" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D465" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E465" s="2">
+        <v>2</v>
+      </c>
+      <c r="F465" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B466" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C466" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D466" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E466" s="2">
+        <v>2</v>
+      </c>
+      <c r="F466" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B467" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C467" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D467" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E467" s="2">
+        <v>2</v>
+      </c>
+      <c r="F467" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B468" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C468" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="D468" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="E468" s="2">
+        <v>2</v>
+      </c>
+      <c r="F468" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B469" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C469" s="0" t="inlineStr">
+        <is>
+          <t>collassociates</t>
+        </is>
+      </c>
+      <c r="D469" s="0" t="inlineStr">
+        <is>
+          <t>birth_collassociates</t>
+        </is>
+      </c>
+      <c r="E469" s="2">
+        <v>1</v>
+      </c>
+      <c r="F469" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B470" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C470" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D470" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E470" s="2">
+        <v>1</v>
+      </c>
+      <c r="F470" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B471" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C471" s="0" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="D471" s="0" t="inlineStr">
+        <is>
+          <t>bus_humor</t>
+        </is>
+      </c>
+      <c r="E471" s="2">
+        <v>1</v>
+      </c>
+      <c r="F471" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B472" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C472" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D472" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E472" s="2">
+        <v>1</v>
+      </c>
+      <c r="F472" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B473" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C473" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D473" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E473" s="2">
+        <v>1</v>
+      </c>
+      <c r="F473" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B474" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C474" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D474" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E474" s="2">
+        <v>1</v>
+      </c>
+      <c r="F474" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B475" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C475" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D475" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E475" s="2">
+        <v>1</v>
+      </c>
+      <c r="F475" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B476" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C476" s="0" t="inlineStr">
+        <is>
+          <t>eaug_dollarday</t>
+        </is>
+      </c>
+      <c r="D476" s="0" t="inlineStr">
+        <is>
+          <t>eaug_dollarday</t>
+        </is>
+      </c>
+      <c r="E476" s="2">
+        <v>1</v>
+      </c>
+      <c r="F476" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B477" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C477" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D477" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E477" s="2">
+        <v>1</v>
+      </c>
+      <c r="F477" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B478" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C478" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="D478" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="E478" s="2">
+        <v>1</v>
+      </c>
+      <c r="F478" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B479" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C479" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationallighthouse_day</t>
+        </is>
+      </c>
+      <c r="D479" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationallighthouse_day</t>
+        </is>
+      </c>
+      <c r="E479" s="2">
+        <v>1</v>
+      </c>
+      <c r="F479" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B480" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C480" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberries_in_cream_day</t>
+        </is>
+      </c>
+      <c r="D480" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberries_in_cream_day</t>
+        </is>
+      </c>
+      <c r="E480" s="2">
+        <v>1</v>
+      </c>
+      <c r="F480" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B481" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C481" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D481" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E481" s="2">
+        <v>1</v>
+      </c>
+      <c r="F481" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B482" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C482" s="0" t="inlineStr">
+        <is>
+          <t>esep_harvestmoonfest</t>
+        </is>
+      </c>
+      <c r="D482" s="0" t="inlineStr">
+        <is>
+          <t>esep_harvestmoonfest</t>
+        </is>
+      </c>
+      <c r="E482" s="2">
+        <v>1</v>
+      </c>
+      <c r="F482" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B483" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C483" s="0" t="inlineStr">
+        <is>
+          <t>brothers</t>
+        </is>
+      </c>
+      <c r="D483" s="0" t="inlineStr">
+        <is>
+          <t>fkt_brothers</t>
+        </is>
+      </c>
+      <c r="E483" s="2">
+        <v>1</v>
+      </c>
+      <c r="F483" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B484" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C484" s="0" t="inlineStr">
+        <is>
+          <t>huswife</t>
+        </is>
+      </c>
+      <c r="D484" s="0" t="inlineStr">
+        <is>
+          <t>fkt_huswife</t>
+        </is>
+      </c>
+      <c r="E484" s="2">
+        <v>1</v>
+      </c>
+      <c r="F484" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B485" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C485" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D485" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E485" s="2">
+        <v>1</v>
+      </c>
+      <c r="F485" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B486" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C486" s="0" t="inlineStr">
+        <is>
+          <t>smiles</t>
+        </is>
+      </c>
+      <c r="D486" s="0" t="inlineStr">
+        <is>
+          <t>friend_smiles</t>
+        </is>
+      </c>
+      <c r="E486" s="2">
+        <v>1</v>
+      </c>
+      <c r="F486" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B487" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C487" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D487" s="0" t="inlineStr">
+        <is>
+          <t>gen_blessings</t>
+        </is>
+      </c>
+      <c r="E487" s="2">
+        <v>1</v>
+      </c>
+      <c r="F487" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B488" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C488" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D488" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E488" s="2">
+        <v>1</v>
+      </c>
+      <c r="F488" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B489" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C489" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D489" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E489" s="2">
+        <v>1</v>
+      </c>
+      <c r="F489" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B490" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C490" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D490" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E490" s="2">
+        <v>1</v>
+      </c>
+      <c r="F490" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B491" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C491" s="0" t="inlineStr">
+        <is>
+          <t>iamsorry</t>
+        </is>
+      </c>
+      <c r="D491" s="0" t="inlineStr">
+        <is>
+          <t>love_iamsorry</t>
+        </is>
+      </c>
+      <c r="E491" s="2">
+        <v>1</v>
+      </c>
+      <c r="F491" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B492" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C492" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D492" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E492" s="2">
+        <v>1</v>
+      </c>
+      <c r="F492" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B493" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C493" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D493" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E493" s="2">
+        <v>1</v>
+      </c>
+      <c r="F493" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B494" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C494" s="0" t="inlineStr">
+        <is>
+          <t>friendship</t>
+        </is>
+      </c>
+      <c r="D494" s="0" t="inlineStr">
+        <is>
+          <t>thank_friendship</t>
+        </is>
+      </c>
+      <c r="E494" s="2">
+        <v>1</v>
+      </c>
+      <c r="F494" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B495" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C495" s="0" t="inlineStr">
+        <is>
+          <t>spanish_birthday</t>
+        </is>
+      </c>
+      <c r="D495" s="0" t="inlineStr">
+        <is>
+          <t>w_spanish_birthday</t>
+        </is>
+      </c>
+      <c r="E495" s="2">
+        <v>1</v>
+      </c>
+      <c r="F495" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B496" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C496" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D496" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E496" s="2">
+        <v>1</v>
+      </c>
+      <c r="F496" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-06</t>
+        </is>
+      </c>
+      <c r="B497" s="4"/>
+      <c r="C497" s="4"/>
+      <c r="D497" s="4"/>
+      <c r="E497" s="5">
+        <v>715</v>
+      </c>
+      <c r="F497" s="4"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B498" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C498" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D498" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E498" s="2">
+        <v>381</v>
+      </c>
+      <c r="F498" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B499" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C499" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D499" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E499" s="2">
+        <v>31</v>
+      </c>
+      <c r="F499" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B500" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C500" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationallighthouse_day</t>
+        </is>
+      </c>
+      <c r="D500" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationallighthouse_day</t>
+        </is>
+      </c>
+      <c r="E500" s="2">
+        <v>28</v>
+      </c>
+      <c r="F500" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B501" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C501" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D501" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E501" s="2">
+        <v>25</v>
+      </c>
+      <c r="F501" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B502" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C502" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D502" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E502" s="2">
+        <v>14</v>
+      </c>
+      <c r="F502" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B503" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C503" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D503" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E503" s="2">
+        <v>13</v>
+      </c>
+      <c r="F503" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B504" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C504" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D504" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E504" s="2">
+        <v>12</v>
+      </c>
+      <c r="F504" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B505" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C505" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D505" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E505" s="2">
+        <v>11</v>
+      </c>
+      <c r="F505" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B506" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C506" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D506" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E506" s="2">
+        <v>11</v>
+      </c>
+      <c r="F506" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B507" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C507" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D507" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E507" s="2">
+        <v>10</v>
+      </c>
+      <c r="F507" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B508" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C508" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D508" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E508" s="2">
+        <v>9</v>
+      </c>
+      <c r="F508" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B509" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C509" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D509" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E509" s="2">
+        <v>8</v>
+      </c>
+      <c r="F509" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B510" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C510" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D510" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E510" s="2">
+        <v>8</v>
+      </c>
+      <c r="F510" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B511" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C511" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D511" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E511" s="2">
+        <v>8</v>
+      </c>
+      <c r="F511" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B512" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C512" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D512" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E512" s="2">
+        <v>7</v>
+      </c>
+      <c r="F512" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B513" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C513" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D513" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E513" s="2">
+        <v>6</v>
+      </c>
+      <c r="F513" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B514" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C514" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="D514" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="E514" s="2">
+        <v>6</v>
+      </c>
+      <c r="F514" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B515" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C515" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D515" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E515" s="2">
+        <v>6</v>
+      </c>
+      <c r="F515" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B516" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C516" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D516" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E516" s="2">
+        <v>6</v>
+      </c>
+      <c r="F516" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B517" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C517" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D517" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E517" s="2">
+        <v>5</v>
+      </c>
+      <c r="F517" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B518" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C518" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D518" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E518" s="2">
+        <v>5</v>
+      </c>
+      <c r="F518" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B519" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C519" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D519" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E519" s="2">
+        <v>5</v>
+      </c>
+      <c r="F519" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B520" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C520" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberries_in_cream_day</t>
+        </is>
+      </c>
+      <c r="D520" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberries_in_cream_day</t>
+        </is>
+      </c>
+      <c r="E520" s="2">
+        <v>5</v>
+      </c>
+      <c r="F520" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B521" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C521" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D521" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E521" s="2">
+        <v>5</v>
+      </c>
+      <c r="F521" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B522" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C522" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D522" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E522" s="2">
+        <v>5</v>
+      </c>
+      <c r="F522" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B523" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C523" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D523" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E523" s="2">
+        <v>5</v>
+      </c>
+      <c r="F523" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B524" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C524" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D524" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E524" s="2">
+        <v>4</v>
+      </c>
+      <c r="F524" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B525" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C525" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D525" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E525" s="2">
+        <v>4</v>
+      </c>
+      <c r="F525" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B526" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C526" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="D526" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="E526" s="2">
+        <v>4</v>
+      </c>
+      <c r="F526" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B527" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C527" s="0" t="inlineStr">
+        <is>
+          <t>loveyoumom</t>
+        </is>
+      </c>
+      <c r="D527" s="0" t="inlineStr">
+        <is>
+          <t>fkt_loveyoumom</t>
+        </is>
+      </c>
+      <c r="E527" s="2">
+        <v>3</v>
+      </c>
+      <c r="F527" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B528" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C528" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D528" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E528" s="2">
+        <v>3</v>
+      </c>
+      <c r="F528" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B529" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C529" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D529" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E529" s="2">
+        <v>3</v>
+      </c>
+      <c r="F529" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B530" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C530" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D530" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E530" s="2">
+        <v>3</v>
+      </c>
+      <c r="F530" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B531" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C531" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D531" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E531" s="2">
+        <v>3</v>
+      </c>
+      <c r="F531" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B532" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C532" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D532" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E532" s="2">
+        <v>2</v>
+      </c>
+      <c r="F532" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B533" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C533" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D533" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E533" s="2">
+        <v>2</v>
+      </c>
+      <c r="F533" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B534" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C534" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D534" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E534" s="2">
+        <v>2</v>
+      </c>
+      <c r="F534" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B535" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C535" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D535" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E535" s="2">
+        <v>2</v>
+      </c>
+      <c r="F535" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B536" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C536" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D536" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E536" s="2">
+        <v>2</v>
+      </c>
+      <c r="F536" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B537" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C537" s="0" t="inlineStr">
+        <is>
+          <t>zodiac</t>
+        </is>
+      </c>
+      <c r="D537" s="0" t="inlineStr">
+        <is>
+          <t>birth_zodiac</t>
+        </is>
+      </c>
+      <c r="E537" s="2">
+        <v>2</v>
+      </c>
+      <c r="F537" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B538" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C538" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D538" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E538" s="2">
+        <v>2</v>
+      </c>
+      <c r="F538" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B539" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C539" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="D539" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="E539" s="2">
+        <v>2</v>
+      </c>
+      <c r="F539" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B540" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C540" s="0" t="inlineStr">
+        <is>
+          <t>eaug_happinesshappens_day</t>
+        </is>
+      </c>
+      <c r="D540" s="0" t="inlineStr">
+        <is>
+          <t>eaug_happinesshappens_day</t>
+        </is>
+      </c>
+      <c r="E540" s="2">
+        <v>2</v>
+      </c>
+      <c r="F540" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B541" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C541" s="0" t="inlineStr">
+        <is>
+          <t>sonsdaughter</t>
+        </is>
+      </c>
+      <c r="D541" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sonsdaughter</t>
+        </is>
+      </c>
+      <c r="E541" s="2">
+        <v>2</v>
+      </c>
+      <c r="F541" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B542" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C542" s="0" t="inlineStr">
+        <is>
+          <t>smiles</t>
+        </is>
+      </c>
+      <c r="D542" s="0" t="inlineStr">
+        <is>
+          <t>friend_smiles</t>
+        </is>
+      </c>
+      <c r="E542" s="2">
+        <v>2</v>
+      </c>
+      <c r="F542" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B543" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C543" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D543" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E543" s="2">
+        <v>2</v>
+      </c>
+      <c r="F543" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B544" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C544" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D544" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E544" s="2">
+        <v>2</v>
+      </c>
+      <c r="F544" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B545" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C545" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D545" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E545" s="2">
+        <v>2</v>
+      </c>
+      <c r="F545" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B546" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C546" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D546" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E546" s="2">
+        <v>2</v>
+      </c>
+      <c r="F546" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B547" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C547" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D547" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E547" s="2">
+        <v>1</v>
+      </c>
+      <c r="F547" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B548" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C548" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D548" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E548" s="2">
+        <v>1</v>
+      </c>
+      <c r="F548" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B549" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C549" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D549" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E549" s="2">
+        <v>1</v>
+      </c>
+      <c r="F549" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B550" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C550" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D550" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E550" s="2">
+        <v>1</v>
+      </c>
+      <c r="F550" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B551" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C551" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D551" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E551" s="2">
+        <v>1</v>
+      </c>
+      <c r="F551" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B552" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C552" s="0" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="D552" s="0" t="inlineStr">
+        <is>
+          <t>bus_humor</t>
+        </is>
+      </c>
+      <c r="E552" s="2">
+        <v>1</v>
+      </c>
+      <c r="F552" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B553" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C553" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D553" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E553" s="2">
+        <v>1</v>
+      </c>
+      <c r="F553" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B554" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C554" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D554" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E554" s="2">
+        <v>1</v>
+      </c>
+      <c r="F554" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B555" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C555" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D555" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E555" s="2">
+        <v>1</v>
+      </c>
+      <c r="F555" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B556" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C556" s="0" t="inlineStr">
+        <is>
+          <t>eaug_dollarday</t>
+        </is>
+      </c>
+      <c r="D556" s="0" t="inlineStr">
+        <is>
+          <t>eaug_dollarday</t>
+        </is>
+      </c>
+      <c r="E556" s="2">
+        <v>1</v>
+      </c>
+      <c r="F556" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B557" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C557" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D557" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E557" s="2">
+        <v>1</v>
+      </c>
+      <c r="F557" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B558" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C558" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D558" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E558" s="2">
+        <v>1</v>
+      </c>
+      <c r="F558" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B559" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C559" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="D559" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="E559" s="2">
+        <v>1</v>
+      </c>
+      <c r="F559" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B560" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C560" s="0" t="inlineStr">
+        <is>
+          <t>enov_worldhelloday</t>
+        </is>
+      </c>
+      <c r="D560" s="0" t="inlineStr">
+        <is>
+          <t>enov_worldhelloday</t>
+        </is>
+      </c>
+      <c r="E560" s="2">
+        <v>1</v>
+      </c>
+      <c r="F560" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B561" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C561" s="0" t="inlineStr">
+        <is>
+          <t>esep_allangelsday</t>
+        </is>
+      </c>
+      <c r="D561" s="0" t="inlineStr">
+        <is>
+          <t>esep_allangelsday</t>
+        </is>
+      </c>
+      <c r="E561" s="2">
+        <v>1</v>
+      </c>
+      <c r="F561" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B562" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C562" s="0" t="inlineStr">
+        <is>
+          <t>esep_angelweek</t>
+        </is>
+      </c>
+      <c r="D562" s="0" t="inlineStr">
+        <is>
+          <t>esep_angelweek</t>
+        </is>
+      </c>
+      <c r="E562" s="2">
+        <v>1</v>
+      </c>
+      <c r="F562" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B563" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C563" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="D563" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="E563" s="2">
+        <v>1</v>
+      </c>
+      <c r="F563" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B564" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C564" s="0" t="inlineStr">
+        <is>
+          <t>esep_internationalpeace_day</t>
+        </is>
+      </c>
+      <c r="D564" s="0" t="inlineStr">
+        <is>
+          <t>esep_internationalpeace_day</t>
+        </is>
+      </c>
+      <c r="E564" s="2">
+        <v>1</v>
+      </c>
+      <c r="F564" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B565" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C565" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D565" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E565" s="2">
+        <v>1</v>
+      </c>
+      <c r="F565" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B566" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C566" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D566" s="0" t="inlineStr">
+        <is>
+          <t>flwr_friend</t>
+        </is>
+      </c>
+      <c r="E566" s="2">
+        <v>1</v>
+      </c>
+      <c r="F566" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B567" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C567" s="0" t="inlineStr">
+        <is>
+          <t>friendsforever</t>
+        </is>
+      </c>
+      <c r="D567" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendsforever</t>
+        </is>
+      </c>
+      <c r="E567" s="2">
+        <v>1</v>
+      </c>
+      <c r="F567" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B568" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C568" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D568" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E568" s="2">
+        <v>1</v>
+      </c>
+      <c r="F568" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B569" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C569" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D569" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E569" s="2">
+        <v>1</v>
+      </c>
+      <c r="F569" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B570" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C570" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D570" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E570" s="2">
+        <v>1</v>
+      </c>
+      <c r="F570" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B571" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C571" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D571" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E571" s="2">
+        <v>1</v>
+      </c>
+      <c r="F571" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B572" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C572" s="0" t="inlineStr">
+        <is>
+          <t>angels</t>
+        </is>
+      </c>
+      <c r="D572" s="0" t="inlineStr">
+        <is>
+          <t>insp_angels</t>
+        </is>
+      </c>
+      <c r="E572" s="2">
+        <v>1</v>
+      </c>
+      <c r="F572" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B573" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C573" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D573" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E573" s="2">
+        <v>1</v>
+      </c>
+      <c r="F573" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B574" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C574" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D574" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E574" s="2">
+        <v>1</v>
+      </c>
+      <c r="F574" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B575" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C575" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D575" s="0" t="inlineStr">
+        <is>
+          <t>love_cute</t>
+        </is>
+      </c>
+      <c r="E575" s="2">
+        <v>1</v>
+      </c>
+      <c r="F575" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B576" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C576" s="0" t="inlineStr">
+        <is>
+          <t>iamsorry</t>
+        </is>
+      </c>
+      <c r="D576" s="0" t="inlineStr">
+        <is>
+          <t>love_iamsorry</t>
+        </is>
+      </c>
+      <c r="E576" s="2">
+        <v>1</v>
+      </c>
+      <c r="F576" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B577" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C577" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_roses</t>
+        </is>
+      </c>
+      <c r="D577" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_roses</t>
+        </is>
+      </c>
+      <c r="E577" s="2">
+        <v>1</v>
+      </c>
+      <c r="F577" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B578" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C578" s="0" t="inlineStr">
+        <is>
+          <t>lovesongs</t>
+        </is>
+      </c>
+      <c r="D578" s="0" t="inlineStr">
+        <is>
+          <t>love_lovesongs</t>
+        </is>
+      </c>
+      <c r="E578" s="2">
+        <v>1</v>
+      </c>
+      <c r="F578" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B579" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C579" s="0" t="inlineStr">
+        <is>
+          <t>thinkingyou</t>
+        </is>
+      </c>
+      <c r="D579" s="0" t="inlineStr">
+        <is>
+          <t>love_thinkingyou</t>
+        </is>
+      </c>
+      <c r="E579" s="2">
+        <v>1</v>
+      </c>
+      <c r="F579" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B580" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C580" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D580" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E580" s="2">
+        <v>1</v>
+      </c>
+      <c r="F580" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B581" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C581" s="0" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="D581" s="0" t="inlineStr">
+        <is>
+          <t>thank_family</t>
+        </is>
+      </c>
+      <c r="E581" s="2">
+        <v>1</v>
+      </c>
+      <c r="F581" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B582" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C582" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D582" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E582" s="2">
+        <v>1</v>
+      </c>
+      <c r="F582" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B583" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C583" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D583" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E583" s="2">
+        <v>1</v>
+      </c>
+      <c r="F583" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B584" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C584" s="0" t="inlineStr">
+        <is>
+          <t>wed_flowers</t>
+        </is>
+      </c>
+      <c r="D584" s="0" t="inlineStr">
+        <is>
+          <t>wed_flowers</t>
+        </is>
+      </c>
+      <c r="E584" s="2">
+        <v>1</v>
+      </c>
+      <c r="F584" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B585" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C585" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D585" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E585" s="2">
+        <v>1</v>
+      </c>
+      <c r="F585" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-07</t>
+        </is>
+      </c>
+      <c r="B586" s="4"/>
+      <c r="C586" s="4"/>
+      <c r="D586" s="4"/>
+      <c r="E586" s="5">
+        <v>731</v>
+      </c>
+      <c r="F586" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -12817,36 +21029,138 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>742</v>
+      </c>
+      <c r="C6" s="2">
+        <v>224</v>
+      </c>
+      <c r="D6" s="2">
+        <v>247</v>
+      </c>
+      <c r="E6" s="2">
+        <v>131</v>
+      </c>
+      <c r="F6" s="2">
+        <v>72</v>
+      </c>
+      <c r="G6" s="2">
+        <v>43</v>
+      </c>
+      <c r="H6" s="2">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>738</v>
+      </c>
+      <c r="C7" s="2">
+        <v>224</v>
+      </c>
+      <c r="D7" s="2">
+        <v>245</v>
+      </c>
+      <c r="E7" s="2">
+        <v>163</v>
+      </c>
+      <c r="F7" s="2">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2">
+        <v>21</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>760</v>
+      </c>
+      <c r="C8" s="2">
+        <v>218</v>
+      </c>
+      <c r="D8" s="2">
+        <v>244</v>
+      </c>
+      <c r="E8" s="2">
+        <v>179</v>
+      </c>
+      <c r="F8" s="2">
+        <v>85</v>
+      </c>
+      <c r="G8" s="2">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <v>3628</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1248</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1052</v>
-      </c>
-      <c r="E6" s="5">
-        <v>659</v>
-      </c>
-      <c r="F6" s="5">
-        <v>382</v>
-      </c>
-      <c r="G6" s="5">
-        <v>134</v>
-      </c>
-      <c r="H6" s="5">
-        <v>124</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="B9" s="5">
+        <v>5868</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1914</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1788</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1132</v>
+      </c>
+      <c r="F9" s="5">
+        <v>616</v>
+      </c>
+      <c r="G9" s="5">
+        <v>216</v>
+      </c>
+      <c r="H9" s="5">
+        <v>173</v>
+      </c>
+      <c r="I9" s="5">
         <v>28</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J9" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -507,28 +507,56 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>839</v>
+      </c>
+      <c r="C9" s="2">
+        <v>576</v>
+      </c>
+      <c r="D9" s="2">
+        <v>263</v>
+      </c>
+      <c r="E9" s="2">
+        <v>776</v>
+      </c>
+      <c r="F9" s="2">
+        <v>63</v>
+      </c>
+      <c r="G9" s="2">
+        <v>257</v>
+      </c>
+      <c r="H9" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <v>5868</v>
-      </c>
-      <c r="C9" s="5">
-        <v>3726</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2142</v>
-      </c>
-      <c r="E9" s="5">
-        <v>5620</v>
-      </c>
-      <c r="F9" s="5">
-        <v>248</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="B10" s="5">
+        <v>6707</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4302</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2405</v>
+      </c>
+      <c r="E10" s="5">
+        <v>6396</v>
+      </c>
+      <c r="F10" s="5">
+        <v>311</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -544,17 +572,17 @@
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -596,14 +624,14 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Friendship</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Love &amp; romance</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Inspirational &amp; sympathy</t>
@@ -626,14 +654,14 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>World languages</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Pets</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Cute</t>
@@ -641,12 +669,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Keeping in touch</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Business &amp; work</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -680,10 +708,10 @@
         <v>30</v>
       </c>
       <c r="H2" s="2">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2">
         <v>28</v>
-      </c>
-      <c r="I2" s="2">
-        <v>19</v>
       </c>
       <c r="J2" s="2">
         <v>10</v>
@@ -698,19 +726,19 @@
         <v>3</v>
       </c>
       <c r="N2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P2" s="2">
         <v>4</v>
       </c>
       <c r="Q2" s="2">
+        <v>2</v>
+      </c>
+      <c r="R2" s="2">
         <v>6</v>
-      </c>
-      <c r="R2" s="2">
-        <v>2</v>
       </c>
       <c r="S2" s="2">
         <v>0</v>
@@ -741,10 +769,10 @@
         <v>52</v>
       </c>
       <c r="H3" s="2">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2">
         <v>41</v>
-      </c>
-      <c r="I3" s="2">
-        <v>24</v>
       </c>
       <c r="J3" s="2">
         <v>19</v>
@@ -759,19 +787,19 @@
         <v>3</v>
       </c>
       <c r="N3" s="2">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2">
         <v>10</v>
       </c>
-      <c r="O3" s="2">
-        <v>1</v>
-      </c>
       <c r="P3" s="2">
         <v>1</v>
       </c>
       <c r="Q3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
@@ -802,10 +830,10 @@
         <v>30</v>
       </c>
       <c r="H4" s="2">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2">
         <v>11</v>
-      </c>
-      <c r="I4" s="2">
-        <v>18</v>
       </c>
       <c r="J4" s="2">
         <v>16</v>
@@ -863,10 +891,10 @@
         <v>28</v>
       </c>
       <c r="H5" s="2">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2">
         <v>22</v>
-      </c>
-      <c r="I5" s="2">
-        <v>26</v>
       </c>
       <c r="J5" s="2">
         <v>15</v>
@@ -890,10 +918,10 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="2">
         <v>0</v>
@@ -924,10 +952,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="2">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2">
         <v>11</v>
-      </c>
-      <c r="I6" s="2">
-        <v>13</v>
       </c>
       <c r="J6" s="2">
         <v>15</v>
@@ -942,19 +970,19 @@
         <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O6" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P6" s="2">
         <v>0</v>
       </c>
       <c r="Q6" s="2">
+        <v>2</v>
+      </c>
+      <c r="R6" s="2">
         <v>0</v>
-      </c>
-      <c r="R6" s="2">
-        <v>2</v>
       </c>
       <c r="S6" s="2">
         <v>1</v>
@@ -985,10 +1013,10 @@
         <v>20</v>
       </c>
       <c r="H7" s="2">
+        <v>11</v>
+      </c>
+      <c r="I7" s="2">
         <v>16</v>
-      </c>
-      <c r="I7" s="2">
-        <v>11</v>
       </c>
       <c r="J7" s="2">
         <v>12</v>
@@ -1003,19 +1031,19 @@
         <v>8</v>
       </c>
       <c r="N7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2">
         <v>0</v>
       </c>
       <c r="Q7" s="2">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2">
         <v>0</v>
-      </c>
-      <c r="R7" s="2">
-        <v>3</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
@@ -1046,10 +1074,10 @@
         <v>30</v>
       </c>
       <c r="H8" s="2">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2">
         <v>7</v>
-      </c>
-      <c r="I8" s="2">
-        <v>17</v>
       </c>
       <c r="J8" s="2">
         <v>14</v>
@@ -1064,82 +1092,143 @@
         <v>6</v>
       </c>
       <c r="N8" s="2">
+        <v>3</v>
+      </c>
+      <c r="O8" s="2">
         <v>0</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>1</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>776</v>
+      </c>
+      <c r="C9" s="2">
+        <v>500</v>
+      </c>
+      <c r="D9" s="2">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2">
+        <v>41</v>
+      </c>
+      <c r="H9" s="2">
+        <v>20</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>12</v>
+      </c>
+      <c r="K9" s="2">
+        <v>8</v>
+      </c>
+      <c r="L9" s="2">
+        <v>39</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2">
+        <v>4</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
         <v>3</v>
       </c>
-      <c r="P8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2">
+      <c r="Q9" s="2">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="2">
-        <v>1</v>
-      </c>
-      <c r="S8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <v>5620</v>
-      </c>
-      <c r="C9" s="5">
-        <v>3697</v>
-      </c>
-      <c r="D9" s="5">
-        <v>588</v>
-      </c>
-      <c r="E9" s="5">
-        <v>328</v>
-      </c>
-      <c r="F9" s="5">
-        <v>238</v>
-      </c>
-      <c r="G9" s="5">
-        <v>214</v>
-      </c>
-      <c r="H9" s="5">
-        <v>136</v>
-      </c>
-      <c r="I9" s="5">
-        <v>128</v>
-      </c>
-      <c r="J9" s="5">
-        <v>101</v>
-      </c>
-      <c r="K9" s="5">
-        <v>70</v>
-      </c>
-      <c r="L9" s="5">
-        <v>32</v>
-      </c>
-      <c r="M9" s="5">
-        <v>26</v>
-      </c>
-      <c r="N9" s="5">
+      <c r="B10" s="5">
+        <v>6396</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4197</v>
+      </c>
+      <c r="D10" s="5">
+        <v>636</v>
+      </c>
+      <c r="E10" s="5">
+        <v>380</v>
+      </c>
+      <c r="F10" s="5">
+        <v>280</v>
+      </c>
+      <c r="G10" s="5">
+        <v>255</v>
+      </c>
+      <c r="H10" s="5">
+        <v>148</v>
+      </c>
+      <c r="I10" s="5">
+        <v>141</v>
+      </c>
+      <c r="J10" s="5">
+        <v>113</v>
+      </c>
+      <c r="K10" s="5">
+        <v>78</v>
+      </c>
+      <c r="L10" s="5">
+        <v>71</v>
+      </c>
+      <c r="M10" s="5">
+        <v>27</v>
+      </c>
+      <c r="N10" s="5">
+        <v>19</v>
+      </c>
+      <c r="O10" s="5">
         <v>16</v>
       </c>
-      <c r="O9" s="5">
+      <c r="P10" s="5">
         <v>15</v>
       </c>
-      <c r="P9" s="5">
-        <v>12</v>
-      </c>
-      <c r="Q9" s="5">
+      <c r="Q10" s="5">
         <v>9</v>
       </c>
-      <c r="R9" s="5">
-        <v>8</v>
-      </c>
-      <c r="S9" s="5">
+      <c r="R10" s="5">
+        <v>9</v>
+      </c>
+      <c r="S10" s="5">
         <v>2</v>
       </c>
     </row>
@@ -4492,6 +4581,476 @@
       </c>
       <c r="H106" s="4"/>
     </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D107" s="2">
+        <v>372</v>
+      </c>
+      <c r="E107" s="2">
+        <v>128</v>
+      </c>
+      <c r="F107" s="2">
+        <v>500</v>
+      </c>
+      <c r="G107" s="3">
+        <v>0.6443298969072165</v>
+      </c>
+      <c r="H107" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D108" s="2">
+        <v>36</v>
+      </c>
+      <c r="E108" s="2">
+        <v>16</v>
+      </c>
+      <c r="F108" s="2">
+        <v>52</v>
+      </c>
+      <c r="G108" s="3">
+        <v>0.06701030927835051</v>
+      </c>
+      <c r="H108" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D109" s="2">
+        <v>40</v>
+      </c>
+      <c r="E109" s="2">
+        <v>8</v>
+      </c>
+      <c r="F109" s="2">
+        <v>48</v>
+      </c>
+      <c r="G109" s="3">
+        <v>0.061855670103092786</v>
+      </c>
+      <c r="H109" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D110" s="2">
+        <v>28</v>
+      </c>
+      <c r="E110" s="2">
+        <v>14</v>
+      </c>
+      <c r="F110" s="2">
+        <v>42</v>
+      </c>
+      <c r="G110" s="3">
+        <v>0.05412371134020619</v>
+      </c>
+      <c r="H110" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D111" s="2">
+        <v>18</v>
+      </c>
+      <c r="E111" s="2">
+        <v>23</v>
+      </c>
+      <c r="F111" s="2">
+        <v>41</v>
+      </c>
+      <c r="G111" s="3">
+        <v>0.05283505154639175</v>
+      </c>
+      <c r="H111" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D112" s="2">
+        <v>38</v>
+      </c>
+      <c r="E112" s="2">
+        <v>1</v>
+      </c>
+      <c r="F112" s="2">
+        <v>39</v>
+      </c>
+      <c r="G112" s="3">
+        <v>0.05025773195876289</v>
+      </c>
+      <c r="H112" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D113" s="2">
+        <v>14</v>
+      </c>
+      <c r="E113" s="2">
+        <v>6</v>
+      </c>
+      <c r="F113" s="2">
+        <v>20</v>
+      </c>
+      <c r="G113" s="3">
+        <v>0.02577319587628866</v>
+      </c>
+      <c r="H113" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D114" s="2">
+        <v>10</v>
+      </c>
+      <c r="E114" s="2">
+        <v>2</v>
+      </c>
+      <c r="F114" s="2">
+        <v>12</v>
+      </c>
+      <c r="G114" s="3">
+        <v>0.015463917525773196</v>
+      </c>
+      <c r="H114" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D115" s="2">
+        <v>6</v>
+      </c>
+      <c r="E115" s="2">
+        <v>2</v>
+      </c>
+      <c r="F115" s="2">
+        <v>8</v>
+      </c>
+      <c r="G115" s="3">
+        <v>0.010309278350515464</v>
+      </c>
+      <c r="H115" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D116" s="2">
+        <v>5</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2">
+        <v>5</v>
+      </c>
+      <c r="G116" s="3">
+        <v>0.006443298969072165</v>
+      </c>
+      <c r="H116" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D117" s="2">
+        <v>4</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2">
+        <v>4</v>
+      </c>
+      <c r="G117" s="3">
+        <v>0.005154639175257732</v>
+      </c>
+      <c r="H117" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D118" s="2">
+        <v>3</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2">
+        <v>3</v>
+      </c>
+      <c r="G118" s="3">
+        <v>0.003865979381443299</v>
+      </c>
+      <c r="H118" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D119" s="2">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1</v>
+      </c>
+      <c r="G119" s="3">
+        <v>0.001288659793814433</v>
+      </c>
+      <c r="H119" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D120" s="2">
+        <v>1</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2">
+        <v>1</v>
+      </c>
+      <c r="G120" s="3">
+        <v>0.001288659793814433</v>
+      </c>
+      <c r="H120" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-08</t>
+        </is>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="5">
+        <v>576</v>
+      </c>
+      <c r="E121" s="5">
+        <v>200</v>
+      </c>
+      <c r="F121" s="5">
+        <v>776</v>
+      </c>
+      <c r="G121" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H121" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -20820,6 +21379,2260 @@
         <v>731</v>
       </c>
       <c r="F586" s="4"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B587" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C587" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D587" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E587" s="2">
+        <v>403</v>
+      </c>
+      <c r="F587" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B588" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C588" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D588" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E588" s="2">
+        <v>38</v>
+      </c>
+      <c r="F588" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B589" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C589" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D589" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E589" s="2">
+        <v>36</v>
+      </c>
+      <c r="F589" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B590" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C590" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D590" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E590" s="2">
+        <v>26</v>
+      </c>
+      <c r="F590" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B591" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C591" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D591" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E591" s="2">
+        <v>20</v>
+      </c>
+      <c r="F591" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B592" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C592" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D592" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E592" s="2">
+        <v>14</v>
+      </c>
+      <c r="F592" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B593" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C593" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D593" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E593" s="2">
+        <v>14</v>
+      </c>
+      <c r="F593" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B594" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C594" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalzucchini_day</t>
+        </is>
+      </c>
+      <c r="D594" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalzucchini_day</t>
+        </is>
+      </c>
+      <c r="E594" s="2">
+        <v>13</v>
+      </c>
+      <c r="F594" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B595" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C595" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D595" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E595" s="2">
+        <v>12</v>
+      </c>
+      <c r="F595" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B596" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C596" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D596" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E596" s="2">
+        <v>12</v>
+      </c>
+      <c r="F596" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B597" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C597" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D597" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E597" s="2">
+        <v>10</v>
+      </c>
+      <c r="F597" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B598" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C598" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D598" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E598" s="2">
+        <v>9</v>
+      </c>
+      <c r="F598" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B599" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C599" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D599" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E599" s="2">
+        <v>7</v>
+      </c>
+      <c r="F599" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B600" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C600" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D600" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E600" s="2">
+        <v>7</v>
+      </c>
+      <c r="F600" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B601" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C601" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D601" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E601" s="2">
+        <v>6</v>
+      </c>
+      <c r="F601" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B602" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C602" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D602" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E602" s="2">
+        <v>6</v>
+      </c>
+      <c r="F602" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B603" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C603" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D603" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E603" s="2">
+        <v>6</v>
+      </c>
+      <c r="F603" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B604" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C604" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D604" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E604" s="2">
+        <v>5</v>
+      </c>
+      <c r="F604" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B605" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C605" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D605" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E605" s="2">
+        <v>5</v>
+      </c>
+      <c r="F605" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B606" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C606" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D606" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E606" s="2">
+        <v>5</v>
+      </c>
+      <c r="F606" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B607" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C607" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D607" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E607" s="2">
+        <v>5</v>
+      </c>
+      <c r="F607" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B608" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C608" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D608" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E608" s="2">
+        <v>5</v>
+      </c>
+      <c r="F608" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B609" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C609" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D609" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E609" s="2">
+        <v>5</v>
+      </c>
+      <c r="F609" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B610" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C610" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D610" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E610" s="2">
+        <v>4</v>
+      </c>
+      <c r="F610" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B611" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C611" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D611" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E611" s="2">
+        <v>4</v>
+      </c>
+      <c r="F611" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B612" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C612" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D612" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E612" s="2">
+        <v>4</v>
+      </c>
+      <c r="F612" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B613" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C613" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D613" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E613" s="2">
+        <v>4</v>
+      </c>
+      <c r="F613" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B614" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C614" s="0" t="inlineStr">
+        <is>
+          <t>eaug_happinesshappens_day</t>
+        </is>
+      </c>
+      <c r="D614" s="0" t="inlineStr">
+        <is>
+          <t>eaug_happinesshappens_day</t>
+        </is>
+      </c>
+      <c r="E614" s="2">
+        <v>4</v>
+      </c>
+      <c r="F614" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B615" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C615" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D615" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E615" s="2">
+        <v>4</v>
+      </c>
+      <c r="F615" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B616" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C616" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D616" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E616" s="2">
+        <v>4</v>
+      </c>
+      <c r="F616" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B617" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C617" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D617" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E617" s="2">
+        <v>4</v>
+      </c>
+      <c r="F617" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B618" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C618" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D618" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E618" s="2">
+        <v>3</v>
+      </c>
+      <c r="F618" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B619" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C619" s="0" t="inlineStr">
+        <is>
+          <t>eaug_booklover_day</t>
+        </is>
+      </c>
+      <c r="D619" s="0" t="inlineStr">
+        <is>
+          <t>eaug_booklover_day</t>
+        </is>
+      </c>
+      <c r="E619" s="2">
+        <v>3</v>
+      </c>
+      <c r="F619" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B620" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C620" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D620" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E620" s="2">
+        <v>3</v>
+      </c>
+      <c r="F620" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B621" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C621" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D621" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E621" s="2">
+        <v>3</v>
+      </c>
+      <c r="F621" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B622" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C622" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D622" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E622" s="2">
+        <v>3</v>
+      </c>
+      <c r="F622" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B623" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C623" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D623" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E623" s="2">
+        <v>2</v>
+      </c>
+      <c r="F623" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B624" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C624" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="D624" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="E624" s="2">
+        <v>2</v>
+      </c>
+      <c r="F624" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B625" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C625" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalcat_day</t>
+        </is>
+      </c>
+      <c r="D625" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalcat_day</t>
+        </is>
+      </c>
+      <c r="E625" s="2">
+        <v>2</v>
+      </c>
+      <c r="F625" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B626" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C626" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_tart_day</t>
+        </is>
+      </c>
+      <c r="D626" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_tart_day</t>
+        </is>
+      </c>
+      <c r="E626" s="2">
+        <v>2</v>
+      </c>
+      <c r="F626" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B627" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C627" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D627" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E627" s="2">
+        <v>2</v>
+      </c>
+      <c r="F627" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B628" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C628" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D628" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E628" s="2">
+        <v>2</v>
+      </c>
+      <c r="F628" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B629" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C629" s="0" t="inlineStr">
+        <is>
+          <t>monblues</t>
+        </is>
+      </c>
+      <c r="D629" s="0" t="inlineStr">
+        <is>
+          <t>gen_monblues</t>
+        </is>
+      </c>
+      <c r="E629" s="2">
+        <v>2</v>
+      </c>
+      <c r="F629" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B630" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C630" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D630" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E630" s="2">
+        <v>2</v>
+      </c>
+      <c r="F630" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B631" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C631" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="D631" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="E631" s="2">
+        <v>2</v>
+      </c>
+      <c r="F631" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B632" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C632" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D632" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E632" s="2">
+        <v>2</v>
+      </c>
+      <c r="F632" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B633" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C633" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D633" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E633" s="2">
+        <v>2</v>
+      </c>
+      <c r="F633" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B634" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C634" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D634" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E634" s="2">
+        <v>2</v>
+      </c>
+      <c r="F634" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B635" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C635" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D635" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E635" s="2">
+        <v>2</v>
+      </c>
+      <c r="F635" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B636" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C636" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D636" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E636" s="2">
+        <v>2</v>
+      </c>
+      <c r="F636" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B637" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C637" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D637" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E637" s="2">
+        <v>2</v>
+      </c>
+      <c r="F637" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B638" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C638" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D638" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E638" s="2">
+        <v>2</v>
+      </c>
+      <c r="F638" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B639" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C639" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D639" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E639" s="2">
+        <v>1</v>
+      </c>
+      <c r="F639" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B640" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C640" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D640" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E640" s="2">
+        <v>1</v>
+      </c>
+      <c r="F640" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B641" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C641" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D641" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E641" s="2">
+        <v>1</v>
+      </c>
+      <c r="F641" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B642" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C642" s="0" t="inlineStr">
+        <is>
+          <t>atworketc</t>
+        </is>
+      </c>
+      <c r="D642" s="0" t="inlineStr">
+        <is>
+          <t>bus_atworketc</t>
+        </is>
+      </c>
+      <c r="E642" s="2">
+        <v>1</v>
+      </c>
+      <c r="F642" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B643" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C643" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D643" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E643" s="2">
+        <v>1</v>
+      </c>
+      <c r="F643" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B644" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C644" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D644" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E644" s="2">
+        <v>1</v>
+      </c>
+      <c r="F644" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B645" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C645" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D645" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E645" s="2">
+        <v>1</v>
+      </c>
+      <c r="F645" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B646" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C646" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D646" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E646" s="2">
+        <v>1</v>
+      </c>
+      <c r="F646" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B647" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C647" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="D647" s="0" t="inlineStr">
+        <is>
+          <t>eaug_girlfriendsday</t>
+        </is>
+      </c>
+      <c r="E647" s="2">
+        <v>1</v>
+      </c>
+      <c r="F647" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B648" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C648" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationallighthouse_day</t>
+        </is>
+      </c>
+      <c r="D648" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationallighthouse_day</t>
+        </is>
+      </c>
+      <c r="E648" s="2">
+        <v>1</v>
+      </c>
+      <c r="F648" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B649" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C649" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="D649" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="E649" s="2">
+        <v>1</v>
+      </c>
+      <c r="F649" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B650" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C650" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D650" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E650" s="2">
+        <v>1</v>
+      </c>
+      <c r="F650" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B651" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C651" s="0" t="inlineStr">
+        <is>
+          <t>eaug_womensequality_day</t>
+        </is>
+      </c>
+      <c r="D651" s="0" t="inlineStr">
+        <is>
+          <t>eaug_womensequality_day</t>
+        </is>
+      </c>
+      <c r="E651" s="2">
+        <v>1</v>
+      </c>
+      <c r="F651" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B652" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C652" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_missingu</t>
+        </is>
+      </c>
+      <c r="D652" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_missingu</t>
+        </is>
+      </c>
+      <c r="E652" s="2">
+        <v>1</v>
+      </c>
+      <c r="F652" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B653" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C653" s="0" t="inlineStr">
+        <is>
+          <t>emay_gethappyweek</t>
+        </is>
+      </c>
+      <c r="D653" s="0" t="inlineStr">
+        <is>
+          <t>emay_gethappyweek</t>
+        </is>
+      </c>
+      <c r="E653" s="2">
+        <v>1</v>
+      </c>
+      <c r="F653" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B654" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C654" s="0" t="inlineStr">
+        <is>
+          <t>eoct_nationalcat_day</t>
+        </is>
+      </c>
+      <c r="D654" s="0" t="inlineStr">
+        <is>
+          <t>eoct_nationalcat_day</t>
+        </is>
+      </c>
+      <c r="E654" s="2">
+        <v>1</v>
+      </c>
+      <c r="F654" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B655" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C655" s="0" t="inlineStr">
+        <is>
+          <t>esep_trueloveforeverday</t>
+        </is>
+      </c>
+      <c r="D655" s="0" t="inlineStr">
+        <is>
+          <t>esep_trueloveforeverday</t>
+        </is>
+      </c>
+      <c r="E655" s="2">
+        <v>1</v>
+      </c>
+      <c r="F655" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B656" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C656" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D656" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E656" s="2">
+        <v>1</v>
+      </c>
+      <c r="F656" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B657" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C657" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D657" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E657" s="2">
+        <v>1</v>
+      </c>
+      <c r="F657" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B658" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C658" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D658" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E658" s="2">
+        <v>1</v>
+      </c>
+      <c r="F658" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B659" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C659" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D659" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E659" s="2">
+        <v>1</v>
+      </c>
+      <c r="F659" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B660" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C660" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D660" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E660" s="2">
+        <v>1</v>
+      </c>
+      <c r="F660" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B661" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C661" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D661" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E661" s="2">
+        <v>1</v>
+      </c>
+      <c r="F661" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B662" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C662" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D662" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E662" s="2">
+        <v>1</v>
+      </c>
+      <c r="F662" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B663" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C663" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="D663" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="E663" s="2">
+        <v>1</v>
+      </c>
+      <c r="F663" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B664" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C664" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D664" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E664" s="2">
+        <v>1</v>
+      </c>
+      <c r="F664" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B665" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C665" s="0" t="inlineStr">
+        <is>
+          <t>lovesongs</t>
+        </is>
+      </c>
+      <c r="D665" s="0" t="inlineStr">
+        <is>
+          <t>love_lovesongs</t>
+        </is>
+      </c>
+      <c r="E665" s="2">
+        <v>1</v>
+      </c>
+      <c r="F665" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B666" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C666" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="D666" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="E666" s="2">
+        <v>1</v>
+      </c>
+      <c r="F666" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-08</t>
+        </is>
+      </c>
+      <c r="B667" s="4"/>
+      <c r="C667" s="4"/>
+      <c r="D667" s="4"/>
+      <c r="E667" s="5">
+        <v>776</v>
+      </c>
+      <c r="F667" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -21131,36 +23944,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>839</v>
+      </c>
+      <c r="C9" s="2">
+        <v>228</v>
+      </c>
+      <c r="D9" s="2">
+        <v>292</v>
+      </c>
+      <c r="E9" s="2">
+        <v>161</v>
+      </c>
+      <c r="F9" s="2">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2">
+        <v>38</v>
+      </c>
+      <c r="H9" s="2">
+        <v>38</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <v>5868</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1914</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1788</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1132</v>
-      </c>
-      <c r="F9" s="5">
-        <v>616</v>
-      </c>
-      <c r="G9" s="5">
-        <v>216</v>
-      </c>
-      <c r="H9" s="5">
-        <v>173</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="B10" s="5">
+        <v>6707</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2142</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2080</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1293</v>
+      </c>
+      <c r="F10" s="5">
+        <v>698</v>
+      </c>
+      <c r="G10" s="5">
+        <v>254</v>
+      </c>
+      <c r="H10" s="5">
+        <v>211</v>
+      </c>
+      <c r="I10" s="5">
         <v>28</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -535,28 +535,84 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>711</v>
+      </c>
+      <c r="C10" s="2">
+        <v>495</v>
+      </c>
+      <c r="D10" s="2">
+        <v>216</v>
+      </c>
+      <c r="E10" s="2">
+        <v>682</v>
+      </c>
+      <c r="F10" s="2">
+        <v>29</v>
+      </c>
+      <c r="G10" s="2">
+        <v>273</v>
+      </c>
+      <c r="H10" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>949</v>
+      </c>
+      <c r="C11" s="2">
+        <v>665</v>
+      </c>
+      <c r="D11" s="2">
+        <v>284</v>
+      </c>
+      <c r="E11" s="2">
+        <v>897</v>
+      </c>
+      <c r="F11" s="2">
+        <v>52</v>
+      </c>
+      <c r="G11" s="2">
+        <v>285</v>
+      </c>
+      <c r="H11" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <v>6707</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4302</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2405</v>
-      </c>
-      <c r="E10" s="5">
-        <v>6396</v>
-      </c>
-      <c r="F10" s="5">
-        <v>311</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="B12" s="5">
+        <v>8367</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5462</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2905</v>
+      </c>
+      <c r="E12" s="5">
+        <v>7975</v>
+      </c>
+      <c r="F12" s="5">
+        <v>392</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -579,10 +635,10 @@
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
     <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -659,22 +715,22 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>World languages</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Cute</t>
-        </is>
-      </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Business &amp; work</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Keeping in touch</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -729,16 +785,16 @@
         <v>3</v>
       </c>
       <c r="O2" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P2" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R2" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S2" s="2">
         <v>0</v>
@@ -790,16 +846,16 @@
         <v>1</v>
       </c>
       <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2">
         <v>10</v>
       </c>
-      <c r="P3" s="2">
-        <v>1</v>
-      </c>
       <c r="Q3" s="2">
+        <v>2</v>
+      </c>
+      <c r="R3" s="2">
         <v>0</v>
-      </c>
-      <c r="R3" s="2">
-        <v>2</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
@@ -851,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="O4" s="2">
+        <v>5</v>
+      </c>
+      <c r="P4" s="2">
         <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>5</v>
       </c>
       <c r="Q4" s="2">
         <v>0</v>
@@ -912,16 +968,16 @@
         <v>2</v>
       </c>
       <c r="O5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="2">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2">
         <v>0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>1</v>
       </c>
       <c r="S5" s="2">
         <v>0</v>
@@ -973,16 +1029,16 @@
         <v>4</v>
       </c>
       <c r="O6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
         <v>0</v>
       </c>
-      <c r="Q6" s="2">
-        <v>2</v>
-      </c>
       <c r="R6" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="2">
         <v>1</v>
@@ -1034,16 +1090,16 @@
         <v>2</v>
       </c>
       <c r="O7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
         <v>0</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>3</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
@@ -1095,16 +1151,16 @@
         <v>3</v>
       </c>
       <c r="O8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2">
         <v>0</v>
       </c>
-      <c r="P8" s="2">
-        <v>1</v>
-      </c>
       <c r="Q8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="2">
         <v>1</v>
@@ -1156,80 +1212,202 @@
         <v>4</v>
       </c>
       <c r="O9" s="2">
+        <v>3</v>
+      </c>
+      <c r="P9" s="2">
         <v>0</v>
       </c>
-      <c r="P9" s="2">
-        <v>3</v>
-      </c>
       <c r="Q9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>682</v>
+      </c>
+      <c r="C10" s="2">
+        <v>436</v>
+      </c>
+      <c r="D10" s="2">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2">
+        <v>42</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46</v>
+      </c>
+      <c r="G10" s="2">
+        <v>25</v>
+      </c>
+      <c r="H10" s="2">
+        <v>35</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7</v>
+      </c>
+      <c r="J10" s="2">
+        <v>20</v>
+      </c>
+      <c r="K10" s="2">
+        <v>6</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2">
+        <v>4</v>
+      </c>
+      <c r="O10" s="2">
+        <v>5</v>
+      </c>
+      <c r="P10" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>897</v>
+      </c>
+      <c r="C11" s="2">
+        <v>586</v>
+      </c>
+      <c r="D11" s="2">
+        <v>88</v>
+      </c>
+      <c r="E11" s="2">
+        <v>57</v>
+      </c>
+      <c r="F11" s="2">
+        <v>53</v>
+      </c>
+      <c r="G11" s="2">
+        <v>41</v>
+      </c>
+      <c r="H11" s="2">
+        <v>14</v>
+      </c>
+      <c r="I11" s="2">
+        <v>11</v>
+      </c>
+      <c r="J11" s="2">
+        <v>16</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>3</v>
+      </c>
+      <c r="M11" s="2">
+        <v>4</v>
+      </c>
+      <c r="N11" s="2">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2">
+        <v>3</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <v>6396</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4197</v>
-      </c>
-      <c r="D10" s="5">
-        <v>636</v>
-      </c>
-      <c r="E10" s="5">
-        <v>380</v>
-      </c>
-      <c r="F10" s="5">
-        <v>280</v>
-      </c>
-      <c r="G10" s="5">
-        <v>255</v>
-      </c>
-      <c r="H10" s="5">
-        <v>148</v>
-      </c>
-      <c r="I10" s="5">
-        <v>141</v>
-      </c>
-      <c r="J10" s="5">
-        <v>113</v>
-      </c>
-      <c r="K10" s="5">
+      <c r="B12" s="5">
+        <v>7975</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5219</v>
+      </c>
+      <c r="D12" s="5">
+        <v>774</v>
+      </c>
+      <c r="E12" s="5">
+        <v>479</v>
+      </c>
+      <c r="F12" s="5">
+        <v>379</v>
+      </c>
+      <c r="G12" s="5">
+        <v>321</v>
+      </c>
+      <c r="H12" s="5">
+        <v>197</v>
+      </c>
+      <c r="I12" s="5">
+        <v>159</v>
+      </c>
+      <c r="J12" s="5">
+        <v>149</v>
+      </c>
+      <c r="K12" s="5">
+        <v>94</v>
+      </c>
+      <c r="L12" s="5">
         <v>78</v>
       </c>
-      <c r="L10" s="5">
-        <v>71</v>
-      </c>
-      <c r="M10" s="5">
-        <v>27</v>
-      </c>
-      <c r="N10" s="5">
-        <v>19</v>
-      </c>
-      <c r="O10" s="5">
-        <v>16</v>
-      </c>
-      <c r="P10" s="5">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="5">
+      <c r="M12" s="5">
+        <v>32</v>
+      </c>
+      <c r="N12" s="5">
+        <v>31</v>
+      </c>
+      <c r="O12" s="5">
+        <v>23</v>
+      </c>
+      <c r="P12" s="5">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>11</v>
+      </c>
+      <c r="R12" s="5">
         <v>9</v>
       </c>
-      <c r="R10" s="5">
-        <v>9</v>
-      </c>
-      <c r="S10" s="5">
-        <v>2</v>
+      <c r="S12" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5051,6 +5229,978 @@
       </c>
       <c r="H121" s="4"/>
     </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D122" s="2">
+        <v>321</v>
+      </c>
+      <c r="E122" s="2">
+        <v>115</v>
+      </c>
+      <c r="F122" s="2">
+        <v>436</v>
+      </c>
+      <c r="G122" s="3">
+        <v>0.6392961876832844</v>
+      </c>
+      <c r="H122" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D123" s="2">
+        <v>43</v>
+      </c>
+      <c r="E123" s="2">
+        <v>7</v>
+      </c>
+      <c r="F123" s="2">
+        <v>50</v>
+      </c>
+      <c r="G123" s="3">
+        <v>0.07331378299120235</v>
+      </c>
+      <c r="H123" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D124" s="2">
+        <v>32</v>
+      </c>
+      <c r="E124" s="2">
+        <v>14</v>
+      </c>
+      <c r="F124" s="2">
+        <v>46</v>
+      </c>
+      <c r="G124" s="3">
+        <v>0.06744868035190615</v>
+      </c>
+      <c r="H124" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D125" s="2">
+        <v>26</v>
+      </c>
+      <c r="E125" s="2">
+        <v>16</v>
+      </c>
+      <c r="F125" s="2">
+        <v>42</v>
+      </c>
+      <c r="G125" s="3">
+        <v>0.06158357771260997</v>
+      </c>
+      <c r="H125" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D126" s="2">
+        <v>27</v>
+      </c>
+      <c r="E126" s="2">
+        <v>8</v>
+      </c>
+      <c r="F126" s="2">
+        <v>35</v>
+      </c>
+      <c r="G126" s="3">
+        <v>0.051319648093841645</v>
+      </c>
+      <c r="H126" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D127" s="2">
+        <v>6</v>
+      </c>
+      <c r="E127" s="2">
+        <v>19</v>
+      </c>
+      <c r="F127" s="2">
+        <v>25</v>
+      </c>
+      <c r="G127" s="3">
+        <v>0.036656891495601175</v>
+      </c>
+      <c r="H127" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D128" s="2">
+        <v>16</v>
+      </c>
+      <c r="E128" s="2">
+        <v>4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>20</v>
+      </c>
+      <c r="G128" s="3">
+        <v>0.02932551319648094</v>
+      </c>
+      <c r="H128" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D129" s="2">
+        <v>7</v>
+      </c>
+      <c r="E129" s="2">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2">
+        <v>7</v>
+      </c>
+      <c r="G129" s="3">
+        <v>0.010263929618768328</v>
+      </c>
+      <c r="H129" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D130" s="2">
+        <v>5</v>
+      </c>
+      <c r="E130" s="2">
+        <v>1</v>
+      </c>
+      <c r="F130" s="2">
+        <v>6</v>
+      </c>
+      <c r="G130" s="3">
+        <v>0.008797653958944282</v>
+      </c>
+      <c r="H130" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D131" s="2">
+        <v>5</v>
+      </c>
+      <c r="E131" s="2">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2">
+        <v>5</v>
+      </c>
+      <c r="G131" s="3">
+        <v>0.007331378299120235</v>
+      </c>
+      <c r="H131" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D132" s="2">
+        <v>2</v>
+      </c>
+      <c r="E132" s="2">
+        <v>2</v>
+      </c>
+      <c r="F132" s="2">
+        <v>4</v>
+      </c>
+      <c r="G132" s="3">
+        <v>0.005865102639296188</v>
+      </c>
+      <c r="H132" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D133" s="2">
+        <v>4</v>
+      </c>
+      <c r="E133" s="2">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2">
+        <v>4</v>
+      </c>
+      <c r="G133" s="3">
+        <v>0.005865102639296188</v>
+      </c>
+      <c r="H133" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" s="2">
+        <v>1</v>
+      </c>
+      <c r="F134" s="2">
+        <v>1</v>
+      </c>
+      <c r="G134" s="3">
+        <v>0.001466275659824047</v>
+      </c>
+      <c r="H134" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D135" s="2">
+        <v>1</v>
+      </c>
+      <c r="E135" s="2">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2">
+        <v>1</v>
+      </c>
+      <c r="G135" s="3">
+        <v>0.001466275659824047</v>
+      </c>
+      <c r="H135" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-09</t>
+        </is>
+      </c>
+      <c r="B136" s="4"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="5">
+        <v>495</v>
+      </c>
+      <c r="E136" s="5">
+        <v>187</v>
+      </c>
+      <c r="F136" s="5">
+        <v>682</v>
+      </c>
+      <c r="G136" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H136" s="4"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D137" s="2">
+        <v>411</v>
+      </c>
+      <c r="E137" s="2">
+        <v>175</v>
+      </c>
+      <c r="F137" s="2">
+        <v>586</v>
+      </c>
+      <c r="G137" s="3">
+        <v>0.653288740245262</v>
+      </c>
+      <c r="H137" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D138" s="2">
+        <v>81</v>
+      </c>
+      <c r="E138" s="2">
+        <v>7</v>
+      </c>
+      <c r="F138" s="2">
+        <v>88</v>
+      </c>
+      <c r="G138" s="3">
+        <v>0.09810479375696766</v>
+      </c>
+      <c r="H138" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D139" s="2">
+        <v>43</v>
+      </c>
+      <c r="E139" s="2">
+        <v>14</v>
+      </c>
+      <c r="F139" s="2">
+        <v>57</v>
+      </c>
+      <c r="G139" s="3">
+        <v>0.06354515050167224</v>
+      </c>
+      <c r="H139" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D140" s="2">
+        <v>39</v>
+      </c>
+      <c r="E140" s="2">
+        <v>14</v>
+      </c>
+      <c r="F140" s="2">
+        <v>53</v>
+      </c>
+      <c r="G140" s="3">
+        <v>0.059085841694537344</v>
+      </c>
+      <c r="H140" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D141" s="2">
+        <v>17</v>
+      </c>
+      <c r="E141" s="2">
+        <v>24</v>
+      </c>
+      <c r="F141" s="2">
+        <v>41</v>
+      </c>
+      <c r="G141" s="3">
+        <v>0.045707915273132664</v>
+      </c>
+      <c r="H141" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D142" s="2">
+        <v>10</v>
+      </c>
+      <c r="E142" s="2">
+        <v>6</v>
+      </c>
+      <c r="F142" s="2">
+        <v>16</v>
+      </c>
+      <c r="G142" s="3">
+        <v>0.017837235228539576</v>
+      </c>
+      <c r="H142" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D143" s="2">
+        <v>12</v>
+      </c>
+      <c r="E143" s="2">
+        <v>2</v>
+      </c>
+      <c r="F143" s="2">
+        <v>14</v>
+      </c>
+      <c r="G143" s="3">
+        <v>0.01560758082497213</v>
+      </c>
+      <c r="H143" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D144" s="2">
+        <v>9</v>
+      </c>
+      <c r="E144" s="2">
+        <v>2</v>
+      </c>
+      <c r="F144" s="2">
+        <v>11</v>
+      </c>
+      <c r="G144" s="3">
+        <v>0.012263099219620958</v>
+      </c>
+      <c r="H144" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D145" s="2">
+        <v>8</v>
+      </c>
+      <c r="E145" s="2">
+        <v>2</v>
+      </c>
+      <c r="F145" s="2">
+        <v>10</v>
+      </c>
+      <c r="G145" s="3">
+        <v>0.011148272017837236</v>
+      </c>
+      <c r="H145" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D146" s="2">
+        <v>6</v>
+      </c>
+      <c r="E146" s="2">
+        <v>2</v>
+      </c>
+      <c r="F146" s="2">
+        <v>8</v>
+      </c>
+      <c r="G146" s="3">
+        <v>0.008918617614269788</v>
+      </c>
+      <c r="H146" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D147" s="2">
+        <v>3</v>
+      </c>
+      <c r="E147" s="2">
+        <v>1</v>
+      </c>
+      <c r="F147" s="2">
+        <v>4</v>
+      </c>
+      <c r="G147" s="3">
+        <v>0.004459308807134894</v>
+      </c>
+      <c r="H147" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D148" s="2">
+        <v>3</v>
+      </c>
+      <c r="E148" s="2">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2">
+        <v>3</v>
+      </c>
+      <c r="G148" s="3">
+        <v>0.0033444816053511705</v>
+      </c>
+      <c r="H148" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D149" s="2">
+        <v>3</v>
+      </c>
+      <c r="E149" s="2">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2">
+        <v>3</v>
+      </c>
+      <c r="G149" s="3">
+        <v>0.0033444816053511705</v>
+      </c>
+      <c r="H149" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D150" s="2">
+        <v>2</v>
+      </c>
+      <c r="E150" s="2">
+        <v>0</v>
+      </c>
+      <c r="F150" s="2">
+        <v>2</v>
+      </c>
+      <c r="G150" s="3">
+        <v>0.002229654403567447</v>
+      </c>
+      <c r="H150" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D151" s="2">
+        <v>1</v>
+      </c>
+      <c r="E151" s="2">
+        <v>0</v>
+      </c>
+      <c r="F151" s="2">
+        <v>1</v>
+      </c>
+      <c r="G151" s="3">
+        <v>0.0011148272017837235</v>
+      </c>
+      <c r="H151" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-10</t>
+        </is>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="5">
+        <v>648</v>
+      </c>
+      <c r="E152" s="5">
+        <v>249</v>
+      </c>
+      <c r="F152" s="5">
+        <v>897</v>
+      </c>
+      <c r="G152" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H152" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -23633,6 +24783,5046 @@
         <v>776</v>
       </c>
       <c r="F667" s="4"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B668" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C668" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D668" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E668" s="2">
+        <v>326</v>
+      </c>
+      <c r="F668" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B669" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C669" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D669" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E669" s="2">
+        <v>33</v>
+      </c>
+      <c r="F669" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B670" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C670" s="0" t="inlineStr">
+        <is>
+          <t>eaug_booklover_day</t>
+        </is>
+      </c>
+      <c r="D670" s="0" t="inlineStr">
+        <is>
+          <t>eaug_booklover_day</t>
+        </is>
+      </c>
+      <c r="E670" s="2">
+        <v>18</v>
+      </c>
+      <c r="F670" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B671" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C671" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D671" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E671" s="2">
+        <v>15</v>
+      </c>
+      <c r="F671" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B672" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C672" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D672" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E672" s="2">
+        <v>14</v>
+      </c>
+      <c r="F672" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B673" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C673" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D673" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E673" s="2">
+        <v>13</v>
+      </c>
+      <c r="F673" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B674" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C674" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D674" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E674" s="2">
+        <v>12</v>
+      </c>
+      <c r="F674" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B675" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C675" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D675" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E675" s="2">
+        <v>11</v>
+      </c>
+      <c r="F675" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B676" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C676" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D676" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E676" s="2">
+        <v>11</v>
+      </c>
+      <c r="F676" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B677" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C677" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D677" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E677" s="2">
+        <v>10</v>
+      </c>
+      <c r="F677" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B678" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C678" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D678" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E678" s="2">
+        <v>10</v>
+      </c>
+      <c r="F678" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B679" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C679" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D679" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E679" s="2">
+        <v>9</v>
+      </c>
+      <c r="F679" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B680" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C680" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D680" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E680" s="2">
+        <v>9</v>
+      </c>
+      <c r="F680" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B681" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C681" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D681" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E681" s="2">
+        <v>8</v>
+      </c>
+      <c r="F681" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B682" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C682" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D682" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E682" s="2">
+        <v>8</v>
+      </c>
+      <c r="F682" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B683" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C683" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D683" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E683" s="2">
+        <v>8</v>
+      </c>
+      <c r="F683" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B684" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C684" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D684" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E684" s="2">
+        <v>8</v>
+      </c>
+      <c r="F684" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B685" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C685" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D685" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E685" s="2">
+        <v>7</v>
+      </c>
+      <c r="F685" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B686" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C686" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D686" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E686" s="2">
+        <v>6</v>
+      </c>
+      <c r="F686" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B687" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C687" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D687" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E687" s="2">
+        <v>6</v>
+      </c>
+      <c r="F687" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B688" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C688" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D688" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E688" s="2">
+        <v>6</v>
+      </c>
+      <c r="F688" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B689" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C689" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrice_pudding_day</t>
+        </is>
+      </c>
+      <c r="D689" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrice_pudding_day</t>
+        </is>
+      </c>
+      <c r="E689" s="2">
+        <v>6</v>
+      </c>
+      <c r="F689" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B690" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C690" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalsmores_day</t>
+        </is>
+      </c>
+      <c r="D690" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalsmores_day</t>
+        </is>
+      </c>
+      <c r="E690" s="2">
+        <v>6</v>
+      </c>
+      <c r="F690" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B691" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C691" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D691" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E691" s="2">
+        <v>6</v>
+      </c>
+      <c r="F691" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B692" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C692" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D692" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E692" s="2">
+        <v>6</v>
+      </c>
+      <c r="F692" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B693" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C693" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D693" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E693" s="2">
+        <v>5</v>
+      </c>
+      <c r="F693" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B694" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C694" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D694" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E694" s="2">
+        <v>5</v>
+      </c>
+      <c r="F694" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B695" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C695" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D695" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E695" s="2">
+        <v>5</v>
+      </c>
+      <c r="F695" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B696" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C696" s="0" t="inlineStr">
+        <is>
+          <t>wed_engaged</t>
+        </is>
+      </c>
+      <c r="D696" s="0" t="inlineStr">
+        <is>
+          <t>wed_engaged</t>
+        </is>
+      </c>
+      <c r="E696" s="2">
+        <v>5</v>
+      </c>
+      <c r="F696" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B697" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C697" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D697" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E697" s="2">
+        <v>4</v>
+      </c>
+      <c r="F697" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B698" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C698" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D698" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E698" s="2">
+        <v>4</v>
+      </c>
+      <c r="F698" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B699" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C699" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D699" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E699" s="2">
+        <v>4</v>
+      </c>
+      <c r="F699" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B700" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C700" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D700" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E700" s="2">
+        <v>4</v>
+      </c>
+      <c r="F700" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B701" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C701" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D701" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E701" s="2">
+        <v>4</v>
+      </c>
+      <c r="F701" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B702" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C702" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D702" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E702" s="2">
+        <v>3</v>
+      </c>
+      <c r="F702" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B703" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C703" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D703" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E703" s="2">
+        <v>3</v>
+      </c>
+      <c r="F703" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B704" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C704" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D704" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E704" s="2">
+        <v>3</v>
+      </c>
+      <c r="F704" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B705" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C705" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D705" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E705" s="2">
+        <v>3</v>
+      </c>
+      <c r="F705" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B706" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C706" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D706" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E706" s="2">
+        <v>2</v>
+      </c>
+      <c r="F706" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B707" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C707" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D707" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E707" s="2">
+        <v>2</v>
+      </c>
+      <c r="F707" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B708" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C708" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D708" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E708" s="2">
+        <v>2</v>
+      </c>
+      <c r="F708" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B709" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C709" s="0" t="inlineStr">
+        <is>
+          <t>eaug_vanillacustard_day</t>
+        </is>
+      </c>
+      <c r="D709" s="0" t="inlineStr">
+        <is>
+          <t>eaug_vanillacustard_day</t>
+        </is>
+      </c>
+      <c r="E709" s="2">
+        <v>2</v>
+      </c>
+      <c r="F709" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B710" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C710" s="0" t="inlineStr">
+        <is>
+          <t>emar_womensday_wishes</t>
+        </is>
+      </c>
+      <c r="D710" s="0" t="inlineStr">
+        <is>
+          <t>emar_womensday_wishes</t>
+        </is>
+      </c>
+      <c r="E710" s="2">
+        <v>2</v>
+      </c>
+      <c r="F710" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B711" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C711" s="0" t="inlineStr">
+        <is>
+          <t>esep_laborday_weekend</t>
+        </is>
+      </c>
+      <c r="D711" s="0" t="inlineStr">
+        <is>
+          <t>esep_laborday_weekend</t>
+        </is>
+      </c>
+      <c r="E711" s="2">
+        <v>2</v>
+      </c>
+      <c r="F711" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B712" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C712" s="0" t="inlineStr">
+        <is>
+          <t>youcare</t>
+        </is>
+      </c>
+      <c r="D712" s="0" t="inlineStr">
+        <is>
+          <t>flwr_youcare</t>
+        </is>
+      </c>
+      <c r="E712" s="2">
+        <v>2</v>
+      </c>
+      <c r="F712" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B713" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C713" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D713" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E713" s="2">
+        <v>2</v>
+      </c>
+      <c r="F713" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B714" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C714" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D714" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E714" s="2">
+        <v>2</v>
+      </c>
+      <c r="F714" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B715" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C715" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="D715" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="E715" s="2">
+        <v>2</v>
+      </c>
+      <c r="F715" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B716" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C716" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D716" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E716" s="2">
+        <v>2</v>
+      </c>
+      <c r="F716" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B717" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C717" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D717" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E717" s="2">
+        <v>1</v>
+      </c>
+      <c r="F717" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B718" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C718" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D718" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E718" s="2">
+        <v>1</v>
+      </c>
+      <c r="F718" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B719" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C719" s="0" t="inlineStr">
+        <is>
+          <t>collassociates</t>
+        </is>
+      </c>
+      <c r="D719" s="0" t="inlineStr">
+        <is>
+          <t>birth_collassociates</t>
+        </is>
+      </c>
+      <c r="E719" s="2">
+        <v>1</v>
+      </c>
+      <c r="F719" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B720" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C720" s="0" t="inlineStr">
+        <is>
+          <t>grandparents</t>
+        </is>
+      </c>
+      <c r="D720" s="0" t="inlineStr">
+        <is>
+          <t>birth_grandparents</t>
+        </is>
+      </c>
+      <c r="E720" s="2">
+        <v>1</v>
+      </c>
+      <c r="F720" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B721" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C721" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D721" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E721" s="2">
+        <v>1</v>
+      </c>
+      <c r="F721" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B722" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C722" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D722" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E722" s="2">
+        <v>1</v>
+      </c>
+      <c r="F722" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B723" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C723" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D723" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E723" s="2">
+        <v>1</v>
+      </c>
+      <c r="F723" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B724" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C724" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D724" s="0" t="inlineStr">
+        <is>
+          <t>congrats_retirement</t>
+        </is>
+      </c>
+      <c r="E724" s="2">
+        <v>1</v>
+      </c>
+      <c r="F724" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B725" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C725" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D725" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E725" s="2">
+        <v>1</v>
+      </c>
+      <c r="F725" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B726" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C726" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D726" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E726" s="2">
+        <v>1</v>
+      </c>
+      <c r="F726" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B727" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C727" s="0" t="inlineStr">
+        <is>
+          <t>ejun_father_frndfamily_nearndearones</t>
+        </is>
+      </c>
+      <c r="D727" s="0" t="inlineStr">
+        <is>
+          <t>ejun_father_frndfamily_nearndearones</t>
+        </is>
+      </c>
+      <c r="E727" s="2">
+        <v>1</v>
+      </c>
+      <c r="F727" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B728" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C728" s="0" t="inlineStr">
+        <is>
+          <t>eoct_boss_womenboss</t>
+        </is>
+      </c>
+      <c r="D728" s="0" t="inlineStr">
+        <is>
+          <t>eoct_boss_womenboss</t>
+        </is>
+      </c>
+      <c r="E728" s="2">
+        <v>1</v>
+      </c>
+      <c r="F728" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B729" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C729" s="0" t="inlineStr">
+        <is>
+          <t>eoct_yougogirlday</t>
+        </is>
+      </c>
+      <c r="D729" s="0" t="inlineStr">
+        <is>
+          <t>eoct_yougogirlday</t>
+        </is>
+      </c>
+      <c r="E729" s="2">
+        <v>1</v>
+      </c>
+      <c r="F729" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B730" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C730" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_thanku</t>
+        </is>
+      </c>
+      <c r="D730" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_thanku</t>
+        </is>
+      </c>
+      <c r="E730" s="2">
+        <v>1</v>
+      </c>
+      <c r="F730" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B731" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C731" s="0" t="inlineStr">
+        <is>
+          <t>familyoccasions</t>
+        </is>
+      </c>
+      <c r="D731" s="0" t="inlineStr">
+        <is>
+          <t>fkt_familyoccasions</t>
+        </is>
+      </c>
+      <c r="E731" s="2">
+        <v>1</v>
+      </c>
+      <c r="F731" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B732" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C732" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D732" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E732" s="2">
+        <v>1</v>
+      </c>
+      <c r="F732" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B733" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C733" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D733" s="0" t="inlineStr">
+        <is>
+          <t>flwr_friend</t>
+        </is>
+      </c>
+      <c r="E733" s="2">
+        <v>1</v>
+      </c>
+      <c r="F733" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B734" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C734" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D734" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E734" s="2">
+        <v>1</v>
+      </c>
+      <c r="F734" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B735" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C735" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D735" s="0" t="inlineStr">
+        <is>
+          <t>friend_missingyou</t>
+        </is>
+      </c>
+      <c r="E735" s="2">
+        <v>1</v>
+      </c>
+      <c r="F735" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B736" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C736" s="0" t="inlineStr">
+        <is>
+          <t>netpals</t>
+        </is>
+      </c>
+      <c r="D736" s="0" t="inlineStr">
+        <is>
+          <t>friend_netpals</t>
+        </is>
+      </c>
+      <c r="E736" s="2">
+        <v>1</v>
+      </c>
+      <c r="F736" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B737" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C737" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D737" s="0" t="inlineStr">
+        <is>
+          <t>gen_blessings</t>
+        </is>
+      </c>
+      <c r="E737" s="2">
+        <v>1</v>
+      </c>
+      <c r="F737" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B738" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C738" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D738" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E738" s="2">
+        <v>1</v>
+      </c>
+      <c r="F738" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B739" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C739" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D739" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E739" s="2">
+        <v>1</v>
+      </c>
+      <c r="F739" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B740" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C740" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D740" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E740" s="2">
+        <v>1</v>
+      </c>
+      <c r="F740" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B741" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C741" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D741" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E741" s="2">
+        <v>1</v>
+      </c>
+      <c r="F741" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B742" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C742" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D742" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E742" s="2">
+        <v>1</v>
+      </c>
+      <c r="F742" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B743" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C743" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D743" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E743" s="2">
+        <v>1</v>
+      </c>
+      <c r="F743" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B744" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C744" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D744" s="0" t="inlineStr">
+        <is>
+          <t>love_hugs</t>
+        </is>
+      </c>
+      <c r="E744" s="2">
+        <v>1</v>
+      </c>
+      <c r="F744" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B745" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C745" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D745" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E745" s="2">
+        <v>1</v>
+      </c>
+      <c r="F745" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B746" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C746" s="0" t="inlineStr">
+        <is>
+          <t>thinkingyou</t>
+        </is>
+      </c>
+      <c r="D746" s="0" t="inlineStr">
+        <is>
+          <t>love_thinkingyou</t>
+        </is>
+      </c>
+      <c r="E746" s="2">
+        <v>1</v>
+      </c>
+      <c r="F746" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B747" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C747" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D747" s="0" t="inlineStr">
+        <is>
+          <t>pet_love</t>
+        </is>
+      </c>
+      <c r="E747" s="2">
+        <v>1</v>
+      </c>
+      <c r="F747" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B748" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C748" s="0" t="inlineStr">
+        <is>
+          <t>friendship</t>
+        </is>
+      </c>
+      <c r="D748" s="0" t="inlineStr">
+        <is>
+          <t>thank_friendship</t>
+        </is>
+      </c>
+      <c r="E748" s="2">
+        <v>1</v>
+      </c>
+      <c r="F748" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B749" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C749" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D749" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E749" s="2">
+        <v>1</v>
+      </c>
+      <c r="F749" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B750" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C750" s="0" t="inlineStr">
+        <is>
+          <t>spanish_birthday</t>
+        </is>
+      </c>
+      <c r="D750" s="0" t="inlineStr">
+        <is>
+          <t>w_spanish_birthday</t>
+        </is>
+      </c>
+      <c r="E750" s="2">
+        <v>1</v>
+      </c>
+      <c r="F750" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B751" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C751" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D751" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E751" s="2">
+        <v>1</v>
+      </c>
+      <c r="F751" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B752" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C752" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D752" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E752" s="2">
+        <v>1</v>
+      </c>
+      <c r="F752" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-09</t>
+        </is>
+      </c>
+      <c r="B753" s="4"/>
+      <c r="C753" s="4"/>
+      <c r="D753" s="4"/>
+      <c r="E753" s="5">
+        <v>682</v>
+      </c>
+      <c r="F753" s="4"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B754" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C754" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D754" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E754" s="2">
+        <v>451</v>
+      </c>
+      <c r="F754" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B755" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C755" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D755" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E755" s="2">
+        <v>36</v>
+      </c>
+      <c r="F755" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B756" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C756" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D756" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E756" s="2">
+        <v>28</v>
+      </c>
+      <c r="F756" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B757" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C757" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D757" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E757" s="2">
+        <v>19</v>
+      </c>
+      <c r="F757" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B758" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C758" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D758" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E758" s="2">
+        <v>18</v>
+      </c>
+      <c r="F758" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B759" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C759" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalsmores_day</t>
+        </is>
+      </c>
+      <c r="D759" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalsmores_day</t>
+        </is>
+      </c>
+      <c r="E759" s="2">
+        <v>18</v>
+      </c>
+      <c r="F759" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B760" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C760" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D760" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E760" s="2">
+        <v>15</v>
+      </c>
+      <c r="F760" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B761" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C761" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D761" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E761" s="2">
+        <v>14</v>
+      </c>
+      <c r="F761" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B762" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C762" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D762" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E762" s="2">
+        <v>12</v>
+      </c>
+      <c r="F762" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B763" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C763" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D763" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E763" s="2">
+        <v>12</v>
+      </c>
+      <c r="F763" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B764" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C764" s="0" t="inlineStr">
+        <is>
+          <t>eaug_juliennefries_day</t>
+        </is>
+      </c>
+      <c r="D764" s="0" t="inlineStr">
+        <is>
+          <t>eaug_juliennefries_day</t>
+        </is>
+      </c>
+      <c r="E764" s="2">
+        <v>12</v>
+      </c>
+      <c r="F764" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B765" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C765" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D765" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E765" s="2">
+        <v>12</v>
+      </c>
+      <c r="F765" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B766" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C766" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="D766" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="E766" s="2">
+        <v>11</v>
+      </c>
+      <c r="F766" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B767" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C767" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D767" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E767" s="2">
+        <v>10</v>
+      </c>
+      <c r="F767" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B768" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C768" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D768" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E768" s="2">
+        <v>10</v>
+      </c>
+      <c r="F768" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B769" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C769" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D769" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E769" s="2">
+        <v>9</v>
+      </c>
+      <c r="F769" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B770" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C770" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D770" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E770" s="2">
+        <v>9</v>
+      </c>
+      <c r="F770" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B771" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C771" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D771" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E771" s="2">
+        <v>8</v>
+      </c>
+      <c r="F771" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B772" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C772" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D772" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E772" s="2">
+        <v>8</v>
+      </c>
+      <c r="F772" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B773" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C773" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D773" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E773" s="2">
+        <v>7</v>
+      </c>
+      <c r="F773" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B774" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C774" s="0" t="inlineStr">
+        <is>
+          <t>morningquotes</t>
+        </is>
+      </c>
+      <c r="D774" s="0" t="inlineStr">
+        <is>
+          <t>gen_morningquotes</t>
+        </is>
+      </c>
+      <c r="E774" s="2">
+        <v>7</v>
+      </c>
+      <c r="F774" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B775" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C775" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D775" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E775" s="2">
+        <v>7</v>
+      </c>
+      <c r="F775" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B776" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C776" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D776" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E776" s="2">
+        <v>6</v>
+      </c>
+      <c r="F776" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B777" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C777" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D777" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E777" s="2">
+        <v>6</v>
+      </c>
+      <c r="F777" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B778" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C778" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D778" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E778" s="2">
+        <v>6</v>
+      </c>
+      <c r="F778" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B779" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C779" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D779" s="0" t="inlineStr">
+        <is>
+          <t>friend_missingyou</t>
+        </is>
+      </c>
+      <c r="E779" s="2">
+        <v>6</v>
+      </c>
+      <c r="F779" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B780" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C780" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D780" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E780" s="2">
+        <v>6</v>
+      </c>
+      <c r="F780" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B781" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C781" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="D781" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="E781" s="2">
+        <v>5</v>
+      </c>
+      <c r="F781" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B782" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C782" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D782" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E782" s="2">
+        <v>5</v>
+      </c>
+      <c r="F782" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B783" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C783" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D783" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E783" s="2">
+        <v>5</v>
+      </c>
+      <c r="F783" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B784" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C784" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D784" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E784" s="2">
+        <v>5</v>
+      </c>
+      <c r="F784" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B785" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C785" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D785" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E785" s="2">
+        <v>5</v>
+      </c>
+      <c r="F785" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B786" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C786" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D786" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E786" s="2">
+        <v>4</v>
+      </c>
+      <c r="F786" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B787" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C787" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D787" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E787" s="2">
+        <v>4</v>
+      </c>
+      <c r="F787" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B788" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C788" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D788" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E788" s="2">
+        <v>4</v>
+      </c>
+      <c r="F788" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B789" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C789" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D789" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E789" s="2">
+        <v>4</v>
+      </c>
+      <c r="F789" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B790" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C790" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D790" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E790" s="2">
+        <v>4</v>
+      </c>
+      <c r="F790" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B791" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C791" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D791" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E791" s="2">
+        <v>4</v>
+      </c>
+      <c r="F791" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B792" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C792" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D792" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E792" s="2">
+        <v>3</v>
+      </c>
+      <c r="F792" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B793" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C793" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="D793" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="E793" s="2">
+        <v>3</v>
+      </c>
+      <c r="F793" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B794" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C794" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_tart_day</t>
+        </is>
+      </c>
+      <c r="D794" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_tart_day</t>
+        </is>
+      </c>
+      <c r="E794" s="2">
+        <v>3</v>
+      </c>
+      <c r="F794" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B795" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C795" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D795" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E795" s="2">
+        <v>3</v>
+      </c>
+      <c r="F795" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B796" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C796" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D796" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E796" s="2">
+        <v>3</v>
+      </c>
+      <c r="F796" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B797" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C797" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D797" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E797" s="2">
+        <v>3</v>
+      </c>
+      <c r="F797" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B798" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C798" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D798" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E798" s="2">
+        <v>3</v>
+      </c>
+      <c r="F798" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B799" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C799" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D799" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E799" s="2">
+        <v>3</v>
+      </c>
+      <c r="F799" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B800" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C800" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D800" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E800" s="2">
+        <v>3</v>
+      </c>
+      <c r="F800" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B801" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C801" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D801" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E801" s="2">
+        <v>2</v>
+      </c>
+      <c r="F801" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B802" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C802" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="D802" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="E802" s="2">
+        <v>2</v>
+      </c>
+      <c r="F802" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B803" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C803" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D803" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E803" s="2">
+        <v>2</v>
+      </c>
+      <c r="F803" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B804" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C804" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_friends</t>
+        </is>
+      </c>
+      <c r="D804" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_friends</t>
+        </is>
+      </c>
+      <c r="E804" s="2">
+        <v>2</v>
+      </c>
+      <c r="F804" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B805" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C805" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D805" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E805" s="2">
+        <v>2</v>
+      </c>
+      <c r="F805" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B806" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C806" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D806" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E806" s="2">
+        <v>2</v>
+      </c>
+      <c r="F806" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B807" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C807" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="D807" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="E807" s="2">
+        <v>2</v>
+      </c>
+      <c r="F807" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B808" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C808" s="0" t="inlineStr">
+        <is>
+          <t>justbecause</t>
+        </is>
+      </c>
+      <c r="D808" s="0" t="inlineStr">
+        <is>
+          <t>intouch_justbecause</t>
+        </is>
+      </c>
+      <c r="E808" s="2">
+        <v>2</v>
+      </c>
+      <c r="F808" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B809" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C809" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D809" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E809" s="2">
+        <v>2</v>
+      </c>
+      <c r="F809" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B810" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C810" s="0" t="inlineStr">
+        <is>
+          <t>atwork</t>
+        </is>
+      </c>
+      <c r="D810" s="0" t="inlineStr">
+        <is>
+          <t>thank_atwork</t>
+        </is>
+      </c>
+      <c r="E810" s="2">
+        <v>2</v>
+      </c>
+      <c r="F810" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B811" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C811" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D811" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E811" s="2">
+        <v>2</v>
+      </c>
+      <c r="F811" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B812" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C812" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D812" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E812" s="2">
+        <v>1</v>
+      </c>
+      <c r="F812" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B813" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C813" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D813" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E813" s="2">
+        <v>1</v>
+      </c>
+      <c r="F813" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B814" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C814" s="0" t="inlineStr">
+        <is>
+          <t>balloons</t>
+        </is>
+      </c>
+      <c r="D814" s="0" t="inlineStr">
+        <is>
+          <t>birth_balloons</t>
+        </is>
+      </c>
+      <c r="E814" s="2">
+        <v>1</v>
+      </c>
+      <c r="F814" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B815" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C815" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D815" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E815" s="2">
+        <v>1</v>
+      </c>
+      <c r="F815" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B816" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C816" s="0" t="inlineStr">
+        <is>
+          <t>grandparents</t>
+        </is>
+      </c>
+      <c r="D816" s="0" t="inlineStr">
+        <is>
+          <t>birth_grandparents</t>
+        </is>
+      </c>
+      <c r="E816" s="2">
+        <v>1</v>
+      </c>
+      <c r="F816" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B817" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C817" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D817" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E817" s="2">
+        <v>1</v>
+      </c>
+      <c r="F817" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B818" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C818" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D818" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E818" s="2">
+        <v>1</v>
+      </c>
+      <c r="F818" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B819" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C819" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D819" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E819" s="2">
+        <v>1</v>
+      </c>
+      <c r="F819" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B820" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C820" s="0" t="inlineStr">
+        <is>
+          <t>businessandworkplace</t>
+        </is>
+      </c>
+      <c r="D820" s="0" t="inlineStr">
+        <is>
+          <t>congrats_businessandworkplace</t>
+        </is>
+      </c>
+      <c r="E820" s="2">
+        <v>1</v>
+      </c>
+      <c r="F820" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B821" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C821" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D821" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E821" s="2">
+        <v>1</v>
+      </c>
+      <c r="F821" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B822" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C822" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D822" s="0" t="inlineStr">
+        <is>
+          <t>congrats_retirement</t>
+        </is>
+      </c>
+      <c r="E822" s="2">
+        <v>1</v>
+      </c>
+      <c r="F822" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B823" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C823" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D823" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E823" s="2">
+        <v>1</v>
+      </c>
+      <c r="F823" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B824" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C824" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalyouth_day</t>
+        </is>
+      </c>
+      <c r="D824" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalyouth_day</t>
+        </is>
+      </c>
+      <c r="E824" s="2">
+        <v>1</v>
+      </c>
+      <c r="F824" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B825" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C825" s="0" t="inlineStr">
+        <is>
+          <t>eaug_sonand_daughter_day</t>
+        </is>
+      </c>
+      <c r="D825" s="0" t="inlineStr">
+        <is>
+          <t>eaug_sonand_daughter_day</t>
+        </is>
+      </c>
+      <c r="E825" s="2">
+        <v>1</v>
+      </c>
+      <c r="F825" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B826" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C826" s="0" t="inlineStr">
+        <is>
+          <t>efeb_supersunday</t>
+        </is>
+      </c>
+      <c r="D826" s="0" t="inlineStr">
+        <is>
+          <t>efeb_supersunday</t>
+        </is>
+      </c>
+      <c r="E826" s="2">
+        <v>1</v>
+      </c>
+      <c r="F826" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B827" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C827" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="D827" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="E827" s="2">
+        <v>1</v>
+      </c>
+      <c r="F827" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B828" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C828" s="0" t="inlineStr">
+        <is>
+          <t>ejul_nationalcousins_day</t>
+        </is>
+      </c>
+      <c r="D828" s="0" t="inlineStr">
+        <is>
+          <t>ejul_nationalcousins_day</t>
+        </is>
+      </c>
+      <c r="E828" s="2">
+        <v>1</v>
+      </c>
+      <c r="F828" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B829" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C829" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_happy</t>
+        </is>
+      </c>
+      <c r="D829" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_happy</t>
+        </is>
+      </c>
+      <c r="E829" s="2">
+        <v>1</v>
+      </c>
+      <c r="F829" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B830" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C830" s="0" t="inlineStr">
+        <is>
+          <t>enov_allsaintsday</t>
+        </is>
+      </c>
+      <c r="D830" s="0" t="inlineStr">
+        <is>
+          <t>enov_allsaintsday</t>
+        </is>
+      </c>
+      <c r="E830" s="2">
+        <v>1</v>
+      </c>
+      <c r="F830" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B831" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C831" s="0" t="inlineStr">
+        <is>
+          <t>enov_thanks_wishes</t>
+        </is>
+      </c>
+      <c r="D831" s="0" t="inlineStr">
+        <is>
+          <t>enov_thanks_wishes</t>
+        </is>
+      </c>
+      <c r="E831" s="2">
+        <v>1</v>
+      </c>
+      <c r="F831" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B832" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C832" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_happy</t>
+        </is>
+      </c>
+      <c r="D832" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_happy</t>
+        </is>
+      </c>
+      <c r="E832" s="2">
+        <v>1</v>
+      </c>
+      <c r="F832" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B833" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C833" s="0" t="inlineStr">
+        <is>
+          <t>sonsdaughter</t>
+        </is>
+      </c>
+      <c r="D833" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sonsdaughter</t>
+        </is>
+      </c>
+      <c r="E833" s="2">
+        <v>1</v>
+      </c>
+      <c r="F833" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B834" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C834" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D834" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E834" s="2">
+        <v>1</v>
+      </c>
+      <c r="F834" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B835" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C835" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D835" s="0" t="inlineStr">
+        <is>
+          <t>friend_sorry</t>
+        </is>
+      </c>
+      <c r="E835" s="2">
+        <v>1</v>
+      </c>
+      <c r="F835" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B836" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C836" s="0" t="inlineStr">
+        <is>
+          <t>specialfriend</t>
+        </is>
+      </c>
+      <c r="D836" s="0" t="inlineStr">
+        <is>
+          <t>friend_specialfriend</t>
+        </is>
+      </c>
+      <c r="E836" s="2">
+        <v>1</v>
+      </c>
+      <c r="F836" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B837" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C837" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D837" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E837" s="2">
+        <v>1</v>
+      </c>
+      <c r="F837" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B838" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C838" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D838" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E838" s="2">
+        <v>1</v>
+      </c>
+      <c r="F838" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B839" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C839" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D839" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E839" s="2">
+        <v>1</v>
+      </c>
+      <c r="F839" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B840" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C840" s="0" t="inlineStr">
+        <is>
+          <t>otherinvitations</t>
+        </is>
+      </c>
+      <c r="D840" s="0" t="inlineStr">
+        <is>
+          <t>invp_otherinvitations</t>
+        </is>
+      </c>
+      <c r="E840" s="2">
+        <v>1</v>
+      </c>
+      <c r="F840" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B841" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C841" s="0" t="inlineStr">
+        <is>
+          <t>iamsorry</t>
+        </is>
+      </c>
+      <c r="D841" s="0" t="inlineStr">
+        <is>
+          <t>love_iamsorry</t>
+        </is>
+      </c>
+      <c r="E841" s="2">
+        <v>1</v>
+      </c>
+      <c r="F841" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B842" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C842" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D842" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E842" s="2">
+        <v>1</v>
+      </c>
+      <c r="F842" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B843" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C843" s="0" t="inlineStr">
+        <is>
+          <t>missing_forhim</t>
+        </is>
+      </c>
+      <c r="D843" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forhim</t>
+        </is>
+      </c>
+      <c r="E843" s="2">
+        <v>1</v>
+      </c>
+      <c r="F843" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B844" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C844" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D844" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E844" s="2">
+        <v>1</v>
+      </c>
+      <c r="F844" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B845" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C845" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D845" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E845" s="2">
+        <v>1</v>
+      </c>
+      <c r="F845" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B846" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C846" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D846" s="0" t="inlineStr">
+        <is>
+          <t>pet_missyou</t>
+        </is>
+      </c>
+      <c r="E846" s="2">
+        <v>1</v>
+      </c>
+      <c r="F846" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B847" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C847" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D847" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E847" s="2">
+        <v>1</v>
+      </c>
+      <c r="F847" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-10</t>
+        </is>
+      </c>
+      <c r="B848" s="4"/>
+      <c r="C848" s="4"/>
+      <c r="D848" s="4"/>
+      <c r="E848" s="5">
+        <v>897</v>
+      </c>
+      <c r="F848" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -23978,36 +30168,104 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>711</v>
+      </c>
+      <c r="C10" s="2">
+        <v>210</v>
+      </c>
+      <c r="D10" s="2">
+        <v>225</v>
+      </c>
+      <c r="E10" s="2">
+        <v>165</v>
+      </c>
+      <c r="F10" s="2">
+        <v>63</v>
+      </c>
+      <c r="G10" s="2">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <v>18</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>949</v>
+      </c>
+      <c r="C11" s="2">
+        <v>288</v>
+      </c>
+      <c r="D11" s="2">
+        <v>290</v>
+      </c>
+      <c r="E11" s="2">
+        <v>200</v>
+      </c>
+      <c r="F11" s="2">
+        <v>99</v>
+      </c>
+      <c r="G11" s="2">
+        <v>24</v>
+      </c>
+      <c r="H11" s="2">
+        <v>48</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <v>6707</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2142</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2080</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1293</v>
-      </c>
-      <c r="F10" s="5">
-        <v>698</v>
-      </c>
-      <c r="G10" s="5">
-        <v>254</v>
-      </c>
-      <c r="H10" s="5">
-        <v>211</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="B12" s="5">
+        <v>8367</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2640</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2595</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1658</v>
+      </c>
+      <c r="F12" s="5">
+        <v>860</v>
+      </c>
+      <c r="G12" s="5">
+        <v>308</v>
+      </c>
+      <c r="H12" s="5">
+        <v>277</v>
+      </c>
+      <c r="I12" s="5">
         <v>28</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J12" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -591,28 +591,56 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>766</v>
+      </c>
+      <c r="C12" s="2">
+        <v>515</v>
+      </c>
+      <c r="D12" s="2">
+        <v>251</v>
+      </c>
+      <c r="E12" s="2">
+        <v>732</v>
+      </c>
+      <c r="F12" s="2">
+        <v>34</v>
+      </c>
+      <c r="G12" s="2">
+        <v>265</v>
+      </c>
+      <c r="H12" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <v>8367</v>
-      </c>
-      <c r="C12" s="5">
-        <v>5462</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2905</v>
-      </c>
-      <c r="E12" s="5">
-        <v>7975</v>
-      </c>
-      <c r="F12" s="5">
-        <v>392</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="B13" s="5">
+        <v>9133</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5977</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3156</v>
+      </c>
+      <c r="E13" s="5">
+        <v>8707</v>
+      </c>
+      <c r="F13" s="5">
+        <v>426</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -636,8 +664,8 @@
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
     <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
@@ -720,12 +748,12 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>World languages</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Keeping in touch</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -788,10 +816,10 @@
         <v>4</v>
       </c>
       <c r="P2" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R2" s="2">
         <v>2</v>
@@ -849,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="P3" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="2">
         <v>10</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>2</v>
       </c>
       <c r="R3" s="2">
         <v>0</v>
@@ -971,10 +999,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="2">
         <v>0</v>
@@ -1032,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2">
         <v>2</v>
@@ -1093,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="2">
         <v>3</v>
@@ -1276,10 +1304,10 @@
         <v>5</v>
       </c>
       <c r="P10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2">
         <v>0</v>
@@ -1337,10 +1365,10 @@
         <v>3</v>
       </c>
       <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>2</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -1350,63 +1378,124 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>732</v>
+      </c>
+      <c r="C12" s="2">
+        <v>481</v>
+      </c>
+      <c r="D12" s="2">
+        <v>81</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46</v>
+      </c>
+      <c r="F12" s="2">
+        <v>37</v>
+      </c>
+      <c r="G12" s="2">
+        <v>31</v>
+      </c>
+      <c r="H12" s="2">
+        <v>13</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" s="2">
+        <v>14</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <v>7975</v>
-      </c>
-      <c r="C12" s="5">
-        <v>5219</v>
-      </c>
-      <c r="D12" s="5">
-        <v>774</v>
-      </c>
-      <c r="E12" s="5">
-        <v>479</v>
-      </c>
-      <c r="F12" s="5">
-        <v>379</v>
-      </c>
-      <c r="G12" s="5">
-        <v>321</v>
-      </c>
-      <c r="H12" s="5">
-        <v>197</v>
-      </c>
-      <c r="I12" s="5">
-        <v>159</v>
-      </c>
-      <c r="J12" s="5">
-        <v>149</v>
-      </c>
-      <c r="K12" s="5">
-        <v>94</v>
-      </c>
-      <c r="L12" s="5">
-        <v>78</v>
-      </c>
-      <c r="M12" s="5">
+      <c r="B13" s="5">
+        <v>8707</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5700</v>
+      </c>
+      <c r="D13" s="5">
+        <v>855</v>
+      </c>
+      <c r="E13" s="5">
+        <v>525</v>
+      </c>
+      <c r="F13" s="5">
+        <v>416</v>
+      </c>
+      <c r="G13" s="5">
+        <v>352</v>
+      </c>
+      <c r="H13" s="5">
+        <v>210</v>
+      </c>
+      <c r="I13" s="5">
+        <v>164</v>
+      </c>
+      <c r="J13" s="5">
+        <v>163</v>
+      </c>
+      <c r="K13" s="5">
+        <v>108</v>
+      </c>
+      <c r="L13" s="5">
+        <v>80</v>
+      </c>
+      <c r="M13" s="5">
+        <v>33</v>
+      </c>
+      <c r="N13" s="5">
         <v>32</v>
       </c>
-      <c r="N12" s="5">
-        <v>31</v>
-      </c>
-      <c r="O12" s="5">
+      <c r="O13" s="5">
         <v>23</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P13" s="5">
         <v>17</v>
       </c>
-      <c r="Q12" s="5">
-        <v>11</v>
-      </c>
-      <c r="R12" s="5">
+      <c r="Q13" s="5">
+        <v>17</v>
+      </c>
+      <c r="R13" s="5">
         <v>9</v>
       </c>
-      <c r="S12" s="5">
+      <c r="S13" s="5">
         <v>3</v>
       </c>
     </row>
@@ -6201,6 +6290,444 @@
       </c>
       <c r="H152" s="4"/>
     </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D153" s="2">
+        <v>325</v>
+      </c>
+      <c r="E153" s="2">
+        <v>156</v>
+      </c>
+      <c r="F153" s="2">
+        <v>481</v>
+      </c>
+      <c r="G153" s="3">
+        <v>0.657103825136612</v>
+      </c>
+      <c r="H153" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D154" s="2">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>12</v>
+      </c>
+      <c r="F154" s="2">
+        <v>81</v>
+      </c>
+      <c r="G154" s="3">
+        <v>0.11065573770491803</v>
+      </c>
+      <c r="H154" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D155" s="2">
+        <v>30</v>
+      </c>
+      <c r="E155" s="2">
+        <v>16</v>
+      </c>
+      <c r="F155" s="2">
+        <v>46</v>
+      </c>
+      <c r="G155" s="3">
+        <v>0.06284153005464481</v>
+      </c>
+      <c r="H155" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D156" s="2">
+        <v>27</v>
+      </c>
+      <c r="E156" s="2">
+        <v>10</v>
+      </c>
+      <c r="F156" s="2">
+        <v>37</v>
+      </c>
+      <c r="G156" s="3">
+        <v>0.050546448087431695</v>
+      </c>
+      <c r="H156" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D157" s="2">
+        <v>9</v>
+      </c>
+      <c r="E157" s="2">
+        <v>22</v>
+      </c>
+      <c r="F157" s="2">
+        <v>31</v>
+      </c>
+      <c r="G157" s="3">
+        <v>0.04234972677595628</v>
+      </c>
+      <c r="H157" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D158" s="2">
+        <v>6</v>
+      </c>
+      <c r="E158" s="2">
+        <v>8</v>
+      </c>
+      <c r="F158" s="2">
+        <v>14</v>
+      </c>
+      <c r="G158" s="3">
+        <v>0.01912568306010929</v>
+      </c>
+      <c r="H158" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D159" s="2">
+        <v>14</v>
+      </c>
+      <c r="E159" s="2">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2">
+        <v>14</v>
+      </c>
+      <c r="G159" s="3">
+        <v>0.01912568306010929</v>
+      </c>
+      <c r="H159" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D160" s="2">
+        <v>9</v>
+      </c>
+      <c r="E160" s="2">
+        <v>4</v>
+      </c>
+      <c r="F160" s="2">
+        <v>13</v>
+      </c>
+      <c r="G160" s="3">
+        <v>0.017759562841530054</v>
+      </c>
+      <c r="H160" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D161" s="2">
+        <v>6</v>
+      </c>
+      <c r="E161" s="2">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2">
+        <v>6</v>
+      </c>
+      <c r="G161" s="3">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="H161" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D162" s="2">
+        <v>4</v>
+      </c>
+      <c r="E162" s="2">
+        <v>1</v>
+      </c>
+      <c r="F162" s="2">
+        <v>5</v>
+      </c>
+      <c r="G162" s="3">
+        <v>0.006830601092896175</v>
+      </c>
+      <c r="H162" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D163" s="2">
+        <v>2</v>
+      </c>
+      <c r="E163" s="2">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2">
+        <v>2</v>
+      </c>
+      <c r="G163" s="3">
+        <v>0.00273224043715847</v>
+      </c>
+      <c r="H163" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D164" s="2">
+        <v>1</v>
+      </c>
+      <c r="E164" s="2">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2">
+        <v>1</v>
+      </c>
+      <c r="G164" s="3">
+        <v>0.001366120218579235</v>
+      </c>
+      <c r="H164" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D165" s="2">
+        <v>1</v>
+      </c>
+      <c r="E165" s="2">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3">
+        <v>0.001366120218579235</v>
+      </c>
+      <c r="H165" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-11</t>
+        </is>
+      </c>
+      <c r="B166" s="4"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="5">
+        <v>503</v>
+      </c>
+      <c r="E166" s="5">
+        <v>229</v>
+      </c>
+      <c r="F166" s="5">
+        <v>732</v>
+      </c>
+      <c r="G166" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H166" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -29823,6 +30350,2344 @@
         <v>897</v>
       </c>
       <c r="F848" s="4"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B849" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C849" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D849" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E849" s="2">
+        <v>338</v>
+      </c>
+      <c r="F849" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B850" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C850" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D850" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E850" s="2">
+        <v>33</v>
+      </c>
+      <c r="F850" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B851" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C851" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D851" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E851" s="2">
+        <v>26</v>
+      </c>
+      <c r="F851" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B852" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C852" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D852" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E852" s="2">
+        <v>21</v>
+      </c>
+      <c r="F852" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B853" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C853" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D853" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E853" s="2">
+        <v>18</v>
+      </c>
+      <c r="F853" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B854" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C854" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D854" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E854" s="2">
+        <v>14</v>
+      </c>
+      <c r="F854" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B855" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C855" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D855" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E855" s="2">
+        <v>13</v>
+      </c>
+      <c r="F855" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B856" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C856" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D856" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E856" s="2">
+        <v>13</v>
+      </c>
+      <c r="F856" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B857" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C857" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_tart_day</t>
+        </is>
+      </c>
+      <c r="D857" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalraspberry_tart_day</t>
+        </is>
+      </c>
+      <c r="E857" s="2">
+        <v>13</v>
+      </c>
+      <c r="F857" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B858" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C858" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D858" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E858" s="2">
+        <v>12</v>
+      </c>
+      <c r="F858" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B859" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C859" s="0" t="inlineStr">
+        <is>
+          <t>eaug_sonand_daughter_day</t>
+        </is>
+      </c>
+      <c r="D859" s="0" t="inlineStr">
+        <is>
+          <t>eaug_sonand_daughter_day</t>
+        </is>
+      </c>
+      <c r="E859" s="2">
+        <v>11</v>
+      </c>
+      <c r="F859" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B860" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C860" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D860" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E860" s="2">
+        <v>10</v>
+      </c>
+      <c r="F860" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B861" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C861" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D861" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E861" s="2">
+        <v>9</v>
+      </c>
+      <c r="F861" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B862" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C862" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D862" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E862" s="2">
+        <v>9</v>
+      </c>
+      <c r="F862" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B863" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C863" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D863" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E863" s="2">
+        <v>8</v>
+      </c>
+      <c r="F863" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B864" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C864" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D864" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E864" s="2">
+        <v>8</v>
+      </c>
+      <c r="F864" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B865" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C865" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D865" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E865" s="2">
+        <v>8</v>
+      </c>
+      <c r="F865" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B866" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C866" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D866" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E866" s="2">
+        <v>7</v>
+      </c>
+      <c r="F866" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B867" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C867" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D867" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E867" s="2">
+        <v>7</v>
+      </c>
+      <c r="F867" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B868" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C868" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D868" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E868" s="2">
+        <v>7</v>
+      </c>
+      <c r="F868" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B869" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C869" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D869" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E869" s="2">
+        <v>7</v>
+      </c>
+      <c r="F869" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B870" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C870" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D870" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E870" s="2">
+        <v>7</v>
+      </c>
+      <c r="F870" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B871" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C871" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D871" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E871" s="2">
+        <v>6</v>
+      </c>
+      <c r="F871" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B872" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C872" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D872" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E872" s="2">
+        <v>6</v>
+      </c>
+      <c r="F872" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B873" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C873" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D873" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E873" s="2">
+        <v>6</v>
+      </c>
+      <c r="F873" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B874" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C874" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D874" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E874" s="2">
+        <v>5</v>
+      </c>
+      <c r="F874" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B875" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C875" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="D875" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="E875" s="2">
+        <v>5</v>
+      </c>
+      <c r="F875" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B876" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C876" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="D876" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="E876" s="2">
+        <v>5</v>
+      </c>
+      <c r="F876" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B877" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C877" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D877" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E877" s="2">
+        <v>5</v>
+      </c>
+      <c r="F877" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B878" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C878" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D878" s="0" t="inlineStr">
+        <is>
+          <t>intouch_missingyou</t>
+        </is>
+      </c>
+      <c r="E878" s="2">
+        <v>5</v>
+      </c>
+      <c r="F878" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B879" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C879" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D879" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E879" s="2">
+        <v>5</v>
+      </c>
+      <c r="F879" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B880" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C880" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D880" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E880" s="2">
+        <v>4</v>
+      </c>
+      <c r="F880" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B881" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C881" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D881" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E881" s="2">
+        <v>4</v>
+      </c>
+      <c r="F881" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B882" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C882" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D882" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E882" s="2">
+        <v>4</v>
+      </c>
+      <c r="F882" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B883" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C883" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D883" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E883" s="2">
+        <v>4</v>
+      </c>
+      <c r="F883" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B884" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C884" s="0" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D884" s="0" t="inlineStr">
+        <is>
+          <t>thank_congratulations</t>
+        </is>
+      </c>
+      <c r="E884" s="2">
+        <v>4</v>
+      </c>
+      <c r="F884" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B885" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C885" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D885" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E885" s="2">
+        <v>3</v>
+      </c>
+      <c r="F885" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B886" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C886" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D886" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E886" s="2">
+        <v>3</v>
+      </c>
+      <c r="F886" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B887" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C887" s="0" t="inlineStr">
+        <is>
+          <t>youarewelcome</t>
+        </is>
+      </c>
+      <c r="D887" s="0" t="inlineStr">
+        <is>
+          <t>gen_youarewelcome</t>
+        </is>
+      </c>
+      <c r="E887" s="2">
+        <v>3</v>
+      </c>
+      <c r="F887" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B888" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C888" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D888" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E888" s="2">
+        <v>3</v>
+      </c>
+      <c r="F888" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B889" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C889" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D889" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E889" s="2">
+        <v>3</v>
+      </c>
+      <c r="F889" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B890" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C890" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalyouth_day</t>
+        </is>
+      </c>
+      <c r="D890" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalyouth_day</t>
+        </is>
+      </c>
+      <c r="E890" s="2">
+        <v>2</v>
+      </c>
+      <c r="F890" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B891" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C891" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D891" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E891" s="2">
+        <v>2</v>
+      </c>
+      <c r="F891" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B892" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C892" s="0" t="inlineStr">
+        <is>
+          <t>youcare</t>
+        </is>
+      </c>
+      <c r="D892" s="0" t="inlineStr">
+        <is>
+          <t>flwr_youcare</t>
+        </is>
+      </c>
+      <c r="E892" s="2">
+        <v>2</v>
+      </c>
+      <c r="F892" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B893" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C893" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D893" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E893" s="2">
+        <v>2</v>
+      </c>
+      <c r="F893" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B894" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C894" s="0" t="inlineStr">
+        <is>
+          <t>tuestoons</t>
+        </is>
+      </c>
+      <c r="D894" s="0" t="inlineStr">
+        <is>
+          <t>gen_tuestoons</t>
+        </is>
+      </c>
+      <c r="E894" s="2">
+        <v>2</v>
+      </c>
+      <c r="F894" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B895" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C895" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D895" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E895" s="2">
+        <v>2</v>
+      </c>
+      <c r="F895" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B896" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C896" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D896" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E896" s="2">
+        <v>2</v>
+      </c>
+      <c r="F896" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B897" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C897" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D897" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E897" s="2">
+        <v>2</v>
+      </c>
+      <c r="F897" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B898" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C898" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D898" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E898" s="2">
+        <v>1</v>
+      </c>
+      <c r="F898" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B899" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C899" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D899" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E899" s="2">
+        <v>1</v>
+      </c>
+      <c r="F899" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B900" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C900" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D900" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E900" s="2">
+        <v>1</v>
+      </c>
+      <c r="F900" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B901" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C901" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D901" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E901" s="2">
+        <v>1</v>
+      </c>
+      <c r="F901" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B902" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C902" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D902" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E902" s="2">
+        <v>1</v>
+      </c>
+      <c r="F902" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B903" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C903" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D903" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E903" s="2">
+        <v>1</v>
+      </c>
+      <c r="F903" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B904" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C904" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D904" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E904" s="2">
+        <v>1</v>
+      </c>
+      <c r="F904" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B905" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C905" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="D905" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="E905" s="2">
+        <v>1</v>
+      </c>
+      <c r="F905" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B906" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C906" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="D906" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="E906" s="2">
+        <v>1</v>
+      </c>
+      <c r="F906" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B907" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C907" s="0" t="inlineStr">
+        <is>
+          <t>efeb_valen_thanku</t>
+        </is>
+      </c>
+      <c r="D907" s="0" t="inlineStr">
+        <is>
+          <t>efeb_valen_thanku</t>
+        </is>
+      </c>
+      <c r="E907" s="2">
+        <v>1</v>
+      </c>
+      <c r="F907" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B908" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C908" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_happy</t>
+        </is>
+      </c>
+      <c r="D908" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_happy</t>
+        </is>
+      </c>
+      <c r="E908" s="2">
+        <v>1</v>
+      </c>
+      <c r="F908" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B909" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C909" s="0" t="inlineStr">
+        <is>
+          <t>emay_mawlidalnabi</t>
+        </is>
+      </c>
+      <c r="D909" s="0" t="inlineStr">
+        <is>
+          <t>emay_mawlidalnabi</t>
+        </is>
+      </c>
+      <c r="E909" s="2">
+        <v>1</v>
+      </c>
+      <c r="F909" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B910" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C910" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_happy</t>
+        </is>
+      </c>
+      <c r="D910" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_happy</t>
+        </is>
+      </c>
+      <c r="E910" s="2">
+        <v>1</v>
+      </c>
+      <c r="F910" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B911" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C911" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_thanku</t>
+        </is>
+      </c>
+      <c r="D911" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_thanku</t>
+        </is>
+      </c>
+      <c r="E911" s="2">
+        <v>1</v>
+      </c>
+      <c r="F911" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B912" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C912" s="0" t="inlineStr">
+        <is>
+          <t>enov_adventday</t>
+        </is>
+      </c>
+      <c r="D912" s="0" t="inlineStr">
+        <is>
+          <t>enov_adventday</t>
+        </is>
+      </c>
+      <c r="E912" s="2">
+        <v>1</v>
+      </c>
+      <c r="F912" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B913" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C913" s="0" t="inlineStr">
+        <is>
+          <t>enov_allsaintsday</t>
+        </is>
+      </c>
+      <c r="D913" s="0" t="inlineStr">
+        <is>
+          <t>enov_allsaintsday</t>
+        </is>
+      </c>
+      <c r="E913" s="2">
+        <v>1</v>
+      </c>
+      <c r="F913" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B914" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C914" s="0" t="inlineStr">
+        <is>
+          <t>enov_remembranceday</t>
+        </is>
+      </c>
+      <c r="D914" s="0" t="inlineStr">
+        <is>
+          <t>enov_remembranceday</t>
+        </is>
+      </c>
+      <c r="E914" s="2">
+        <v>1</v>
+      </c>
+      <c r="F914" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B915" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C915" s="0" t="inlineStr">
+        <is>
+          <t>enov_thanks_wishes</t>
+        </is>
+      </c>
+      <c r="D915" s="0" t="inlineStr">
+        <is>
+          <t>enov_thanks_wishes</t>
+        </is>
+      </c>
+      <c r="E915" s="2">
+        <v>1</v>
+      </c>
+      <c r="F915" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B916" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C916" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_happy</t>
+        </is>
+      </c>
+      <c r="D916" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_happy</t>
+        </is>
+      </c>
+      <c r="E916" s="2">
+        <v>1</v>
+      </c>
+      <c r="F916" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B917" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C917" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D917" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E917" s="2">
+        <v>1</v>
+      </c>
+      <c r="F917" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B918" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C918" s="0" t="inlineStr">
+        <is>
+          <t>friendsforever</t>
+        </is>
+      </c>
+      <c r="D918" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendsforever</t>
+        </is>
+      </c>
+      <c r="E918" s="2">
+        <v>1</v>
+      </c>
+      <c r="F918" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B919" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C919" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D919" s="0" t="inlineStr">
+        <is>
+          <t>friend_missingyou</t>
+        </is>
+      </c>
+      <c r="E919" s="2">
+        <v>1</v>
+      </c>
+      <c r="F919" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B920" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C920" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D920" s="0" t="inlineStr">
+        <is>
+          <t>gen_blessings</t>
+        </is>
+      </c>
+      <c r="E920" s="2">
+        <v>1</v>
+      </c>
+      <c r="F920" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B921" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C921" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D921" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E921" s="2">
+        <v>1</v>
+      </c>
+      <c r="F921" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B922" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C922" s="0" t="inlineStr">
+        <is>
+          <t>joke</t>
+        </is>
+      </c>
+      <c r="D922" s="0" t="inlineStr">
+        <is>
+          <t>gen_joke</t>
+        </is>
+      </c>
+      <c r="E922" s="2">
+        <v>1</v>
+      </c>
+      <c r="F922" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B923" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C923" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D923" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E923" s="2">
+        <v>1</v>
+      </c>
+      <c r="F923" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B924" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C924" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D924" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E924" s="2">
+        <v>1</v>
+      </c>
+      <c r="F924" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B925" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C925" s="0" t="inlineStr">
+        <is>
+          <t>poetry</t>
+        </is>
+      </c>
+      <c r="D925" s="0" t="inlineStr">
+        <is>
+          <t>insp_poetry</t>
+        </is>
+      </c>
+      <c r="E925" s="2">
+        <v>1</v>
+      </c>
+      <c r="F925" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B926" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C926" s="0" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D926" s="0" t="inlineStr">
+        <is>
+          <t>insp_support</t>
+        </is>
+      </c>
+      <c r="E926" s="2">
+        <v>1</v>
+      </c>
+      <c r="F926" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B927" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C927" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D927" s="0" t="inlineStr">
+        <is>
+          <t>intouch_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E927" s="2">
+        <v>1</v>
+      </c>
+      <c r="F927" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B928" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C928" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D928" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E928" s="2">
+        <v>1</v>
+      </c>
+      <c r="F928" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B929" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C929" s="0" t="inlineStr">
+        <is>
+          <t>lovesongs</t>
+        </is>
+      </c>
+      <c r="D929" s="0" t="inlineStr">
+        <is>
+          <t>love_lovesongs</t>
+        </is>
+      </c>
+      <c r="E929" s="2">
+        <v>1</v>
+      </c>
+      <c r="F929" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B930" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C930" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D930" s="0" t="inlineStr">
+        <is>
+          <t>pet_love</t>
+        </is>
+      </c>
+      <c r="E930" s="2">
+        <v>1</v>
+      </c>
+      <c r="F930" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B931" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C931" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D931" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E931" s="2">
+        <v>1</v>
+      </c>
+      <c r="F931" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-11</t>
+        </is>
+      </c>
+      <c r="B932" s="4"/>
+      <c r="C932" s="4"/>
+      <c r="D932" s="4"/>
+      <c r="E932" s="5">
+        <v>732</v>
+      </c>
+      <c r="F932" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -30236,36 +33101,70 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>766</v>
+      </c>
+      <c r="C12" s="2">
+        <v>226</v>
+      </c>
+      <c r="D12" s="2">
+        <v>237</v>
+      </c>
+      <c r="E12" s="2">
+        <v>155</v>
+      </c>
+      <c r="F12" s="2">
+        <v>95</v>
+      </c>
+      <c r="G12" s="2">
+        <v>28</v>
+      </c>
+      <c r="H12" s="2">
+        <v>25</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <v>8367</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2640</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2595</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1658</v>
-      </c>
-      <c r="F12" s="5">
-        <v>860</v>
-      </c>
-      <c r="G12" s="5">
-        <v>308</v>
-      </c>
-      <c r="H12" s="5">
-        <v>277</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="B13" s="5">
+        <v>9133</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2866</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2832</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1813</v>
+      </c>
+      <c r="F13" s="5">
+        <v>955</v>
+      </c>
+      <c r="G13" s="5">
+        <v>336</v>
+      </c>
+      <c r="H13" s="5">
+        <v>302</v>
+      </c>
+      <c r="I13" s="5">
         <v>28</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -619,28 +619,56 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>835</v>
+      </c>
+      <c r="C13" s="2">
+        <v>570</v>
+      </c>
+      <c r="D13" s="2">
+        <v>265</v>
+      </c>
+      <c r="E13" s="2">
+        <v>773</v>
+      </c>
+      <c r="F13" s="2">
+        <v>62</v>
+      </c>
+      <c r="G13" s="2">
+        <v>250</v>
+      </c>
+      <c r="H13" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <v>9133</v>
-      </c>
-      <c r="C13" s="5">
-        <v>5977</v>
-      </c>
-      <c r="D13" s="5">
-        <v>3156</v>
-      </c>
-      <c r="E13" s="5">
-        <v>8707</v>
-      </c>
-      <c r="F13" s="5">
-        <v>426</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="B14" s="5">
+        <v>9968</v>
+      </c>
+      <c r="C14" s="5">
+        <v>6547</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3421</v>
+      </c>
+      <c r="E14" s="5">
+        <v>9480</v>
+      </c>
+      <c r="F14" s="5">
+        <v>488</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -657,15 +685,15 @@
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
     <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
@@ -713,14 +741,14 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Friendship</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Inspirational &amp; sympathy</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Congratulations</t>
@@ -748,12 +776,12 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Keeping in touch</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>World languages</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -795,10 +823,10 @@
         <v>19</v>
       </c>
       <c r="I2" s="2">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2">
         <v>28</v>
-      </c>
-      <c r="J2" s="2">
-        <v>10</v>
       </c>
       <c r="K2" s="2">
         <v>12</v>
@@ -816,10 +844,10 @@
         <v>4</v>
       </c>
       <c r="P2" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="2">
         <v>6</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>2</v>
       </c>
       <c r="R2" s="2">
         <v>2</v>
@@ -856,10 +884,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="2">
+        <v>19</v>
+      </c>
+      <c r="J3" s="2">
         <v>41</v>
-      </c>
-      <c r="J3" s="2">
-        <v>19</v>
       </c>
       <c r="K3" s="2">
         <v>11</v>
@@ -877,10 +905,10 @@
         <v>1</v>
       </c>
       <c r="P3" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q3" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R3" s="2">
         <v>0</v>
@@ -917,10 +945,10 @@
         <v>18</v>
       </c>
       <c r="I4" s="2">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2">
         <v>11</v>
-      </c>
-      <c r="J4" s="2">
-        <v>16</v>
       </c>
       <c r="K4" s="2">
         <v>17</v>
@@ -978,10 +1006,10 @@
         <v>26</v>
       </c>
       <c r="I5" s="2">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2">
         <v>22</v>
-      </c>
-      <c r="J5" s="2">
-        <v>15</v>
       </c>
       <c r="K5" s="2">
         <v>4</v>
@@ -999,10 +1027,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2">
         <v>0</v>
@@ -1039,10 +1067,10 @@
         <v>13</v>
       </c>
       <c r="I6" s="2">
+        <v>15</v>
+      </c>
+      <c r="J6" s="2">
         <v>11</v>
-      </c>
-      <c r="J6" s="2">
-        <v>15</v>
       </c>
       <c r="K6" s="2">
         <v>8</v>
@@ -1060,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
         <v>0</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>1</v>
       </c>
       <c r="R6" s="2">
         <v>2</v>
@@ -1100,10 +1128,10 @@
         <v>11</v>
       </c>
       <c r="I7" s="2">
+        <v>12</v>
+      </c>
+      <c r="J7" s="2">
         <v>16</v>
-      </c>
-      <c r="J7" s="2">
-        <v>12</v>
       </c>
       <c r="K7" s="2">
         <v>10</v>
@@ -1121,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
         <v>0</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>1</v>
       </c>
       <c r="R7" s="2">
         <v>3</v>
@@ -1161,10 +1189,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="2">
+        <v>14</v>
+      </c>
+      <c r="J8" s="2">
         <v>7</v>
-      </c>
-      <c r="J8" s="2">
-        <v>14</v>
       </c>
       <c r="K8" s="2">
         <v>8</v>
@@ -1222,10 +1250,10 @@
         <v>20</v>
       </c>
       <c r="I9" s="2">
+        <v>12</v>
+      </c>
+      <c r="J9" s="2">
         <v>5</v>
-      </c>
-      <c r="J9" s="2">
-        <v>12</v>
       </c>
       <c r="K9" s="2">
         <v>8</v>
@@ -1283,10 +1311,10 @@
         <v>35</v>
       </c>
       <c r="I10" s="2">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2">
         <v>7</v>
-      </c>
-      <c r="J10" s="2">
-        <v>20</v>
       </c>
       <c r="K10" s="2">
         <v>6</v>
@@ -1304,10 +1332,10 @@
         <v>5</v>
       </c>
       <c r="P10" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
         <v>0</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>1</v>
       </c>
       <c r="R10" s="2">
         <v>0</v>
@@ -1344,10 +1372,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="2">
+        <v>16</v>
+      </c>
+      <c r="J11" s="2">
         <v>11</v>
-      </c>
-      <c r="J11" s="2">
-        <v>16</v>
       </c>
       <c r="K11" s="2">
         <v>10</v>
@@ -1365,10 +1393,10 @@
         <v>3</v>
       </c>
       <c r="P11" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -1405,10 +1433,10 @@
         <v>13</v>
       </c>
       <c r="I12" s="2">
+        <v>14</v>
+      </c>
+      <c r="J12" s="2">
         <v>5</v>
-      </c>
-      <c r="J12" s="2">
-        <v>14</v>
       </c>
       <c r="K12" s="2">
         <v>14</v>
@@ -1426,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
         <v>6</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>0</v>
       </c>
       <c r="R12" s="2">
         <v>0</v>
@@ -1439,63 +1467,124 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>773</v>
+      </c>
+      <c r="C13" s="2">
+        <v>567</v>
+      </c>
+      <c r="D13" s="2">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46</v>
+      </c>
+      <c r="F13" s="2">
+        <v>38</v>
+      </c>
+      <c r="G13" s="2">
+        <v>24</v>
+      </c>
+      <c r="H13" s="2">
+        <v>16</v>
+      </c>
+      <c r="I13" s="2">
+        <v>16</v>
+      </c>
+      <c r="J13" s="2">
+        <v>7</v>
+      </c>
+      <c r="K13" s="2">
+        <v>5</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2</v>
+      </c>
+      <c r="M13" s="2">
+        <v>2</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2">
+        <v>2</v>
+      </c>
+      <c r="P13" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>2</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <v>8707</v>
-      </c>
-      <c r="C13" s="5">
-        <v>5700</v>
-      </c>
-      <c r="D13" s="5">
-        <v>855</v>
-      </c>
-      <c r="E13" s="5">
-        <v>525</v>
-      </c>
-      <c r="F13" s="5">
-        <v>416</v>
-      </c>
-      <c r="G13" s="5">
-        <v>352</v>
-      </c>
-      <c r="H13" s="5">
-        <v>210</v>
-      </c>
-      <c r="I13" s="5">
-        <v>164</v>
-      </c>
-      <c r="J13" s="5">
-        <v>163</v>
-      </c>
-      <c r="K13" s="5">
-        <v>108</v>
-      </c>
-      <c r="L13" s="5">
-        <v>80</v>
-      </c>
-      <c r="M13" s="5">
+      <c r="B14" s="5">
+        <v>9480</v>
+      </c>
+      <c r="C14" s="5">
+        <v>6267</v>
+      </c>
+      <c r="D14" s="5">
+        <v>897</v>
+      </c>
+      <c r="E14" s="5">
+        <v>571</v>
+      </c>
+      <c r="F14" s="5">
+        <v>454</v>
+      </c>
+      <c r="G14" s="5">
+        <v>376</v>
+      </c>
+      <c r="H14" s="5">
+        <v>226</v>
+      </c>
+      <c r="I14" s="5">
+        <v>179</v>
+      </c>
+      <c r="J14" s="5">
+        <v>171</v>
+      </c>
+      <c r="K14" s="5">
+        <v>113</v>
+      </c>
+      <c r="L14" s="5">
+        <v>82</v>
+      </c>
+      <c r="M14" s="5">
+        <v>35</v>
+      </c>
+      <c r="N14" s="5">
         <v>33</v>
       </c>
-      <c r="N13" s="5">
-        <v>32</v>
-      </c>
-      <c r="O13" s="5">
-        <v>23</v>
-      </c>
-      <c r="P13" s="5">
-        <v>17</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>17</v>
-      </c>
-      <c r="R13" s="5">
+      <c r="O14" s="5">
+        <v>25</v>
+      </c>
+      <c r="P14" s="5">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>19</v>
+      </c>
+      <c r="R14" s="5">
         <v>9</v>
       </c>
-      <c r="S13" s="5">
+      <c r="S14" s="5">
         <v>3</v>
       </c>
     </row>
@@ -6728,6 +6817,508 @@
       </c>
       <c r="H166" s="4"/>
     </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D167" s="2">
+        <v>414</v>
+      </c>
+      <c r="E167" s="2">
+        <v>153</v>
+      </c>
+      <c r="F167" s="2">
+        <v>567</v>
+      </c>
+      <c r="G167" s="3">
+        <v>0.7335058214747736</v>
+      </c>
+      <c r="H167" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D168" s="2">
+        <v>33</v>
+      </c>
+      <c r="E168" s="2">
+        <v>13</v>
+      </c>
+      <c r="F168" s="2">
+        <v>46</v>
+      </c>
+      <c r="G168" s="3">
+        <v>0.059508408796895215</v>
+      </c>
+      <c r="H168" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D169" s="2">
+        <v>36</v>
+      </c>
+      <c r="E169" s="2">
+        <v>6</v>
+      </c>
+      <c r="F169" s="2">
+        <v>42</v>
+      </c>
+      <c r="G169" s="3">
+        <v>0.054333764553686936</v>
+      </c>
+      <c r="H169" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D170" s="2">
+        <v>26</v>
+      </c>
+      <c r="E170" s="2">
+        <v>12</v>
+      </c>
+      <c r="F170" s="2">
+        <v>38</v>
+      </c>
+      <c r="G170" s="3">
+        <v>0.04915912031047866</v>
+      </c>
+      <c r="H170" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D171" s="2">
+        <v>5</v>
+      </c>
+      <c r="E171" s="2">
+        <v>19</v>
+      </c>
+      <c r="F171" s="2">
+        <v>24</v>
+      </c>
+      <c r="G171" s="3">
+        <v>0.031047865459249677</v>
+      </c>
+      <c r="H171" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D172" s="2">
+        <v>14</v>
+      </c>
+      <c r="E172" s="2">
+        <v>2</v>
+      </c>
+      <c r="F172" s="2">
+        <v>16</v>
+      </c>
+      <c r="G172" s="3">
+        <v>0.02069857697283312</v>
+      </c>
+      <c r="H172" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D173" s="2">
+        <v>11</v>
+      </c>
+      <c r="E173" s="2">
+        <v>5</v>
+      </c>
+      <c r="F173" s="2">
+        <v>16</v>
+      </c>
+      <c r="G173" s="3">
+        <v>0.02069857697283312</v>
+      </c>
+      <c r="H173" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D174" s="2">
+        <v>3</v>
+      </c>
+      <c r="E174" s="2">
+        <v>4</v>
+      </c>
+      <c r="F174" s="2">
+        <v>7</v>
+      </c>
+      <c r="G174" s="3">
+        <v>0.009055627425614488</v>
+      </c>
+      <c r="H174" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D175" s="2">
+        <v>1</v>
+      </c>
+      <c r="E175" s="2">
+        <v>4</v>
+      </c>
+      <c r="F175" s="2">
+        <v>5</v>
+      </c>
+      <c r="G175" s="3">
+        <v>0.00646830530401035</v>
+      </c>
+      <c r="H175" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D176" s="2">
+        <v>0</v>
+      </c>
+      <c r="E176" s="2">
+        <v>3</v>
+      </c>
+      <c r="F176" s="2">
+        <v>3</v>
+      </c>
+      <c r="G176" s="3">
+        <v>0.0038809831824062097</v>
+      </c>
+      <c r="H176" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D177" s="2">
+        <v>2</v>
+      </c>
+      <c r="E177" s="2">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2">
+        <v>2</v>
+      </c>
+      <c r="G177" s="3">
+        <v>0.00258732212160414</v>
+      </c>
+      <c r="H177" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D178" s="2">
+        <v>1</v>
+      </c>
+      <c r="E178" s="2">
+        <v>1</v>
+      </c>
+      <c r="F178" s="2">
+        <v>2</v>
+      </c>
+      <c r="G178" s="3">
+        <v>0.00258732212160414</v>
+      </c>
+      <c r="H178" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D179" s="2">
+        <v>2</v>
+      </c>
+      <c r="E179" s="2">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2">
+        <v>2</v>
+      </c>
+      <c r="G179" s="3">
+        <v>0.00258732212160414</v>
+      </c>
+      <c r="H179" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D180" s="2">
+        <v>2</v>
+      </c>
+      <c r="E180" s="2">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2">
+        <v>2</v>
+      </c>
+      <c r="G180" s="3">
+        <v>0.00258732212160414</v>
+      </c>
+      <c r="H180" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D181" s="2">
+        <v>1</v>
+      </c>
+      <c r="E181" s="2">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2">
+        <v>1</v>
+      </c>
+      <c r="G181" s="3">
+        <v>0.00129366106080207</v>
+      </c>
+      <c r="H181" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-12</t>
+        </is>
+      </c>
+      <c r="B182" s="4"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="5">
+        <v>551</v>
+      </c>
+      <c r="E182" s="5">
+        <v>222</v>
+      </c>
+      <c r="F182" s="5">
+        <v>773</v>
+      </c>
+      <c r="G182" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H182" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -32688,6 +33279,2344 @@
         <v>732</v>
       </c>
       <c r="F932" s="4"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B933" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C933" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D933" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E933" s="2">
+        <v>458</v>
+      </c>
+      <c r="F933" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B934" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C934" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D934" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E934" s="2">
+        <v>29</v>
+      </c>
+      <c r="F934" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B935" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C935" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D935" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E935" s="2">
+        <v>22</v>
+      </c>
+      <c r="F935" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B936" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C936" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D936" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E936" s="2">
+        <v>13</v>
+      </c>
+      <c r="F936" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B937" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C937" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D937" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E937" s="2">
+        <v>11</v>
+      </c>
+      <c r="F937" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B938" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C938" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D938" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E938" s="2">
+        <v>11</v>
+      </c>
+      <c r="F938" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B939" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C939" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D939" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E939" s="2">
+        <v>11</v>
+      </c>
+      <c r="F939" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B940" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C940" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D940" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E940" s="2">
+        <v>10</v>
+      </c>
+      <c r="F940" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B941" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C941" s="0" t="inlineStr">
+        <is>
+          <t>eaug_juliennefries_day</t>
+        </is>
+      </c>
+      <c r="D941" s="0" t="inlineStr">
+        <is>
+          <t>eaug_juliennefries_day</t>
+        </is>
+      </c>
+      <c r="E941" s="2">
+        <v>10</v>
+      </c>
+      <c r="F941" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B942" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C942" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D942" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E942" s="2">
+        <v>10</v>
+      </c>
+      <c r="F942" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B943" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C943" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D943" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E943" s="2">
+        <v>9</v>
+      </c>
+      <c r="F943" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B944" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C944" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D944" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E944" s="2">
+        <v>9</v>
+      </c>
+      <c r="F944" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B945" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C945" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D945" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E945" s="2">
+        <v>9</v>
+      </c>
+      <c r="F945" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B946" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C946" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D946" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E946" s="2">
+        <v>9</v>
+      </c>
+      <c r="F946" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B947" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C947" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D947" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E947" s="2">
+        <v>8</v>
+      </c>
+      <c r="F947" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B948" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C948" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D948" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E948" s="2">
+        <v>8</v>
+      </c>
+      <c r="F948" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B949" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C949" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D949" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E949" s="2">
+        <v>7</v>
+      </c>
+      <c r="F949" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B950" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C950" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D950" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E950" s="2">
+        <v>7</v>
+      </c>
+      <c r="F950" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B951" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C951" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D951" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E951" s="2">
+        <v>6</v>
+      </c>
+      <c r="F951" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B952" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C952" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D952" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E952" s="2">
+        <v>6</v>
+      </c>
+      <c r="F952" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B953" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C953" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D953" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E953" s="2">
+        <v>5</v>
+      </c>
+      <c r="F953" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B954" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C954" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D954" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E954" s="2">
+        <v>4</v>
+      </c>
+      <c r="F954" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B955" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C955" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D955" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E955" s="2">
+        <v>4</v>
+      </c>
+      <c r="F955" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B956" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C956" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D956" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E956" s="2">
+        <v>4</v>
+      </c>
+      <c r="F956" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B957" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C957" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D957" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E957" s="2">
+        <v>4</v>
+      </c>
+      <c r="F957" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B958" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C958" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D958" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E958" s="2">
+        <v>4</v>
+      </c>
+      <c r="F958" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B959" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C959" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D959" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E959" s="2">
+        <v>4</v>
+      </c>
+      <c r="F959" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B960" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C960" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D960" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E960" s="2">
+        <v>4</v>
+      </c>
+      <c r="F960" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B961" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C961" s="0" t="inlineStr">
+        <is>
+          <t>eaug_vanillacustard_day</t>
+        </is>
+      </c>
+      <c r="D961" s="0" t="inlineStr">
+        <is>
+          <t>eaug_vanillacustard_day</t>
+        </is>
+      </c>
+      <c r="E961" s="2">
+        <v>3</v>
+      </c>
+      <c r="F961" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B962" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C962" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D962" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E962" s="2">
+        <v>3</v>
+      </c>
+      <c r="F962" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B963" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C963" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D963" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E963" s="2">
+        <v>3</v>
+      </c>
+      <c r="F963" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B964" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C964" s="0" t="inlineStr">
+        <is>
+          <t>russian_birthday</t>
+        </is>
+      </c>
+      <c r="D964" s="0" t="inlineStr">
+        <is>
+          <t>w_russian_birthday</t>
+        </is>
+      </c>
+      <c r="E964" s="2">
+        <v>3</v>
+      </c>
+      <c r="F964" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B965" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C965" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D965" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E965" s="2">
+        <v>2</v>
+      </c>
+      <c r="F965" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B966" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C966" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D966" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E966" s="2">
+        <v>2</v>
+      </c>
+      <c r="F966" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B967" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C967" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D967" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E967" s="2">
+        <v>2</v>
+      </c>
+      <c r="F967" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B968" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C968" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D968" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E968" s="2">
+        <v>2</v>
+      </c>
+      <c r="F968" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B969" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C969" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D969" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E969" s="2">
+        <v>2</v>
+      </c>
+      <c r="F969" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B970" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C970" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="D970" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="E970" s="2">
+        <v>2</v>
+      </c>
+      <c r="F970" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B971" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C971" s="0" t="inlineStr">
+        <is>
+          <t>eaug_justbecauseday</t>
+        </is>
+      </c>
+      <c r="D971" s="0" t="inlineStr">
+        <is>
+          <t>eaug_justbecauseday</t>
+        </is>
+      </c>
+      <c r="E971" s="2">
+        <v>2</v>
+      </c>
+      <c r="F971" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B972" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C972" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D972" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E972" s="2">
+        <v>2</v>
+      </c>
+      <c r="F972" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B973" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C973" s="0" t="inlineStr">
+        <is>
+          <t>esep_wifeappreciation_day</t>
+        </is>
+      </c>
+      <c r="D973" s="0" t="inlineStr">
+        <is>
+          <t>esep_wifeappreciation_day</t>
+        </is>
+      </c>
+      <c r="E973" s="2">
+        <v>2</v>
+      </c>
+      <c r="F973" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B974" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C974" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D974" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E974" s="2">
+        <v>2</v>
+      </c>
+      <c r="F974" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B975" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C975" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D975" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E975" s="2">
+        <v>2</v>
+      </c>
+      <c r="F975" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B976" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C976" s="0" t="inlineStr">
+        <is>
+          <t>justbecause</t>
+        </is>
+      </c>
+      <c r="D976" s="0" t="inlineStr">
+        <is>
+          <t>intouch_justbecause</t>
+        </is>
+      </c>
+      <c r="E976" s="2">
+        <v>2</v>
+      </c>
+      <c r="F976" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B977" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C977" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D977" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E977" s="2">
+        <v>2</v>
+      </c>
+      <c r="F977" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B978" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C978" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D978" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E978" s="2">
+        <v>2</v>
+      </c>
+      <c r="F978" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B979" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C979" s="0" t="inlineStr">
+        <is>
+          <t>balloons</t>
+        </is>
+      </c>
+      <c r="D979" s="0" t="inlineStr">
+        <is>
+          <t>birth_balloons</t>
+        </is>
+      </c>
+      <c r="E979" s="2">
+        <v>1</v>
+      </c>
+      <c r="F979" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B980" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C980" s="0" t="inlineStr">
+        <is>
+          <t>grandparents</t>
+        </is>
+      </c>
+      <c r="D980" s="0" t="inlineStr">
+        <is>
+          <t>birth_grandparents</t>
+        </is>
+      </c>
+      <c r="E980" s="2">
+        <v>1</v>
+      </c>
+      <c r="F980" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B981" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C981" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D981" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E981" s="2">
+        <v>1</v>
+      </c>
+      <c r="F981" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B982" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C982" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D982" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E982" s="2">
+        <v>1</v>
+      </c>
+      <c r="F982" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B983" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C983" s="0" t="inlineStr">
+        <is>
+          <t>eapr_easter_humor</t>
+        </is>
+      </c>
+      <c r="D983" s="0" t="inlineStr">
+        <is>
+          <t>eapr_easter_humor</t>
+        </is>
+      </c>
+      <c r="E983" s="2">
+        <v>1</v>
+      </c>
+      <c r="F983" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B984" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C984" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrelaxation_day</t>
+        </is>
+      </c>
+      <c r="D984" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrelaxation_day</t>
+        </is>
+      </c>
+      <c r="E984" s="2">
+        <v>1</v>
+      </c>
+      <c r="F984" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B985" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C985" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="D985" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="E985" s="2">
+        <v>1</v>
+      </c>
+      <c r="F985" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B986" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C986" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D986" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E986" s="2">
+        <v>1</v>
+      </c>
+      <c r="F986" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B987" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C987" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_birthday</t>
+        </is>
+      </c>
+      <c r="D987" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_birthday</t>
+        </is>
+      </c>
+      <c r="E987" s="2">
+        <v>1</v>
+      </c>
+      <c r="F987" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B988" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C988" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_wishes</t>
+        </is>
+      </c>
+      <c r="D988" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_wishes</t>
+        </is>
+      </c>
+      <c r="E988" s="2">
+        <v>1</v>
+      </c>
+      <c r="F988" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B989" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C989" s="0" t="inlineStr">
+        <is>
+          <t>enov_adventday</t>
+        </is>
+      </c>
+      <c r="D989" s="0" t="inlineStr">
+        <is>
+          <t>enov_adventday</t>
+        </is>
+      </c>
+      <c r="E989" s="2">
+        <v>1</v>
+      </c>
+      <c r="F989" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B990" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C990" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_specials</t>
+        </is>
+      </c>
+      <c r="D990" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_specials</t>
+        </is>
+      </c>
+      <c r="E990" s="2">
+        <v>1</v>
+      </c>
+      <c r="F990" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B991" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C991" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="D991" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="E991" s="2">
+        <v>1</v>
+      </c>
+      <c r="F991" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B992" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C992" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="D992" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="E992" s="2">
+        <v>1</v>
+      </c>
+      <c r="F992" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B993" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C993" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D993" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E993" s="2">
+        <v>1</v>
+      </c>
+      <c r="F993" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B994" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C994" s="0" t="inlineStr">
+        <is>
+          <t>sonsdaughter</t>
+        </is>
+      </c>
+      <c r="D994" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sonsdaughter</t>
+        </is>
+      </c>
+      <c r="E994" s="2">
+        <v>1</v>
+      </c>
+      <c r="F994" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B995" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C995" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D995" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E995" s="2">
+        <v>1</v>
+      </c>
+      <c r="F995" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B996" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C996" s="0" t="inlineStr">
+        <is>
+          <t>youcare</t>
+        </is>
+      </c>
+      <c r="D996" s="0" t="inlineStr">
+        <is>
+          <t>flwr_youcare</t>
+        </is>
+      </c>
+      <c r="E996" s="2">
+        <v>1</v>
+      </c>
+      <c r="F996" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B997" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C997" s="0" t="inlineStr">
+        <is>
+          <t>foryou</t>
+        </is>
+      </c>
+      <c r="D997" s="0" t="inlineStr">
+        <is>
+          <t>friend_foryou</t>
+        </is>
+      </c>
+      <c r="E997" s="2">
+        <v>1</v>
+      </c>
+      <c r="F997" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B998" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C998" s="0" t="inlineStr">
+        <is>
+          <t>friendsforever</t>
+        </is>
+      </c>
+      <c r="D998" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendsforever</t>
+        </is>
+      </c>
+      <c r="E998" s="2">
+        <v>1</v>
+      </c>
+      <c r="F998" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B999" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C999" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D999" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E999" s="2">
+        <v>1</v>
+      </c>
+      <c r="F999" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1000" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1000" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D1000" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E1000" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1000" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1001" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1001" s="0" t="inlineStr">
+        <is>
+          <t>midcrisis</t>
+        </is>
+      </c>
+      <c r="D1001" s="0" t="inlineStr">
+        <is>
+          <t>gen_midcrisis</t>
+        </is>
+      </c>
+      <c r="E1001" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1001" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1002" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1002" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D1002" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E1002" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1002" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1003" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1003" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D1003" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E1003" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1003" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1004" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1004" s="0" t="inlineStr">
+        <is>
+          <t>youarewelcome</t>
+        </is>
+      </c>
+      <c r="D1004" s="0" t="inlineStr">
+        <is>
+          <t>gen_youarewelcome</t>
+        </is>
+      </c>
+      <c r="E1004" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1004" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1005" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1005" s="0" t="inlineStr">
+        <is>
+          <t>poetry</t>
+        </is>
+      </c>
+      <c r="D1005" s="0" t="inlineStr">
+        <is>
+          <t>insp_poetry</t>
+        </is>
+      </c>
+      <c r="E1005" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1005" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1006" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1006" s="0" t="inlineStr">
+        <is>
+          <t>quotes</t>
+        </is>
+      </c>
+      <c r="D1006" s="0" t="inlineStr">
+        <is>
+          <t>insp_quotes</t>
+        </is>
+      </c>
+      <c r="E1006" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1006" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1007" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1007" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1007" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1007" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1007" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1008" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1008" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D1008" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E1008" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1008" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1009" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1009" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1009" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1009" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1009" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1010" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1010" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1010" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1010" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1010" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1011" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1011" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D1011" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E1011" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1011" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1012" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1012" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D1012" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E1012" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1012" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1013" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1013" s="0" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D1013" s="0" t="inlineStr">
+        <is>
+          <t>thank_congratulations</t>
+        </is>
+      </c>
+      <c r="E1013" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1013" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1014" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1014" s="0" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="D1014" s="0" t="inlineStr">
+        <is>
+          <t>thank_family</t>
+        </is>
+      </c>
+      <c r="E1014" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1014" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1015" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1015" s="0" t="inlineStr">
+        <is>
+          <t>stayintouch</t>
+        </is>
+      </c>
+      <c r="D1015" s="0" t="inlineStr">
+        <is>
+          <t>thank_stayintouch</t>
+        </is>
+      </c>
+      <c r="E1015" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1015" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1016" s="4"/>
+      <c r="C1016" s="4"/>
+      <c r="D1016" s="4"/>
+      <c r="E1016" s="5">
+        <v>773</v>
+      </c>
+      <c r="F1016" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -32721,12 +35650,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Whatsapp</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Text</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -32770,10 +35699,10 @@
         <v>1059</v>
       </c>
       <c r="C2" s="2">
+        <v>280</v>
+      </c>
+      <c r="D2" s="2">
         <v>404</v>
-      </c>
-      <c r="D2" s="2">
-        <v>280</v>
       </c>
       <c r="E2" s="2">
         <v>177</v>
@@ -32804,10 +35733,10 @@
         <v>999</v>
       </c>
       <c r="C3" s="2">
+        <v>266</v>
+      </c>
+      <c r="D3" s="2">
         <v>355</v>
-      </c>
-      <c r="D3" s="2">
-        <v>266</v>
       </c>
       <c r="E3" s="2">
         <v>174</v>
@@ -32838,10 +35767,10 @@
         <v>765</v>
       </c>
       <c r="C4" s="2">
+        <v>238</v>
+      </c>
+      <c r="D4" s="2">
         <v>242</v>
-      </c>
-      <c r="D4" s="2">
-        <v>238</v>
       </c>
       <c r="E4" s="2">
         <v>148</v>
@@ -32872,10 +35801,10 @@
         <v>805</v>
       </c>
       <c r="C5" s="2">
+        <v>268</v>
+      </c>
+      <c r="D5" s="2">
         <v>247</v>
-      </c>
-      <c r="D5" s="2">
-        <v>268</v>
       </c>
       <c r="E5" s="2">
         <v>160</v>
@@ -32906,10 +35835,10 @@
         <v>742</v>
       </c>
       <c r="C6" s="2">
+        <v>247</v>
+      </c>
+      <c r="D6" s="2">
         <v>224</v>
-      </c>
-      <c r="D6" s="2">
-        <v>247</v>
       </c>
       <c r="E6" s="2">
         <v>131</v>
@@ -32940,10 +35869,10 @@
         <v>738</v>
       </c>
       <c r="C7" s="2">
+        <v>245</v>
+      </c>
+      <c r="D7" s="2">
         <v>224</v>
-      </c>
-      <c r="D7" s="2">
-        <v>245</v>
       </c>
       <c r="E7" s="2">
         <v>163</v>
@@ -32974,10 +35903,10 @@
         <v>760</v>
       </c>
       <c r="C8" s="2">
+        <v>244</v>
+      </c>
+      <c r="D8" s="2">
         <v>218</v>
-      </c>
-      <c r="D8" s="2">
-        <v>244</v>
       </c>
       <c r="E8" s="2">
         <v>179</v>
@@ -33008,10 +35937,10 @@
         <v>839</v>
       </c>
       <c r="C9" s="2">
+        <v>292</v>
+      </c>
+      <c r="D9" s="2">
         <v>228</v>
-      </c>
-      <c r="D9" s="2">
-        <v>292</v>
       </c>
       <c r="E9" s="2">
         <v>161</v>
@@ -33042,10 +35971,10 @@
         <v>711</v>
       </c>
       <c r="C10" s="2">
+        <v>225</v>
+      </c>
+      <c r="D10" s="2">
         <v>210</v>
-      </c>
-      <c r="D10" s="2">
-        <v>225</v>
       </c>
       <c r="E10" s="2">
         <v>165</v>
@@ -33076,10 +36005,10 @@
         <v>949</v>
       </c>
       <c r="C11" s="2">
+        <v>290</v>
+      </c>
+      <c r="D11" s="2">
         <v>288</v>
-      </c>
-      <c r="D11" s="2">
-        <v>290</v>
       </c>
       <c r="E11" s="2">
         <v>200</v>
@@ -33110,10 +36039,10 @@
         <v>766</v>
       </c>
       <c r="C12" s="2">
+        <v>237</v>
+      </c>
+      <c r="D12" s="2">
         <v>226</v>
-      </c>
-      <c r="D12" s="2">
-        <v>237</v>
       </c>
       <c r="E12" s="2">
         <v>155</v>
@@ -33135,36 +36064,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>835</v>
+      </c>
+      <c r="C13" s="2">
+        <v>312</v>
+      </c>
+      <c r="D13" s="2">
+        <v>211</v>
+      </c>
+      <c r="E13" s="2">
+        <v>162</v>
+      </c>
+      <c r="F13" s="2">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2">
+        <v>41</v>
+      </c>
+      <c r="H13" s="2">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <v>9133</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2866</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2832</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1813</v>
-      </c>
-      <c r="F13" s="5">
-        <v>955</v>
-      </c>
-      <c r="G13" s="5">
-        <v>336</v>
-      </c>
-      <c r="H13" s="5">
-        <v>302</v>
-      </c>
-      <c r="I13" s="5">
+      <c r="B14" s="5">
+        <v>9968</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3144</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3077</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1975</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1043</v>
+      </c>
+      <c r="G14" s="5">
+        <v>377</v>
+      </c>
+      <c r="H14" s="5">
+        <v>323</v>
+      </c>
+      <c r="I14" s="5">
         <v>28</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J14" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -647,28 +647,56 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>808</v>
+      </c>
+      <c r="C14" s="2">
+        <v>548</v>
+      </c>
+      <c r="D14" s="2">
+        <v>260</v>
+      </c>
+      <c r="E14" s="2">
+        <v>710</v>
+      </c>
+      <c r="F14" s="2">
+        <v>98</v>
+      </c>
+      <c r="G14" s="2">
+        <v>253</v>
+      </c>
+      <c r="H14" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="5">
-        <v>9968</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6547</v>
-      </c>
-      <c r="D14" s="5">
-        <v>3421</v>
-      </c>
-      <c r="E14" s="5">
-        <v>9480</v>
-      </c>
-      <c r="F14" s="5">
-        <v>488</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="B15" s="5">
+        <v>10776</v>
+      </c>
+      <c r="C15" s="5">
+        <v>7095</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3681</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10190</v>
+      </c>
+      <c r="F15" s="5">
+        <v>586</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -689,8 +717,8 @@
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
     <col min="16" max="16" width="17" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
@@ -761,12 +789,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Family &amp; loved ones</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Pets</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -896,10 +924,10 @@
         <v>8</v>
       </c>
       <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2">
         <v>3</v>
-      </c>
-      <c r="N3" s="2">
-        <v>1</v>
       </c>
       <c r="O3" s="2">
         <v>1</v>
@@ -1018,10 +1046,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
+        <v>2</v>
+      </c>
+      <c r="N5" s="2">
         <v>5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>2</v>
       </c>
       <c r="O5" s="2">
         <v>1</v>
@@ -1079,10 +1107,10 @@
         <v>17</v>
       </c>
       <c r="M6" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N6" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2">
         <v>0</v>
@@ -1140,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
+        <v>2</v>
+      </c>
+      <c r="N7" s="2">
         <v>8</v>
-      </c>
-      <c r="N7" s="2">
-        <v>2</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
@@ -1201,10 +1229,10 @@
         <v>6</v>
       </c>
       <c r="M8" s="2">
+        <v>3</v>
+      </c>
+      <c r="N8" s="2">
         <v>6</v>
-      </c>
-      <c r="N8" s="2">
-        <v>3</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -1262,10 +1290,10 @@
         <v>39</v>
       </c>
       <c r="M9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N9" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2">
         <v>3</v>
@@ -1323,10 +1351,10 @@
         <v>4</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2">
         <v>5</v>
@@ -1384,10 +1412,10 @@
         <v>3</v>
       </c>
       <c r="M11" s="2">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2">
         <v>4</v>
-      </c>
-      <c r="N11" s="2">
-        <v>8</v>
       </c>
       <c r="O11" s="2">
         <v>3</v>
@@ -1506,10 +1534,10 @@
         <v>2</v>
       </c>
       <c r="M13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="2">
         <v>2</v>
@@ -1528,64 +1556,125 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>710</v>
+      </c>
+      <c r="C14" s="2">
+        <v>481</v>
+      </c>
+      <c r="D14" s="2">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2">
+        <v>55</v>
+      </c>
+      <c r="F14" s="2">
+        <v>38</v>
+      </c>
+      <c r="G14" s="2">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2">
+        <v>2</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5</v>
+      </c>
+      <c r="L14" s="2">
+        <v>3</v>
+      </c>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2">
+        <v>3</v>
+      </c>
+      <c r="S14" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="5">
-        <v>9480</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6267</v>
-      </c>
-      <c r="D14" s="5">
-        <v>897</v>
-      </c>
-      <c r="E14" s="5">
-        <v>571</v>
-      </c>
-      <c r="F14" s="5">
-        <v>454</v>
-      </c>
-      <c r="G14" s="5">
-        <v>376</v>
-      </c>
-      <c r="H14" s="5">
-        <v>226</v>
-      </c>
-      <c r="I14" s="5">
-        <v>179</v>
-      </c>
-      <c r="J14" s="5">
-        <v>171</v>
-      </c>
-      <c r="K14" s="5">
-        <v>113</v>
-      </c>
-      <c r="L14" s="5">
-        <v>82</v>
-      </c>
-      <c r="M14" s="5">
-        <v>35</v>
-      </c>
-      <c r="N14" s="5">
-        <v>33</v>
-      </c>
-      <c r="O14" s="5">
+      <c r="B15" s="5">
+        <v>10190</v>
+      </c>
+      <c r="C15" s="5">
+        <v>6748</v>
+      </c>
+      <c r="D15" s="5">
+        <v>949</v>
+      </c>
+      <c r="E15" s="5">
+        <v>626</v>
+      </c>
+      <c r="F15" s="5">
+        <v>492</v>
+      </c>
+      <c r="G15" s="5">
+        <v>406</v>
+      </c>
+      <c r="H15" s="5">
+        <v>244</v>
+      </c>
+      <c r="I15" s="5">
+        <v>191</v>
+      </c>
+      <c r="J15" s="5">
+        <v>173</v>
+      </c>
+      <c r="K15" s="5">
+        <v>118</v>
+      </c>
+      <c r="L15" s="5">
+        <v>85</v>
+      </c>
+      <c r="M15" s="5">
+        <v>38</v>
+      </c>
+      <c r="N15" s="5">
+        <v>36</v>
+      </c>
+      <c r="O15" s="5">
         <v>25</v>
       </c>
-      <c r="P14" s="5">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="5">
+      <c r="P15" s="5">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="5">
         <v>19</v>
       </c>
-      <c r="R14" s="5">
-        <v>9</v>
-      </c>
-      <c r="S14" s="5">
-        <v>3</v>
+      <c r="R15" s="5">
+        <v>12</v>
+      </c>
+      <c r="S15" s="5">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7319,6 +7408,508 @@
       </c>
       <c r="H182" s="4"/>
     </row>
+    <row r="183">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D183" s="2">
+        <v>334</v>
+      </c>
+      <c r="E183" s="2">
+        <v>147</v>
+      </c>
+      <c r="F183" s="2">
+        <v>481</v>
+      </c>
+      <c r="G183" s="3">
+        <v>0.6774647887323944</v>
+      </c>
+      <c r="H183" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D184" s="2">
+        <v>47</v>
+      </c>
+      <c r="E184" s="2">
+        <v>8</v>
+      </c>
+      <c r="F184" s="2">
+        <v>55</v>
+      </c>
+      <c r="G184" s="3">
+        <v>0.07746478873239436</v>
+      </c>
+      <c r="H184" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D185" s="2">
+        <v>36</v>
+      </c>
+      <c r="E185" s="2">
+        <v>16</v>
+      </c>
+      <c r="F185" s="2">
+        <v>52</v>
+      </c>
+      <c r="G185" s="3">
+        <v>0.07323943661971831</v>
+      </c>
+      <c r="H185" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D186" s="2">
+        <v>28</v>
+      </c>
+      <c r="E186" s="2">
+        <v>10</v>
+      </c>
+      <c r="F186" s="2">
+        <v>38</v>
+      </c>
+      <c r="G186" s="3">
+        <v>0.05352112676056338</v>
+      </c>
+      <c r="H186" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D187" s="2">
+        <v>9</v>
+      </c>
+      <c r="E187" s="2">
+        <v>21</v>
+      </c>
+      <c r="F187" s="2">
+        <v>30</v>
+      </c>
+      <c r="G187" s="3">
+        <v>0.04225352112676056</v>
+      </c>
+      <c r="H187" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D188" s="2">
+        <v>13</v>
+      </c>
+      <c r="E188" s="2">
+        <v>5</v>
+      </c>
+      <c r="F188" s="2">
+        <v>18</v>
+      </c>
+      <c r="G188" s="3">
+        <v>0.02535211267605634</v>
+      </c>
+      <c r="H188" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D189" s="2">
+        <v>12</v>
+      </c>
+      <c r="E189" s="2">
+        <v>0</v>
+      </c>
+      <c r="F189" s="2">
+        <v>12</v>
+      </c>
+      <c r="G189" s="3">
+        <v>0.016901408450704224</v>
+      </c>
+      <c r="H189" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D190" s="2">
+        <v>2</v>
+      </c>
+      <c r="E190" s="2">
+        <v>3</v>
+      </c>
+      <c r="F190" s="2">
+        <v>5</v>
+      </c>
+      <c r="G190" s="3">
+        <v>0.007042253521126761</v>
+      </c>
+      <c r="H190" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D191" s="2">
+        <v>4</v>
+      </c>
+      <c r="E191" s="2">
+        <v>1</v>
+      </c>
+      <c r="F191" s="2">
+        <v>5</v>
+      </c>
+      <c r="G191" s="3">
+        <v>0.007042253521126761</v>
+      </c>
+      <c r="H191" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D192" s="2">
+        <v>3</v>
+      </c>
+      <c r="E192" s="2">
+        <v>0</v>
+      </c>
+      <c r="F192" s="2">
+        <v>3</v>
+      </c>
+      <c r="G192" s="3">
+        <v>0.004225352112676056</v>
+      </c>
+      <c r="H192" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D193" s="2">
+        <v>3</v>
+      </c>
+      <c r="E193" s="2">
+        <v>0</v>
+      </c>
+      <c r="F193" s="2">
+        <v>3</v>
+      </c>
+      <c r="G193" s="3">
+        <v>0.004225352112676056</v>
+      </c>
+      <c r="H193" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D194" s="2">
+        <v>3</v>
+      </c>
+      <c r="E194" s="2">
+        <v>0</v>
+      </c>
+      <c r="F194" s="2">
+        <v>3</v>
+      </c>
+      <c r="G194" s="3">
+        <v>0.004225352112676056</v>
+      </c>
+      <c r="H194" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D195" s="2">
+        <v>2</v>
+      </c>
+      <c r="E195" s="2">
+        <v>0</v>
+      </c>
+      <c r="F195" s="2">
+        <v>2</v>
+      </c>
+      <c r="G195" s="3">
+        <v>0.0028169014084507044</v>
+      </c>
+      <c r="H195" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D196" s="2">
+        <v>1</v>
+      </c>
+      <c r="E196" s="2">
+        <v>1</v>
+      </c>
+      <c r="F196" s="2">
+        <v>2</v>
+      </c>
+      <c r="G196" s="3">
+        <v>0.0028169014084507044</v>
+      </c>
+      <c r="H196" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B197" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D197" s="2">
+        <v>1</v>
+      </c>
+      <c r="E197" s="2">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2">
+        <v>1</v>
+      </c>
+      <c r="G197" s="3">
+        <v>0.0014084507042253522</v>
+      </c>
+      <c r="H197" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-13</t>
+        </is>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="4"/>
+      <c r="D198" s="5">
+        <v>498</v>
+      </c>
+      <c r="E198" s="5">
+        <v>212</v>
+      </c>
+      <c r="F198" s="5">
+        <v>710</v>
+      </c>
+      <c r="G198" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H198" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -35617,6 +36208,2176 @@
         <v>773</v>
       </c>
       <c r="F1016" s="4"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1017" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1017" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1017" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1017" s="2">
+        <v>363</v>
+      </c>
+      <c r="F1017" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1018" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1018" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1018" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1018" s="2">
+        <v>32</v>
+      </c>
+      <c r="F1018" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1019" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1019" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1019" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1019" s="2">
+        <v>22</v>
+      </c>
+      <c r="F1019" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1020" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1020" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1020" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1020" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1020" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1021" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1021" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D1021" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E1021" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1021" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1022" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1022" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="D1022" s="0" t="inlineStr">
+        <is>
+          <t>eaug_internationalleft_handers_day</t>
+        </is>
+      </c>
+      <c r="E1022" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1022" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1023" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1023" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1023" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1023" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1023" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1024" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1024" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1024" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1024" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1024" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1025" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1025" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1025" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1025" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1025" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1026" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1026" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1026" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1026" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1026" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1027" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1027" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1027" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1027" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1027" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1028" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1028" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1028" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1028" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1028" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1029" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1029" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1029" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1029" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1029" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1030" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1030" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1030" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1030" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1030" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1031" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1031" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1031" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1031" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1031" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1032" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1032" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1032" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1032" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1032" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1033" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1033" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1033" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1033" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1033" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1034" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1034" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1034" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1034" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1034" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1035" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1035" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1035" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1035" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1035" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1036" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1036" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1036" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1036" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1036" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1037" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1037" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D1037" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E1037" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1037" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1038" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1038" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1038" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1038" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1038" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1039" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1039" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1039" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E1039" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1039" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1040" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1040" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1040" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1040" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1040" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1041" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1041" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1041" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1041" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1041" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1042" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1042" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_birthday</t>
+        </is>
+      </c>
+      <c r="D1042" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_birthday</t>
+        </is>
+      </c>
+      <c r="E1042" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1042" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1043" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1043" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1043" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1043" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1043" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1044" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1044" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1044" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1044" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1044" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1045" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1045" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1045" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1045" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1045" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1046" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1046" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1046" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1046" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1046" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1047" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1047" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D1047" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E1047" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1047" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1048" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1048" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D1048" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E1048" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1048" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1049" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1049" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1049" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E1049" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1049" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1050" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1050" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1050" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1050" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1050" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1051" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1051" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D1051" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E1051" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1051" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1052" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1052" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1052" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1052" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1052" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1053" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1053" s="0" t="inlineStr">
+        <is>
+          <t>onotheroccasions</t>
+        </is>
+      </c>
+      <c r="D1053" s="0" t="inlineStr">
+        <is>
+          <t>congrats_onotheroccasions</t>
+        </is>
+      </c>
+      <c r="E1053" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1053" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1054" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1054" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D1054" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E1054" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1054" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1055" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1055" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="D1055" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="E1055" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1055" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1056" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1056" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D1056" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E1056" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1056" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1057" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1057" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="D1057" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romanceday</t>
+        </is>
+      </c>
+      <c r="E1057" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1057" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1058" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1058" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="D1058" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="E1058" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1058" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1059" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1059" s="0" t="inlineStr">
+        <is>
+          <t>eoct_nationaliloveyou_day</t>
+        </is>
+      </c>
+      <c r="D1059" s="0" t="inlineStr">
+        <is>
+          <t>eoct_nationaliloveyou_day</t>
+        </is>
+      </c>
+      <c r="E1059" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1059" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1060" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1060" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D1060" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E1060" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1060" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1061" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1061" s="0" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D1061" s="0" t="inlineStr">
+        <is>
+          <t>insp_support</t>
+        </is>
+      </c>
+      <c r="E1061" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1061" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1062" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1062" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1062" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E1062" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1062" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1063" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1063" s="0" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D1063" s="0" t="inlineStr">
+        <is>
+          <t>thank_congratulations</t>
+        </is>
+      </c>
+      <c r="E1063" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1063" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1064" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1064" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D1064" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E1064" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1064" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1065" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1065" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1065" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1065" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1065" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1066" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1066" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D1066" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E1066" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1066" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1067" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1067" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D1067" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E1067" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1067" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1068" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1068" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D1068" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E1068" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1068" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1069" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1069" s="0" t="inlineStr">
+        <is>
+          <t>accolades</t>
+        </is>
+      </c>
+      <c r="D1069" s="0" t="inlineStr">
+        <is>
+          <t>bus_accolades</t>
+        </is>
+      </c>
+      <c r="E1069" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1069" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1070" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1070" s="0" t="inlineStr">
+        <is>
+          <t>apologies</t>
+        </is>
+      </c>
+      <c r="D1070" s="0" t="inlineStr">
+        <is>
+          <t>bus_apologies</t>
+        </is>
+      </c>
+      <c r="E1070" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1070" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1071" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1071" s="0" t="inlineStr">
+        <is>
+          <t>farewell</t>
+        </is>
+      </c>
+      <c r="D1071" s="0" t="inlineStr">
+        <is>
+          <t>bus_farewell</t>
+        </is>
+      </c>
+      <c r="E1071" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1071" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1072" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1072" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D1072" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E1072" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1072" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1073" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1073" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="D1073" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="E1073" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1073" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1074" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1074" s="0" t="inlineStr">
+        <is>
+          <t>efeb_lent</t>
+        </is>
+      </c>
+      <c r="D1074" s="0" t="inlineStr">
+        <is>
+          <t>efeb_lent</t>
+        </is>
+      </c>
+      <c r="E1074" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1074" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1075" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1075" s="0" t="inlineStr">
+        <is>
+          <t>emar_stjosephs_day</t>
+        </is>
+      </c>
+      <c r="D1075" s="0" t="inlineStr">
+        <is>
+          <t>emar_stjosephs_day</t>
+        </is>
+      </c>
+      <c r="E1075" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1075" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1076" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1076" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="D1076" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="E1076" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1076" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1077" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1077" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="D1077" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="E1077" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1077" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1078" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1078" s="0" t="inlineStr">
+        <is>
+          <t>esep_wifeappreciation_day</t>
+        </is>
+      </c>
+      <c r="D1078" s="0" t="inlineStr">
+        <is>
+          <t>esep_wifeappreciation_day</t>
+        </is>
+      </c>
+      <c r="E1078" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1078" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1079" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1079" s="0" t="inlineStr">
+        <is>
+          <t>sonsdaughter</t>
+        </is>
+      </c>
+      <c r="D1079" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sonsdaughter</t>
+        </is>
+      </c>
+      <c r="E1079" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1079" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1080" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1080" s="0" t="inlineStr">
+        <is>
+          <t>youcare</t>
+        </is>
+      </c>
+      <c r="D1080" s="0" t="inlineStr">
+        <is>
+          <t>flwr_youcare</t>
+        </is>
+      </c>
+      <c r="E1080" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1080" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1081" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1081" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D1081" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E1081" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1081" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1082" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1082" s="0" t="inlineStr">
+        <is>
+          <t>justpals</t>
+        </is>
+      </c>
+      <c r="D1082" s="0" t="inlineStr">
+        <is>
+          <t>friend_justpals</t>
+        </is>
+      </c>
+      <c r="E1082" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1082" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1083" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1083" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1083" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1083" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1083" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1084" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1084" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D1084" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E1084" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1084" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1085" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1085" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D1085" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E1085" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1085" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1086" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1086" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1086" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E1086" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1086" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1087" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1087" s="0" t="inlineStr">
+        <is>
+          <t>iamsorry</t>
+        </is>
+      </c>
+      <c r="D1087" s="0" t="inlineStr">
+        <is>
+          <t>love_iamsorry</t>
+        </is>
+      </c>
+      <c r="E1087" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1087" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1088" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1088" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D1088" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E1088" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1088" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1089" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1089" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D1089" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E1089" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1089" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1090" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1090" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D1090" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E1090" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1090" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1091" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C1091" s="0" t="inlineStr">
+        <is>
+          <t>hindi_rakshabandhan</t>
+        </is>
+      </c>
+      <c r="D1091" s="0" t="inlineStr">
+        <is>
+          <t>w_hindi_rakshabandhan</t>
+        </is>
+      </c>
+      <c r="E1091" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1091" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1092" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C1092" s="0" t="inlineStr">
+        <is>
+          <t>mandarin_birthday</t>
+        </is>
+      </c>
+      <c r="D1092" s="0" t="inlineStr">
+        <is>
+          <t>w_mandarin_birthday</t>
+        </is>
+      </c>
+      <c r="E1092" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1092" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1093" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1093" s="0" t="inlineStr">
+        <is>
+          <t>wed_foreachother</t>
+        </is>
+      </c>
+      <c r="D1093" s="0" t="inlineStr">
+        <is>
+          <t>wed_foreachother</t>
+        </is>
+      </c>
+      <c r="E1093" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1093" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1094" s="4"/>
+      <c r="C1094" s="4"/>
+      <c r="D1094" s="4"/>
+      <c r="E1094" s="5">
+        <v>710</v>
+      </c>
+      <c r="F1094" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -36098,36 +38859,70 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>808</v>
+      </c>
+      <c r="C14" s="2">
+        <v>296</v>
+      </c>
+      <c r="D14" s="2">
+        <v>216</v>
+      </c>
+      <c r="E14" s="2">
+        <v>156</v>
+      </c>
+      <c r="F14" s="2">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2">
+        <v>37</v>
+      </c>
+      <c r="H14" s="2">
+        <v>27</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="5">
-        <v>9968</v>
-      </c>
-      <c r="C14" s="5">
-        <v>3144</v>
-      </c>
-      <c r="D14" s="5">
-        <v>3077</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1975</v>
-      </c>
-      <c r="F14" s="5">
-        <v>1043</v>
-      </c>
-      <c r="G14" s="5">
-        <v>377</v>
-      </c>
-      <c r="H14" s="5">
-        <v>323</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="B15" s="5">
+        <v>10776</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3440</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3293</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2131</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1119</v>
+      </c>
+      <c r="G15" s="5">
+        <v>414</v>
+      </c>
+      <c r="H15" s="5">
+        <v>350</v>
+      </c>
+      <c r="I15" s="5">
         <v>28</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J15" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -675,28 +675,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>914</v>
+      </c>
+      <c r="C15" s="2">
+        <v>603</v>
+      </c>
+      <c r="D15" s="2">
+        <v>311</v>
+      </c>
+      <c r="E15" s="2">
+        <v>811</v>
+      </c>
+      <c r="F15" s="2">
+        <v>103</v>
+      </c>
+      <c r="G15" s="2">
+        <v>272</v>
+      </c>
+      <c r="H15" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="5">
-        <v>10776</v>
-      </c>
-      <c r="C15" s="5">
-        <v>7095</v>
-      </c>
-      <c r="D15" s="5">
-        <v>3681</v>
-      </c>
-      <c r="E15" s="5">
-        <v>10190</v>
-      </c>
-      <c r="F15" s="5">
-        <v>586</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="B16" s="5">
+        <v>11690</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7698</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3992</v>
+      </c>
+      <c r="E16" s="5">
+        <v>11001</v>
+      </c>
+      <c r="F16" s="5">
+        <v>689</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -717,8 +745,8 @@
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
     <col min="16" max="16" width="17" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
@@ -789,12 +817,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Pets</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Family &amp; loved ones</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -924,10 +952,10 @@
         <v>8</v>
       </c>
       <c r="M3" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2">
         <v>1</v>
@@ -1046,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O5" s="2">
         <v>1</v>
@@ -1107,10 +1135,10 @@
         <v>17</v>
       </c>
       <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2">
         <v>4</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1</v>
       </c>
       <c r="O6" s="2">
         <v>0</v>
@@ -1168,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N7" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
@@ -1229,10 +1257,10 @@
         <v>6</v>
       </c>
       <c r="M8" s="2">
+        <v>6</v>
+      </c>
+      <c r="N8" s="2">
         <v>3</v>
-      </c>
-      <c r="N8" s="2">
-        <v>6</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -1290,10 +1318,10 @@
         <v>39</v>
       </c>
       <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2">
         <v>4</v>
-      </c>
-      <c r="N9" s="2">
-        <v>1</v>
       </c>
       <c r="O9" s="2">
         <v>3</v>
@@ -1351,10 +1379,10 @@
         <v>4</v>
       </c>
       <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2">
         <v>4</v>
-      </c>
-      <c r="N10" s="2">
-        <v>1</v>
       </c>
       <c r="O10" s="2">
         <v>5</v>
@@ -1412,10 +1440,10 @@
         <v>3</v>
       </c>
       <c r="M11" s="2">
+        <v>4</v>
+      </c>
+      <c r="N11" s="2">
         <v>8</v>
-      </c>
-      <c r="N11" s="2">
-        <v>4</v>
       </c>
       <c r="O11" s="2">
         <v>3</v>
@@ -1534,10 +1562,10 @@
         <v>2</v>
       </c>
       <c r="M13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2">
         <v>2</v>
@@ -1595,10 +1623,10 @@
         <v>3</v>
       </c>
       <c r="M14" s="2">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2">
         <v>5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>1</v>
       </c>
       <c r="O14" s="2">
         <v>0</v>
@@ -1617,63 +1645,124 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>811</v>
+      </c>
+      <c r="C15" s="2">
+        <v>441</v>
+      </c>
+      <c r="D15" s="2">
+        <v>187</v>
+      </c>
+      <c r="E15" s="2">
+        <v>47</v>
+      </c>
+      <c r="F15" s="2">
+        <v>50</v>
+      </c>
+      <c r="G15" s="2">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2">
+        <v>28</v>
+      </c>
+      <c r="J15" s="2">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2">
+        <v>14</v>
+      </c>
+      <c r="L15" s="2">
+        <v>3</v>
+      </c>
+      <c r="M15" s="2">
+        <v>3</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2">
+        <v>3</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="5">
-        <v>10190</v>
-      </c>
-      <c r="C15" s="5">
-        <v>6748</v>
-      </c>
-      <c r="D15" s="5">
-        <v>949</v>
-      </c>
-      <c r="E15" s="5">
-        <v>626</v>
-      </c>
-      <c r="F15" s="5">
-        <v>492</v>
-      </c>
-      <c r="G15" s="5">
-        <v>406</v>
-      </c>
-      <c r="H15" s="5">
-        <v>244</v>
-      </c>
-      <c r="I15" s="5">
-        <v>191</v>
-      </c>
-      <c r="J15" s="5">
-        <v>173</v>
-      </c>
-      <c r="K15" s="5">
-        <v>118</v>
-      </c>
-      <c r="L15" s="5">
-        <v>85</v>
-      </c>
-      <c r="M15" s="5">
+      <c r="B16" s="5">
+        <v>11001</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7189</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1136</v>
+      </c>
+      <c r="E16" s="5">
+        <v>673</v>
+      </c>
+      <c r="F16" s="5">
+        <v>542</v>
+      </c>
+      <c r="G16" s="5">
+        <v>428</v>
+      </c>
+      <c r="H16" s="5">
+        <v>254</v>
+      </c>
+      <c r="I16" s="5">
+        <v>219</v>
+      </c>
+      <c r="J16" s="5">
+        <v>175</v>
+      </c>
+      <c r="K16" s="5">
+        <v>132</v>
+      </c>
+      <c r="L16" s="5">
+        <v>88</v>
+      </c>
+      <c r="M16" s="5">
+        <v>39</v>
+      </c>
+      <c r="N16" s="5">
         <v>38</v>
       </c>
-      <c r="N15" s="5">
-        <v>36</v>
-      </c>
-      <c r="O15" s="5">
+      <c r="O16" s="5">
         <v>25</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P16" s="5">
         <v>22</v>
       </c>
-      <c r="Q15" s="5">
-        <v>19</v>
-      </c>
-      <c r="R15" s="5">
-        <v>12</v>
-      </c>
-      <c r="S15" s="5">
+      <c r="Q16" s="5">
+        <v>20</v>
+      </c>
+      <c r="R16" s="5">
+        <v>15</v>
+      </c>
+      <c r="S16" s="5">
         <v>6</v>
       </c>
     </row>
@@ -7910,6 +7999,444 @@
       </c>
       <c r="H198" s="4"/>
     </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D199" s="2">
+        <v>302</v>
+      </c>
+      <c r="E199" s="2">
+        <v>139</v>
+      </c>
+      <c r="F199" s="2">
+        <v>441</v>
+      </c>
+      <c r="G199" s="3">
+        <v>0.5437731196054254</v>
+      </c>
+      <c r="H199" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D200" s="2">
+        <v>127</v>
+      </c>
+      <c r="E200" s="2">
+        <v>60</v>
+      </c>
+      <c r="F200" s="2">
+        <v>187</v>
+      </c>
+      <c r="G200" s="3">
+        <v>0.23057953144266338</v>
+      </c>
+      <c r="H200" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D201" s="2">
+        <v>41</v>
+      </c>
+      <c r="E201" s="2">
+        <v>9</v>
+      </c>
+      <c r="F201" s="2">
+        <v>50</v>
+      </c>
+      <c r="G201" s="3">
+        <v>0.06165228113440197</v>
+      </c>
+      <c r="H201" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D202" s="2">
+        <v>33</v>
+      </c>
+      <c r="E202" s="2">
+        <v>14</v>
+      </c>
+      <c r="F202" s="2">
+        <v>47</v>
+      </c>
+      <c r="G202" s="3">
+        <v>0.05795314426633785</v>
+      </c>
+      <c r="H202" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D203" s="2">
+        <v>22</v>
+      </c>
+      <c r="E203" s="2">
+        <v>6</v>
+      </c>
+      <c r="F203" s="2">
+        <v>28</v>
+      </c>
+      <c r="G203" s="3">
+        <v>0.0345252774352651</v>
+      </c>
+      <c r="H203" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D204" s="2">
+        <v>2</v>
+      </c>
+      <c r="E204" s="2">
+        <v>20</v>
+      </c>
+      <c r="F204" s="2">
+        <v>22</v>
+      </c>
+      <c r="G204" s="3">
+        <v>0.027127003699136867</v>
+      </c>
+      <c r="H204" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D205" s="2">
+        <v>10</v>
+      </c>
+      <c r="E205" s="2">
+        <v>4</v>
+      </c>
+      <c r="F205" s="2">
+        <v>14</v>
+      </c>
+      <c r="G205" s="3">
+        <v>0.01726263871763255</v>
+      </c>
+      <c r="H205" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D206" s="2">
+        <v>7</v>
+      </c>
+      <c r="E206" s="2">
+        <v>3</v>
+      </c>
+      <c r="F206" s="2">
+        <v>10</v>
+      </c>
+      <c r="G206" s="3">
+        <v>0.012330456226880395</v>
+      </c>
+      <c r="H206" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B207" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D207" s="2">
+        <v>3</v>
+      </c>
+      <c r="E207" s="2">
+        <v>0</v>
+      </c>
+      <c r="F207" s="2">
+        <v>3</v>
+      </c>
+      <c r="G207" s="3">
+        <v>0.0036991368680641184</v>
+      </c>
+      <c r="H207" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B208" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D208" s="2">
+        <v>1</v>
+      </c>
+      <c r="E208" s="2">
+        <v>2</v>
+      </c>
+      <c r="F208" s="2">
+        <v>3</v>
+      </c>
+      <c r="G208" s="3">
+        <v>0.0036991368680641184</v>
+      </c>
+      <c r="H208" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D209" s="2">
+        <v>2</v>
+      </c>
+      <c r="E209" s="2">
+        <v>1</v>
+      </c>
+      <c r="F209" s="2">
+        <v>3</v>
+      </c>
+      <c r="G209" s="3">
+        <v>0.0036991368680641184</v>
+      </c>
+      <c r="H209" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D210" s="2">
+        <v>1</v>
+      </c>
+      <c r="E210" s="2">
+        <v>1</v>
+      </c>
+      <c r="F210" s="2">
+        <v>2</v>
+      </c>
+      <c r="G210" s="3">
+        <v>0.002466091245376079</v>
+      </c>
+      <c r="H210" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B211" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D211" s="2">
+        <v>1</v>
+      </c>
+      <c r="E211" s="2">
+        <v>0</v>
+      </c>
+      <c r="F211" s="2">
+        <v>1</v>
+      </c>
+      <c r="G211" s="3">
+        <v>0.0012330456226880395</v>
+      </c>
+      <c r="H211" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-14</t>
+        </is>
+      </c>
+      <c r="B212" s="4"/>
+      <c r="C212" s="4"/>
+      <c r="D212" s="5">
+        <v>552</v>
+      </c>
+      <c r="E212" s="5">
+        <v>259</v>
+      </c>
+      <c r="F212" s="5">
+        <v>811</v>
+      </c>
+      <c r="G212" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H212" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -38378,6 +38905,2260 @@
         <v>710</v>
       </c>
       <c r="F1094" s="4"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1095" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1095" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1095" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1095" s="2">
+        <v>326</v>
+      </c>
+      <c r="F1095" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1096" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1096" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="D1096" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="E1096" s="2">
+        <v>114</v>
+      </c>
+      <c r="F1096" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1097" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1097" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1097" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1097" s="2">
+        <v>29</v>
+      </c>
+      <c r="F1097" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1098" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1098" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="D1098" s="0" t="inlineStr">
+        <is>
+          <t>eaug_creamsicleday</t>
+        </is>
+      </c>
+      <c r="E1098" s="2">
+        <v>24</v>
+      </c>
+      <c r="F1098" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1099" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1099" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="D1099" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="E1099" s="2">
+        <v>19</v>
+      </c>
+      <c r="F1099" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1100" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1100" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1100" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1100" s="2">
+        <v>19</v>
+      </c>
+      <c r="F1100" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1101" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1101" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1101" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1101" s="2">
+        <v>18</v>
+      </c>
+      <c r="F1101" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1102" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1102" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1102" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1102" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1102" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1103" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1103" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1103" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1103" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1103" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1104" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1104" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1104" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1104" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1104" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1105" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1105" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D1105" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E1105" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1105" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1106" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1106" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1106" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1106" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1106" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1107" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1107" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1107" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1107" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1107" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1108" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1108" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1108" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1108" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1108" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1109" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1109" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1109" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1109" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1109" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1110" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1110" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1110" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1110" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1110" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1111" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1111" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1111" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1111" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1111" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1112" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1112" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D1112" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E1112" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1112" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1113" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1113" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D1113" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E1113" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1113" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1114" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1114" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1114" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1114" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1114" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1115" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1115" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1115" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1115" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1115" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1116" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1116" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1116" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1116" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1116" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1117" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1117" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1117" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1117" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1117" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1118" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1118" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1118" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1118" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1118" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1119" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1119" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1119" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1119" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1119" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1120" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1120" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1120" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1120" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1120" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1121" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1121" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D1121" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E1121" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1121" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1122" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1122" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1122" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1122" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1122" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1123" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1123" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1123" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E1123" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1123" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1124" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1124" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1124" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1124" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1124" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1125" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1125" s="0" t="inlineStr">
+        <is>
+          <t>zodiac</t>
+        </is>
+      </c>
+      <c r="D1125" s="0" t="inlineStr">
+        <is>
+          <t>birth_zodiac</t>
+        </is>
+      </c>
+      <c r="E1125" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1125" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1126" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1126" s="0" t="inlineStr">
+        <is>
+          <t>eapr_goodfriday</t>
+        </is>
+      </c>
+      <c r="D1126" s="0" t="inlineStr">
+        <is>
+          <t>eapr_goodfriday</t>
+        </is>
+      </c>
+      <c r="E1126" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1126" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1127" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1127" s="0" t="inlineStr">
+        <is>
+          <t>enov_cappuccinoday</t>
+        </is>
+      </c>
+      <c r="D1127" s="0" t="inlineStr">
+        <is>
+          <t>enov_cappuccinoday</t>
+        </is>
+      </c>
+      <c r="E1127" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1127" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1128" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1128" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1128" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1128" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1128" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1129" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1129" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D1129" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E1129" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1129" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1130" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1130" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1130" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1130" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1130" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1131" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1131" s="0" t="inlineStr">
+        <is>
+          <t>atworketc</t>
+        </is>
+      </c>
+      <c r="D1131" s="0" t="inlineStr">
+        <is>
+          <t>bus_atworketc</t>
+        </is>
+      </c>
+      <c r="E1131" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1131" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1132" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1132" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1132" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1132" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1132" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1133" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1133" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D1133" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E1133" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1133" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1134" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1134" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D1134" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E1134" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1134" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1135" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1135" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D1135" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E1135" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1135" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1136" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1136" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrelaxation_day</t>
+        </is>
+      </c>
+      <c r="D1136" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrelaxation_day</t>
+        </is>
+      </c>
+      <c r="E1136" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1136" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1137" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1137" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_happy</t>
+        </is>
+      </c>
+      <c r="D1137" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_happy</t>
+        </is>
+      </c>
+      <c r="E1137" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1137" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1138" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1138" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D1138" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E1138" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1138" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1139" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1139" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D1139" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E1139" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1139" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1140" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1140" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1140" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1140" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1140" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1141" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1141" s="0" t="inlineStr">
+        <is>
+          <t>nameday</t>
+        </is>
+      </c>
+      <c r="D1141" s="0" t="inlineStr">
+        <is>
+          <t>gen_nameday</t>
+        </is>
+      </c>
+      <c r="E1141" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1141" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1142" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1142" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D1142" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E1142" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1142" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1143" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1143" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_quotes</t>
+        </is>
+      </c>
+      <c r="D1143" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_quotes</t>
+        </is>
+      </c>
+      <c r="E1143" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1143" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1144" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1144" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1144" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1144" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1144" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1145" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1145" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1145" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1145" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1145" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1146" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1146" s="0" t="inlineStr">
+        <is>
+          <t>wed_arndworld</t>
+        </is>
+      </c>
+      <c r="D1146" s="0" t="inlineStr">
+        <is>
+          <t>wed_arndworld</t>
+        </is>
+      </c>
+      <c r="E1146" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1146" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1147" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1147" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D1147" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E1147" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1147" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1148" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1148" s="0" t="inlineStr">
+        <is>
+          <t>collassociates</t>
+        </is>
+      </c>
+      <c r="D1148" s="0" t="inlineStr">
+        <is>
+          <t>birth_collassociates</t>
+        </is>
+      </c>
+      <c r="E1148" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1148" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1149" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1149" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D1149" s="0" t="inlineStr">
+        <is>
+          <t>bus_retirement</t>
+        </is>
+      </c>
+      <c r="E1149" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1149" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1150" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1150" s="0" t="inlineStr">
+        <is>
+          <t>businessandworkplace</t>
+        </is>
+      </c>
+      <c r="D1150" s="0" t="inlineStr">
+        <is>
+          <t>congrats_businessandworkplace</t>
+        </is>
+      </c>
+      <c r="E1150" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1150" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1151" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1151" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D1151" s="0" t="inlineStr">
+        <is>
+          <t>congrats_retirement</t>
+        </is>
+      </c>
+      <c r="E1151" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1151" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1152" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1152" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D1152" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E1152" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1152" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1153" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1153" s="0" t="inlineStr">
+        <is>
+          <t>eaug_lemonmeringue_pie_day</t>
+        </is>
+      </c>
+      <c r="D1153" s="0" t="inlineStr">
+        <is>
+          <t>eaug_lemonmeringue_pie_day</t>
+        </is>
+      </c>
+      <c r="E1153" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1153" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1154" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1154" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D1154" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E1154" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1154" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1155" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1155" s="0" t="inlineStr">
+        <is>
+          <t>edec_c_thankyou</t>
+        </is>
+      </c>
+      <c r="D1155" s="0" t="inlineStr">
+        <is>
+          <t>edec_c_thankyou</t>
+        </is>
+      </c>
+      <c r="E1155" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1155" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1156" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1156" s="0" t="inlineStr">
+        <is>
+          <t>edec_feastof_immaculate_conception</t>
+        </is>
+      </c>
+      <c r="D1156" s="0" t="inlineStr">
+        <is>
+          <t>edec_feastof_immaculate_conception</t>
+        </is>
+      </c>
+      <c r="E1156" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1156" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1157" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1157" s="0" t="inlineStr">
+        <is>
+          <t>ejan_danceday</t>
+        </is>
+      </c>
+      <c r="D1157" s="0" t="inlineStr">
+        <is>
+          <t>ejan_danceday</t>
+        </is>
+      </c>
+      <c r="E1157" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1157" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1158" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1158" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="D1158" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="E1158" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1158" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1159" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1159" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_missingu</t>
+        </is>
+      </c>
+      <c r="D1159" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_missingu</t>
+        </is>
+      </c>
+      <c r="E1159" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1159" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1160" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1160" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_thank</t>
+        </is>
+      </c>
+      <c r="D1160" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_thank</t>
+        </is>
+      </c>
+      <c r="E1160" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1160" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1161" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1161" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_thanku</t>
+        </is>
+      </c>
+      <c r="D1161" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_thanku</t>
+        </is>
+      </c>
+      <c r="E1161" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1161" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1162" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1162" s="0" t="inlineStr">
+        <is>
+          <t>familyoccasions</t>
+        </is>
+      </c>
+      <c r="D1162" s="0" t="inlineStr">
+        <is>
+          <t>fkt_familyoccasions</t>
+        </is>
+      </c>
+      <c r="E1162" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1162" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1163" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1163" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1163" s="0" t="inlineStr">
+        <is>
+          <t>flwr_love</t>
+        </is>
+      </c>
+      <c r="E1163" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1163" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1164" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1164" s="0" t="inlineStr">
+        <is>
+          <t>friendsforever</t>
+        </is>
+      </c>
+      <c r="D1164" s="0" t="inlineStr">
+        <is>
+          <t>friend_friendsforever</t>
+        </is>
+      </c>
+      <c r="E1164" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1164" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1165" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1165" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D1165" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E1165" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1165" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1166" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1166" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D1166" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E1166" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1166" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1167" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1167" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D1167" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E1167" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1167" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1168" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1168" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D1168" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E1168" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1168" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1169" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1169" s="0" t="inlineStr">
+        <is>
+          <t>angels</t>
+        </is>
+      </c>
+      <c r="D1169" s="0" t="inlineStr">
+        <is>
+          <t>insp_angels</t>
+        </is>
+      </c>
+      <c r="E1169" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1169" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1170" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1170" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1170" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1170" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1170" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1171" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1171" s="0" t="inlineStr">
+        <is>
+          <t>justbecause</t>
+        </is>
+      </c>
+      <c r="D1171" s="0" t="inlineStr">
+        <is>
+          <t>intouch_justbecause</t>
+        </is>
+      </c>
+      <c r="E1171" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1171" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1172" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1172" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1172" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1172" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1172" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1173" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1173" s="0" t="inlineStr">
+        <is>
+          <t>missing_forher</t>
+        </is>
+      </c>
+      <c r="D1173" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forher</t>
+        </is>
+      </c>
+      <c r="E1173" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1173" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1174" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1174" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D1174" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E1174" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1174" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1175" s="4"/>
+      <c r="C1175" s="4"/>
+      <c r="D1175" s="4"/>
+      <c r="E1175" s="5">
+        <v>811</v>
+      </c>
+      <c r="F1175" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -38893,36 +41674,70 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>914</v>
+      </c>
+      <c r="C15" s="2">
+        <v>233</v>
+      </c>
+      <c r="D15" s="2">
+        <v>363</v>
+      </c>
+      <c r="E15" s="2">
+        <v>183</v>
+      </c>
+      <c r="F15" s="2">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2">
+        <v>34</v>
+      </c>
+      <c r="H15" s="2">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="5">
-        <v>10776</v>
-      </c>
-      <c r="C15" s="5">
-        <v>3440</v>
-      </c>
-      <c r="D15" s="5">
-        <v>3293</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2131</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1119</v>
-      </c>
-      <c r="G15" s="5">
-        <v>414</v>
-      </c>
-      <c r="H15" s="5">
-        <v>350</v>
-      </c>
-      <c r="I15" s="5">
+      <c r="B16" s="5">
+        <v>11690</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3673</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3656</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2314</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1190</v>
+      </c>
+      <c r="G16" s="5">
+        <v>448</v>
+      </c>
+      <c r="H16" s="5">
+        <v>380</v>
+      </c>
+      <c r="I16" s="5">
         <v>28</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J16" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -703,28 +703,56 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>828</v>
+      </c>
+      <c r="C16" s="2">
+        <v>594</v>
+      </c>
+      <c r="D16" s="2">
+        <v>234</v>
+      </c>
+      <c r="E16" s="2">
+        <v>797</v>
+      </c>
+      <c r="F16" s="2">
+        <v>31</v>
+      </c>
+      <c r="G16" s="2">
+        <v>247</v>
+      </c>
+      <c r="H16" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="5">
-        <v>11690</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7698</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3992</v>
-      </c>
-      <c r="E16" s="5">
-        <v>11241</v>
-      </c>
-      <c r="F16" s="5">
-        <v>449</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="B17" s="5">
+        <v>12518</v>
+      </c>
+      <c r="C17" s="5">
+        <v>8292</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4226</v>
+      </c>
+      <c r="E17" s="5">
+        <v>12038</v>
+      </c>
+      <c r="F17" s="5">
+        <v>480</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -1706,64 +1734,125 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>797</v>
+      </c>
+      <c r="C16" s="2">
+        <v>485</v>
+      </c>
+      <c r="D16" s="2">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2">
+        <v>58</v>
+      </c>
+      <c r="F16" s="2">
+        <v>27</v>
+      </c>
+      <c r="G16" s="2">
+        <v>34</v>
+      </c>
+      <c r="H16" s="2">
+        <v>19</v>
+      </c>
+      <c r="I16" s="2">
+        <v>18</v>
+      </c>
+      <c r="J16" s="2">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2">
+        <v>7</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1</v>
+      </c>
+      <c r="S16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="5">
-        <v>11241</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7356</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1145</v>
-      </c>
-      <c r="E16" s="5">
-        <v>685</v>
-      </c>
-      <c r="F16" s="5">
-        <v>542</v>
-      </c>
-      <c r="G16" s="5">
-        <v>428</v>
-      </c>
-      <c r="H16" s="5">
-        <v>262</v>
-      </c>
-      <c r="I16" s="5">
-        <v>219</v>
-      </c>
-      <c r="J16" s="5">
-        <v>175</v>
-      </c>
-      <c r="K16" s="5">
-        <v>133</v>
-      </c>
-      <c r="L16" s="5">
-        <v>88</v>
-      </c>
-      <c r="M16" s="5">
-        <v>58</v>
-      </c>
-      <c r="N16" s="5">
-        <v>49</v>
-      </c>
-      <c r="O16" s="5">
-        <v>38</v>
-      </c>
-      <c r="P16" s="5">
+      <c r="B17" s="5">
+        <v>12038</v>
+      </c>
+      <c r="C17" s="5">
+        <v>7841</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1285</v>
+      </c>
+      <c r="E17" s="5">
+        <v>743</v>
+      </c>
+      <c r="F17" s="5">
+        <v>569</v>
+      </c>
+      <c r="G17" s="5">
+        <v>462</v>
+      </c>
+      <c r="H17" s="5">
+        <v>281</v>
+      </c>
+      <c r="I17" s="5">
+        <v>237</v>
+      </c>
+      <c r="J17" s="5">
+        <v>178</v>
+      </c>
+      <c r="K17" s="5">
+        <v>140</v>
+      </c>
+      <c r="L17" s="5">
+        <v>89</v>
+      </c>
+      <c r="M17" s="5">
+        <v>59</v>
+      </c>
+      <c r="N17" s="5">
+        <v>50</v>
+      </c>
+      <c r="O17" s="5">
+        <v>39</v>
+      </c>
+      <c r="P17" s="5">
         <v>22</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q17" s="5">
         <v>20</v>
       </c>
-      <c r="R16" s="5">
-        <v>15</v>
-      </c>
-      <c r="S16" s="5">
-        <v>6</v>
+      <c r="R17" s="5">
+        <v>16</v>
+      </c>
+      <c r="S17" s="5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8501,6 +8590,508 @@
       </c>
       <c r="H214" s="4"/>
     </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D215" s="2">
+        <v>363</v>
+      </c>
+      <c r="E215" s="2">
+        <v>122</v>
+      </c>
+      <c r="F215" s="2">
+        <v>485</v>
+      </c>
+      <c r="G215" s="3">
+        <v>0.6085319949811794</v>
+      </c>
+      <c r="H215" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D216" s="2">
+        <v>114</v>
+      </c>
+      <c r="E216" s="2">
+        <v>26</v>
+      </c>
+      <c r="F216" s="2">
+        <v>140</v>
+      </c>
+      <c r="G216" s="3">
+        <v>0.17565872020075282</v>
+      </c>
+      <c r="H216" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D217" s="2">
+        <v>48</v>
+      </c>
+      <c r="E217" s="2">
+        <v>10</v>
+      </c>
+      <c r="F217" s="2">
+        <v>58</v>
+      </c>
+      <c r="G217" s="3">
+        <v>0.07277289836888332</v>
+      </c>
+      <c r="H217" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D218" s="2">
+        <v>16</v>
+      </c>
+      <c r="E218" s="2">
+        <v>18</v>
+      </c>
+      <c r="F218" s="2">
+        <v>34</v>
+      </c>
+      <c r="G218" s="3">
+        <v>0.04265997490589712</v>
+      </c>
+      <c r="H218" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D219" s="2">
+        <v>19</v>
+      </c>
+      <c r="E219" s="2">
+        <v>8</v>
+      </c>
+      <c r="F219" s="2">
+        <v>27</v>
+      </c>
+      <c r="G219" s="3">
+        <v>0.033877038895859475</v>
+      </c>
+      <c r="H219" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D220" s="2">
+        <v>10</v>
+      </c>
+      <c r="E220" s="2">
+        <v>9</v>
+      </c>
+      <c r="F220" s="2">
+        <v>19</v>
+      </c>
+      <c r="G220" s="3">
+        <v>0.02383939774153074</v>
+      </c>
+      <c r="H220" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D221" s="2">
+        <v>15</v>
+      </c>
+      <c r="E221" s="2">
+        <v>3</v>
+      </c>
+      <c r="F221" s="2">
+        <v>18</v>
+      </c>
+      <c r="G221" s="3">
+        <v>0.02258469259723965</v>
+      </c>
+      <c r="H221" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D222" s="2">
+        <v>3</v>
+      </c>
+      <c r="E222" s="2">
+        <v>4</v>
+      </c>
+      <c r="F222" s="2">
+        <v>7</v>
+      </c>
+      <c r="G222" s="3">
+        <v>0.00878293601003764</v>
+      </c>
+      <c r="H222" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D223" s="2">
+        <v>2</v>
+      </c>
+      <c r="E223" s="2">
+        <v>1</v>
+      </c>
+      <c r="F223" s="2">
+        <v>3</v>
+      </c>
+      <c r="G223" s="3">
+        <v>0.0037641154328732747</v>
+      </c>
+      <c r="H223" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D224" s="2">
+        <v>1</v>
+      </c>
+      <c r="E224" s="2">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2">
+        <v>1</v>
+      </c>
+      <c r="G224" s="3">
+        <v>0.0012547051442910915</v>
+      </c>
+      <c r="H224" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D225" s="2">
+        <v>1</v>
+      </c>
+      <c r="E225" s="2">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2">
+        <v>1</v>
+      </c>
+      <c r="G225" s="3">
+        <v>0.0012547051442910915</v>
+      </c>
+      <c r="H225" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D226" s="2">
+        <v>1</v>
+      </c>
+      <c r="E226" s="2">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2">
+        <v>1</v>
+      </c>
+      <c r="G226" s="3">
+        <v>0.0012547051442910915</v>
+      </c>
+      <c r="H226" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D227" s="2">
+        <v>0</v>
+      </c>
+      <c r="E227" s="2">
+        <v>1</v>
+      </c>
+      <c r="F227" s="2">
+        <v>1</v>
+      </c>
+      <c r="G227" s="3">
+        <v>0.0012547051442910915</v>
+      </c>
+      <c r="H227" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B228" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D228" s="2">
+        <v>0</v>
+      </c>
+      <c r="E228" s="2">
+        <v>1</v>
+      </c>
+      <c r="F228" s="2">
+        <v>1</v>
+      </c>
+      <c r="G228" s="3">
+        <v>0.0012547051442910915</v>
+      </c>
+      <c r="H228" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B229" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D229" s="2">
+        <v>1</v>
+      </c>
+      <c r="E229" s="2">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2">
+        <v>1</v>
+      </c>
+      <c r="G229" s="3">
+        <v>0.0012547051442910915</v>
+      </c>
+      <c r="H229" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-15</t>
+        </is>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="5">
+        <v>594</v>
+      </c>
+      <c r="E230" s="5">
+        <v>203</v>
+      </c>
+      <c r="F230" s="5">
+        <v>797</v>
+      </c>
+      <c r="G230" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H230" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -41391,6 +41982,2344 @@
         <v>884</v>
       </c>
       <c r="F1181" s="4"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1182" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1182" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1182" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1182" s="2">
+        <v>388</v>
+      </c>
+      <c r="F1182" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1183" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1183" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="D1183" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="E1183" s="2">
+        <v>62</v>
+      </c>
+      <c r="F1183" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1184" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1184" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1184" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1184" s="2">
+        <v>37</v>
+      </c>
+      <c r="F1184" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1185" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1185" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrelaxation_day</t>
+        </is>
+      </c>
+      <c r="D1185" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrelaxation_day</t>
+        </is>
+      </c>
+      <c r="E1185" s="2">
+        <v>29</v>
+      </c>
+      <c r="F1185" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1186" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1186" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1186" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1186" s="2">
+        <v>17</v>
+      </c>
+      <c r="F1186" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1187" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1187" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1187" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1187" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1187" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1188" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1188" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1188" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1188" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1188" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1189" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1189" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1189" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1189" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1189" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1190" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1190" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1190" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1190" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1190" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1191" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1191" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1191" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1191" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1191" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1192" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1192" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1192" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1192" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1192" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1193" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1193" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1193" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1193" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1193" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1194" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1194" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1194" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1194" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1194" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1195" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1195" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1195" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1195" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1195" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1196" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1196" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1196" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1196" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1196" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1197" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1197" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1197" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1197" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1197" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1198" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1198" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1198" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1198" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1198" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1199" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1199" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="D1199" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="E1199" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1199" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1200" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1200" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D1200" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E1200" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1200" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1201" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1201" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1201" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1201" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1201" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1202" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1202" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1202" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1202" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1202" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1203" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1203" s="0" t="inlineStr">
+        <is>
+          <t>eaug_lemonmeringue_pie_day</t>
+        </is>
+      </c>
+      <c r="D1203" s="0" t="inlineStr">
+        <is>
+          <t>eaug_lemonmeringue_pie_day</t>
+        </is>
+      </c>
+      <c r="E1203" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1203" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1204" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1204" s="0" t="inlineStr">
+        <is>
+          <t>nameday</t>
+        </is>
+      </c>
+      <c r="D1204" s="0" t="inlineStr">
+        <is>
+          <t>gen_nameday</t>
+        </is>
+      </c>
+      <c r="E1204" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1204" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1205" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1205" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1205" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1205" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1205" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1206" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1206" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1206" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1206" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1206" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1207" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1207" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D1207" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E1207" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1207" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1208" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1208" s="0" t="inlineStr">
+        <is>
+          <t>esep_trueloveforeverday</t>
+        </is>
+      </c>
+      <c r="D1208" s="0" t="inlineStr">
+        <is>
+          <t>esep_trueloveforeverday</t>
+        </is>
+      </c>
+      <c r="E1208" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1208" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1209" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1209" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1209" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1209" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1209" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1210" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1210" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D1210" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E1210" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1210" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1211" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1211" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1211" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1211" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1211" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1212" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1212" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="D1212" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="E1212" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1212" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1213" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1213" s="0" t="inlineStr">
+        <is>
+          <t>edec_feastof_immaculate_conception</t>
+        </is>
+      </c>
+      <c r="D1213" s="0" t="inlineStr">
+        <is>
+          <t>edec_feastof_immaculate_conception</t>
+        </is>
+      </c>
+      <c r="E1213" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1213" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1214" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1214" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_happy</t>
+        </is>
+      </c>
+      <c r="D1214" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_happy</t>
+        </is>
+      </c>
+      <c r="E1214" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1214" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1215" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1215" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D1215" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E1215" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1215" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1216" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1216" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1216" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1216" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1216" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1217" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1217" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D1217" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E1217" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1217" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1218" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1218" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1218" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1218" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1218" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1219" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1219" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1219" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1219" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1219" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1220" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1220" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D1220" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E1220" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1220" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1221" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1221" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D1221" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E1221" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1221" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1222" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1222" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrum_day</t>
+        </is>
+      </c>
+      <c r="D1222" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrum_day</t>
+        </is>
+      </c>
+      <c r="E1222" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1222" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1223" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1223" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="D1223" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="E1223" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1223" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1224" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1224" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_fnd</t>
+        </is>
+      </c>
+      <c r="D1224" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_fnd</t>
+        </is>
+      </c>
+      <c r="E1224" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1224" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1225" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1225" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D1225" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E1225" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1225" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1226" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1226" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D1226" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E1226" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1226" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1227" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1227" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1227" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1227" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1227" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1228" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1228" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1228" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E1228" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1228" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1229" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1229" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1229" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1229" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1229" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1230" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1230" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D1230" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E1230" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1230" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1231" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1231" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1231" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1231" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1231" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1232" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1232" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D1232" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E1232" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1232" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1233" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1233" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D1233" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E1233" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1233" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1234" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1234" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D1234" s="0" t="inlineStr">
+        <is>
+          <t>bus_retirement</t>
+        </is>
+      </c>
+      <c r="E1234" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1234" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1235" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1235" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D1235" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E1235" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1235" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1236" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1236" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D1236" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E1236" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1236" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1237" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1237" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="D1237" s="0" t="inlineStr">
+        <is>
+          <t>eaug_flwrmonthaug</t>
+        </is>
+      </c>
+      <c r="E1237" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1237" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1238" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1238" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="D1238" s="0" t="inlineStr">
+        <is>
+          <t>ejul_livebetterday</t>
+        </is>
+      </c>
+      <c r="E1238" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1238" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1239" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1239" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_birthday</t>
+        </is>
+      </c>
+      <c r="D1239" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_birthday</t>
+        </is>
+      </c>
+      <c r="E1239" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1239" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1240" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1240" s="0" t="inlineStr">
+        <is>
+          <t>emar_mothersdayuk</t>
+        </is>
+      </c>
+      <c r="D1240" s="0" t="inlineStr">
+        <is>
+          <t>emar_mothersdayuk</t>
+        </is>
+      </c>
+      <c r="E1240" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1240" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1241" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1241" s="0" t="inlineStr">
+        <is>
+          <t>emar_rollercoaster_day</t>
+        </is>
+      </c>
+      <c r="D1241" s="0" t="inlineStr">
+        <is>
+          <t>emar_rollercoaster_day</t>
+        </is>
+      </c>
+      <c r="E1241" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1241" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1242" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1242" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_friends</t>
+        </is>
+      </c>
+      <c r="D1242" s="0" t="inlineStr">
+        <is>
+          <t>emay_mothersday_friends</t>
+        </is>
+      </c>
+      <c r="E1242" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1242" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1243" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1243" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_romance</t>
+        </is>
+      </c>
+      <c r="D1243" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_romance</t>
+        </is>
+      </c>
+      <c r="E1243" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1243" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1244" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1244" s="0" t="inlineStr">
+        <is>
+          <t>eoct_yomkippur</t>
+        </is>
+      </c>
+      <c r="D1244" s="0" t="inlineStr">
+        <is>
+          <t>eoct_yomkippur</t>
+        </is>
+      </c>
+      <c r="E1244" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1244" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1245" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1245" s="0" t="inlineStr">
+        <is>
+          <t>esep_beerlovers_day</t>
+        </is>
+      </c>
+      <c r="D1245" s="0" t="inlineStr">
+        <is>
+          <t>esep_beerlovers_day</t>
+        </is>
+      </c>
+      <c r="E1245" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1245" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1246" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1246" s="0" t="inlineStr">
+        <is>
+          <t>esep_durgapuja_blessings</t>
+        </is>
+      </c>
+      <c r="D1246" s="0" t="inlineStr">
+        <is>
+          <t>esep_durgapuja_blessings</t>
+        </is>
+      </c>
+      <c r="E1246" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1246" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1247" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1247" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="D1247" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="E1247" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1247" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1248" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1248" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D1248" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E1248" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1248" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1249" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1249" s="0" t="inlineStr">
+        <is>
+          <t>youcare</t>
+        </is>
+      </c>
+      <c r="D1249" s="0" t="inlineStr">
+        <is>
+          <t>flwr_youcare</t>
+        </is>
+      </c>
+      <c r="E1249" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1249" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1250" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1250" s="0" t="inlineStr">
+        <is>
+          <t>foryou</t>
+        </is>
+      </c>
+      <c r="D1250" s="0" t="inlineStr">
+        <is>
+          <t>friend_foryou</t>
+        </is>
+      </c>
+      <c r="E1250" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1250" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1251" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1251" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1251" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1251" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1251" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1252" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1252" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="D1252" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="E1252" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1252" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1253" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1253" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1253" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1253" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1253" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1254" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1254" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D1254" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E1254" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1254" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1255" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1255" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D1255" s="0" t="inlineStr">
+        <is>
+          <t>love_cute</t>
+        </is>
+      </c>
+      <c r="E1255" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1255" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1256" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1256" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D1256" s="0" t="inlineStr">
+        <is>
+          <t>love_hugs</t>
+        </is>
+      </c>
+      <c r="E1256" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1256" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1257" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1257" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1257" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1257" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1257" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1258" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1258" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="D1258" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="E1258" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1258" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1259" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1259" s="0" t="inlineStr">
+        <is>
+          <t>missing_forher</t>
+        </is>
+      </c>
+      <c r="D1259" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forher</t>
+        </is>
+      </c>
+      <c r="E1259" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1259" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1260" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1260" s="0" t="inlineStr">
+        <is>
+          <t>thinkingyou</t>
+        </is>
+      </c>
+      <c r="D1260" s="0" t="inlineStr">
+        <is>
+          <t>love_thinkingyou</t>
+        </is>
+      </c>
+      <c r="E1260" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1260" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1261" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1261" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D1261" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E1261" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1261" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1262" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1262" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1262" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E1262" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1262" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1263" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1263" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D1263" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E1263" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1263" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1264" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1264" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1264" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1264" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1264" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1265" s="4"/>
+      <c r="C1265" s="4"/>
+      <c r="D1265" s="4"/>
+      <c r="E1265" s="5">
+        <v>797</v>
+      </c>
+      <c r="F1265" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -41940,36 +44869,70 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>828</v>
+      </c>
+      <c r="C16" s="2">
+        <v>249</v>
+      </c>
+      <c r="D16" s="2">
+        <v>266</v>
+      </c>
+      <c r="E16" s="2">
+        <v>208</v>
+      </c>
+      <c r="F16" s="2">
+        <v>61</v>
+      </c>
+      <c r="G16" s="2">
+        <v>28</v>
+      </c>
+      <c r="H16" s="2">
+        <v>16</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="5">
-        <v>11690</v>
-      </c>
-      <c r="C16" s="5">
-        <v>3673</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3656</v>
-      </c>
-      <c r="E16" s="5">
-        <v>2314</v>
-      </c>
-      <c r="F16" s="5">
-        <v>1190</v>
-      </c>
-      <c r="G16" s="5">
-        <v>448</v>
-      </c>
-      <c r="H16" s="5">
-        <v>380</v>
-      </c>
-      <c r="I16" s="5">
+      <c r="B17" s="5">
+        <v>12518</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3922</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3922</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2522</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1251</v>
+      </c>
+      <c r="G17" s="5">
+        <v>476</v>
+      </c>
+      <c r="H17" s="5">
+        <v>396</v>
+      </c>
+      <c r="I17" s="5">
         <v>28</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J17" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -731,28 +731,56 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>761</v>
+      </c>
+      <c r="C17" s="2">
+        <v>518</v>
+      </c>
+      <c r="D17" s="2">
+        <v>243</v>
+      </c>
+      <c r="E17" s="2">
+        <v>720</v>
+      </c>
+      <c r="F17" s="2">
+        <v>41</v>
+      </c>
+      <c r="G17" s="2">
+        <v>263</v>
+      </c>
+      <c r="H17" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="5">
-        <v>12518</v>
-      </c>
-      <c r="C17" s="5">
-        <v>8292</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4226</v>
-      </c>
-      <c r="E17" s="5">
-        <v>12038</v>
-      </c>
-      <c r="F17" s="5">
-        <v>480</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="B18" s="5">
+        <v>13279</v>
+      </c>
+      <c r="C18" s="5">
+        <v>8810</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4469</v>
+      </c>
+      <c r="E18" s="5">
+        <v>12758</v>
+      </c>
+      <c r="F18" s="5">
+        <v>521</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -776,8 +804,8 @@
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
     <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
@@ -860,12 +888,12 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>World languages</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Keeping in touch</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -928,10 +956,10 @@
         <v>3</v>
       </c>
       <c r="P2" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R2" s="2">
         <v>2</v>
@@ -989,10 +1017,10 @@
         <v>1</v>
       </c>
       <c r="P3" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="2">
         <v>10</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>2</v>
       </c>
       <c r="R3" s="2">
         <v>0</v>
@@ -1111,10 +1139,10 @@
         <v>2</v>
       </c>
       <c r="P5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="2">
         <v>0</v>
@@ -1172,10 +1200,10 @@
         <v>4</v>
       </c>
       <c r="P6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2">
         <v>2</v>
@@ -1233,10 +1261,10 @@
         <v>2</v>
       </c>
       <c r="P7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="2">
         <v>3</v>
@@ -1416,10 +1444,10 @@
         <v>4</v>
       </c>
       <c r="P10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2">
         <v>0</v>
@@ -1477,10 +1505,10 @@
         <v>8</v>
       </c>
       <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>2</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -1538,10 +1566,10 @@
         <v>1</v>
       </c>
       <c r="P12" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2">
         <v>0</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>6</v>
       </c>
       <c r="R12" s="2">
         <v>0</v>
@@ -1599,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="P13" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="2">
         <v>3</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>2</v>
       </c>
       <c r="R13" s="2">
         <v>0</v>
@@ -1660,10 +1688,10 @@
         <v>5</v>
       </c>
       <c r="P14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" s="2">
         <v>3</v>
@@ -1721,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2">
         <v>0</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>1</v>
       </c>
       <c r="R15" s="2">
         <v>3</v>
@@ -1795,64 +1823,125 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>720</v>
+      </c>
+      <c r="C17" s="2">
+        <v>482</v>
+      </c>
+      <c r="D17" s="2">
+        <v>36</v>
+      </c>
+      <c r="E17" s="2">
+        <v>56</v>
+      </c>
+      <c r="F17" s="2">
+        <v>46</v>
+      </c>
+      <c r="G17" s="2">
+        <v>23</v>
+      </c>
+      <c r="H17" s="2">
+        <v>19</v>
+      </c>
+      <c r="I17" s="2">
+        <v>14</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="K17" s="2">
+        <v>17</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2">
+        <v>4</v>
+      </c>
+      <c r="N17" s="2">
+        <v>12</v>
+      </c>
+      <c r="O17" s="2">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2">
+        <v>1</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="5">
-        <v>12038</v>
-      </c>
-      <c r="C17" s="5">
-        <v>7841</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1285</v>
-      </c>
-      <c r="E17" s="5">
-        <v>743</v>
-      </c>
-      <c r="F17" s="5">
-        <v>569</v>
-      </c>
-      <c r="G17" s="5">
-        <v>462</v>
-      </c>
-      <c r="H17" s="5">
-        <v>281</v>
-      </c>
-      <c r="I17" s="5">
-        <v>237</v>
-      </c>
-      <c r="J17" s="5">
-        <v>178</v>
-      </c>
-      <c r="K17" s="5">
-        <v>140</v>
-      </c>
-      <c r="L17" s="5">
-        <v>89</v>
-      </c>
-      <c r="M17" s="5">
-        <v>59</v>
-      </c>
-      <c r="N17" s="5">
-        <v>50</v>
-      </c>
-      <c r="O17" s="5">
-        <v>39</v>
-      </c>
-      <c r="P17" s="5">
+      <c r="B18" s="5">
+        <v>12758</v>
+      </c>
+      <c r="C18" s="5">
+        <v>8323</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1321</v>
+      </c>
+      <c r="E18" s="5">
+        <v>799</v>
+      </c>
+      <c r="F18" s="5">
+        <v>615</v>
+      </c>
+      <c r="G18" s="5">
+        <v>485</v>
+      </c>
+      <c r="H18" s="5">
+        <v>300</v>
+      </c>
+      <c r="I18" s="5">
+        <v>251</v>
+      </c>
+      <c r="J18" s="5">
+        <v>181</v>
+      </c>
+      <c r="K18" s="5">
+        <v>157</v>
+      </c>
+      <c r="L18" s="5">
+        <v>90</v>
+      </c>
+      <c r="M18" s="5">
+        <v>63</v>
+      </c>
+      <c r="N18" s="5">
+        <v>62</v>
+      </c>
+      <c r="O18" s="5">
+        <v>40</v>
+      </c>
+      <c r="P18" s="5">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="5">
         <v>22</v>
       </c>
-      <c r="Q17" s="5">
-        <v>20</v>
-      </c>
-      <c r="R17" s="5">
-        <v>16</v>
-      </c>
-      <c r="S17" s="5">
-        <v>7</v>
+      <c r="R18" s="5">
+        <v>17</v>
+      </c>
+      <c r="S18" s="5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9092,6 +9181,540 @@
       </c>
       <c r="H230" s="4"/>
     </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D231" s="2">
+        <v>352</v>
+      </c>
+      <c r="E231" s="2">
+        <v>130</v>
+      </c>
+      <c r="F231" s="2">
+        <v>482</v>
+      </c>
+      <c r="G231" s="3">
+        <v>0.6694444444444444</v>
+      </c>
+      <c r="H231" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D232" s="2">
+        <v>43</v>
+      </c>
+      <c r="E232" s="2">
+        <v>13</v>
+      </c>
+      <c r="F232" s="2">
+        <v>56</v>
+      </c>
+      <c r="G232" s="3">
+        <v>0.07777777777777778</v>
+      </c>
+      <c r="H232" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D233" s="2">
+        <v>34</v>
+      </c>
+      <c r="E233" s="2">
+        <v>12</v>
+      </c>
+      <c r="F233" s="2">
+        <v>46</v>
+      </c>
+      <c r="G233" s="3">
+        <v>0.06388888888888888</v>
+      </c>
+      <c r="H233" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B234" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D234" s="2">
+        <v>24</v>
+      </c>
+      <c r="E234" s="2">
+        <v>12</v>
+      </c>
+      <c r="F234" s="2">
+        <v>36</v>
+      </c>
+      <c r="G234" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H234" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D235" s="2">
+        <v>6</v>
+      </c>
+      <c r="E235" s="2">
+        <v>17</v>
+      </c>
+      <c r="F235" s="2">
+        <v>23</v>
+      </c>
+      <c r="G235" s="3">
+        <v>0.03194444444444444</v>
+      </c>
+      <c r="H235" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D236" s="2">
+        <v>15</v>
+      </c>
+      <c r="E236" s="2">
+        <v>4</v>
+      </c>
+      <c r="F236" s="2">
+        <v>19</v>
+      </c>
+      <c r="G236" s="3">
+        <v>0.02638888888888889</v>
+      </c>
+      <c r="H236" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D237" s="2">
+        <v>12</v>
+      </c>
+      <c r="E237" s="2">
+        <v>5</v>
+      </c>
+      <c r="F237" s="2">
+        <v>17</v>
+      </c>
+      <c r="G237" s="3">
+        <v>0.02361111111111111</v>
+      </c>
+      <c r="H237" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B238" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D238" s="2">
+        <v>12</v>
+      </c>
+      <c r="E238" s="2">
+        <v>2</v>
+      </c>
+      <c r="F238" s="2">
+        <v>14</v>
+      </c>
+      <c r="G238" s="3">
+        <v>0.019444444444444445</v>
+      </c>
+      <c r="H238" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B239" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D239" s="2">
+        <v>12</v>
+      </c>
+      <c r="E239" s="2">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2">
+        <v>12</v>
+      </c>
+      <c r="G239" s="3">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="H239" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B240" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D240" s="2">
+        <v>2</v>
+      </c>
+      <c r="E240" s="2">
+        <v>2</v>
+      </c>
+      <c r="F240" s="2">
+        <v>4</v>
+      </c>
+      <c r="G240" s="3">
+        <v>0.005555555555555556</v>
+      </c>
+      <c r="H240" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D241" s="2">
+        <v>2</v>
+      </c>
+      <c r="E241" s="2">
+        <v>2</v>
+      </c>
+      <c r="F241" s="2">
+        <v>4</v>
+      </c>
+      <c r="G241" s="3">
+        <v>0.005555555555555556</v>
+      </c>
+      <c r="H241" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B242" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D242" s="2">
+        <v>2</v>
+      </c>
+      <c r="E242" s="2">
+        <v>1</v>
+      </c>
+      <c r="F242" s="2">
+        <v>3</v>
+      </c>
+      <c r="G242" s="3">
+        <v>0.004166666666666667</v>
+      </c>
+      <c r="H242" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B243" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D243" s="2">
+        <v>0</v>
+      </c>
+      <c r="E243" s="2">
+        <v>1</v>
+      </c>
+      <c r="F243" s="2">
+        <v>1</v>
+      </c>
+      <c r="G243" s="3">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="H243" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D244" s="2">
+        <v>1</v>
+      </c>
+      <c r="E244" s="2">
+        <v>0</v>
+      </c>
+      <c r="F244" s="2">
+        <v>1</v>
+      </c>
+      <c r="G244" s="3">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="H244" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D245" s="2">
+        <v>0</v>
+      </c>
+      <c r="E245" s="2">
+        <v>1</v>
+      </c>
+      <c r="F245" s="2">
+        <v>1</v>
+      </c>
+      <c r="G245" s="3">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="H245" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B246" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D246" s="2">
+        <v>1</v>
+      </c>
+      <c r="E246" s="2">
+        <v>0</v>
+      </c>
+      <c r="F246" s="2">
+        <v>1</v>
+      </c>
+      <c r="G246" s="3">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="H246" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-16</t>
+        </is>
+      </c>
+      <c r="B247" s="4"/>
+      <c r="C247" s="4"/>
+      <c r="D247" s="5">
+        <v>518</v>
+      </c>
+      <c r="E247" s="5">
+        <v>202</v>
+      </c>
+      <c r="F247" s="5">
+        <v>720</v>
+      </c>
+      <c r="G247" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H247" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -44320,6 +44943,2540 @@
         <v>797</v>
       </c>
       <c r="F1265" s="4"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1266" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1266" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1266" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1266" s="2">
+        <v>367</v>
+      </c>
+      <c r="F1266" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1267" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1267" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1267" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1267" s="2">
+        <v>38</v>
+      </c>
+      <c r="F1267" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1268" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1268" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1268" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1268" s="2">
+        <v>20</v>
+      </c>
+      <c r="F1268" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1269" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1269" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1269" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1269" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1269" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1270" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1270" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1270" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1270" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1270" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1271" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1271" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1271" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1271" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1271" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1272" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1272" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1272" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1272" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1272" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1273" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1273" s="0" t="inlineStr">
+        <is>
+          <t>cuteetc</t>
+        </is>
+      </c>
+      <c r="D1273" s="0" t="inlineStr">
+        <is>
+          <t>cute_cuteetc</t>
+        </is>
+      </c>
+      <c r="E1273" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1273" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1274" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1274" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1274" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1274" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1274" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1275" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1275" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D1275" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E1275" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1275" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1276" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1276" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1276" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1276" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1276" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1277" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1277" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1277" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1277" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1277" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1278" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1278" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1278" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1278" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1278" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1279" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1279" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1279" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1279" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1279" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1280" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1280" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1280" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1280" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1280" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1281" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1281" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1281" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1281" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1281" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1282" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1282" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="D1282" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="E1282" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1282" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1283" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1283" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D1283" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E1283" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1283" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1284" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1284" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1284" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1284" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1284" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1285" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1285" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1285" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1285" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1285" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1286" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1286" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1286" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1286" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1286" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1287" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1287" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1287" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1287" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1287" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1288" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1288" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D1288" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E1288" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1288" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1289" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1289" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1289" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1289" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1289" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1290" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1290" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrum_day</t>
+        </is>
+      </c>
+      <c r="D1290" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalrum_day</t>
+        </is>
+      </c>
+      <c r="E1290" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1290" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1291" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1291" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D1291" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E1291" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1291" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1292" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1292" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1292" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1292" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1292" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1293" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1293" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1293" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1293" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1293" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1294" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1294" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1294" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1294" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1294" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1295" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1295" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="D1295" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="E1295" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1295" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1296" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1296" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1296" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1296" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1296" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1297" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1297" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1297" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1297" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1297" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1298" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1298" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1298" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1298" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1298" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1299" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1299" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1299" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1299" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1299" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1300" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1300" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D1300" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E1300" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1300" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1301" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1301" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D1301" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E1301" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1301" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1302" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1302" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1302" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1302" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1302" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1303" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1303" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D1303" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E1303" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1303" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1304" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1304" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1304" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1304" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1304" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1305" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1305" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1305" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1305" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1305" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1306" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1306" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1306" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E1306" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1306" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1307" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1307" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1307" s="0" t="inlineStr">
+        <is>
+          <t>anniv_belated</t>
+        </is>
+      </c>
+      <c r="E1307" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1307" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1308" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1308" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D1308" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E1308" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1308" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1309" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1309" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D1309" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E1309" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1309" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1310" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1310" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1310" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1310" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1310" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1311" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1311" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D1311" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E1311" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1311" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1312" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1312" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="D1312" s="0" t="inlineStr">
+        <is>
+          <t>eaug_zorastriannewyear</t>
+        </is>
+      </c>
+      <c r="E1312" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1312" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1313" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1313" s="0" t="inlineStr">
+        <is>
+          <t>ejun_internationalchildrens_day</t>
+        </is>
+      </c>
+      <c r="D1313" s="0" t="inlineStr">
+        <is>
+          <t>ejun_internationalchildrens_day</t>
+        </is>
+      </c>
+      <c r="E1313" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1313" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1314" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1314" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_thank</t>
+        </is>
+      </c>
+      <c r="D1314" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_thank</t>
+        </is>
+      </c>
+      <c r="E1314" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1314" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1315" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1315" s="0" t="inlineStr">
+        <is>
+          <t>emar_rollercoaster_day</t>
+        </is>
+      </c>
+      <c r="D1315" s="0" t="inlineStr">
+        <is>
+          <t>emar_rollercoaster_day</t>
+        </is>
+      </c>
+      <c r="E1315" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1315" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1316" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1316" s="0" t="inlineStr">
+        <is>
+          <t>esep_trueloveforeverday</t>
+        </is>
+      </c>
+      <c r="D1316" s="0" t="inlineStr">
+        <is>
+          <t>esep_trueloveforeverday</t>
+        </is>
+      </c>
+      <c r="E1316" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1316" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1317" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1317" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D1317" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E1317" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1317" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1318" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1318" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D1318" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E1318" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1318" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1319" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1319" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D1319" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E1319" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1319" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1320" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1320" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_thankyou_quotes</t>
+        </is>
+      </c>
+      <c r="D1320" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_thankyou_quotes</t>
+        </is>
+      </c>
+      <c r="E1320" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1320" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1321" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1321" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1321" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E1321" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1321" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1322" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1322" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D1322" s="0" t="inlineStr">
+        <is>
+          <t>intouch_hi</t>
+        </is>
+      </c>
+      <c r="E1322" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1322" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1323" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1323" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D1323" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E1323" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1323" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1324" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1324" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D1324" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E1324" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1324" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1325" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1325" s="0" t="inlineStr">
+        <is>
+          <t>pets</t>
+        </is>
+      </c>
+      <c r="D1325" s="0" t="inlineStr">
+        <is>
+          <t>birth_pets</t>
+        </is>
+      </c>
+      <c r="E1325" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1325" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1326" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1326" s="0" t="inlineStr">
+        <is>
+          <t>accolades</t>
+        </is>
+      </c>
+      <c r="D1326" s="0" t="inlineStr">
+        <is>
+          <t>bus_accolades</t>
+        </is>
+      </c>
+      <c r="E1326" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1326" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1327" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1327" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D1327" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E1327" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1327" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1328" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1328" s="0" t="inlineStr">
+        <is>
+          <t>newjob</t>
+        </is>
+      </c>
+      <c r="D1328" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newjob</t>
+        </is>
+      </c>
+      <c r="E1328" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1328" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1329" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1329" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D1329" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E1329" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1329" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1330" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1330" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="D1330" s="0" t="inlineStr">
+        <is>
+          <t>eaug_indindependenceday</t>
+        </is>
+      </c>
+      <c r="E1330" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1330" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1331" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1331" s="0" t="inlineStr">
+        <is>
+          <t>eaug_jokeday</t>
+        </is>
+      </c>
+      <c r="D1331" s="0" t="inlineStr">
+        <is>
+          <t>eaug_jokeday</t>
+        </is>
+      </c>
+      <c r="E1331" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1331" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1332" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1332" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="D1332" s="0" t="inlineStr">
+        <is>
+          <t>eaug_thankyouday</t>
+        </is>
+      </c>
+      <c r="E1332" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1332" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1333" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1333" s="0" t="inlineStr">
+        <is>
+          <t>eaug_vanillacustard_day</t>
+        </is>
+      </c>
+      <c r="D1333" s="0" t="inlineStr">
+        <is>
+          <t>eaug_vanillacustard_day</t>
+        </is>
+      </c>
+      <c r="E1333" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1333" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1334" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1334" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_love</t>
+        </is>
+      </c>
+      <c r="D1334" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_love</t>
+        </is>
+      </c>
+      <c r="E1334" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1334" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1335" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1335" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_thanku</t>
+        </is>
+      </c>
+      <c r="D1335" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_thanku</t>
+        </is>
+      </c>
+      <c r="E1335" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1335" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1336" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1336" s="0" t="inlineStr">
+        <is>
+          <t>esep_nationalcoffee_day</t>
+        </is>
+      </c>
+      <c r="D1336" s="0" t="inlineStr">
+        <is>
+          <t>esep_nationalcoffee_day</t>
+        </is>
+      </c>
+      <c r="E1336" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1336" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1337" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1337" s="0" t="inlineStr">
+        <is>
+          <t>huswife</t>
+        </is>
+      </c>
+      <c r="D1337" s="0" t="inlineStr">
+        <is>
+          <t>fkt_huswife</t>
+        </is>
+      </c>
+      <c r="E1337" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1337" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1338" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1338" s="0" t="inlineStr">
+        <is>
+          <t>youcare</t>
+        </is>
+      </c>
+      <c r="D1338" s="0" t="inlineStr">
+        <is>
+          <t>flwr_youcare</t>
+        </is>
+      </c>
+      <c r="E1338" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1338" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1339" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1339" s="0" t="inlineStr">
+        <is>
+          <t>bestfriends</t>
+        </is>
+      </c>
+      <c r="D1339" s="0" t="inlineStr">
+        <is>
+          <t>friend_bestfriends</t>
+        </is>
+      </c>
+      <c r="E1339" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1339" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1340" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1340" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D1340" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E1340" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1340" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1341" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1341" s="0" t="inlineStr">
+        <is>
+          <t>morningquotes</t>
+        </is>
+      </c>
+      <c r="D1341" s="0" t="inlineStr">
+        <is>
+          <t>gen_morningquotes</t>
+        </is>
+      </c>
+      <c r="E1341" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1341" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1342" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1342" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D1342" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E1342" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1342" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1343" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1343" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D1343" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E1343" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1343" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1344" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1344" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D1344" s="0" t="inlineStr">
+        <is>
+          <t>intouch_missingyou</t>
+        </is>
+      </c>
+      <c r="E1344" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1344" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1345" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1345" s="0" t="inlineStr">
+        <is>
+          <t>sendsmile</t>
+        </is>
+      </c>
+      <c r="D1345" s="0" t="inlineStr">
+        <is>
+          <t>intouch_sendsmile</t>
+        </is>
+      </c>
+      <c r="E1345" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1345" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1346" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1346" s="0" t="inlineStr">
+        <is>
+          <t>otherinvitations</t>
+        </is>
+      </c>
+      <c r="D1346" s="0" t="inlineStr">
+        <is>
+          <t>invp_otherinvitations</t>
+        </is>
+      </c>
+      <c r="E1346" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1346" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1347" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1347" s="0" t="inlineStr">
+        <is>
+          <t>foreverlove</t>
+        </is>
+      </c>
+      <c r="D1347" s="0" t="inlineStr">
+        <is>
+          <t>love_foreverlove</t>
+        </is>
+      </c>
+      <c r="E1347" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1347" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1348" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1348" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1348" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1348" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1348" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1349" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1349" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="D1349" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_kisses</t>
+        </is>
+      </c>
+      <c r="E1349" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1349" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1350" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1350" s="0" t="inlineStr">
+        <is>
+          <t>youarespecial</t>
+        </is>
+      </c>
+      <c r="D1350" s="0" t="inlineStr">
+        <is>
+          <t>love_youarespecial</t>
+        </is>
+      </c>
+      <c r="E1350" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1350" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1351" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1351" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D1351" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E1351" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1351" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1352" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1352" s="0" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D1352" s="0" t="inlineStr">
+        <is>
+          <t>thank_congratulations</t>
+        </is>
+      </c>
+      <c r="E1352" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1352" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1353" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1353" s="0" t="inlineStr">
+        <is>
+          <t>friendship</t>
+        </is>
+      </c>
+      <c r="D1353" s="0" t="inlineStr">
+        <is>
+          <t>thank_friendship</t>
+        </is>
+      </c>
+      <c r="E1353" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1353" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1354" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1354" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1354" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1354" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1354" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1355" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1355" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D1355" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E1355" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1355" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1356" s="4"/>
+      <c r="C1356" s="4"/>
+      <c r="D1356" s="4"/>
+      <c r="E1356" s="5">
+        <v>720</v>
+      </c>
+      <c r="F1356" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -44903,36 +48060,70 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>761</v>
+      </c>
+      <c r="C17" s="2">
+        <v>267</v>
+      </c>
+      <c r="D17" s="2">
+        <v>207</v>
+      </c>
+      <c r="E17" s="2">
+        <v>150</v>
+      </c>
+      <c r="F17" s="2">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2">
+        <v>41</v>
+      </c>
+      <c r="H17" s="2">
+        <v>20</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="5">
-        <v>12518</v>
-      </c>
-      <c r="C17" s="5">
-        <v>3922</v>
-      </c>
-      <c r="D17" s="5">
-        <v>3922</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2522</v>
-      </c>
-      <c r="F17" s="5">
-        <v>1251</v>
-      </c>
-      <c r="G17" s="5">
-        <v>476</v>
-      </c>
-      <c r="H17" s="5">
-        <v>396</v>
-      </c>
-      <c r="I17" s="5">
+      <c r="B18" s="5">
+        <v>13279</v>
+      </c>
+      <c r="C18" s="5">
+        <v>4189</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4129</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2672</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1327</v>
+      </c>
+      <c r="G18" s="5">
+        <v>517</v>
+      </c>
+      <c r="H18" s="5">
+        <v>416</v>
+      </c>
+      <c r="I18" s="5">
         <v>28</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J18" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -787,28 +787,56 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>822</v>
+      </c>
+      <c r="C19" s="2">
+        <v>520</v>
+      </c>
+      <c r="D19" s="2">
+        <v>302</v>
+      </c>
+      <c r="E19" s="2">
+        <v>771</v>
+      </c>
+      <c r="F19" s="2">
+        <v>51</v>
+      </c>
+      <c r="G19" s="2">
+        <v>264</v>
+      </c>
+      <c r="H19" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="5">
-        <v>13973</v>
-      </c>
-      <c r="C19" s="5">
-        <v>9311</v>
-      </c>
-      <c r="D19" s="5">
-        <v>4662</v>
-      </c>
-      <c r="E19" s="5">
-        <v>13426</v>
-      </c>
-      <c r="F19" s="5">
-        <v>547</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="B20" s="5">
+        <v>14795</v>
+      </c>
+      <c r="C20" s="5">
+        <v>9831</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4964</v>
+      </c>
+      <c r="E20" s="5">
+        <v>14197</v>
+      </c>
+      <c r="F20" s="5">
+        <v>598</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -1973,64 +2001,125 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>771</v>
+      </c>
+      <c r="C19" s="2">
+        <v>523</v>
+      </c>
+      <c r="D19" s="2">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2">
+        <v>63</v>
+      </c>
+      <c r="F19" s="2">
+        <v>44</v>
+      </c>
+      <c r="G19" s="2">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2">
+        <v>20</v>
+      </c>
+      <c r="I19" s="2">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
+        <v>13</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5</v>
+      </c>
+      <c r="M19" s="2">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2">
+        <v>6</v>
+      </c>
+      <c r="O19" s="2">
+        <v>2</v>
+      </c>
+      <c r="P19" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="5">
-        <v>13426</v>
-      </c>
-      <c r="C19" s="5">
-        <v>8742</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1365</v>
-      </c>
-      <c r="E19" s="5">
-        <v>837</v>
-      </c>
-      <c r="F19" s="5">
-        <v>680</v>
-      </c>
-      <c r="G19" s="5">
-        <v>502</v>
-      </c>
-      <c r="H19" s="5">
-        <v>323</v>
-      </c>
-      <c r="I19" s="5">
-        <v>264</v>
-      </c>
-      <c r="J19" s="5">
-        <v>194</v>
-      </c>
-      <c r="K19" s="5">
-        <v>174</v>
-      </c>
-      <c r="L19" s="5">
-        <v>97</v>
-      </c>
-      <c r="M19" s="5">
-        <v>70</v>
-      </c>
-      <c r="N19" s="5">
-        <v>66</v>
-      </c>
-      <c r="O19" s="5">
-        <v>40</v>
-      </c>
-      <c r="P19" s="5">
-        <v>24</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>22</v>
-      </c>
-      <c r="R19" s="5">
-        <v>17</v>
-      </c>
-      <c r="S19" s="5">
-        <v>9</v>
+      <c r="B20" s="5">
+        <v>14197</v>
+      </c>
+      <c r="C20" s="5">
+        <v>9265</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1403</v>
+      </c>
+      <c r="E20" s="5">
+        <v>900</v>
+      </c>
+      <c r="F20" s="5">
+        <v>724</v>
+      </c>
+      <c r="G20" s="5">
+        <v>525</v>
+      </c>
+      <c r="H20" s="5">
+        <v>343</v>
+      </c>
+      <c r="I20" s="5">
+        <v>284</v>
+      </c>
+      <c r="J20" s="5">
+        <v>195</v>
+      </c>
+      <c r="K20" s="5">
+        <v>187</v>
+      </c>
+      <c r="L20" s="5">
+        <v>102</v>
+      </c>
+      <c r="M20" s="5">
+        <v>76</v>
+      </c>
+      <c r="N20" s="5">
+        <v>72</v>
+      </c>
+      <c r="O20" s="5">
+        <v>42</v>
+      </c>
+      <c r="P20" s="5">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>23</v>
+      </c>
+      <c r="R20" s="5">
+        <v>18</v>
+      </c>
+      <c r="S20" s="5">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10242,6 +10331,572 @@
       </c>
       <c r="H261" s="4"/>
     </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B262" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D262" s="2">
+        <v>359</v>
+      </c>
+      <c r="E262" s="2">
+        <v>164</v>
+      </c>
+      <c r="F262" s="2">
+        <v>523</v>
+      </c>
+      <c r="G262" s="3">
+        <v>0.6783398184176395</v>
+      </c>
+      <c r="H262" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B263" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D263" s="2">
+        <v>34</v>
+      </c>
+      <c r="E263" s="2">
+        <v>29</v>
+      </c>
+      <c r="F263" s="2">
+        <v>63</v>
+      </c>
+      <c r="G263" s="3">
+        <v>0.08171206225680934</v>
+      </c>
+      <c r="H263" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B264" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D264" s="2">
+        <v>29</v>
+      </c>
+      <c r="E264" s="2">
+        <v>15</v>
+      </c>
+      <c r="F264" s="2">
+        <v>44</v>
+      </c>
+      <c r="G264" s="3">
+        <v>0.057068741893644616</v>
+      </c>
+      <c r="H264" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B265" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D265" s="2">
+        <v>28</v>
+      </c>
+      <c r="E265" s="2">
+        <v>10</v>
+      </c>
+      <c r="F265" s="2">
+        <v>38</v>
+      </c>
+      <c r="G265" s="3">
+        <v>0.04928664072632944</v>
+      </c>
+      <c r="H265" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B266" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D266" s="2">
+        <v>5</v>
+      </c>
+      <c r="E266" s="2">
+        <v>18</v>
+      </c>
+      <c r="F266" s="2">
+        <v>23</v>
+      </c>
+      <c r="G266" s="3">
+        <v>0.029831387808041506</v>
+      </c>
+      <c r="H266" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B267" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D267" s="2">
+        <v>15</v>
+      </c>
+      <c r="E267" s="2">
+        <v>5</v>
+      </c>
+      <c r="F267" s="2">
+        <v>20</v>
+      </c>
+      <c r="G267" s="3">
+        <v>0.02594033722438392</v>
+      </c>
+      <c r="H267" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B268" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D268" s="2">
+        <v>12</v>
+      </c>
+      <c r="E268" s="2">
+        <v>8</v>
+      </c>
+      <c r="F268" s="2">
+        <v>20</v>
+      </c>
+      <c r="G268" s="3">
+        <v>0.02594033722438392</v>
+      </c>
+      <c r="H268" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B269" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D269" s="2">
+        <v>13</v>
+      </c>
+      <c r="E269" s="2">
+        <v>0</v>
+      </c>
+      <c r="F269" s="2">
+        <v>13</v>
+      </c>
+      <c r="G269" s="3">
+        <v>0.016861219195849545</v>
+      </c>
+      <c r="H269" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B270" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D270" s="2">
+        <v>6</v>
+      </c>
+      <c r="E270" s="2">
+        <v>0</v>
+      </c>
+      <c r="F270" s="2">
+        <v>6</v>
+      </c>
+      <c r="G270" s="3">
+        <v>0.007782101167315175</v>
+      </c>
+      <c r="H270" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B271" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D271" s="2">
+        <v>6</v>
+      </c>
+      <c r="E271" s="2">
+        <v>0</v>
+      </c>
+      <c r="F271" s="2">
+        <v>6</v>
+      </c>
+      <c r="G271" s="3">
+        <v>0.007782101167315175</v>
+      </c>
+      <c r="H271" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B272" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D272" s="2">
+        <v>4</v>
+      </c>
+      <c r="E272" s="2">
+        <v>1</v>
+      </c>
+      <c r="F272" s="2">
+        <v>5</v>
+      </c>
+      <c r="G272" s="3">
+        <v>0.00648508430609598</v>
+      </c>
+      <c r="H272" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B273" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D273" s="2">
+        <v>3</v>
+      </c>
+      <c r="E273" s="2">
+        <v>0</v>
+      </c>
+      <c r="F273" s="2">
+        <v>3</v>
+      </c>
+      <c r="G273" s="3">
+        <v>0.0038910505836575876</v>
+      </c>
+      <c r="H273" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B274" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D274" s="2">
+        <v>2</v>
+      </c>
+      <c r="E274" s="2">
+        <v>0</v>
+      </c>
+      <c r="F274" s="2">
+        <v>2</v>
+      </c>
+      <c r="G274" s="3">
+        <v>0.0025940337224383916</v>
+      </c>
+      <c r="H274" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B275" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D275" s="2">
+        <v>2</v>
+      </c>
+      <c r="E275" s="2">
+        <v>0</v>
+      </c>
+      <c r="F275" s="2">
+        <v>2</v>
+      </c>
+      <c r="G275" s="3">
+        <v>0.0025940337224383916</v>
+      </c>
+      <c r="H275" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B276" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D276" s="2">
+        <v>1</v>
+      </c>
+      <c r="E276" s="2">
+        <v>0</v>
+      </c>
+      <c r="F276" s="2">
+        <v>1</v>
+      </c>
+      <c r="G276" s="3">
+        <v>0.0012970168612191958</v>
+      </c>
+      <c r="H276" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B277" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D277" s="2">
+        <v>1</v>
+      </c>
+      <c r="E277" s="2">
+        <v>0</v>
+      </c>
+      <c r="F277" s="2">
+        <v>1</v>
+      </c>
+      <c r="G277" s="3">
+        <v>0.0012970168612191958</v>
+      </c>
+      <c r="H277" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B278" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D278" s="2">
+        <v>0</v>
+      </c>
+      <c r="E278" s="2">
+        <v>1</v>
+      </c>
+      <c r="F278" s="2">
+        <v>1</v>
+      </c>
+      <c r="G278" s="3">
+        <v>0.0012970168612191958</v>
+      </c>
+      <c r="H278" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-18</t>
+        </is>
+      </c>
+      <c r="B279" s="4"/>
+      <c r="C279" s="4"/>
+      <c r="D279" s="5">
+        <v>520</v>
+      </c>
+      <c r="E279" s="5">
+        <v>251</v>
+      </c>
+      <c r="F279" s="5">
+        <v>771</v>
+      </c>
+      <c r="G279" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H279" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -50370,6 +51025,2540 @@
         <v>730</v>
       </c>
       <c r="F1441" s="4"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1442" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1442" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1442" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1442" s="2">
+        <v>421</v>
+      </c>
+      <c r="F1442" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1443" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1443" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1443" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1443" s="2">
+        <v>41</v>
+      </c>
+      <c r="F1443" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1444" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1444" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1444" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1444" s="2">
+        <v>17</v>
+      </c>
+      <c r="F1444" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1445" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1445" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1445" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1445" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1445" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1446" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1446" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1446" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1446" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1446" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1447" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1447" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1447" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1447" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1447" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1448" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1448" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1448" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1448" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1448" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1449" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1449" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1449" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1449" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1449" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1450" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1450" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1450" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1450" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1450" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1451" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1451" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1451" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1451" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1451" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1452" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1452" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1452" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1452" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1452" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1453" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1453" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1453" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1453" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1453" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1454" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1454" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1454" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1454" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1454" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1455" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1455" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="D1455" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="E1455" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1455" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1456" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1456" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1456" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1456" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1456" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1457" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1457" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1457" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1457" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1457" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1458" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1458" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1458" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1458" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1458" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1459" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1459" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1459" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1459" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1459" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1460" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1460" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1460" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1460" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1460" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1461" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1461" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D1461" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E1461" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1461" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1462" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1462" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1462" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1462" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1462" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1463" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1463" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1463" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1463" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1463" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1464" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1464" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D1464" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E1464" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1464" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1465" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1465" s="0" t="inlineStr">
+        <is>
+          <t>eaug_icecream_pie_day</t>
+        </is>
+      </c>
+      <c r="D1465" s="0" t="inlineStr">
+        <is>
+          <t>eaug_icecream_pie_day</t>
+        </is>
+      </c>
+      <c r="E1465" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1465" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1466" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1466" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1466" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1466" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1466" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1467" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1467" s="0" t="inlineStr">
+        <is>
+          <t>balloons</t>
+        </is>
+      </c>
+      <c r="D1467" s="0" t="inlineStr">
+        <is>
+          <t>birth_balloons</t>
+        </is>
+      </c>
+      <c r="E1467" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1467" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1468" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1468" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1468" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1468" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1468" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1469" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1469" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1469" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1469" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1469" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1470" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1470" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1470" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1470" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1470" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1471" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1471" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D1471" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E1471" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1471" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1472" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1472" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D1472" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E1472" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1472" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1473" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1473" s="0" t="inlineStr">
+        <is>
+          <t>ejul_kissingday</t>
+        </is>
+      </c>
+      <c r="D1473" s="0" t="inlineStr">
+        <is>
+          <t>ejul_kissingday</t>
+        </is>
+      </c>
+      <c r="E1473" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1473" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1474" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1474" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="D1474" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="E1474" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1474" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1475" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1475" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D1475" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E1475" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1475" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1476" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1476" s="0" t="inlineStr">
+        <is>
+          <t>sonsdaughter</t>
+        </is>
+      </c>
+      <c r="D1476" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sonsdaughter</t>
+        </is>
+      </c>
+      <c r="E1476" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1476" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1477" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1477" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D1477" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E1477" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1477" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1478" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1478" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D1478" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E1478" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1478" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1479" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1479" s="0" t="inlineStr">
+        <is>
+          <t>loveetc</t>
+        </is>
+      </c>
+      <c r="D1479" s="0" t="inlineStr">
+        <is>
+          <t>love_loveetc</t>
+        </is>
+      </c>
+      <c r="E1479" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1479" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1480" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1480" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1480" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1480" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1480" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1481" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1481" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1481" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1481" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1481" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1482" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1482" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1482" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1482" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1482" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1483" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1483" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalaviation_day</t>
+        </is>
+      </c>
+      <c r="D1483" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalaviation_day</t>
+        </is>
+      </c>
+      <c r="E1483" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1483" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1484" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1484" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="D1484" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="E1484" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1484" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1485" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1485" s="0" t="inlineStr">
+        <is>
+          <t>esep_janmashtami</t>
+        </is>
+      </c>
+      <c r="D1485" s="0" t="inlineStr">
+        <is>
+          <t>esep_janmashtami</t>
+        </is>
+      </c>
+      <c r="E1485" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1485" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1486" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1486" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="D1486" s="0" t="inlineStr">
+        <is>
+          <t>esep_longestkissday</t>
+        </is>
+      </c>
+      <c r="E1486" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1486" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1487" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1487" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D1487" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E1487" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1487" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1488" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1488" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D1488" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E1488" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1488" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1489" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1489" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D1489" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E1489" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1489" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1490" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1490" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1490" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E1490" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1490" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1491" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1491" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1491" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1491" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1491" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1492" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1492" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1492" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1492" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1492" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1493" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1493" s="0" t="inlineStr">
+        <is>
+          <t>missing_forhim</t>
+        </is>
+      </c>
+      <c r="D1493" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forhim</t>
+        </is>
+      </c>
+      <c r="E1493" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1493" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1494" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1494" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1494" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E1494" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1494" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1495" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1495" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D1495" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E1495" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1495" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1496" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1496" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1496" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E1496" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1496" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1497" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1497" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D1497" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E1497" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1497" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1498" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1498" s="0" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="D1498" s="0" t="inlineStr">
+        <is>
+          <t>bus_retirement</t>
+        </is>
+      </c>
+      <c r="E1498" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1498" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1499" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1499" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D1499" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E1499" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1499" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1500" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1500" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D1500" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E1500" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1500" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1501" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1501" s="0" t="inlineStr">
+        <is>
+          <t>onotheroccasions</t>
+        </is>
+      </c>
+      <c r="D1501" s="0" t="inlineStr">
+        <is>
+          <t>congrats_onotheroccasions</t>
+        </is>
+      </c>
+      <c r="E1501" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1501" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1502" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1502" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D1502" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E1502" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1502" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1503" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1503" s="0" t="inlineStr">
+        <is>
+          <t>heart</t>
+        </is>
+      </c>
+      <c r="D1503" s="0" t="inlineStr">
+        <is>
+          <t>cute_heart</t>
+        </is>
+      </c>
+      <c r="E1503" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1503" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1504" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1504" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="D1504" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="E1504" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1504" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1505" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1505" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalpotato_day</t>
+        </is>
+      </c>
+      <c r="D1505" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalpotato_day</t>
+        </is>
+      </c>
+      <c r="E1505" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1505" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1506" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1506" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_interactive</t>
+        </is>
+      </c>
+      <c r="D1506" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_interactive</t>
+        </is>
+      </c>
+      <c r="E1506" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1506" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1507" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1507" s="0" t="inlineStr">
+        <is>
+          <t>eaug_seniorcitizen_day</t>
+        </is>
+      </c>
+      <c r="D1507" s="0" t="inlineStr">
+        <is>
+          <t>eaug_seniorcitizen_day</t>
+        </is>
+      </c>
+      <c r="E1507" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1507" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1508" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1508" s="0" t="inlineStr">
+        <is>
+          <t>ejul_summerleisure_day</t>
+        </is>
+      </c>
+      <c r="D1508" s="0" t="inlineStr">
+        <is>
+          <t>ejul_summerleisure_day</t>
+        </is>
+      </c>
+      <c r="E1508" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1508" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1509" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1509" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_love</t>
+        </is>
+      </c>
+      <c r="D1509" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_love</t>
+        </is>
+      </c>
+      <c r="E1509" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1509" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1510" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1510" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_happy</t>
+        </is>
+      </c>
+      <c r="D1510" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_happy</t>
+        </is>
+      </c>
+      <c r="E1510" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1510" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1511" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1511" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_wishes</t>
+        </is>
+      </c>
+      <c r="D1511" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_wishes</t>
+        </is>
+      </c>
+      <c r="E1511" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1511" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1512" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1512" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_missyou</t>
+        </is>
+      </c>
+      <c r="D1512" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_missyou</t>
+        </is>
+      </c>
+      <c r="E1512" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1512" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1513" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1513" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D1513" s="0" t="inlineStr">
+        <is>
+          <t>friend_missingyou</t>
+        </is>
+      </c>
+      <c r="E1513" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1513" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1514" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1514" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D1514" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E1514" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1514" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1515" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1515" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D1515" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E1515" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1515" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1516" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1516" s="0" t="inlineStr">
+        <is>
+          <t>morningquotes</t>
+        </is>
+      </c>
+      <c r="D1516" s="0" t="inlineStr">
+        <is>
+          <t>gen_morningquotes</t>
+        </is>
+      </c>
+      <c r="E1516" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1516" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1517" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1517" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D1517" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E1517" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1517" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1518" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1518" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_missyou_messages</t>
+        </is>
+      </c>
+      <c r="D1518" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_missyou_messages</t>
+        </is>
+      </c>
+      <c r="E1518" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1518" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1519" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1519" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D1519" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E1519" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1519" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1520" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1520" s="0" t="inlineStr">
+        <is>
+          <t>tuestoons</t>
+        </is>
+      </c>
+      <c r="D1520" s="0" t="inlineStr">
+        <is>
+          <t>gen_tuestoons</t>
+        </is>
+      </c>
+      <c r="E1520" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1520" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1521" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1521" s="0" t="inlineStr">
+        <is>
+          <t>youarewelcome</t>
+        </is>
+      </c>
+      <c r="D1521" s="0" t="inlineStr">
+        <is>
+          <t>gen_youarewelcome</t>
+        </is>
+      </c>
+      <c r="E1521" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1521" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1522" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1522" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D1522" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E1522" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1522" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1523" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1523" s="0" t="inlineStr">
+        <is>
+          <t>keepintouch</t>
+        </is>
+      </c>
+      <c r="D1523" s="0" t="inlineStr">
+        <is>
+          <t>intouch_keepintouch</t>
+        </is>
+      </c>
+      <c r="E1523" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1523" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1524" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1524" s="0" t="inlineStr">
+        <is>
+          <t>missingyou</t>
+        </is>
+      </c>
+      <c r="D1524" s="0" t="inlineStr">
+        <is>
+          <t>intouch_missingyou</t>
+        </is>
+      </c>
+      <c r="E1524" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1524" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1525" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1525" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D1525" s="0" t="inlineStr">
+        <is>
+          <t>love_cute</t>
+        </is>
+      </c>
+      <c r="E1525" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1525" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1526" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1526" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D1526" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E1526" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1526" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1527" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1527" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1527" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1527" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1527" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1528" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1528" s="0" t="inlineStr">
+        <is>
+          <t>missing_forher</t>
+        </is>
+      </c>
+      <c r="D1528" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forher</t>
+        </is>
+      </c>
+      <c r="E1528" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1528" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1529" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1529" s="0" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D1529" s="0" t="inlineStr">
+        <is>
+          <t>thank_congratulations</t>
+        </is>
+      </c>
+      <c r="E1529" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1529" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1530" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1530" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D1530" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E1530" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1530" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1531" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C1531" s="0" t="inlineStr">
+        <is>
+          <t>hindi_birthday</t>
+        </is>
+      </c>
+      <c r="D1531" s="0" t="inlineStr">
+        <is>
+          <t>w_hindi_birthday</t>
+        </is>
+      </c>
+      <c r="E1531" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1531" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1532" s="4"/>
+      <c r="C1532" s="4"/>
+      <c r="D1532" s="4"/>
+      <c r="E1532" s="5">
+        <v>771</v>
+      </c>
+      <c r="F1532" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -51021,36 +54210,70 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>822</v>
+      </c>
+      <c r="C19" s="2">
+        <v>264</v>
+      </c>
+      <c r="D19" s="2">
+        <v>275</v>
+      </c>
+      <c r="E19" s="2">
+        <v>126</v>
+      </c>
+      <c r="F19" s="2">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2">
+        <v>55</v>
+      </c>
+      <c r="H19" s="2">
+        <v>25</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="5">
-        <v>13973</v>
-      </c>
-      <c r="C19" s="5">
-        <v>4439</v>
-      </c>
-      <c r="D19" s="5">
-        <v>4339</v>
-      </c>
-      <c r="E19" s="5">
-        <v>2800</v>
-      </c>
-      <c r="F19" s="5">
-        <v>1390</v>
-      </c>
-      <c r="G19" s="5">
-        <v>536</v>
-      </c>
-      <c r="H19" s="5">
-        <v>440</v>
-      </c>
-      <c r="I19" s="5">
+      <c r="B20" s="5">
+        <v>14795</v>
+      </c>
+      <c r="C20" s="5">
+        <v>4703</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4614</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2926</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1467</v>
+      </c>
+      <c r="G20" s="5">
+        <v>591</v>
+      </c>
+      <c r="H20" s="5">
+        <v>465</v>
+      </c>
+      <c r="I20" s="5">
         <v>28</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J20" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -815,28 +815,56 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>773</v>
+      </c>
+      <c r="C20" s="2">
+        <v>505</v>
+      </c>
+      <c r="D20" s="2">
+        <v>268</v>
+      </c>
+      <c r="E20" s="2">
+        <v>730</v>
+      </c>
+      <c r="F20" s="2">
+        <v>43</v>
+      </c>
+      <c r="G20" s="2">
+        <v>236</v>
+      </c>
+      <c r="H20" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="5">
-        <v>14795</v>
-      </c>
-      <c r="C20" s="5">
-        <v>9831</v>
-      </c>
-      <c r="D20" s="5">
-        <v>4964</v>
-      </c>
-      <c r="E20" s="5">
-        <v>14205</v>
-      </c>
-      <c r="F20" s="5">
-        <v>590</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="B21" s="5">
+        <v>15568</v>
+      </c>
+      <c r="C21" s="5">
+        <v>10336</v>
+      </c>
+      <c r="D21" s="5">
+        <v>5232</v>
+      </c>
+      <c r="E21" s="5">
+        <v>14935</v>
+      </c>
+      <c r="F21" s="5">
+        <v>633</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -2062,63 +2090,124 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>730</v>
+      </c>
+      <c r="C20" s="2">
+        <v>532</v>
+      </c>
+      <c r="D20" s="2">
+        <v>26</v>
+      </c>
+      <c r="E20" s="2">
+        <v>31</v>
+      </c>
+      <c r="F20" s="2">
+        <v>44</v>
+      </c>
+      <c r="G20" s="2">
+        <v>32</v>
+      </c>
+      <c r="H20" s="2">
+        <v>14</v>
+      </c>
+      <c r="I20" s="2">
+        <v>22</v>
+      </c>
+      <c r="J20" s="2">
+        <v>2</v>
+      </c>
+      <c r="K20" s="2">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2">
+        <v>2</v>
+      </c>
+      <c r="M20" s="2">
+        <v>4</v>
+      </c>
+      <c r="N20" s="2">
+        <v>5</v>
+      </c>
+      <c r="O20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>1</v>
+      </c>
+      <c r="R20" s="2">
+        <v>2</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="5">
-        <v>14205</v>
-      </c>
-      <c r="C20" s="5">
-        <v>9271</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1405</v>
-      </c>
-      <c r="E20" s="5">
-        <v>900</v>
-      </c>
-      <c r="F20" s="5">
-        <v>724</v>
-      </c>
-      <c r="G20" s="5">
-        <v>525</v>
-      </c>
-      <c r="H20" s="5">
-        <v>343</v>
-      </c>
-      <c r="I20" s="5">
-        <v>284</v>
-      </c>
-      <c r="J20" s="5">
+      <c r="B21" s="5">
+        <v>14935</v>
+      </c>
+      <c r="C21" s="5">
+        <v>9803</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1431</v>
+      </c>
+      <c r="E21" s="5">
+        <v>931</v>
+      </c>
+      <c r="F21" s="5">
+        <v>768</v>
+      </c>
+      <c r="G21" s="5">
+        <v>557</v>
+      </c>
+      <c r="H21" s="5">
+        <v>357</v>
+      </c>
+      <c r="I21" s="5">
+        <v>306</v>
+      </c>
+      <c r="J21" s="5">
+        <v>197</v>
+      </c>
+      <c r="K21" s="5">
         <v>195</v>
       </c>
-      <c r="K20" s="5">
-        <v>187</v>
-      </c>
-      <c r="L20" s="5">
-        <v>102</v>
-      </c>
-      <c r="M20" s="5">
-        <v>76</v>
-      </c>
-      <c r="N20" s="5">
-        <v>72</v>
-      </c>
-      <c r="O20" s="5">
-        <v>42</v>
-      </c>
-      <c r="P20" s="5">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>23</v>
-      </c>
-      <c r="R20" s="5">
-        <v>18</v>
-      </c>
-      <c r="S20" s="5">
+      <c r="L21" s="5">
+        <v>104</v>
+      </c>
+      <c r="M21" s="5">
+        <v>80</v>
+      </c>
+      <c r="N21" s="5">
+        <v>77</v>
+      </c>
+      <c r="O21" s="5">
+        <v>43</v>
+      </c>
+      <c r="P21" s="5">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>24</v>
+      </c>
+      <c r="R21" s="5">
+        <v>20</v>
+      </c>
+      <c r="S21" s="5">
         <v>12</v>
       </c>
     </row>
@@ -10897,6 +10986,540 @@
       </c>
       <c r="H279" s="4"/>
     </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B280" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D280" s="2">
+        <v>362</v>
+      </c>
+      <c r="E280" s="2">
+        <v>170</v>
+      </c>
+      <c r="F280" s="2">
+        <v>532</v>
+      </c>
+      <c r="G280" s="3">
+        <v>0.7287671232876712</v>
+      </c>
+      <c r="H280" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B281" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D281" s="2">
+        <v>33</v>
+      </c>
+      <c r="E281" s="2">
+        <v>11</v>
+      </c>
+      <c r="F281" s="2">
+        <v>44</v>
+      </c>
+      <c r="G281" s="3">
+        <v>0.06027397260273973</v>
+      </c>
+      <c r="H281" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B282" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D282" s="2">
+        <v>9</v>
+      </c>
+      <c r="E282" s="2">
+        <v>23</v>
+      </c>
+      <c r="F282" s="2">
+        <v>32</v>
+      </c>
+      <c r="G282" s="3">
+        <v>0.043835616438356165</v>
+      </c>
+      <c r="H282" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B283" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D283" s="2">
+        <v>26</v>
+      </c>
+      <c r="E283" s="2">
+        <v>5</v>
+      </c>
+      <c r="F283" s="2">
+        <v>31</v>
+      </c>
+      <c r="G283" s="3">
+        <v>0.04246575342465753</v>
+      </c>
+      <c r="H283" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B284" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D284" s="2">
+        <v>24</v>
+      </c>
+      <c r="E284" s="2">
+        <v>2</v>
+      </c>
+      <c r="F284" s="2">
+        <v>26</v>
+      </c>
+      <c r="G284" s="3">
+        <v>0.03561643835616438</v>
+      </c>
+      <c r="H284" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B285" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D285" s="2">
+        <v>20</v>
+      </c>
+      <c r="E285" s="2">
+        <v>2</v>
+      </c>
+      <c r="F285" s="2">
+        <v>22</v>
+      </c>
+      <c r="G285" s="3">
+        <v>0.030136986301369864</v>
+      </c>
+      <c r="H285" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B286" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D286" s="2">
+        <v>9</v>
+      </c>
+      <c r="E286" s="2">
+        <v>5</v>
+      </c>
+      <c r="F286" s="2">
+        <v>14</v>
+      </c>
+      <c r="G286" s="3">
+        <v>0.019178082191780823</v>
+      </c>
+      <c r="H286" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B287" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D287" s="2">
+        <v>3</v>
+      </c>
+      <c r="E287" s="2">
+        <v>5</v>
+      </c>
+      <c r="F287" s="2">
+        <v>8</v>
+      </c>
+      <c r="G287" s="3">
+        <v>0.010958904109589041</v>
+      </c>
+      <c r="H287" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B288" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D288" s="2">
+        <v>4</v>
+      </c>
+      <c r="E288" s="2">
+        <v>1</v>
+      </c>
+      <c r="F288" s="2">
+        <v>5</v>
+      </c>
+      <c r="G288" s="3">
+        <v>0.00684931506849315</v>
+      </c>
+      <c r="H288" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B289" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D289" s="2">
+        <v>4</v>
+      </c>
+      <c r="E289" s="2">
+        <v>0</v>
+      </c>
+      <c r="F289" s="2">
+        <v>4</v>
+      </c>
+      <c r="G289" s="3">
+        <v>0.005479452054794521</v>
+      </c>
+      <c r="H289" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B290" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D290" s="2">
+        <v>4</v>
+      </c>
+      <c r="E290" s="2">
+        <v>0</v>
+      </c>
+      <c r="F290" s="2">
+        <v>4</v>
+      </c>
+      <c r="G290" s="3">
+        <v>0.005479452054794521</v>
+      </c>
+      <c r="H290" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B291" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D291" s="2">
+        <v>2</v>
+      </c>
+      <c r="E291" s="2">
+        <v>0</v>
+      </c>
+      <c r="F291" s="2">
+        <v>2</v>
+      </c>
+      <c r="G291" s="3">
+        <v>0.0027397260273972603</v>
+      </c>
+      <c r="H291" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B292" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D292" s="2">
+        <v>2</v>
+      </c>
+      <c r="E292" s="2">
+        <v>0</v>
+      </c>
+      <c r="F292" s="2">
+        <v>2</v>
+      </c>
+      <c r="G292" s="3">
+        <v>0.0027397260273972603</v>
+      </c>
+      <c r="H292" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B293" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D293" s="2">
+        <v>2</v>
+      </c>
+      <c r="E293" s="2">
+        <v>0</v>
+      </c>
+      <c r="F293" s="2">
+        <v>2</v>
+      </c>
+      <c r="G293" s="3">
+        <v>0.0027397260273972603</v>
+      </c>
+      <c r="H293" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B294" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D294" s="2">
+        <v>1</v>
+      </c>
+      <c r="E294" s="2">
+        <v>0</v>
+      </c>
+      <c r="F294" s="2">
+        <v>1</v>
+      </c>
+      <c r="G294" s="3">
+        <v>0.0013698630136986301</v>
+      </c>
+      <c r="H294" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B295" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D295" s="2">
+        <v>0</v>
+      </c>
+      <c r="E295" s="2">
+        <v>1</v>
+      </c>
+      <c r="F295" s="2">
+        <v>1</v>
+      </c>
+      <c r="G295" s="3">
+        <v>0.0013698630136986301</v>
+      </c>
+      <c r="H295" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-19</t>
+        </is>
+      </c>
+      <c r="B296" s="4"/>
+      <c r="C296" s="4"/>
+      <c r="D296" s="5">
+        <v>505</v>
+      </c>
+      <c r="E296" s="5">
+        <v>225</v>
+      </c>
+      <c r="F296" s="5">
+        <v>730</v>
+      </c>
+      <c r="G296" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H296" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -53615,6 +54238,2036 @@
         <v>771</v>
       </c>
       <c r="F1534" s="4"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1535" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1535" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1535" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1535" s="2">
+        <v>413</v>
+      </c>
+      <c r="F1535" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1536" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1536" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1536" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1536" s="2">
+        <v>26</v>
+      </c>
+      <c r="F1536" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1537" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1537" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1537" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1537" s="2">
+        <v>18</v>
+      </c>
+      <c r="F1537" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1538" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1538" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1538" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1538" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1538" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1539" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1539" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1539" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1539" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1539" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1540" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1540" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1540" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1540" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1540" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1541" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1541" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1541" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1541" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1541" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1542" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1542" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1542" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1542" s="2">
+        <v>13</v>
+      </c>
+      <c r="F1542" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1543" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1543" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1543" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1543" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1543" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1544" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1544" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1544" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1544" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1544" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1545" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1545" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1545" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1545" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1545" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1546" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1546" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1546" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1546" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1546" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1547" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1547" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1547" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1547" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1547" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1548" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1548" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1548" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1548" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1548" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1549" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1549" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1549" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1549" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1549" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1550" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1550" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1550" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1550" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1550" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1551" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1551" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1551" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1551" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1551" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1552" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1552" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1552" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1552" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1552" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1553" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1553" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1553" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1553" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1553" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1554" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1554" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1554" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1554" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1554" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1555" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1555" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalpotato_day</t>
+        </is>
+      </c>
+      <c r="D1555" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalpotato_day</t>
+        </is>
+      </c>
+      <c r="E1555" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1555" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1556" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1556" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1556" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1556" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1556" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1557" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1557" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D1557" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E1557" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1557" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1558" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1558" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="D1558" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="E1558" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1558" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1559" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1559" s="0" t="inlineStr">
+        <is>
+          <t>eaug_softice_cream_day</t>
+        </is>
+      </c>
+      <c r="D1559" s="0" t="inlineStr">
+        <is>
+          <t>eaug_softice_cream_day</t>
+        </is>
+      </c>
+      <c r="E1559" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1559" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1560" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1560" s="0" t="inlineStr">
+        <is>
+          <t>lovedones</t>
+        </is>
+      </c>
+      <c r="D1560" s="0" t="inlineStr">
+        <is>
+          <t>fkt_lovedones</t>
+        </is>
+      </c>
+      <c r="E1560" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1560" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1561" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1561" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D1561" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E1561" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1561" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1562" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1562" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1562" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1562" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1562" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1563" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1563" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D1563" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E1563" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1563" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1564" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1564" s="0" t="inlineStr">
+        <is>
+          <t>stressbusters</t>
+        </is>
+      </c>
+      <c r="D1564" s="0" t="inlineStr">
+        <is>
+          <t>insp_stressbusters</t>
+        </is>
+      </c>
+      <c r="E1564" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1564" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1565" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1565" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1565" s="0" t="inlineStr">
+        <is>
+          <t>intouch_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1565" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1565" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1566" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1566" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1566" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1566" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1566" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1567" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1567" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D1567" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E1567" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1567" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1568" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1568" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalaviation_day</t>
+        </is>
+      </c>
+      <c r="D1568" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalaviation_day</t>
+        </is>
+      </c>
+      <c r="E1568" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1568" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1569" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1569" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D1569" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E1569" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1569" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1570" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1570" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1570" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1570" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1570" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1571" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1571" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1571" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1571" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1571" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1572" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1572" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1572" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1572" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1572" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1573" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1573" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D1573" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E1573" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1573" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1574" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1574" s="0" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="D1574" s="0" t="inlineStr">
+        <is>
+          <t>congrats_engagement</t>
+        </is>
+      </c>
+      <c r="E1574" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1574" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1575" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1575" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwaffle_day</t>
+        </is>
+      </c>
+      <c r="D1575" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalwaffle_day</t>
+        </is>
+      </c>
+      <c r="E1575" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1575" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1576" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1576" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D1576" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E1576" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1576" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1577" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1577" s="0" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="D1577" s="0" t="inlineStr">
+        <is>
+          <t>gen_luck</t>
+        </is>
+      </c>
+      <c r="E1577" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1577" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1578" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1578" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1578" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1578" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1578" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1579" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1579" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1579" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1579" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1579" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1580" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1580" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D1580" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E1580" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1580" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1581" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1581" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1581" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E1581" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1581" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1582" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1582" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1582" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1582" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1582" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1583" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1583" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1583" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1583" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1583" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1584" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1584" s="0" t="inlineStr">
+        <is>
+          <t>apologies</t>
+        </is>
+      </c>
+      <c r="D1584" s="0" t="inlineStr">
+        <is>
+          <t>bus_apologies</t>
+        </is>
+      </c>
+      <c r="E1584" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1584" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1585" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1585" s="0" t="inlineStr">
+        <is>
+          <t>appreciate</t>
+        </is>
+      </c>
+      <c r="D1585" s="0" t="inlineStr">
+        <is>
+          <t>bus_appreciate</t>
+        </is>
+      </c>
+      <c r="E1585" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1585" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1586" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1586" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D1586" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E1586" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1586" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1587" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1587" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D1587" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E1587" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1587" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1588" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1588" s="0" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="D1588" s="0" t="inlineStr">
+        <is>
+          <t>cute_smile</t>
+        </is>
+      </c>
+      <c r="E1588" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1588" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1589" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1589" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="D1589" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="E1589" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1589" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1590" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1590" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalradio_day</t>
+        </is>
+      </c>
+      <c r="D1590" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalradio_day</t>
+        </is>
+      </c>
+      <c r="E1590" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1590" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1591" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1591" s="0" t="inlineStr">
+        <is>
+          <t>ejan_danceday</t>
+        </is>
+      </c>
+      <c r="D1591" s="0" t="inlineStr">
+        <is>
+          <t>ejan_danceday</t>
+        </is>
+      </c>
+      <c r="E1591" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1591" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1592" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1592" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_wishes</t>
+        </is>
+      </c>
+      <c r="D1592" s="0" t="inlineStr">
+        <is>
+          <t>emay_graduation_wishes</t>
+        </is>
+      </c>
+      <c r="E1592" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1592" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1593" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1593" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_missyou</t>
+        </is>
+      </c>
+      <c r="D1593" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_missyou</t>
+        </is>
+      </c>
+      <c r="E1593" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1593" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1594" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1594" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_romance</t>
+        </is>
+      </c>
+      <c r="D1594" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_romance</t>
+        </is>
+      </c>
+      <c r="E1594" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1594" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1595" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1595" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="D1595" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_specials</t>
+        </is>
+      </c>
+      <c r="E1595" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1595" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1596" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1596" s="0" t="inlineStr">
+        <is>
+          <t>teenfriends</t>
+        </is>
+      </c>
+      <c r="D1596" s="0" t="inlineStr">
+        <is>
+          <t>friend_teenfriends</t>
+        </is>
+      </c>
+      <c r="E1596" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1596" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1597" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1597" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D1597" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E1597" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1597" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1598" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1598" s="0" t="inlineStr">
+        <is>
+          <t>midcrisis</t>
+        </is>
+      </c>
+      <c r="D1598" s="0" t="inlineStr">
+        <is>
+          <t>gen_midcrisis</t>
+        </is>
+      </c>
+      <c r="E1598" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1598" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1599" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1599" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_quotes</t>
+        </is>
+      </c>
+      <c r="D1599" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_quotes</t>
+        </is>
+      </c>
+      <c r="E1599" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1599" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1600" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1600" s="0" t="inlineStr">
+        <is>
+          <t>loveetc</t>
+        </is>
+      </c>
+      <c r="D1600" s="0" t="inlineStr">
+        <is>
+          <t>love_loveetc</t>
+        </is>
+      </c>
+      <c r="E1600" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1600" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1601" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1601" s="0" t="inlineStr">
+        <is>
+          <t>missing_forher</t>
+        </is>
+      </c>
+      <c r="D1601" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forher</t>
+        </is>
+      </c>
+      <c r="E1601" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1601" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1602" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1602" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D1602" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E1602" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1602" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1603" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1603" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1603" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E1603" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1603" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1604" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1604" s="0" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="D1604" s="0" t="inlineStr">
+        <is>
+          <t>thank_flower</t>
+        </is>
+      </c>
+      <c r="E1604" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1604" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1605" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C1605" s="0" t="inlineStr">
+        <is>
+          <t>german_birthday</t>
+        </is>
+      </c>
+      <c r="D1605" s="0" t="inlineStr">
+        <is>
+          <t>w_german_birthday</t>
+        </is>
+      </c>
+      <c r="E1605" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1605" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1606" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1606" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1606" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1606" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1606" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1607" s="4"/>
+      <c r="C1607" s="4"/>
+      <c r="D1607" s="4"/>
+      <c r="E1607" s="5">
+        <v>730</v>
+      </c>
+      <c r="F1607" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -54300,36 +56953,70 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>773</v>
+      </c>
+      <c r="C20" s="2">
+        <v>237</v>
+      </c>
+      <c r="D20" s="2">
+        <v>242</v>
+      </c>
+      <c r="E20" s="2">
+        <v>148</v>
+      </c>
+      <c r="F20" s="2">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2">
+        <v>42</v>
+      </c>
+      <c r="H20" s="2">
+        <v>22</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="5">
-        <v>14795</v>
-      </c>
-      <c r="C20" s="5">
-        <v>4703</v>
-      </c>
-      <c r="D20" s="5">
-        <v>4614</v>
-      </c>
-      <c r="E20" s="5">
-        <v>2926</v>
-      </c>
-      <c r="F20" s="5">
-        <v>1467</v>
-      </c>
-      <c r="G20" s="5">
-        <v>591</v>
-      </c>
-      <c r="H20" s="5">
-        <v>465</v>
-      </c>
-      <c r="I20" s="5">
+      <c r="B21" s="5">
+        <v>15568</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4940</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4856</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3074</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1549</v>
+      </c>
+      <c r="G21" s="5">
+        <v>633</v>
+      </c>
+      <c r="H21" s="5">
+        <v>487</v>
+      </c>
+      <c r="I21" s="5">
         <v>28</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J21" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -843,28 +843,56 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>758</v>
+      </c>
+      <c r="C21" s="2">
+        <v>534</v>
+      </c>
+      <c r="D21" s="2">
+        <v>224</v>
+      </c>
+      <c r="E21" s="2">
+        <v>725</v>
+      </c>
+      <c r="F21" s="2">
+        <v>33</v>
+      </c>
+      <c r="G21" s="2">
+        <v>243</v>
+      </c>
+      <c r="H21" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="5">
-        <v>15568</v>
-      </c>
-      <c r="C21" s="5">
-        <v>10336</v>
-      </c>
-      <c r="D21" s="5">
-        <v>5232</v>
-      </c>
-      <c r="E21" s="5">
-        <v>14935</v>
-      </c>
-      <c r="F21" s="5">
-        <v>633</v>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="B22" s="5">
+        <v>16326</v>
+      </c>
+      <c r="C22" s="5">
+        <v>10870</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5456</v>
+      </c>
+      <c r="E22" s="5">
+        <v>15660</v>
+      </c>
+      <c r="F22" s="5">
+        <v>666</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -882,8 +910,8 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
@@ -942,12 +970,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Friendship</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Congratulations</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -1022,10 +1050,10 @@
         <v>10</v>
       </c>
       <c r="J2" s="2">
+        <v>12</v>
+      </c>
+      <c r="K2" s="2">
         <v>28</v>
-      </c>
-      <c r="K2" s="2">
-        <v>12</v>
       </c>
       <c r="L2" s="2">
         <v>1</v>
@@ -1083,10 +1111,10 @@
         <v>19</v>
       </c>
       <c r="J3" s="2">
+        <v>11</v>
+      </c>
+      <c r="K3" s="2">
         <v>41</v>
-      </c>
-      <c r="K3" s="2">
-        <v>11</v>
       </c>
       <c r="L3" s="2">
         <v>8</v>
@@ -1144,10 +1172,10 @@
         <v>16</v>
       </c>
       <c r="J4" s="2">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2">
         <v>11</v>
-      </c>
-      <c r="K4" s="2">
-        <v>17</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1205,10 +1233,10 @@
         <v>15</v>
       </c>
       <c r="J5" s="2">
+        <v>4</v>
+      </c>
+      <c r="K5" s="2">
         <v>22</v>
-      </c>
-      <c r="K5" s="2">
-        <v>4</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -1266,10 +1294,10 @@
         <v>15</v>
       </c>
       <c r="J6" s="2">
+        <v>8</v>
+      </c>
+      <c r="K6" s="2">
         <v>11</v>
-      </c>
-      <c r="K6" s="2">
-        <v>8</v>
       </c>
       <c r="L6" s="2">
         <v>17</v>
@@ -1327,10 +1355,10 @@
         <v>12</v>
       </c>
       <c r="J7" s="2">
+        <v>10</v>
+      </c>
+      <c r="K7" s="2">
         <v>16</v>
-      </c>
-      <c r="K7" s="2">
-        <v>10</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1388,10 +1416,10 @@
         <v>14</v>
       </c>
       <c r="J8" s="2">
+        <v>8</v>
+      </c>
+      <c r="K8" s="2">
         <v>7</v>
-      </c>
-      <c r="K8" s="2">
-        <v>8</v>
       </c>
       <c r="L8" s="2">
         <v>6</v>
@@ -1449,10 +1477,10 @@
         <v>14</v>
       </c>
       <c r="J9" s="2">
+        <v>9</v>
+      </c>
+      <c r="K9" s="2">
         <v>10</v>
-      </c>
-      <c r="K9" s="2">
-        <v>9</v>
       </c>
       <c r="L9" s="2">
         <v>39</v>
@@ -1510,10 +1538,10 @@
         <v>20</v>
       </c>
       <c r="J10" s="2">
+        <v>6</v>
+      </c>
+      <c r="K10" s="2">
         <v>7</v>
-      </c>
-      <c r="K10" s="2">
-        <v>6</v>
       </c>
       <c r="L10" s="2">
         <v>4</v>
@@ -1571,10 +1599,10 @@
         <v>16</v>
       </c>
       <c r="J11" s="2">
+        <v>10</v>
+      </c>
+      <c r="K11" s="2">
         <v>11</v>
-      </c>
-      <c r="K11" s="2">
-        <v>10</v>
       </c>
       <c r="L11" s="2">
         <v>3</v>
@@ -1632,10 +1660,10 @@
         <v>14</v>
       </c>
       <c r="J12" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" s="2">
         <v>5</v>
-      </c>
-      <c r="K12" s="2">
-        <v>14</v>
       </c>
       <c r="L12" s="2">
         <v>2</v>
@@ -1693,10 +1721,10 @@
         <v>16</v>
       </c>
       <c r="J13" s="2">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2">
         <v>7</v>
-      </c>
-      <c r="K13" s="2">
-        <v>5</v>
       </c>
       <c r="L13" s="2">
         <v>2</v>
@@ -1754,10 +1782,10 @@
         <v>12</v>
       </c>
       <c r="J14" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K14" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2">
         <v>3</v>
@@ -1815,10 +1843,10 @@
         <v>28</v>
       </c>
       <c r="J15" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2">
         <v>3</v>
@@ -1876,10 +1904,10 @@
         <v>18</v>
       </c>
       <c r="J16" s="2">
+        <v>7</v>
+      </c>
+      <c r="K16" s="2">
         <v>3</v>
-      </c>
-      <c r="K16" s="2">
-        <v>7</v>
       </c>
       <c r="L16" s="2">
         <v>1</v>
@@ -1937,10 +1965,10 @@
         <v>14</v>
       </c>
       <c r="J17" s="2">
+        <v>17</v>
+      </c>
+      <c r="K17" s="2">
         <v>3</v>
-      </c>
-      <c r="K17" s="2">
-        <v>17</v>
       </c>
       <c r="L17" s="2">
         <v>1</v>
@@ -1998,10 +2026,10 @@
         <v>11</v>
       </c>
       <c r="J18" s="2">
+        <v>17</v>
+      </c>
+      <c r="K18" s="2">
         <v>8</v>
-      </c>
-      <c r="K18" s="2">
-        <v>17</v>
       </c>
       <c r="L18" s="2">
         <v>7</v>
@@ -2059,10 +2087,10 @@
         <v>20</v>
       </c>
       <c r="J19" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2">
         <v>5</v>
@@ -2120,10 +2148,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K20" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2">
         <v>2</v>
@@ -2151,64 +2179,125 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>725</v>
+      </c>
+      <c r="C21" s="2">
+        <v>494</v>
+      </c>
+      <c r="D21" s="2">
+        <v>47</v>
+      </c>
+      <c r="E21" s="2">
+        <v>72</v>
+      </c>
+      <c r="F21" s="2">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2">
+        <v>12</v>
+      </c>
+      <c r="H21" s="2">
+        <v>14</v>
+      </c>
+      <c r="I21" s="2">
+        <v>24</v>
+      </c>
+      <c r="J21" s="2">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>3</v>
+      </c>
+      <c r="M21" s="2">
+        <v>4</v>
+      </c>
+      <c r="N21" s="2">
+        <v>4</v>
+      </c>
+      <c r="O21" s="2">
+        <v>3</v>
+      </c>
+      <c r="P21" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>2</v>
+      </c>
+      <c r="R21" s="2">
+        <v>3</v>
+      </c>
+      <c r="S21" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="5">
-        <v>14935</v>
-      </c>
-      <c r="C21" s="5">
-        <v>9803</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1431</v>
-      </c>
-      <c r="E21" s="5">
-        <v>931</v>
-      </c>
-      <c r="F21" s="5">
-        <v>768</v>
-      </c>
-      <c r="G21" s="5">
-        <v>557</v>
-      </c>
-      <c r="H21" s="5">
-        <v>357</v>
-      </c>
-      <c r="I21" s="5">
-        <v>306</v>
-      </c>
-      <c r="J21" s="5">
+      <c r="B22" s="5">
+        <v>15660</v>
+      </c>
+      <c r="C22" s="5">
+        <v>10297</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1478</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1003</v>
+      </c>
+      <c r="F22" s="5">
+        <v>798</v>
+      </c>
+      <c r="G22" s="5">
+        <v>569</v>
+      </c>
+      <c r="H22" s="5">
+        <v>371</v>
+      </c>
+      <c r="I22" s="5">
+        <v>330</v>
+      </c>
+      <c r="J22" s="5">
+        <v>203</v>
+      </c>
+      <c r="K22" s="5">
         <v>197</v>
       </c>
-      <c r="K21" s="5">
-        <v>195</v>
-      </c>
-      <c r="L21" s="5">
-        <v>104</v>
-      </c>
-      <c r="M21" s="5">
-        <v>80</v>
-      </c>
-      <c r="N21" s="5">
-        <v>77</v>
-      </c>
-      <c r="O21" s="5">
-        <v>43</v>
-      </c>
-      <c r="P21" s="5">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>24</v>
-      </c>
-      <c r="R21" s="5">
-        <v>20</v>
-      </c>
-      <c r="S21" s="5">
-        <v>12</v>
+      <c r="L22" s="5">
+        <v>107</v>
+      </c>
+      <c r="M22" s="5">
+        <v>84</v>
+      </c>
+      <c r="N22" s="5">
+        <v>81</v>
+      </c>
+      <c r="O22" s="5">
+        <v>46</v>
+      </c>
+      <c r="P22" s="5">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>26</v>
+      </c>
+      <c r="R22" s="5">
+        <v>23</v>
+      </c>
+      <c r="S22" s="5">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -11520,6 +11609,540 @@
       </c>
       <c r="H296" s="4"/>
     </row>
+    <row r="297">
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B297" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D297" s="2">
+        <v>369</v>
+      </c>
+      <c r="E297" s="2">
+        <v>125</v>
+      </c>
+      <c r="F297" s="2">
+        <v>494</v>
+      </c>
+      <c r="G297" s="3">
+        <v>0.6813793103448276</v>
+      </c>
+      <c r="H297" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B298" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D298" s="2">
+        <v>47</v>
+      </c>
+      <c r="E298" s="2">
+        <v>25</v>
+      </c>
+      <c r="F298" s="2">
+        <v>72</v>
+      </c>
+      <c r="G298" s="3">
+        <v>0.0993103448275862</v>
+      </c>
+      <c r="H298" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B299" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D299" s="2">
+        <v>42</v>
+      </c>
+      <c r="E299" s="2">
+        <v>5</v>
+      </c>
+      <c r="F299" s="2">
+        <v>47</v>
+      </c>
+      <c r="G299" s="3">
+        <v>0.06482758620689655</v>
+      </c>
+      <c r="H299" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B300" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D300" s="2">
+        <v>28</v>
+      </c>
+      <c r="E300" s="2">
+        <v>2</v>
+      </c>
+      <c r="F300" s="2">
+        <v>30</v>
+      </c>
+      <c r="G300" s="3">
+        <v>0.041379310344827586</v>
+      </c>
+      <c r="H300" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B301" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C301" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D301" s="2">
+        <v>14</v>
+      </c>
+      <c r="E301" s="2">
+        <v>10</v>
+      </c>
+      <c r="F301" s="2">
+        <v>24</v>
+      </c>
+      <c r="G301" s="3">
+        <v>0.03310344827586207</v>
+      </c>
+      <c r="H301" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B302" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C302" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D302" s="2">
+        <v>9</v>
+      </c>
+      <c r="E302" s="2">
+        <v>5</v>
+      </c>
+      <c r="F302" s="2">
+        <v>14</v>
+      </c>
+      <c r="G302" s="3">
+        <v>0.019310344827586208</v>
+      </c>
+      <c r="H302" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C303" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D303" s="2">
+        <v>0</v>
+      </c>
+      <c r="E303" s="2">
+        <v>12</v>
+      </c>
+      <c r="F303" s="2">
+        <v>12</v>
+      </c>
+      <c r="G303" s="3">
+        <v>0.016551724137931035</v>
+      </c>
+      <c r="H303" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B304" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C304" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D304" s="2">
+        <v>6</v>
+      </c>
+      <c r="E304" s="2">
+        <v>2</v>
+      </c>
+      <c r="F304" s="2">
+        <v>8</v>
+      </c>
+      <c r="G304" s="3">
+        <v>0.011034482758620689</v>
+      </c>
+      <c r="H304" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B305" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="D305" s="2">
+        <v>4</v>
+      </c>
+      <c r="E305" s="2">
+        <v>0</v>
+      </c>
+      <c r="F305" s="2">
+        <v>4</v>
+      </c>
+      <c r="G305" s="3">
+        <v>0.005517241379310344</v>
+      </c>
+      <c r="H305" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B306" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t>fkt</t>
+        </is>
+      </c>
+      <c r="D306" s="2">
+        <v>3</v>
+      </c>
+      <c r="E306" s="2">
+        <v>1</v>
+      </c>
+      <c r="F306" s="2">
+        <v>4</v>
+      </c>
+      <c r="G306" s="3">
+        <v>0.005517241379310344</v>
+      </c>
+      <c r="H306" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B307" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D307" s="2">
+        <v>2</v>
+      </c>
+      <c r="E307" s="2">
+        <v>1</v>
+      </c>
+      <c r="F307" s="2">
+        <v>3</v>
+      </c>
+      <c r="G307" s="3">
+        <v>0.004137931034482759</v>
+      </c>
+      <c r="H307" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B308" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D308" s="2">
+        <v>3</v>
+      </c>
+      <c r="E308" s="2">
+        <v>0</v>
+      </c>
+      <c r="F308" s="2">
+        <v>3</v>
+      </c>
+      <c r="G308" s="3">
+        <v>0.004137931034482759</v>
+      </c>
+      <c r="H308" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B309" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D309" s="2">
+        <v>3</v>
+      </c>
+      <c r="E309" s="2">
+        <v>0</v>
+      </c>
+      <c r="F309" s="2">
+        <v>3</v>
+      </c>
+      <c r="G309" s="3">
+        <v>0.004137931034482759</v>
+      </c>
+      <c r="H309" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B310" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D310" s="2">
+        <v>2</v>
+      </c>
+      <c r="E310" s="2">
+        <v>1</v>
+      </c>
+      <c r="F310" s="2">
+        <v>3</v>
+      </c>
+      <c r="G310" s="3">
+        <v>0.004137931034482759</v>
+      </c>
+      <c r="H310" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B311" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D311" s="2">
+        <v>2</v>
+      </c>
+      <c r="E311" s="2">
+        <v>0</v>
+      </c>
+      <c r="F311" s="2">
+        <v>2</v>
+      </c>
+      <c r="G311" s="3">
+        <v>0.002758620689655172</v>
+      </c>
+      <c r="H311" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B312" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="D312" s="2">
+        <v>0</v>
+      </c>
+      <c r="E312" s="2">
+        <v>2</v>
+      </c>
+      <c r="F312" s="2">
+        <v>2</v>
+      </c>
+      <c r="G312" s="3">
+        <v>0.002758620689655172</v>
+      </c>
+      <c r="H312" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-20</t>
+        </is>
+      </c>
+      <c r="B313" s="4"/>
+      <c r="C313" s="4"/>
+      <c r="D313" s="5">
+        <v>534</v>
+      </c>
+      <c r="E313" s="5">
+        <v>191</v>
+      </c>
+      <c r="F313" s="5">
+        <v>725</v>
+      </c>
+      <c r="G313" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H313" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -56268,6 +56891,2344 @@
         <v>730</v>
       </c>
       <c r="F1607" s="4"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1608" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1608" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1608" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1608" s="2">
+        <v>389</v>
+      </c>
+      <c r="F1608" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1609" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1609" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1609" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1609" s="2">
+        <v>52</v>
+      </c>
+      <c r="F1609" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1610" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1610" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1610" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1610" s="2">
+        <v>21</v>
+      </c>
+      <c r="F1610" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1611" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1611" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1611" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1611" s="2">
+        <v>18</v>
+      </c>
+      <c r="F1611" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1612" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1612" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1612" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1612" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1612" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1613" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1613" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1613" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1613" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1613" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1614" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1614" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1614" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1614" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1614" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1615" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1615" s="0" t="inlineStr">
+        <is>
+          <t>eaug_seniorcitizen_day</t>
+        </is>
+      </c>
+      <c r="D1615" s="0" t="inlineStr">
+        <is>
+          <t>eaug_seniorcitizen_day</t>
+        </is>
+      </c>
+      <c r="E1615" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1615" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1616" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1616" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1616" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1616" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1616" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1617" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1617" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1617" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1617" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1617" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1618" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1618" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1618" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1618" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1618" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1619" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1619" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="D1619" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipweek</t>
+        </is>
+      </c>
+      <c r="E1619" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1619" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1620" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1620" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D1620" s="0" t="inlineStr">
+        <is>
+          <t>gen_missyou</t>
+        </is>
+      </c>
+      <c r="E1620" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1620" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1621" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1621" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1621" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1621" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1621" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1622" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1622" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1622" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1622" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1622" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1623" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1623" s="0" t="inlineStr">
+        <is>
+          <t>zodiac</t>
+        </is>
+      </c>
+      <c r="D1623" s="0" t="inlineStr">
+        <is>
+          <t>birth_zodiac</t>
+        </is>
+      </c>
+      <c r="E1623" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1623" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1624" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1624" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1624" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1624" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1624" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1625" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1625" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1625" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1625" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1625" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1626" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1626" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1626" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1626" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1626" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1627" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1627" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1627" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1627" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1627" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1628" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1628" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1628" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1628" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1628" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1629" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1629" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1629" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1629" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1629" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1630" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1630" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1630" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1630" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1630" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1631" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1631" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1631" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1631" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1631" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1632" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1632" s="0" t="inlineStr">
+        <is>
+          <t>cuteetc</t>
+        </is>
+      </c>
+      <c r="D1632" s="0" t="inlineStr">
+        <is>
+          <t>cute_cuteetc</t>
+        </is>
+      </c>
+      <c r="E1632" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1632" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1633" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1633" s="0" t="inlineStr">
+        <is>
+          <t>ejun_gofishing_day</t>
+        </is>
+      </c>
+      <c r="D1633" s="0" t="inlineStr">
+        <is>
+          <t>ejun_gofishing_day</t>
+        </is>
+      </c>
+      <c r="E1633" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1633" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1634" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1634" s="0" t="inlineStr">
+        <is>
+          <t>sisters</t>
+        </is>
+      </c>
+      <c r="D1634" s="0" t="inlineStr">
+        <is>
+          <t>fkt_sisters</t>
+        </is>
+      </c>
+      <c r="E1634" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1634" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1635" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1635" s="0" t="inlineStr">
+        <is>
+          <t>roses</t>
+        </is>
+      </c>
+      <c r="D1635" s="0" t="inlineStr">
+        <is>
+          <t>flwr_roses</t>
+        </is>
+      </c>
+      <c r="E1635" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1635" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1636" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1636" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D1636" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E1636" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1636" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1637" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1637" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="D1637" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forher</t>
+        </is>
+      </c>
+      <c r="E1637" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1637" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1638" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1638" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_family</t>
+        </is>
+      </c>
+      <c r="D1638" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_family</t>
+        </is>
+      </c>
+      <c r="E1638" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1638" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1639" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1639" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1639" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1639" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1639" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1640" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1640" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1640" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1640" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1640" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1641" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1641" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D1641" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E1641" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1641" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1642" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1642" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1642" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1642" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1642" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1643" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1643" s="0" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="D1643" s="0" t="inlineStr">
+        <is>
+          <t>bus_humor</t>
+        </is>
+      </c>
+      <c r="E1643" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1643" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1644" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1644" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="D1644" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugmonth</t>
+        </is>
+      </c>
+      <c r="E1644" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1644" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1645" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1645" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalpotato_day</t>
+        </is>
+      </c>
+      <c r="D1645" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalpotato_day</t>
+        </is>
+      </c>
+      <c r="E1645" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1645" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1646" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1646" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalradio_day</t>
+        </is>
+      </c>
+      <c r="D1646" s="0" t="inlineStr">
+        <is>
+          <t>eaug_nationalradio_day</t>
+        </is>
+      </c>
+      <c r="E1646" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1646" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1647" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1647" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="D1647" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="E1647" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1647" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1648" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1648" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D1648" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E1648" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1648" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1649" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1649" s="0" t="inlineStr">
+        <is>
+          <t>ejul_kissingday</t>
+        </is>
+      </c>
+      <c r="D1649" s="0" t="inlineStr">
+        <is>
+          <t>ejul_kissingday</t>
+        </is>
+      </c>
+      <c r="E1649" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1649" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1650" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1650" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sndsmileday</t>
+        </is>
+      </c>
+      <c r="D1650" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sndsmileday</t>
+        </is>
+      </c>
+      <c r="E1650" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1650" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1651" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1651" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_happy</t>
+        </is>
+      </c>
+      <c r="D1651" s="0" t="inlineStr">
+        <is>
+          <t>esep_roshhashanah_happy</t>
+        </is>
+      </c>
+      <c r="E1651" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1651" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1652" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1652" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1652" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E1652" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1652" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1653" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1653" s="0" t="inlineStr">
+        <is>
+          <t>keepintouch</t>
+        </is>
+      </c>
+      <c r="D1653" s="0" t="inlineStr">
+        <is>
+          <t>intouch_keepintouch</t>
+        </is>
+      </c>
+      <c r="E1653" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1653" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1654" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1654" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1654" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1654" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1654" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1655" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1655" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1655" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1655" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1655" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1656" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1656" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D1656" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E1656" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1656" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1657" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1657" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1657" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E1657" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1657" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1658" s="0" t="inlineStr">
+        <is>
+          <t>World languages</t>
+        </is>
+      </c>
+      <c r="C1658" s="0" t="inlineStr">
+        <is>
+          <t>russian_thankyou</t>
+        </is>
+      </c>
+      <c r="D1658" s="0" t="inlineStr">
+        <is>
+          <t>w_russian_thankyou</t>
+        </is>
+      </c>
+      <c r="E1658" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1658" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1659" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1659" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1659" s="0" t="inlineStr">
+        <is>
+          <t>anniv_milestone</t>
+        </is>
+      </c>
+      <c r="E1659" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1659" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1660" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1660" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1660" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1660" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1660" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1661" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1661" s="0" t="inlineStr">
+        <is>
+          <t>collassociates</t>
+        </is>
+      </c>
+      <c r="D1661" s="0" t="inlineStr">
+        <is>
+          <t>birth_collassociates</t>
+        </is>
+      </c>
+      <c r="E1661" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1661" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1662" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1662" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D1662" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E1662" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1662" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1663" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1663" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1663" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1663" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1663" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1664" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1664" s="0" t="inlineStr">
+        <is>
+          <t>atworketc</t>
+        </is>
+      </c>
+      <c r="D1664" s="0" t="inlineStr">
+        <is>
+          <t>bus_atworketc</t>
+        </is>
+      </c>
+      <c r="E1664" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1664" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1665" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1665" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D1665" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E1665" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1665" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1666" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1666" s="0" t="inlineStr">
+        <is>
+          <t>studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="D1666" s="0" t="inlineStr">
+        <is>
+          <t>congrats_studentsandnewgrads</t>
+        </is>
+      </c>
+      <c r="E1666" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1666" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1667" s="0" t="inlineStr">
+        <is>
+          <t>Cute</t>
+        </is>
+      </c>
+      <c r="C1667" s="0" t="inlineStr">
+        <is>
+          <t>hugs</t>
+        </is>
+      </c>
+      <c r="D1667" s="0" t="inlineStr">
+        <is>
+          <t>cute_hugs</t>
+        </is>
+      </c>
+      <c r="E1667" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1667" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1668" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1668" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="D1668" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beachparty_day</t>
+        </is>
+      </c>
+      <c r="E1668" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1668" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1669" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1669" s="0" t="inlineStr">
+        <is>
+          <t>eaug_spongecake_day</t>
+        </is>
+      </c>
+      <c r="D1669" s="0" t="inlineStr">
+        <is>
+          <t>eaug_spongecake_day</t>
+        </is>
+      </c>
+      <c r="E1669" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1669" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1670" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1670" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_missingu</t>
+        </is>
+      </c>
+      <c r="D1670" s="0" t="inlineStr">
+        <is>
+          <t>ejun_summer_missingu</t>
+        </is>
+      </c>
+      <c r="E1670" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1670" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1671" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1671" s="0" t="inlineStr">
+        <is>
+          <t>emay_mawlidalnabi</t>
+        </is>
+      </c>
+      <c r="D1671" s="0" t="inlineStr">
+        <is>
+          <t>emay_mawlidalnabi</t>
+        </is>
+      </c>
+      <c r="E1671" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1671" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1672" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1672" s="0" t="inlineStr">
+        <is>
+          <t>enov_flowerofthemonth</t>
+        </is>
+      </c>
+      <c r="D1672" s="0" t="inlineStr">
+        <is>
+          <t>enov_flowerofthemonth</t>
+        </is>
+      </c>
+      <c r="E1672" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1672" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1673" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1673" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_romance</t>
+        </is>
+      </c>
+      <c r="D1673" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_romance</t>
+        </is>
+      </c>
+      <c r="E1673" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1673" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1674" s="0" t="inlineStr">
+        <is>
+          <t>Family &amp; loved ones</t>
+        </is>
+      </c>
+      <c r="C1674" s="0" t="inlineStr">
+        <is>
+          <t>huswife</t>
+        </is>
+      </c>
+      <c r="D1674" s="0" t="inlineStr">
+        <is>
+          <t>fkt_huswife</t>
+        </is>
+      </c>
+      <c r="E1674" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1674" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1675" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1675" s="0" t="inlineStr">
+        <is>
+          <t>morningquotes</t>
+        </is>
+      </c>
+      <c r="D1675" s="0" t="inlineStr">
+        <is>
+          <t>gen_morningquotes</t>
+        </is>
+      </c>
+      <c r="E1675" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1675" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1676" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1676" s="0" t="inlineStr">
+        <is>
+          <t>nameday</t>
+        </is>
+      </c>
+      <c r="D1676" s="0" t="inlineStr">
+        <is>
+          <t>gen_nameday</t>
+        </is>
+      </c>
+      <c r="E1676" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1676" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1677" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1677" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="D1677" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_images</t>
+        </is>
+      </c>
+      <c r="E1677" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1677" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1678" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1678" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D1678" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E1678" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1678" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1679" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1679" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="D1679" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_goodmorning_images</t>
+        </is>
+      </c>
+      <c r="E1679" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1679" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1680" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1680" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D1680" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E1680" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1680" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1681" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1681" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D1681" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E1681" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1681" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1682" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1682" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1682" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1682" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1682" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1683" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1683" s="0" t="inlineStr">
+        <is>
+          <t>dating</t>
+        </is>
+      </c>
+      <c r="D1683" s="0" t="inlineStr">
+        <is>
+          <t>love_dating</t>
+        </is>
+      </c>
+      <c r="E1683" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1683" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1684" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1684" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1684" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1684" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1684" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1685" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1685" s="0" t="inlineStr">
+        <is>
+          <t>lovesongs</t>
+        </is>
+      </c>
+      <c r="D1685" s="0" t="inlineStr">
+        <is>
+          <t>love_lovesongs</t>
+        </is>
+      </c>
+      <c r="E1685" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1685" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1686" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1686" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D1686" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E1686" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1686" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1687" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1687" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D1687" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E1687" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1687" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1688" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1688" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1688" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E1688" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1688" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1689" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1689" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1689" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1689" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1689" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1690" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1690" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="D1690" s="0" t="inlineStr">
+        <is>
+          <t>wed_wishes</t>
+        </is>
+      </c>
+      <c r="E1690" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1690" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1691" s="4"/>
+      <c r="C1691" s="4"/>
+      <c r="D1691" s="4"/>
+      <c r="E1691" s="5">
+        <v>725</v>
+      </c>
+      <c r="F1691" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -56987,36 +59948,70 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>758</v>
+      </c>
+      <c r="C21" s="2">
+        <v>284</v>
+      </c>
+      <c r="D21" s="2">
+        <v>216</v>
+      </c>
+      <c r="E21" s="2">
+        <v>144</v>
+      </c>
+      <c r="F21" s="2">
+        <v>62</v>
+      </c>
+      <c r="G21" s="2">
+        <v>33</v>
+      </c>
+      <c r="H21" s="2">
+        <v>19</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="5">
-        <v>15568</v>
-      </c>
-      <c r="C21" s="5">
-        <v>4940</v>
-      </c>
-      <c r="D21" s="5">
-        <v>4856</v>
-      </c>
-      <c r="E21" s="5">
-        <v>3074</v>
-      </c>
-      <c r="F21" s="5">
-        <v>1549</v>
-      </c>
-      <c r="G21" s="5">
-        <v>633</v>
-      </c>
-      <c r="H21" s="5">
-        <v>487</v>
-      </c>
-      <c r="I21" s="5">
+      <c r="B22" s="5">
+        <v>16326</v>
+      </c>
+      <c r="C22" s="5">
+        <v>5224</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5072</v>
+      </c>
+      <c r="E22" s="5">
+        <v>3218</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1611</v>
+      </c>
+      <c r="G22" s="5">
+        <v>666</v>
+      </c>
+      <c r="H22" s="5">
+        <v>506</v>
+      </c>
+      <c r="I22" s="5">
         <v>28</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J22" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -247,7 +247,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -871,28 +871,56 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>769</v>
+      </c>
+      <c r="C22" s="2">
+        <v>541</v>
+      </c>
+      <c r="D22" s="2">
+        <v>228</v>
+      </c>
+      <c r="E22" s="2">
+        <v>735</v>
+      </c>
+      <c r="F22" s="2">
+        <v>34</v>
+      </c>
+      <c r="G22" s="2">
+        <v>255</v>
+      </c>
+      <c r="H22" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="5">
-        <v>16326</v>
-      </c>
-      <c r="C22" s="5">
-        <v>10870</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5456</v>
-      </c>
-      <c r="E22" s="5">
-        <v>15660</v>
-      </c>
-      <c r="F22" s="5">
-        <v>666</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="B23" s="5">
+        <v>17095</v>
+      </c>
+      <c r="C23" s="5">
+        <v>11411</v>
+      </c>
+      <c r="D23" s="5">
+        <v>5684</v>
+      </c>
+      <c r="E23" s="5">
+        <v>16395</v>
+      </c>
+      <c r="F23" s="5">
+        <v>700</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -910,8 +938,8 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
@@ -970,12 +998,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Congratulations</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Friendship</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -1050,10 +1078,10 @@
         <v>10</v>
       </c>
       <c r="J2" s="2">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2">
         <v>12</v>
-      </c>
-      <c r="K2" s="2">
-        <v>28</v>
       </c>
       <c r="L2" s="2">
         <v>1</v>
@@ -1111,10 +1139,10 @@
         <v>19</v>
       </c>
       <c r="J3" s="2">
+        <v>41</v>
+      </c>
+      <c r="K3" s="2">
         <v>11</v>
-      </c>
-      <c r="K3" s="2">
-        <v>41</v>
       </c>
       <c r="L3" s="2">
         <v>8</v>
@@ -1172,10 +1200,10 @@
         <v>16</v>
       </c>
       <c r="J4" s="2">
+        <v>11</v>
+      </c>
+      <c r="K4" s="2">
         <v>17</v>
-      </c>
-      <c r="K4" s="2">
-        <v>11</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1233,10 +1261,10 @@
         <v>15</v>
       </c>
       <c r="J5" s="2">
+        <v>22</v>
+      </c>
+      <c r="K5" s="2">
         <v>4</v>
-      </c>
-      <c r="K5" s="2">
-        <v>22</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -1294,10 +1322,10 @@
         <v>15</v>
       </c>
       <c r="J6" s="2">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2">
         <v>8</v>
-      </c>
-      <c r="K6" s="2">
-        <v>11</v>
       </c>
       <c r="L6" s="2">
         <v>17</v>
@@ -1355,10 +1383,10 @@
         <v>12</v>
       </c>
       <c r="J7" s="2">
+        <v>16</v>
+      </c>
+      <c r="K7" s="2">
         <v>10</v>
-      </c>
-      <c r="K7" s="2">
-        <v>16</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1416,10 +1444,10 @@
         <v>14</v>
       </c>
       <c r="J8" s="2">
+        <v>7</v>
+      </c>
+      <c r="K8" s="2">
         <v>8</v>
-      </c>
-      <c r="K8" s="2">
-        <v>7</v>
       </c>
       <c r="L8" s="2">
         <v>6</v>
@@ -1477,10 +1505,10 @@
         <v>14</v>
       </c>
       <c r="J9" s="2">
+        <v>10</v>
+      </c>
+      <c r="K9" s="2">
         <v>9</v>
-      </c>
-      <c r="K9" s="2">
-        <v>10</v>
       </c>
       <c r="L9" s="2">
         <v>39</v>
@@ -1538,10 +1566,10 @@
         <v>20</v>
       </c>
       <c r="J10" s="2">
+        <v>7</v>
+      </c>
+      <c r="K10" s="2">
         <v>6</v>
-      </c>
-      <c r="K10" s="2">
-        <v>7</v>
       </c>
       <c r="L10" s="2">
         <v>4</v>
@@ -1599,10 +1627,10 @@
         <v>16</v>
       </c>
       <c r="J11" s="2">
+        <v>11</v>
+      </c>
+      <c r="K11" s="2">
         <v>10</v>
-      </c>
-      <c r="K11" s="2">
-        <v>11</v>
       </c>
       <c r="L11" s="2">
         <v>3</v>
@@ -1660,10 +1688,10 @@
         <v>14</v>
       </c>
       <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2">
         <v>14</v>
-      </c>
-      <c r="K12" s="2">
-        <v>5</v>
       </c>
       <c r="L12" s="2">
         <v>2</v>
@@ -1721,10 +1749,10 @@
         <v>16</v>
       </c>
       <c r="J13" s="2">
+        <v>7</v>
+      </c>
+      <c r="K13" s="2">
         <v>5</v>
-      </c>
-      <c r="K13" s="2">
-        <v>7</v>
       </c>
       <c r="L13" s="2">
         <v>2</v>
@@ -1782,10 +1810,10 @@
         <v>12</v>
       </c>
       <c r="J14" s="2">
+        <v>2</v>
+      </c>
+      <c r="K14" s="2">
         <v>5</v>
-      </c>
-      <c r="K14" s="2">
-        <v>2</v>
       </c>
       <c r="L14" s="2">
         <v>3</v>
@@ -1843,10 +1871,10 @@
         <v>28</v>
       </c>
       <c r="J15" s="2">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2">
         <v>14</v>
-      </c>
-      <c r="K15" s="2">
-        <v>2</v>
       </c>
       <c r="L15" s="2">
         <v>3</v>
@@ -1904,10 +1932,10 @@
         <v>18</v>
       </c>
       <c r="J16" s="2">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2">
         <v>7</v>
-      </c>
-      <c r="K16" s="2">
-        <v>3</v>
       </c>
       <c r="L16" s="2">
         <v>1</v>
@@ -1965,10 +1993,10 @@
         <v>14</v>
       </c>
       <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="K17" s="2">
         <v>17</v>
-      </c>
-      <c r="K17" s="2">
-        <v>3</v>
       </c>
       <c r="L17" s="2">
         <v>1</v>
@@ -2026,10 +2054,10 @@
         <v>11</v>
       </c>
       <c r="J18" s="2">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2">
         <v>17</v>
-      </c>
-      <c r="K18" s="2">
-        <v>8</v>
       </c>
       <c r="L18" s="2">
         <v>7</v>
@@ -2087,10 +2115,10 @@
         <v>20</v>
       </c>
       <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
         <v>13</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
       </c>
       <c r="L19" s="2">
         <v>5</v>
@@ -2148,10 +2176,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2">
+        <v>2</v>
+      </c>
+      <c r="K20" s="2">
         <v>8</v>
-      </c>
-      <c r="K20" s="2">
-        <v>2</v>
       </c>
       <c r="L20" s="2">
         <v>2</v>
@@ -2209,10 +2237,10 @@
         <v>24</v>
       </c>
       <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
         <v>8</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0</v>
       </c>
       <c r="L21" s="2">
         <v>3</v>
@@ -2240,64 +2268,125 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>735</v>
+      </c>
+      <c r="C22" s="2">
+        <v>506</v>
+      </c>
+      <c r="D22" s="2">
+        <v>55</v>
+      </c>
+      <c r="E22" s="2">
+        <v>43</v>
+      </c>
+      <c r="F22" s="2">
+        <v>25</v>
+      </c>
+      <c r="G22" s="2">
+        <v>21</v>
+      </c>
+      <c r="H22" s="2">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2">
+        <v>11</v>
+      </c>
+      <c r="J22" s="2">
+        <v>25</v>
+      </c>
+      <c r="K22" s="2">
+        <v>15</v>
+      </c>
+      <c r="L22" s="2">
+        <v>4</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>5</v>
+      </c>
+      <c r="P22" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>1</v>
+      </c>
+      <c r="S22" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="5">
-        <v>15660</v>
-      </c>
-      <c r="C22" s="5">
-        <v>10297</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1478</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1003</v>
-      </c>
-      <c r="F22" s="5">
-        <v>798</v>
-      </c>
-      <c r="G22" s="5">
-        <v>569</v>
-      </c>
-      <c r="H22" s="5">
-        <v>371</v>
-      </c>
-      <c r="I22" s="5">
-        <v>330</v>
-      </c>
-      <c r="J22" s="5">
-        <v>203</v>
-      </c>
-      <c r="K22" s="5">
-        <v>197</v>
-      </c>
-      <c r="L22" s="5">
-        <v>107</v>
-      </c>
-      <c r="M22" s="5">
+      <c r="B23" s="5">
+        <v>16395</v>
+      </c>
+      <c r="C23" s="5">
+        <v>10803</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1533</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1046</v>
+      </c>
+      <c r="F23" s="5">
+        <v>823</v>
+      </c>
+      <c r="G23" s="5">
+        <v>590</v>
+      </c>
+      <c r="H23" s="5">
+        <v>387</v>
+      </c>
+      <c r="I23" s="5">
+        <v>341</v>
+      </c>
+      <c r="J23" s="5">
+        <v>222</v>
+      </c>
+      <c r="K23" s="5">
+        <v>218</v>
+      </c>
+      <c r="L23" s="5">
+        <v>111</v>
+      </c>
+      <c r="M23" s="5">
         <v>84</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N23" s="5">
         <v>81</v>
       </c>
-      <c r="O22" s="5">
-        <v>46</v>
-      </c>
-      <c r="P22" s="5">
-        <v>32</v>
-      </c>
-      <c r="Q22" s="5">
+      <c r="O23" s="5">
+        <v>51</v>
+      </c>
+      <c r="P23" s="5">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="5">
         <v>26</v>
       </c>
-      <c r="R22" s="5">
-        <v>23</v>
-      </c>
-      <c r="S22" s="5">
-        <v>15</v>
+      <c r="R23" s="5">
+        <v>24</v>
+      </c>
+      <c r="S23" s="5">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -12143,6 +12232,476 @@
       </c>
       <c r="H313" s="4"/>
     </row>
+    <row r="314">
+      <c r="A314" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B314" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C314" s="0" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="D314" s="2">
+        <v>369</v>
+      </c>
+      <c r="E314" s="2">
+        <v>137</v>
+      </c>
+      <c r="F314" s="2">
+        <v>506</v>
+      </c>
+      <c r="G314" s="3">
+        <v>0.6884353741496598</v>
+      </c>
+      <c r="H314" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B315" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C315" s="0" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D315" s="2">
+        <v>47</v>
+      </c>
+      <c r="E315" s="2">
+        <v>8</v>
+      </c>
+      <c r="F315" s="2">
+        <v>55</v>
+      </c>
+      <c r="G315" s="3">
+        <v>0.07482993197278912</v>
+      </c>
+      <c r="H315" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B316" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C316" s="0" t="inlineStr">
+        <is>
+          <t>anniv</t>
+        </is>
+      </c>
+      <c r="D316" s="2">
+        <v>32</v>
+      </c>
+      <c r="E316" s="2">
+        <v>11</v>
+      </c>
+      <c r="F316" s="2">
+        <v>43</v>
+      </c>
+      <c r="G316" s="3">
+        <v>0.058503401360544216</v>
+      </c>
+      <c r="H316" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B317" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C317" s="0" t="inlineStr">
+        <is>
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="D317" s="2">
+        <v>20</v>
+      </c>
+      <c r="E317" s="2">
+        <v>5</v>
+      </c>
+      <c r="F317" s="2">
+        <v>25</v>
+      </c>
+      <c r="G317" s="3">
+        <v>0.034013605442176874</v>
+      </c>
+      <c r="H317" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B318" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C318" s="0" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="D318" s="2">
+        <v>25</v>
+      </c>
+      <c r="E318" s="2">
+        <v>0</v>
+      </c>
+      <c r="F318" s="2">
+        <v>25</v>
+      </c>
+      <c r="G318" s="3">
+        <v>0.034013605442176874</v>
+      </c>
+      <c r="H318" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B319" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C319" s="0" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="D319" s="2">
+        <v>4</v>
+      </c>
+      <c r="E319" s="2">
+        <v>17</v>
+      </c>
+      <c r="F319" s="2">
+        <v>21</v>
+      </c>
+      <c r="G319" s="3">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="H319" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B320" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C320" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D320" s="2">
+        <v>13</v>
+      </c>
+      <c r="E320" s="2">
+        <v>3</v>
+      </c>
+      <c r="F320" s="2">
+        <v>16</v>
+      </c>
+      <c r="G320" s="3">
+        <v>0.021768707482993196</v>
+      </c>
+      <c r="H320" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B321" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C321" s="0" t="inlineStr">
+        <is>
+          <t>congrats</t>
+        </is>
+      </c>
+      <c r="D321" s="2">
+        <v>9</v>
+      </c>
+      <c r="E321" s="2">
+        <v>6</v>
+      </c>
+      <c r="F321" s="2">
+        <v>15</v>
+      </c>
+      <c r="G321" s="3">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="H321" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B322" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C322" s="0" t="inlineStr">
+        <is>
+          <t>insp</t>
+        </is>
+      </c>
+      <c r="D322" s="2">
+        <v>9</v>
+      </c>
+      <c r="E322" s="2">
+        <v>2</v>
+      </c>
+      <c r="F322" s="2">
+        <v>11</v>
+      </c>
+      <c r="G322" s="3">
+        <v>0.014965986394557823</v>
+      </c>
+      <c r="H322" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B323" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C323" s="0" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="D323" s="2">
+        <v>2</v>
+      </c>
+      <c r="E323" s="2">
+        <v>3</v>
+      </c>
+      <c r="F323" s="2">
+        <v>5</v>
+      </c>
+      <c r="G323" s="3">
+        <v>0.006802721088435374</v>
+      </c>
+      <c r="H323" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B324" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C324" s="0" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="D324" s="2">
+        <v>4</v>
+      </c>
+      <c r="E324" s="2">
+        <v>1</v>
+      </c>
+      <c r="F324" s="2">
+        <v>5</v>
+      </c>
+      <c r="G324" s="3">
+        <v>0.006802721088435374</v>
+      </c>
+      <c r="H324" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C325" s="0" t="inlineStr">
+        <is>
+          <t>flwr</t>
+        </is>
+      </c>
+      <c r="D325" s="2">
+        <v>1</v>
+      </c>
+      <c r="E325" s="2">
+        <v>3</v>
+      </c>
+      <c r="F325" s="2">
+        <v>4</v>
+      </c>
+      <c r="G325" s="3">
+        <v>0.005442176870748299</v>
+      </c>
+      <c r="H325" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B326" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C326" s="0" t="inlineStr">
+        <is>
+          <t>invp</t>
+        </is>
+      </c>
+      <c r="D326" s="2">
+        <v>1</v>
+      </c>
+      <c r="E326" s="2">
+        <v>2</v>
+      </c>
+      <c r="F326" s="2">
+        <v>3</v>
+      </c>
+      <c r="G326" s="3">
+        <v>0.004081632653061225</v>
+      </c>
+      <c r="H326" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B327" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C327" s="0" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D327" s="2">
+        <v>1</v>
+      </c>
+      <c r="E327" s="2">
+        <v>0</v>
+      </c>
+      <c r="F327" s="2">
+        <v>1</v>
+      </c>
+      <c r="G327" s="3">
+        <v>0.0013605442176870747</v>
+      </c>
+      <c r="H327" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-21</t>
+        </is>
+      </c>
+      <c r="B328" s="4"/>
+      <c r="C328" s="4"/>
+      <c r="D328" s="5">
+        <v>537</v>
+      </c>
+      <c r="E328" s="5">
+        <v>198</v>
+      </c>
+      <c r="F328" s="5">
+        <v>735</v>
+      </c>
+      <c r="G328" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H328" s="4"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -59229,6 +59788,2512 @@
         <v>725</v>
       </c>
       <c r="F1691" s="4"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1692" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1692" s="0" t="inlineStr">
+        <is>
+          <t>happybirthday</t>
+        </is>
+      </c>
+      <c r="D1692" s="0" t="inlineStr">
+        <is>
+          <t>birth_happybirthday</t>
+        </is>
+      </c>
+      <c r="E1692" s="2">
+        <v>384</v>
+      </c>
+      <c r="F1692" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1693" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1693" s="0" t="inlineStr">
+        <is>
+          <t>wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="D1693" s="0" t="inlineStr">
+        <is>
+          <t>anniv_wedanniv_couple</t>
+        </is>
+      </c>
+      <c r="E1693" s="2">
+        <v>38</v>
+      </c>
+      <c r="F1693" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1694" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1694" s="0" t="inlineStr">
+        <is>
+          <t>belated</t>
+        </is>
+      </c>
+      <c r="D1694" s="0" t="inlineStr">
+        <is>
+          <t>birth_belated</t>
+        </is>
+      </c>
+      <c r="E1694" s="2">
+        <v>27</v>
+      </c>
+      <c r="F1694" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1695" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1695" s="0" t="inlineStr">
+        <is>
+          <t>eaug_seniorcitizen_day</t>
+        </is>
+      </c>
+      <c r="D1695" s="0" t="inlineStr">
+        <is>
+          <t>eaug_seniorcitizen_day</t>
+        </is>
+      </c>
+      <c r="E1695" s="2">
+        <v>27</v>
+      </c>
+      <c r="F1695" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1696" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1696" s="0" t="inlineStr">
+        <is>
+          <t>thoughts</t>
+        </is>
+      </c>
+      <c r="D1696" s="0" t="inlineStr">
+        <is>
+          <t>friend_thoughts</t>
+        </is>
+      </c>
+      <c r="E1696" s="2">
+        <v>21</v>
+      </c>
+      <c r="F1696" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1697" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1697" s="0" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="D1697" s="0" t="inlineStr">
+        <is>
+          <t>birth_fun</t>
+        </is>
+      </c>
+      <c r="E1697" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1697" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1698" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1698" s="0" t="inlineStr">
+        <is>
+          <t>bronsis</t>
+        </is>
+      </c>
+      <c r="D1698" s="0" t="inlineStr">
+        <is>
+          <t>birth_bronsis</t>
+        </is>
+      </c>
+      <c r="E1698" s="2">
+        <v>14</v>
+      </c>
+      <c r="F1698" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1699" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1699" s="0" t="inlineStr">
+        <is>
+          <t>blessings</t>
+        </is>
+      </c>
+      <c r="D1699" s="0" t="inlineStr">
+        <is>
+          <t>birth_blessings</t>
+        </is>
+      </c>
+      <c r="E1699" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1699" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1700" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1700" s="0" t="inlineStr">
+        <is>
+          <t>sonanddaughter</t>
+        </is>
+      </c>
+      <c r="D1700" s="0" t="inlineStr">
+        <is>
+          <t>birth_sonanddaughter</t>
+        </is>
+      </c>
+      <c r="E1700" s="2">
+        <v>10</v>
+      </c>
+      <c r="F1700" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1701" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1701" s="0" t="inlineStr">
+        <is>
+          <t>friends</t>
+        </is>
+      </c>
+      <c r="D1701" s="0" t="inlineStr">
+        <is>
+          <t>birth_friends</t>
+        </is>
+      </c>
+      <c r="E1701" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1701" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1702" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1702" s="0" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="D1702" s="0" t="inlineStr">
+        <is>
+          <t>thank_birthday</t>
+        </is>
+      </c>
+      <c r="E1702" s="2">
+        <v>9</v>
+      </c>
+      <c r="F1702" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1703" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1703" s="0" t="inlineStr">
+        <is>
+          <t>wishes</t>
+        </is>
+      </c>
+      <c r="D1703" s="0" t="inlineStr">
+        <is>
+          <t>birth_wishes</t>
+        </is>
+      </c>
+      <c r="E1703" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1703" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1704" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1704" s="0" t="inlineStr">
+        <is>
+          <t>foreveryone</t>
+        </is>
+      </c>
+      <c r="D1704" s="0" t="inlineStr">
+        <is>
+          <t>congrats_foreveryone</t>
+        </is>
+      </c>
+      <c r="E1704" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1704" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1705" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1705" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1705" s="0" t="inlineStr">
+        <is>
+          <t>gen_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1705" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1705" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1706" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1706" s="0" t="inlineStr">
+        <is>
+          <t>sympathy</t>
+        </is>
+      </c>
+      <c r="D1706" s="0" t="inlineStr">
+        <is>
+          <t>insp_sympathy</t>
+        </is>
+      </c>
+      <c r="E1706" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1706" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1707" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1707" s="0" t="inlineStr">
+        <is>
+          <t>extfamily</t>
+        </is>
+      </c>
+      <c r="D1707" s="0" t="inlineStr">
+        <is>
+          <t>birth_extfamily</t>
+        </is>
+      </c>
+      <c r="E1707" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1707" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1708" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1708" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1708" s="0" t="inlineStr">
+        <is>
+          <t>gen_getwell</t>
+        </is>
+      </c>
+      <c r="E1708" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1708" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1709" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1709" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="D1709" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_crazy</t>
+        </is>
+      </c>
+      <c r="E1709" s="2">
+        <v>5</v>
+      </c>
+      <c r="F1709" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1710" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1710" s="0" t="inlineStr">
+        <is>
+          <t>anniversaryetc</t>
+        </is>
+      </c>
+      <c r="D1710" s="0" t="inlineStr">
+        <is>
+          <t>anniv_anniversaryetc</t>
+        </is>
+      </c>
+      <c r="E1710" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1710" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1711" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1711" s="0" t="inlineStr">
+        <is>
+          <t>songs</t>
+        </is>
+      </c>
+      <c r="D1711" s="0" t="inlineStr">
+        <is>
+          <t>birth_songs</t>
+        </is>
+      </c>
+      <c r="E1711" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1711" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1712" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1712" s="0" t="inlineStr">
+        <is>
+          <t>newhome</t>
+        </is>
+      </c>
+      <c r="D1712" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newhome</t>
+        </is>
+      </c>
+      <c r="E1712" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1712" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1713" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1713" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="D1713" s="0" t="inlineStr">
+        <is>
+          <t>eaug_smilemonth</t>
+        </is>
+      </c>
+      <c r="E1713" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1713" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1714" s="0" t="inlineStr">
+        <is>
+          <t>Friendship</t>
+        </is>
+      </c>
+      <c r="C1714" s="0" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="D1714" s="0" t="inlineStr">
+        <is>
+          <t>friend_hello</t>
+        </is>
+      </c>
+      <c r="E1714" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1714" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1715" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1715" s="0" t="inlineStr">
+        <is>
+          <t>sweetheart</t>
+        </is>
+      </c>
+      <c r="D1715" s="0" t="inlineStr">
+        <is>
+          <t>love_sweetheart</t>
+        </is>
+      </c>
+      <c r="E1715" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1715" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1716" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1716" s="0" t="inlineStr">
+        <is>
+          <t>inspirational</t>
+        </is>
+      </c>
+      <c r="D1716" s="0" t="inlineStr">
+        <is>
+          <t>thank_inspirational</t>
+        </is>
+      </c>
+      <c r="E1716" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1716" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1717" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1717" s="0" t="inlineStr">
+        <is>
+          <t>wed_flowers</t>
+        </is>
+      </c>
+      <c r="D1717" s="0" t="inlineStr">
+        <is>
+          <t>wed_flowers</t>
+        </is>
+      </c>
+      <c r="E1717" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1717" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1718" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1718" s="0" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="D1718" s="0" t="inlineStr">
+        <is>
+          <t>birth_milestone</t>
+        </is>
+      </c>
+      <c r="E1718" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1718" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1719" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1719" s="0" t="inlineStr">
+        <is>
+          <t>momndad</t>
+        </is>
+      </c>
+      <c r="D1719" s="0" t="inlineStr">
+        <is>
+          <t>birth_momndad</t>
+        </is>
+      </c>
+      <c r="E1719" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1719" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1720" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1720" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1720" s="0" t="inlineStr">
+        <is>
+          <t>flwr_love</t>
+        </is>
+      </c>
+      <c r="E1720" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1720" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1721" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1721" s="0" t="inlineStr">
+        <is>
+          <t>morningquotes</t>
+        </is>
+      </c>
+      <c r="D1721" s="0" t="inlineStr">
+        <is>
+          <t>gen_morningquotes</t>
+        </is>
+      </c>
+      <c r="E1721" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1721" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1722" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1722" s="0" t="inlineStr">
+        <is>
+          <t>encour</t>
+        </is>
+      </c>
+      <c r="D1722" s="0" t="inlineStr">
+        <is>
+          <t>insp_encour</t>
+        </is>
+      </c>
+      <c r="E1722" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1722" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1723" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1723" s="0" t="inlineStr">
+        <is>
+          <t>thinkingofyou</t>
+        </is>
+      </c>
+      <c r="D1723" s="0" t="inlineStr">
+        <is>
+          <t>intouch_thinkingofyou</t>
+        </is>
+      </c>
+      <c r="E1723" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1723" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1724" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1724" s="0" t="inlineStr">
+        <is>
+          <t>getwell</t>
+        </is>
+      </c>
+      <c r="D1724" s="0" t="inlineStr">
+        <is>
+          <t>pet_getwell</t>
+        </is>
+      </c>
+      <c r="E1724" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1724" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1725" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1725" s="0" t="inlineStr">
+        <is>
+          <t>everyday</t>
+        </is>
+      </c>
+      <c r="D1725" s="0" t="inlineStr">
+        <is>
+          <t>thank_everyday</t>
+        </is>
+      </c>
+      <c r="E1725" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1725" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1726" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1726" s="0" t="inlineStr">
+        <is>
+          <t>wedding</t>
+        </is>
+      </c>
+      <c r="D1726" s="0" t="inlineStr">
+        <is>
+          <t>thank_wedding</t>
+        </is>
+      </c>
+      <c r="E1726" s="2">
+        <v>3</v>
+      </c>
+      <c r="F1726" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1727" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1727" s="0" t="inlineStr">
+        <is>
+          <t>flowers</t>
+        </is>
+      </c>
+      <c r="D1727" s="0" t="inlineStr">
+        <is>
+          <t>birth_flowers</t>
+        </is>
+      </c>
+      <c r="E1727" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1727" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1728" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1728" s="0" t="inlineStr">
+        <is>
+          <t>missyou</t>
+        </is>
+      </c>
+      <c r="D1728" s="0" t="inlineStr">
+        <is>
+          <t>birth_missyou</t>
+        </is>
+      </c>
+      <c r="E1728" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1728" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1729" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1729" s="0" t="inlineStr">
+        <is>
+          <t>zodiac</t>
+        </is>
+      </c>
+      <c r="D1729" s="0" t="inlineStr">
+        <is>
+          <t>birth_zodiac</t>
+        </is>
+      </c>
+      <c r="E1729" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1729" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1730" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1730" s="0" t="inlineStr">
+        <is>
+          <t>newbaby</t>
+        </is>
+      </c>
+      <c r="D1730" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newbaby</t>
+        </is>
+      </c>
+      <c r="E1730" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1730" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1731" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1731" s="0" t="inlineStr">
+        <is>
+          <t>newcarandlicense</t>
+        </is>
+      </c>
+      <c r="D1731" s="0" t="inlineStr">
+        <is>
+          <t>congrats_newcarandlicense</t>
+        </is>
+      </c>
+      <c r="E1731" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1731" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1732" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1732" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="D1732" s="0" t="inlineStr">
+        <is>
+          <t>eaug_hugsweetheartday</t>
+        </is>
+      </c>
+      <c r="E1732" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1732" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1733" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1733" s="0" t="inlineStr">
+        <is>
+          <t>esep_flowerofthemonth</t>
+        </is>
+      </c>
+      <c r="D1733" s="0" t="inlineStr">
+        <is>
+          <t>esep_flowerofthemonth</t>
+        </is>
+      </c>
+      <c r="E1733" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1733" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1734" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1734" s="0" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="D1734" s="0" t="inlineStr">
+        <is>
+          <t>gen_hi</t>
+        </is>
+      </c>
+      <c r="E1734" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1734" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1735" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1735" s="0" t="inlineStr">
+        <is>
+          <t>hvgtday</t>
+        </is>
+      </c>
+      <c r="D1735" s="0" t="inlineStr">
+        <is>
+          <t>gen_hvgtday</t>
+        </is>
+      </c>
+      <c r="E1735" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1735" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1736" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1736" s="0" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D1736" s="0" t="inlineStr">
+        <is>
+          <t>gen_morning</t>
+        </is>
+      </c>
+      <c r="E1736" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1736" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1737" s="0" t="inlineStr">
+        <is>
+          <t>Keeping in touch</t>
+        </is>
+      </c>
+      <c r="C1737" s="0" t="inlineStr">
+        <is>
+          <t>justbecause</t>
+        </is>
+      </c>
+      <c r="D1737" s="0" t="inlineStr">
+        <is>
+          <t>intouch_justbecause</t>
+        </is>
+      </c>
+      <c r="E1737" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1737" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1738" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1738" s="0" t="inlineStr">
+        <is>
+          <t>otherinvitations</t>
+        </is>
+      </c>
+      <c r="D1738" s="0" t="inlineStr">
+        <is>
+          <t>invp_otherinvitations</t>
+        </is>
+      </c>
+      <c r="E1738" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1738" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1739" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1739" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_general</t>
+        </is>
+      </c>
+      <c r="D1739" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_general</t>
+        </is>
+      </c>
+      <c r="E1739" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1739" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1740" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1740" s="0" t="inlineStr">
+        <is>
+          <t>lovepoems</t>
+        </is>
+      </c>
+      <c r="D1740" s="0" t="inlineStr">
+        <is>
+          <t>love_lovepoems</t>
+        </is>
+      </c>
+      <c r="E1740" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1740" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1741" s="0" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="C1741" s="0" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="D1741" s="0" t="inlineStr">
+        <is>
+          <t>thank_love</t>
+        </is>
+      </c>
+      <c r="E1741" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1741" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1742" s="0" t="inlineStr">
+        <is>
+          <t>Anniversary</t>
+        </is>
+      </c>
+      <c r="C1742" s="0" t="inlineStr">
+        <is>
+          <t>ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="D1742" s="0" t="inlineStr">
+        <is>
+          <t>anniv_ouranniversary_forhim</t>
+        </is>
+      </c>
+      <c r="E1742" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1742" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1743" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1743" s="0" t="inlineStr">
+        <is>
+          <t>forher</t>
+        </is>
+      </c>
+      <c r="D1743" s="0" t="inlineStr">
+        <is>
+          <t>birth_forher</t>
+        </is>
+      </c>
+      <c r="E1743" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1743" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1744" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1744" s="0" t="inlineStr">
+        <is>
+          <t>forhim</t>
+        </is>
+      </c>
+      <c r="D1744" s="0" t="inlineStr">
+        <is>
+          <t>birth_forhim</t>
+        </is>
+      </c>
+      <c r="E1744" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1744" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1745" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1745" s="0" t="inlineStr">
+        <is>
+          <t>grandparents</t>
+        </is>
+      </c>
+      <c r="D1745" s="0" t="inlineStr">
+        <is>
+          <t>birth_grandparents</t>
+        </is>
+      </c>
+      <c r="E1745" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1745" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1746" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1746" s="0" t="inlineStr">
+        <is>
+          <t>hubbywife</t>
+        </is>
+      </c>
+      <c r="D1746" s="0" t="inlineStr">
+        <is>
+          <t>birth_hubbywife</t>
+        </is>
+      </c>
+      <c r="E1746" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1746" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1747" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1747" s="0" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="D1747" s="0" t="inlineStr">
+        <is>
+          <t>birth_kids</t>
+        </is>
+      </c>
+      <c r="E1747" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1747" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1748" s="0" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="C1748" s="0" t="inlineStr">
+        <is>
+          <t>specials</t>
+        </is>
+      </c>
+      <c r="D1748" s="0" t="inlineStr">
+        <is>
+          <t>birth_specials</t>
+        </is>
+      </c>
+      <c r="E1748" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1748" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1749" s="0" t="inlineStr">
+        <is>
+          <t>Business &amp; work</t>
+        </is>
+      </c>
+      <c r="C1749" s="0" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="D1749" s="0" t="inlineStr">
+        <is>
+          <t>bus_humor</t>
+        </is>
+      </c>
+      <c r="E1749" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1749" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1750" s="0" t="inlineStr">
+        <is>
+          <t>Congratulations</t>
+        </is>
+      </c>
+      <c r="C1750" s="0" t="inlineStr">
+        <is>
+          <t>onotheroccasions</t>
+        </is>
+      </c>
+      <c r="D1750" s="0" t="inlineStr">
+        <is>
+          <t>congrats_onotheroccasions</t>
+        </is>
+      </c>
+      <c r="E1750" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1750" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1751" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1751" s="0" t="inlineStr">
+        <is>
+          <t>eapr_goodfriday</t>
+        </is>
+      </c>
+      <c r="D1751" s="0" t="inlineStr">
+        <is>
+          <t>eapr_goodfriday</t>
+        </is>
+      </c>
+      <c r="E1751" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1751" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1752" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1752" s="0" t="inlineStr">
+        <is>
+          <t>eaug_bananasplit_day</t>
+        </is>
+      </c>
+      <c r="D1752" s="0" t="inlineStr">
+        <is>
+          <t>eaug_bananasplit_day</t>
+        </is>
+      </c>
+      <c r="E1752" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1752" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1753" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1753" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beanangelday</t>
+        </is>
+      </c>
+      <c r="D1753" s="0" t="inlineStr">
+        <is>
+          <t>eaug_beanangelday</t>
+        </is>
+      </c>
+      <c r="E1753" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1753" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1754" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1754" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="D1754" s="0" t="inlineStr">
+        <is>
+          <t>eaug_cardssister</t>
+        </is>
+      </c>
+      <c r="E1754" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1754" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1755" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1755" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="D1755" s="0" t="inlineStr">
+        <is>
+          <t>eaug_friendshipday_happy</t>
+        </is>
+      </c>
+      <c r="E1755" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1755" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1756" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1756" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="D1756" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_happy</t>
+        </is>
+      </c>
+      <c r="E1756" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1756" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1757" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1757" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_interactive</t>
+        </is>
+      </c>
+      <c r="D1757" s="0" t="inlineStr">
+        <is>
+          <t>eaug_rakshabandhan_interactive</t>
+        </is>
+      </c>
+      <c r="E1757" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1757" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1758" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1758" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="D1758" s="0" t="inlineStr">
+        <is>
+          <t>eaug_romawaremonth</t>
+        </is>
+      </c>
+      <c r="E1758" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1758" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1759" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1759" s="0" t="inlineStr">
+        <is>
+          <t>eaug_womensequality_day</t>
+        </is>
+      </c>
+      <c r="D1759" s="0" t="inlineStr">
+        <is>
+          <t>eaug_womensequality_day</t>
+        </is>
+      </c>
+      <c r="E1759" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1759" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1760" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1760" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="D1760" s="0" t="inlineStr">
+        <is>
+          <t>ejan_thankyoucards</t>
+        </is>
+      </c>
+      <c r="E1760" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1760" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1761" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1761" s="0" t="inlineStr">
+        <is>
+          <t>eoct_nationaliloveyou_day</t>
+        </is>
+      </c>
+      <c r="D1761" s="0" t="inlineStr">
+        <is>
+          <t>eoct_nationaliloveyou_day</t>
+        </is>
+      </c>
+      <c r="E1761" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1761" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1762" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1762" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_hugnkiss</t>
+        </is>
+      </c>
+      <c r="D1762" s="0" t="inlineStr">
+        <is>
+          <t>eoct_sweetday_hugnkiss</t>
+        </is>
+      </c>
+      <c r="E1762" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1762" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1763" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1763" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_poem</t>
+        </is>
+      </c>
+      <c r="D1763" s="0" t="inlineStr">
+        <is>
+          <t>esep_fall_poem</t>
+        </is>
+      </c>
+      <c r="E1763" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1763" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1764" s="0" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C1764" s="0" t="inlineStr">
+        <is>
+          <t>flrwishes</t>
+        </is>
+      </c>
+      <c r="D1764" s="0" t="inlineStr">
+        <is>
+          <t>flwr_flrwishes</t>
+        </is>
+      </c>
+      <c r="E1764" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1764" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1765" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1765" s="0" t="inlineStr">
+        <is>
+          <t>goodnight</t>
+        </is>
+      </c>
+      <c r="D1765" s="0" t="inlineStr">
+        <is>
+          <t>gen_goodnight</t>
+        </is>
+      </c>
+      <c r="E1765" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1765" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1766" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1766" s="0" t="inlineStr">
+        <is>
+          <t>quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="D1766" s="0" t="inlineStr">
+        <is>
+          <t>gen_quotesmessages_images_getwell_messages</t>
+        </is>
+      </c>
+      <c r="E1766" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1766" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1767" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1767" s="0" t="inlineStr">
+        <is>
+          <t>sorry</t>
+        </is>
+      </c>
+      <c r="D1767" s="0" t="inlineStr">
+        <is>
+          <t>gen_sorry</t>
+        </is>
+      </c>
+      <c r="E1767" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1767" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1768" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1768" s="0" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+      <c r="D1768" s="0" t="inlineStr">
+        <is>
+          <t>gen_voyage</t>
+        </is>
+      </c>
+      <c r="E1768" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1768" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1769" s="0" t="inlineStr">
+        <is>
+          <t>Everyday greetings</t>
+        </is>
+      </c>
+      <c r="C1769" s="0" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D1769" s="0" t="inlineStr">
+        <is>
+          <t>gen_weekend</t>
+        </is>
+      </c>
+      <c r="E1769" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1769" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1770" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1770" s="0" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1770" s="0" t="inlineStr">
+        <is>
+          <t>insp_health</t>
+        </is>
+      </c>
+      <c r="E1770" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1770" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1771" s="0" t="inlineStr">
+        <is>
+          <t>Inspirational &amp; sympathy</t>
+        </is>
+      </c>
+      <c r="C1771" s="0" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="D1771" s="0" t="inlineStr">
+        <is>
+          <t>insp_recovery</t>
+        </is>
+      </c>
+      <c r="E1771" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1771" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1772" s="0" t="inlineStr">
+        <is>
+          <t>Invitations &amp; parties</t>
+        </is>
+      </c>
+      <c r="C1772" s="0" t="inlineStr">
+        <is>
+          <t>birth_gen</t>
+        </is>
+      </c>
+      <c r="D1772" s="0" t="inlineStr">
+        <is>
+          <t>invp_birth_gen</t>
+        </is>
+      </c>
+      <c r="E1772" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1772" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1773" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1773" s="0" t="inlineStr">
+        <is>
+          <t>iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="D1773" s="0" t="inlineStr">
+        <is>
+          <t>love_iloveyou_couples</t>
+        </is>
+      </c>
+      <c r="E1773" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1773" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1774" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1774" s="0" t="inlineStr">
+        <is>
+          <t>missing_forher</t>
+        </is>
+      </c>
+      <c r="D1774" s="0" t="inlineStr">
+        <is>
+          <t>love_missing_forher</t>
+        </is>
+      </c>
+      <c r="E1774" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1774" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1775" s="0" t="inlineStr">
+        <is>
+          <t>Love &amp; romance</t>
+        </is>
+      </c>
+      <c r="C1775" s="0" t="inlineStr">
+        <is>
+          <t>newlove</t>
+        </is>
+      </c>
+      <c r="D1775" s="0" t="inlineStr">
+        <is>
+          <t>love_newlove</t>
+        </is>
+      </c>
+      <c r="E1775" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1775" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1776" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1776" s="0" t="inlineStr">
+        <is>
+          <t>hihello</t>
+        </is>
+      </c>
+      <c r="D1776" s="0" t="inlineStr">
+        <is>
+          <t>pet_hihello</t>
+        </is>
+      </c>
+      <c r="E1776" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1776" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1777" s="0" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="C1777" s="0" t="inlineStr">
+        <is>
+          <t>lossofpet</t>
+        </is>
+      </c>
+      <c r="D1777" s="0" t="inlineStr">
+        <is>
+          <t>pet_lossofpet</t>
+        </is>
+      </c>
+      <c r="E1777" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1777" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1778" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1778" s="0" t="inlineStr">
+        <is>
+          <t>wed_justmarried</t>
+        </is>
+      </c>
+      <c r="D1778" s="0" t="inlineStr">
+        <is>
+          <t>wed_justmarried</t>
+        </is>
+      </c>
+      <c r="E1778" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1778" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1779" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1779" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1779" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1779" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1779" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1780" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1780" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="D1780" s="0" t="inlineStr">
+        <is>
+          <t>wed_weddingetc</t>
+        </is>
+      </c>
+      <c r="E1780" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1780" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL 2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1781" s="4"/>
+      <c r="C1781" s="4"/>
+      <c r="D1781" s="4"/>
+      <c r="E1781" s="5">
+        <v>735</v>
+      </c>
+      <c r="F1781" s="4"/>
     </row>
   </sheetData>
 </worksheet>
@@ -59982,36 +63047,70 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>769</v>
+      </c>
+      <c r="C22" s="2">
+        <v>270</v>
+      </c>
+      <c r="D22" s="2">
+        <v>228</v>
+      </c>
+      <c r="E22" s="2">
+        <v>154</v>
+      </c>
+      <c r="F22" s="2">
+        <v>66</v>
+      </c>
+      <c r="G22" s="2">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="5">
-        <v>16326</v>
-      </c>
-      <c r="C22" s="5">
-        <v>5224</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5072</v>
-      </c>
-      <c r="E22" s="5">
-        <v>3218</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1611</v>
-      </c>
-      <c r="G22" s="5">
-        <v>666</v>
-      </c>
-      <c r="H22" s="5">
-        <v>506</v>
-      </c>
-      <c r="I22" s="5">
+      <c r="B23" s="5">
+        <v>17095</v>
+      </c>
+      <c r="C23" s="5">
+        <v>5494</v>
+      </c>
+      <c r="D23" s="5">
+        <v>5300</v>
+      </c>
+      <c r="E23" s="5">
+        <v>3372</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1677</v>
+      </c>
+      <c r="G23" s="5">
+        <v>696</v>
+      </c>
+      <c r="H23" s="5">
+        <v>527</v>
+      </c>
+      <c r="I23" s="5">
         <v>28</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J23" s="5">
         <v>1</v>
       </c>
     </row>

--- a/reports/daily_tracking.xlsx
+++ b/reports/daily_tracking.xlsx
@@ -886,10 +886,10 @@
         <v>228</v>
       </c>
       <c r="E22" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F22" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G22" s="2">
         <v>255</v>
@@ -914,10 +914,10 @@
         <v>5684</v>
       </c>
       <c r="E23" s="5">
-        <v>16395</v>
+        <v>16399</v>
       </c>
       <c r="F23" s="5">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C22" s="2">
         <v>506</v>
@@ -2292,7 +2292,7 @@
         <v>21</v>
       </c>
       <c r="H22" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2">
         <v>11</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <v>16395</v>
+        <v>16399</v>
       </c>
       <c r="C23" s="5">
         <v>10803</v>
@@ -2353,7 +2353,7 @@
         <v>590</v>
       </c>
       <c r="H23" s="5">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I23" s="5">
         <v>341</v>
@@ -12258,7 +12258,7 @@
         <v>506</v>
       </c>
       <c r="G314" s="3">
-        <v>0.6884353741496598</v>
+        <v>0.6847090663058186</v>
       </c>
       <c r="H314" s="2">
         <v>123</v>
@@ -12290,7 +12290,7 @@
         <v>55</v>
       </c>
       <c r="G315" s="3">
-        <v>0.07482993197278912</v>
+        <v>0.07442489851150202</v>
       </c>
       <c r="H315" s="2">
         <v>26</v>
@@ -12322,7 +12322,7 @@
         <v>43</v>
       </c>
       <c r="G316" s="3">
-        <v>0.058503401360544216</v>
+        <v>0.058186738836265225</v>
       </c>
       <c r="H316" s="2">
         <v>22</v>
@@ -12354,7 +12354,7 @@
         <v>25</v>
       </c>
       <c r="G317" s="3">
-        <v>0.034013605442176874</v>
+        <v>0.03382949932341001</v>
       </c>
       <c r="H317" s="2">
         <v>18</v>
@@ -12386,7 +12386,7 @@
         <v>25</v>
       </c>
       <c r="G318" s="3">
-        <v>0.034013605442176874</v>
+        <v>0.03382949932341001</v>
       </c>
       <c r="H318" s="2">
         <v>9</v>
@@ -12418,7 +12418,7 @@
         <v>21</v>
       </c>
       <c r="G319" s="3">
-        <v>0.02857142857142857</v>
+        <v>0.028416779431664412</v>
       </c>
       <c r="H319" s="2">
         <v>9</v>
@@ -12441,19 +12441,19 @@
         </is>
       </c>
       <c r="D320" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E320" s="2">
         <v>3</v>
       </c>
       <c r="F320" s="2">
+        <v>20</v>
+      </c>
+      <c r="G320" s="3">
+        <v>0.02706359945872801</v>
+      </c>
+      <c r="H320" s="2">
         <v>16</v>
-      </c>
-      <c r="G320" s="3">
-        <v>0.021768707482993196</v>
-      </c>
-      <c r="H320" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="321">
@@ -12482,7 +12482,7 @@
         <v>15</v>
       </c>
       <c r="G321" s="3">
-        <v>0.02040816326530612</v>
+        <v>0.02029769959404601</v>
       </c>
       <c r="H321" s="2">
         <v>10</v>
@@ -12514,7 +12514,7 @@
         <v>11</v>
       </c>
       <c r="G322" s="3">
-        <v>0.014965986394557823</v>
+        <v>0.014884979702300407</v>
       </c>
       <c r="H322" s="2">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>5</v>
       </c>
       <c r="G323" s="3">
-        <v>0.006802721088435374</v>
+        <v>0.006765899864682003</v>
       </c>
       <c r="H323" s="2">
         <v>2</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G324" s="3">
-        <v>0.006802721088435374</v>
+        <v>0.006765899864682003</v>
       </c>
       <c r="H324" s="2">
         <v>5</v>
@@ -12610,7 +12610,7 @@
         <v>4</v>
       </c>
       <c r="G325" s="3">
-        <v>0.005442176870748299</v>
+        <v>0.005412719891745603</v>
       </c>
       <c r="H325" s="2">
         <v>2</v>
@@ -12642,7 +12642,7 @@
         <v>3</v>
       </c>
       <c r="G326" s="3">
-        <v>0.004081632653061225</v>
+        <v>0.0040595399188092015</v>
       </c>
       <c r="H326" s="2">
         <v>2</v>
@@ -12674,7 +12674,7 @@
         <v>1</v>
       </c>
       <c r="G327" s="3">
-        <v>0.0013605442176870747</v>
+        <v>0.0013531799729364006</v>
       </c>
       <c r="H327" s="2">
         <v>1</v>
@@ -12689,13 +12689,13 @@
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
       <c r="D328" s="5">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E328" s="5">
         <v>198</v>
       </c>
       <c r="F328" s="5">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="G328" s="5">
         <v>1.0</v>
@@ -60446,19 +60446,19 @@
       </c>
       <c r="C1715" s="0" t="inlineStr">
         <is>
-          <t>sweetheart</t>
+          <t>iloveyou_kisses</t>
         </is>
       </c>
       <c r="D1715" s="0" t="inlineStr">
         <is>
-          <t>love_sweetheart</t>
+          <t>love_iloveyou_kisses</t>
         </is>
       </c>
       <c r="E1715" s="2">
         <v>4</v>
       </c>
       <c r="F1715" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1716">
@@ -60469,24 +60469,24 @@
       </c>
       <c r="B1716" s="0" t="inlineStr">
         <is>
-          <t>Thank you</t>
+          <t>Love &amp; romance</t>
         </is>
       </c>
       <c r="C1716" s="0" t="inlineStr">
         <is>
-          <t>inspirational</t>
+          <t>sweetheart</t>
         </is>
       </c>
       <c r="D1716" s="0" t="inlineStr">
         <is>
-          <t>thank_inspirational</t>
+          <t>love_sweetheart</t>
         </is>
       </c>
       <c r="E1716" s="2">
         <v>4</v>
       </c>
       <c r="F1716" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1717">
@@ -60497,24 +60497,24 @@
       </c>
       <c r="B1717" s="0" t="inlineStr">
         <is>
-          <t>Events cards</t>
+          <t>Thank you</t>
         </is>
       </c>
       <c r="C1717" s="0" t="inlineStr">
         <is>
-          <t>wed_flowers</t>
+          <t>inspirational</t>
         </is>
       </c>
       <c r="D1717" s="0" t="inlineStr">
         <is>
-          <t>wed_flowers</t>
+          <t>thank_inspirational</t>
         </is>
       </c>
       <c r="E1717" s="2">
         <v>4</v>
       </c>
       <c r="F1717" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1718">
@@ -60525,24 +60525,24 @@
       </c>
       <c r="B1718" s="0" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>Events cards</t>
         </is>
       </c>
       <c r="C1718" s="0" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>wed_flowers</t>
         </is>
       </c>
       <c r="D1718" s="0" t="inlineStr">
         <is>
-          <t>birth_milestone</t>
+          <t>wed_flowers</t>
         </is>
       </c>
       <c r="E1718" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1718" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1719">
@@ -60558,12 +60558,12 @@
       </c>
       <c r="C1719" s="0" t="inlineStr">
         <is>
-          <t>momndad</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="D1719" s="0" t="inlineStr">
         <is>
-          <t>birth_momndad</t>
+          <t>birth_milestone</t>
         </is>
       </c>
       <c r="E1719" s="2">
@@ -60581,24 +60581,24 @@
       </c>
       <c r="B1720" s="0" t="inlineStr">
         <is>
-          <t>Flowers</t>
+          <t>Birthday</t>
         </is>
       </c>
       <c r="C1720" s="0" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>momndad</t>
         </is>
       </c>
       <c r="D1720" s="0" t="inlineStr">
         <is>
-          <t>flwr_love</t>
+          <t>birth_momndad</t>
         </is>
       </c>
       <c r="E1720" s="2">
         <v>3</v>
       </c>
       <c r="F1720" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1721">
@@ -60609,17 +60609,17 @@
       </c>
       <c r="B1721" s="0" t="inlineStr">
         <is>
-          <t>Everyday greetings</t>
+          <t>Flowers</t>
         </is>
       </c>
       <c r="C1721" s="0" t="inlineStr">
         <is>
-          <t>morningquotes</t>
+          <t>love</t>
         </is>
       </c>
       <c r="D1721" s="0" t="inlineStr">
         <is>
-          <t>gen_morningquotes</t>
+          <t>flwr_love</t>
         </is>
       </c>
       <c r="E1721" s="2">
@@ -60637,24 +60637,24 @@
       </c>
       <c r="B1722" s="0" t="inlineStr">
         <is>
-          <t>Inspirational &amp; sympathy</t>
+          <t>Everyday greetings</t>
         </is>
       </c>
       <c r="C1722" s="0" t="inlineStr">
         <is>
-          <t>encour</t>
+          <t>morningquotes</t>
         </is>
       </c>
       <c r="D1722" s="0" t="inlineStr">
         <is>
-          <t>insp_encour</t>
+          <t>gen_morningquotes</t>
         </is>
       </c>
       <c r="E1722" s="2">
         <v>3</v>
       </c>
       <c r="F1722" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1723">
@@ -60665,24 +60665,24 @@
       </c>
       <c r="B1723" s="0" t="inlineStr">
         <is>
-          <t>Keeping in touch</t>
+          <t>Inspirational &amp; sympathy</t>
         </is>
       </c>
       <c r="C1723" s="0" t="inlineStr">
         <is>
-          <t>thinkingofyou</t>
+          <t>encour</t>
         </is>
       </c>
       <c r="D1723" s="0" t="inlineStr">
         <is>
-          <t>intouch_thinkingofyou</t>
+          <t>insp_encour</t>
         </is>
       </c>
       <c r="E1723" s="2">
         <v>3</v>
       </c>
       <c r="F1723" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1724">
@@ -60693,24 +60693,24 @@
       </c>
       <c r="B1724" s="0" t="inlineStr">
         <is>
-          <t>Pets</t>
+          <t>Keeping in touch</t>
         </is>
       </c>
       <c r="C1724" s="0" t="inlineStr">
         <is>
-          <t>getwell</t>
+          <t>thinkingofyou</t>
         </is>
       </c>
       <c r="D1724" s="0" t="inlineStr">
         <is>
-          <t>pet_getwell</t>
+          <t>intouch_thinkingofyou</t>
         </is>
       </c>
       <c r="E1724" s="2">
         <v>3</v>
       </c>
       <c r="F1724" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1725">
@@ -60721,24 +60721,24 @@
       </c>
       <c r="B1725" s="0" t="inlineStr">
         <is>
-          <t>Thank you</t>
+          <t>Pets</t>
         </is>
       </c>
       <c r="C1725" s="0" t="inlineStr">
         <is>
-          <t>everyday</t>
+          <t>getwell</t>
         </is>
       </c>
       <c r="D1725" s="0" t="inlineStr">
         <is>
-          <t>thank_everyday</t>
+          <t>pet_getwell</t>
         </is>
       </c>
       <c r="E1725" s="2">
         <v>3</v>
       </c>
       <c r="F1725" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1726">
@@ -60754,19 +60754,19 @@
       </c>
       <c r="C1726" s="0" t="inlineStr">
         <is>
-          <t>wedding</t>
+          <t>everyday</t>
         </is>
       </c>
       <c r="D1726" s="0" t="inlineStr">
         <is>
-          <t>thank_wedding</t>
+          <t>thank_everyday</t>
         </is>
       </c>
       <c r="E1726" s="2">
         <v>3</v>
       </c>
       <c r="F1726" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1727">
@@ -60777,21 +60777,21 @@
       </c>
       <c r="B1727" s="0" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>Thank you</t>
         </is>
       </c>
       <c r="C1727" s="0" t="inlineStr">
         <is>
-          <t>flowers</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="D1727" s="0" t="inlineStr">
         <is>
-          <t>birth_flowers</t>
+          <t>thank_wedding</t>
         </is>
       </c>
       <c r="E1727" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1727" s="2">
         <v>1</v>
@@ -60810,12 +60810,12 @@
       </c>
       <c r="C1728" s="0" t="inlineStr">
         <is>
-          <t>missyou</t>
+          <t>flowers</t>
         </is>
       </c>
       <c r="D1728" s="0" t="inlineStr">
         <is>
-          <t>birth_missyou</t>
+          <t>birth_flowers</t>
         </is>
       </c>
       <c r="E1728" s="2">
@@ -60838,19 +60838,19 @@
       </c>
       <c r="C1729" s="0" t="inlineStr">
         <is>
-          <t>zodiac</t>
+          <t>missyou</t>
         </is>
       </c>
       <c r="D1729" s="0" t="inlineStr">
         <is>
-          <t>birth_zodiac</t>
+          <t>birth_missyou</t>
         </is>
       </c>
       <c r="E1729" s="2">
         <v>2</v>
       </c>
       <c r="F1729" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1730">
@@ -60861,24 +60861,24 @@
       </c>
       <c r="B1730" s="0" t="inlineStr">
         <is>
-          <t>Congratulations</t>
+          <t>Birthday</t>
         </is>
       </c>
       <c r="C1730" s="0" t="inlineStr">
         <is>
-          <t>newbaby</t>
+          <t>zodiac</t>
         </is>
       </c>
       <c r="D1730" s="0" t="inlineStr">
         <is>
-          <t>congrats_newbaby</t>
+          <t>birth_zodiac</t>
         </is>
       </c>
       <c r="E1730" s="2">
         <v>2</v>
       </c>
       <c r="F1730" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1731">
@@ -60894,19 +60894,19 @@
       </c>
       <c r="C1731" s="0" t="inlineStr">
         <is>
-          <t>newcarandlicense</t>
+          <t>newbaby</t>
         </is>
       </c>
       <c r="D1731" s="0" t="inlineStr">
         <is>
-          <t>congrats_newcarandlicense</t>
+          <t>congrats_newbaby</t>
         </is>
       </c>
       <c r="E1731" s="2">
         <v>2</v>
       </c>
       <c r="F1731" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1732">
@@ -60917,24 +60917,24 @@
       </c>
       <c r="B1732" s="0" t="inlineStr">
         <is>
-          <t>Events cards</t>
+          <t>Congratulations</t>
         </is>
       </c>
       <c r="C1732" s="0" t="inlineStr">
         <is>
-          <t>eaug_hugsweetheartday</t>
+          <t>newcarandlicense</t>
         </is>
       </c>
       <c r="D1732" s="0" t="inlineStr">
         <is>
-          <t>eaug_hugsweetheartday</t>
+          <t>congrats_newcarandlicense</t>
         </is>
       </c>
       <c r="E1732" s="2">
         <v>2</v>
       </c>
       <c r="F1732" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1733">
@@ -60950,12 +60950,12 @@
       </c>
       <c r="C1733" s="0" t="inlineStr">
         <is>
-          <t>esep_flowerofthemonth</t>
+          <t>eaug_hugsweetheartday</t>
         </is>
       </c>
       <c r="D1733" s="0" t="inlineStr">
         <is>
-          <t>esep_flowerofthemonth</t>
+          <t>eaug_hugsweetheartday</t>
         </is>
       </c>
       <c r="E1733" s="2">
@@ -60973,17 +60973,17 @@
       </c>
       <c r="B1734" s="0" t="inlineStr">
         <is>
-          <t>Everyday greetings</t>
+          <t>Events cards</t>
         </is>
       </c>
       <c r="C1734" s="0" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>esep_flowerofthemonth</t>
         </is>
       </c>
       <c r="D1734" s="0" t="inlineStr">
         <is>
-          <t>gen_hi</t>
+          <t>esep_flowerofthemonth</t>
         </is>
       </c>
       <c r="E1734" s="2">
@@ -61006,19 +61006,19 @@
       </c>
       <c r="C1735" s="0" t="inlineStr">
         <is>
-          <t>hvgtday</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="D1735" s="0" t="inlineStr">
         <is>
-          <t>gen_hvgtday</t>
+          <t>gen_hi</t>
         </is>
       </c>
       <c r="E1735" s="2">
         <v>2</v>
       </c>
       <c r="F1735" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1736">
@@ -61034,12 +61034,12 @@
       </c>
       <c r="C1736" s="0" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>hvgtday</t>
         </is>
       </c>
       <c r="D1736" s="0" t="inlineStr">
         <is>
-          <t>gen_morning</t>
+          <t>gen_hvgtday</t>
         </is>
       </c>
       <c r="E1736" s="2">
@@ -61057,24 +61057,24 @@
       </c>
       <c r="B1737" s="0" t="inlineStr">
         <is>
-          <t>Keeping in touch</t>
+          <t>Everyday greetings</t>
         </is>
       </c>
       <c r="C1737" s="0" t="inlineStr">
         <is>
-          <t>justbecause</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="D1737" s="0" t="inlineStr">
         <is>
-          <t>intouch_justbecause</t>
+          <t>gen_morning</t>
         </is>
       </c>
       <c r="E1737" s="2">
         <v>2</v>
       </c>
       <c r="F1737" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1738">
@@ -61085,17 +61085,17 @@
       </c>
       <c r="B1738" s="0" t="inlineStr">
         <is>
-          <t>Invitations &amp; parties</t>
+          <t>Keeping in touch</t>
         </is>
       </c>
       <c r="C1738" s="0" t="inlineStr">
         <is>
-          <t>otherinvitations</t>
+          <t>justbecause</t>
         </is>
       </c>
       <c r="D1738" s="0" t="inlineStr">
         <is>
-          <t>invp_otherinvitations</t>
+          <t>intouch_justbecause</t>
         </is>
       </c>
       <c r="E1738" s="2">
@@ -61113,24 +61113,24 @@
       </c>
       <c r="B1739" s="0" t="inlineStr">
         <is>
-          <t>Love &amp; romance</t>
+          <t>Invitations &amp; parties</t>
         </is>
       </c>
       <c r="C1739" s="0" t="inlineStr">
         <is>
-          <t>iloveyou_general</t>
+          <t>otherinvitations</t>
         </is>
       </c>
       <c r="D1739" s="0" t="inlineStr">
         <is>
-          <t>love_iloveyou_general</t>
+          <t>invp_otherinvitations</t>
         </is>
       </c>
       <c r="E1739" s="2">
         <v>2</v>
       </c>
       <c r="F1739" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1740">
@@ -61146,12 +61146,12 @@
       </c>
       <c r="C1740" s="0" t="inlineStr">
         <is>
-          <t>lovepoems</t>
+          <t>iloveyou_general</t>
         </is>
       </c>
       <c r="D1740" s="0" t="inlineStr">
         <is>
-          <t>love_lovepoems</t>
+          <t>love_iloveyou_general</t>
         </is>
       </c>
       <c r="E1740" s="2">
@@ -61169,17 +61169,17 @@
       </c>
       <c r="B1741" s="0" t="inlineStr">
         <is>
-          <t>Thank you</t>
+          <t>Love &amp; romance</t>
         </is>
       </c>
       <c r="C1741" s="0" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>lovepoems</t>
         </is>
       </c>
       <c r="D1741" s="0" t="inlineStr">
         <is>
-          <t>thank_love</t>
+          <t>love_lovepoems</t>
         </is>
       </c>
       <c r="E1741" s="2">
@@ -61197,24 +61197,24 @@
       </c>
       <c r="B1742" s="0" t="inlineStr">
         <is>
-          <t>Anniversary</t>
+          <t>Thank you</t>
         </is>
       </c>
       <c r="C1742" s="0" t="inlineStr">
         <is>
-          <t>ouranniversary_forhim</t>
+          <t>love</t>
         </is>
       </c>
       <c r="D1742" s="0" t="inlineStr">
         <is>
-          <t>anniv_ouranniversary_forhim</t>
+          <t>thank_love</t>
         </is>
       </c>
       <c r="E1742" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1742" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1743">
@@ -61225,17 +61225,17 @@
       </c>
       <c r="B1743" s="0" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>Anniversary</t>
         </is>
       </c>
       <c r="C1743" s="0" t="inlineStr">
         <is>
-          <t>forher</t>
+          <t>ouranniversary_forhim</t>
         </is>
       </c>
       <c r="D1743" s="0" t="inlineStr">
         <is>
-          <t>birth_forher</t>
+          <t>anniv_ouranniversary_forhim</t>
         </is>
       </c>
       <c r="E1743" s="2">
@@ -61258,12 +61258,12 @@
       </c>
       <c r="C1744" s="0" t="inlineStr">
         <is>
-          <t>forhim</t>
+          <t>forher</t>
         </is>
       </c>
       <c r="D1744" s="0" t="inlineStr">
         <is>
-          <t>birth_forhim</t>
+          <t>birth_forher</t>
         </is>
       </c>
       <c r="E1744" s="2">
@@ -61286,12 +61286,12 @@
       </c>
       <c r="C1745" s="0" t="inlineStr">
         <is>
-          <t>grandparents</t>
+          <t>forhim</t>
         </is>
       </c>
       <c r="D1745" s="0" t="inlineStr">
         <is>
-          <t>birth_grandparents</t>
+          <t>birth_forhim</t>
         </is>
       </c>
       <c r="E1745" s="2">
@@ -61314,12 +61314,12 @@
       </c>
       <c r="C1746" s="0" t="inlineStr">
         <is>
-          <t>hubbywife</t>
+          <t>grandparents</t>
         </is>
       </c>
       <c r="D1746" s="0" t="inlineStr">
         <is>
-          <t>birth_hubbywife</t>
+          <t>birth_grandparents</t>
         </is>
       </c>
       <c r="E1746" s="2">
@@ -61342,12 +61342,12 @@
       </c>
       <c r="C1747" s="0" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hubbywife</t>
         </is>
       </c>
       <c r="D1747" s="0" t="inlineStr">
         <is>
-          <t>birth_kids</t>
+          <t>birth_hubbywife</t>
         </is>
       </c>
       <c r="E1747" s="2">
@@ -61370,12 +61370,12 @@
       </c>
       <c r="C1748" s="0" t="inlineStr">
         <is>
-          <t>specials</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="D1748" s="0" t="inlineStr">
         <is>
-          <t>birth_specials</t>
+          <t>birth_kids</t>
         </is>
       </c>
       <c r="E1748" s="2">
@@ -61393,17 +61393,17 @@
       </c>
       <c r="B1749" s="0" t="inlineStr">
         <is>
-          <t>Business &amp; work</t>
+          <t>Birthday</t>
         </is>
       </c>
       <c r="C1749" s="0" t="inlineStr">
         <is>
-          <t>humor</t>
+          <t>specials</t>
         </is>
       </c>
       <c r="D1749" s="0" t="inlineStr">
         <is>
-          <t>bus_humor</t>
+          <t>birth_specials</t>
         </is>
       </c>
       <c r="E1749" s="2">
@@ -61421,17 +61421,17 @@
       </c>
       <c r="B1750" s="0" t="inlineStr">
         <is>
-          <t>Congratulations</t>
+          <t>Business &amp; work</t>
         </is>
       </c>
       <c r="C1750" s="0" t="inlineStr">
         <is>
-          <t>onotheroccasions</t>
+          <t>humor</t>
         </is>
       </c>
       <c r="D1750" s="0" t="inlineStr">
         <is>
-          <t>congrats_onotheroccasions</t>
+          <t>bus_humor</t>
         </is>
       </c>
       <c r="E1750" s="2">
@@ -61449,17 +61449,17 @@
       </c>
       <c r="B1751" s="0" t="inlineStr">
         <is>
-          <t>Events cards</t>
+          <t>Congratulations</t>
         </is>
       </c>
       <c r="C1751" s="0" t="inlineStr">
         <is>
-          <t>eapr_goodfriday</t>
+          <t>onotheroccasions</t>
         </is>
       </c>
       <c r="D1751" s="0" t="inlineStr">
         <is>
-          <t>eapr_goodfriday</t>
+          <t>congrats_onotheroccasions</t>
         </is>
       </c>
       <c r="E1751" s="2">
@@ -61482,12 +61482,12 @@
       </c>
       <c r="C1752" s="0" t="inlineStr">
         <is>
-          <t>eaug_bananasplit_day</t>
+          <t>eapr_goodfriday</t>
         </is>
       </c>
       <c r="D1752" s="0" t="inlineStr">
         <is>
-          <t>eaug_bananasplit_day</t>
+          <t>eapr_goodfriday</t>
         </is>
       </c>
       <c r="E1752" s="2">
@@ -61510,12 +61510,12 @@
       </c>
       <c r="C1753" s="0" t="inlineStr">
         <is>
-          <t>eaug_beanangelday</t>
+          <t>eaug_bananasplit_day</t>
         </is>
       </c>
       <c r="D1753" s="0" t="inlineStr">
         <is>
-          <t>eaug_beanangelday</t>
+          <t>eaug_bananasplit_day</t>
         </is>
       </c>
       <c r="E1753" s="2">
@@ -61538,12 +61538,12 @@
       </c>
       <c r="C1754" s="0" t="inlineStr">
         <is>
-          <t>eaug_cardssister</t>
+          <t>eaug_beanangelday</t>
         </is>
       </c>
       <c r="D1754" s="0" t="inlineStr">
         <is>
-          <t>eaug_cardssister</t>
+          <t>eaug_beanangelday</t>
         </is>
       </c>
       <c r="E1754" s="2">
@@ -61566,12 +61566,12 @@
       </c>
       <c r="C1755" s="0" t="inlineStr">
         <is>
-          <t>eaug_friendshipday_happy</t>
+          <t>eaug_cardssister</t>
         </is>
       </c>
       <c r="D1755" s="0" t="inlineStr">
         <is>
-          <t>eaug_friendshipday_happy</t>
+          <t>eaug_cardssister</t>
         </is>
       </c>
       <c r="E1755" s="2">
@@ -61594,12 +61594,12 @@
       </c>
       <c r="C1756" s="0" t="inlineStr">
         <is>
-          <t>eaug_rakshabandhan_happy</t>
+          <t>eaug_friendshipday_happy</t>
         </is>
       </c>
       <c r="D1756" s="0" t="inlineStr">
         <is>
-          <t>eaug_rakshabandhan_happy</t>
+          <t>eaug_friendshipday_happy</t>
         </is>
       </c>
       <c r="E1756" s="2">
@@ -61622,12 +61622,12 @@
       </c>
       <c r="C1757" s="0" t="inlineStr">
         <is>
-          <t>eaug_rakshabandhan_interactive</t>
+          <t>eaug_rakshabandhan_happy</t>
         </is>
       </c>
       <c r="D1757" s="0" t="inlineStr">
         <is>
-          <t>eaug_rakshabandhan_interactive</t>
+          <t>eaug_rakshabandhan_happy</t>
         </is>
       </c>
       <c r="E1757" s="2">
@@ -61650,12 +61650,12 @@
       </c>
       <c r="C1758" s="0" t="inlineStr">
         <is>
-          <t>eaug_romawaremonth</t>
+          <t>eaug_rakshabandhan_interactive</t>
         </is>
       </c>
       <c r="D1758" s="0" t="inlineStr">
         <is>
-          <t>eaug_romawaremonth</t>
+          <t>eaug_rakshabandhan_interactive</t>
         </is>
       </c>
       <c r="E1758" s="2">
@@ -61678,12 +61678,12 @@
       </c>
       <c r="C1759" s="0" t="inlineStr">
         <is>
-          <t>eaug_womensequality_day</t>
+          <t>eaug_romawaremonth</t>
         </is>
       </c>
       <c r="D1759" s="0" t="inlineStr">
         <is>
-          <t>eaug_womensequality_day</t>
+          <t>eaug_romawaremonth</t>
         </is>
       </c>
       <c r="E1759" s="2">
@@ -61706,12 +61706,12 @@
       </c>
       <c r="C1760" s="0" t="inlineStr">
         <is>
-          <t>ejan_thankyoucards</t>
+          <t>eaug_womensequality_day</t>
         </is>
       </c>
       <c r="D1760" s="0" t="inlineStr">
         <is>
-          <t>ejan_thankyoucards</t>
+          <t>eaug_womensequality_day</t>
         </is>
       </c>
       <c r="E1760" s="2">
@@ -61734,12 +61734,12 @@
       </c>
       <c r="C1761" s="0" t="inlineStr">
         <is>
-          <t>eoct_nationaliloveyou_day</t>
+          <t>ejan_thankyoucards</t>
         </is>
       </c>
       <c r="D1761" s="0" t="inlineStr">
         <is>
-          <t>eoct_nationaliloveyou_day</t>
+          <t>ejan_thankyoucards</t>
         </is>
       </c>
       <c r="E1761" s="2">
@@ -61762,12 +61762,12 @@
       </c>
       <c r="C1762" s="0" t="inlineStr">
         <is>
-          <t>eoct_sweetday_hugnkiss</t>
+          <t>eoct_nationaliloveyou_day</t>
         </is>
       </c>
       <c r="D1762" s="0" t="inlineStr">
         <is>
-          <t>eoct_sweetday_hugnkiss</t>
+          <t>eoct_nationaliloveyou_day</t>
         </is>
       </c>
       <c r="E1762" s="2">
@@ -61790,12 +61790,12 @@
       </c>
       <c r="C1763" s="0" t="inlineStr">
         <is>
-          <t>esep_fall_poem</t>
+          <t>eoct_sweetday_hugnkiss</t>
         </is>
       </c>
       <c r="D1763" s="0" t="inlineStr">
         <is>
-          <t>esep_fall_poem</t>
+          <t>eoct_sweetday_hugnkiss</t>
         </is>
       </c>
       <c r="E1763" s="2">
@@ -61813,17 +61813,17 @@
       </c>
       <c r="B1764" s="0" t="inlineStr">
         <is>
-          <t>Flowers</t>
+          <t>Events cards</t>
         </is>
       </c>
       <c r="C1764" s="0" t="inlineStr">
         <is>
-          <t>flrwishes</t>
+          <t>esep_fall_poem</t>
         </is>
       </c>
       <c r="D1764" s="0" t="inlineStr">
         <is>
-          <t>flwr_flrwishes</t>
+          <t>esep_fall_poem</t>
         </is>
       </c>
       <c r="E1764" s="2">
@@ -61841,17 +61841,17 @@
       </c>
       <c r="B1765" s="0" t="inlineStr">
         <is>
-          <t>Everyday greetings</t>
+          <t>Flowers</t>
         </is>
       </c>
       <c r="C1765" s="0" t="inlineStr">
         <is>
-          <t>goodnight</t>
+          <t>flrwishes</t>
         </is>
       </c>
       <c r="D1765" s="0" t="inlineStr">
         <is>
-          <t>gen_goodnight</t>
+          <t>flwr_flrwishes</t>
         </is>
       </c>
       <c r="E1765" s="2">
@@ -61874,12 +61874,12 @@
       </c>
       <c r="C1766" s="0" t="inlineStr">
         <is>
-          <t>quotesmessages_images_getwell_messages</t>
+          <t>goodnight</t>
         </is>
       </c>
       <c r="D1766" s="0" t="inlineStr">
         <is>
-          <t>gen_quotesmessages_images_getwell_messages</t>
+          <t>gen_goodnight</t>
         </is>
       </c>
       <c r="E1766" s="2">
@@ -61902,12 +61902,12 @@
       </c>
       <c r="C1767" s="0" t="inlineStr">
         <is>
-          <t>sorry</t>
+          <t>quotesmessages_images_getwell_messages</t>
         </is>
       </c>
       <c r="D1767" s="0" t="inlineStr">
         <is>
-          <t>gen_sorry</t>
+          <t>gen_quotesmessages_images_getwell_messages</t>
         </is>
       </c>
       <c r="E1767" s="2">
@@ -61930,12 +61930,12 @@
       </c>
       <c r="C1768" s="0" t="inlineStr">
         <is>
-          <t>voyage</t>
+          <t>sorry</t>
         </is>
       </c>
       <c r="D1768" s="0" t="inlineStr">
         <is>
-          <t>gen_voyage</t>
+          <t>gen_sorry</t>
         </is>
       </c>
       <c r="E1768" s="2">
@@ -61958,12 +61958,12 @@
       </c>
       <c r="C1769" s="0" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>voyage</t>
         </is>
       </c>
       <c r="D1769" s="0" t="inlineStr">
         <is>
-          <t>gen_weekend</t>
+          <t>gen_voyage</t>
         </is>
       </c>
       <c r="E1769" s="2">
@@ -61981,17 +61981,17 @@
       </c>
       <c r="B1770" s="0" t="inlineStr">
         <is>
-          <t>Inspirational &amp; sympathy</t>
+          <t>Everyday greetings</t>
         </is>
       </c>
       <c r="C1770" s="0" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D1770" s="0" t="inlineStr">
         <is>
-          <t>insp_health</t>
+          <t>gen_weekend</t>
         </is>
       </c>
       <c r="E1770" s="2">
@@ -62014,12 +62014,12 @@
       </c>
       <c r="C1771" s="0" t="inlineStr">
         <is>
-          <t>recovery</t>
+          <t>health</t>
         </is>
       </c>
       <c r="D1771" s="0" t="inlineStr">
         <is>
-          <t>insp_recovery</t>
+          <t>insp_health</t>
         </is>
       </c>
       <c r="E1771" s="2">
@@ -62037,17 +62037,17 @@
       </c>
       <c r="B1772" s="0" t="inlineStr">
         <is>
-          <t>Invitations &amp; parties</t>
+          <t>Inspirational &amp; sympathy</t>
         </is>
       </c>
       <c r="C1772" s="0" t="inlineStr">
         <is>
-          <t>birth_gen</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="D1772" s="0" t="inlineStr">
         <is>
-          <t>invp_birth_gen</t>
+          <t>insp_recovery</t>
         </is>
       </c>
       <c r="E1772" s="2">
@@ -62065,17 +62065,17 @@
       </c>
       <c r="B1773" s="0" t="inlineStr">
         <is>
-          <t>Love &amp; romance</t>
+          <t>Invitations &amp; parties</t>
         </is>
       </c>
       <c r="C1773" s="0" t="inlineStr">
         <is>
-          <t>iloveyou_couples</t>
+          <t>birth_gen</t>
         </is>
       </c>
       <c r="D1773" s="0" t="inlineStr">
         <is>
-          <t>love_iloveyou_couples</t>
+          <t>invp_birth_gen</t>
         </is>
       </c>
       <c r="E1773" s="2">
@@ -62098,12 +62098,12 @@
       </c>
       <c r="C1774" s="0" t="inlineStr">
         <is>
-          <t>missing_forher</t>
+          <t>iloveyou_couples</t>
         </is>
       </c>
       <c r="D1774" s="0" t="inlineStr">
         <is>
-          <t>love_missing_forher</t>
+          <t>love_iloveyou_couples</t>
         </is>
       </c>
       <c r="E1774" s="2">
@@ -62126,12 +62126,12 @@
       </c>
       <c r="C1775" s="0" t="inlineStr">
         <is>
-          <t>newlove</t>
+          <t>missing_forher</t>
         </is>
       </c>
       <c r="D1775" s="0" t="inlineStr">
         <is>
-          <t>love_newlove</t>
+          <t>love_missing_forher</t>
         </is>
       </c>
       <c r="E1775" s="2">
@@ -62149,17 +62149,17 @@
       </c>
       <c r="B1776" s="0" t="inlineStr">
         <is>
-          <t>Pets</t>
+          <t>Love &amp; romance</t>
         </is>
       </c>
       <c r="C1776" s="0" t="inlineStr">
         <is>
-          <t>hihello</t>
+          <t>newlove</t>
         </is>
       </c>
       <c r="D1776" s="0" t="inlineStr">
         <is>
-          <t>pet_hihello</t>
+          <t>love_newlove</t>
         </is>
       </c>
       <c r="E1776" s="2">
@@ -62182,12 +62182,12 @@
       </c>
       <c r="C1777" s="0" t="inlineStr">
         <is>
-          <t>lossofpet</t>
+          <t>hihello</t>
         </is>
       </c>
       <c r="D1777" s="0" t="inlineStr">
         <is>
-          <t>pet_lossofpet</t>
+          <t>pet_hihello</t>
         </is>
       </c>
       <c r="E1777" s="2">
@@ -62205,17 +62205,17 @@
       </c>
       <c r="B1778" s="0" t="inlineStr">
         <is>
-          <t>Events cards</t>
+          <t>Pets</t>
         </is>
       </c>
       <c r="C1778" s="0" t="inlineStr">
         <is>
-          <t>wed_justmarried</t>
+          <t>lossofpet</t>
         </is>
       </c>
       <c r="D1778" s="0" t="inlineStr">
         <is>
-          <t>wed_justmarried</t>
+          <t>pet_lossofpet</t>
         </is>
       </c>
       <c r="E1778" s="2">
@@ -62238,12 +62238,12 @@
       </c>
       <c r="C1779" s="0" t="inlineStr">
         <is>
-          <t>wed_wed_congrats</t>
+          <t>wed_justmarried</t>
         </is>
       </c>
       <c r="D1779" s="0" t="inlineStr">
         <is>
-          <t>wed_wed_congrats</t>
+          <t>wed_justmarried</t>
         </is>
       </c>
       <c r="E1779" s="2">
@@ -62266,34 +62266,62 @@
       </c>
       <c r="C1780" s="0" t="inlineStr">
         <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="D1780" s="0" t="inlineStr">
+        <is>
+          <t>wed_wed_congrats</t>
+        </is>
+      </c>
+      <c r="E1780" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1780" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1781" s="0" t="inlineStr">
+        <is>
+          <t>Events cards</t>
+        </is>
+      </c>
+      <c r="C1781" s="0" t="inlineStr">
+        <is>
           <t>wed_weddingetc</t>
         </is>
       </c>
-      <c r="D1780" s="0" t="inlineStr">
+      <c r="D1781" s="0" t="inlineStr">
         <is>
           <t>wed_weddingetc</t>
         </is>
       </c>
-      <c r="E1780" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1780" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1781">
-      <c r="A1781" s="4" t="inlineStr">
+      <c r="E1781" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1781" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="4" t="inlineStr">
         <is>
           <t>TOTAL 2026-08-21</t>
         </is>
       </c>
-      <c r="B1781" s="4"/>
-      <c r="C1781" s="4"/>
-      <c r="D1781" s="4"/>
-      <c r="E1781" s="5">
-        <v>735</v>
-      </c>
-      <c r="F1781" s="4"/>
+      <c r="B1782" s="4"/>
+      <c r="C1782" s="4"/>
+      <c r="D1782" s="4"/>
+      <c r="E1782" s="5">
+        <v>739</v>
+      </c>
+      <c r="F1782" s="4"/>
     </row>
   </sheetData>
 </worksheet>
